--- a/data/house/house.xlsx
+++ b/data/house/house.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,6018 +413,7653 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C546"/>
+  <dimension ref="A1:D546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>loyer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>surface</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
-          <t>loyers_m2</t>
+          <t>loyer_m2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
         <v>1330</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>37</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>35.94594594594594</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
         <v>1400</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>32</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>43.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
         <v>904</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>26</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>34.76923076923077</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
         <v>955</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>30</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>31.83333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
         <v>2545</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>70</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>36.35714285714285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
         <v>970</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>24</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>40.41666666666666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
         <v>1560</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>41</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>38.04878048780488</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
         <v>1960</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>67</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>29.25373134328358</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
         <v>2000</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>63</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>31.74603174603175</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
         <v>2600</v>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>70</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>37.14285714285715</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
         <v>3280</v>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" t="n">
         <v>81</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>40.49382716049383</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
         <v>16000</v>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>347</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>46.10951008645533</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
         <v>980</v>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" t="n">
         <v>26</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>37.69230769230769</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
         <v>1250</v>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" t="n">
         <v>36</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>34.72222222222222</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
         <v>752</v>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" t="n">
         <v>19</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>39.57894736842105</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
         <v>815</v>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" t="n">
         <v>20</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>40.75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
         <v>1147</v>
       </c>
-      <c r="B18" t="n">
+      <c r="C18" t="n">
         <v>25</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>45.88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
         <v>1500</v>
       </c>
-      <c r="B19" t="n">
+      <c r="C19" t="n">
         <v>35</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>42.85714285714285</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
         <v>3587</v>
       </c>
-      <c r="B20" t="n">
+      <c r="C20" t="n">
         <v>120</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>29.89166666666667</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
         <v>1355</v>
       </c>
-      <c r="B21" t="n">
+      <c r="C21" t="n">
         <v>40</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>33.875</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
         <v>1245</v>
       </c>
-      <c r="B22" t="n">
+      <c r="C22" t="n">
         <v>30</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>41.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
         <v>1100</v>
       </c>
-      <c r="B23" t="n">
+      <c r="C23" t="n">
         <v>25</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
         <v>1120</v>
       </c>
-      <c r="B24" t="n">
+      <c r="C24" t="n">
         <v>21</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
         <v>1225</v>
       </c>
-      <c r="B25" t="n">
+      <c r="C25" t="n">
         <v>44</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>27.84090909090909</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
         <v>1250</v>
       </c>
-      <c r="B26" t="n">
+      <c r="C26" t="n">
         <v>35</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
         <v>1280</v>
       </c>
-      <c r="B27" t="n">
+      <c r="C27" t="n">
         <v>54</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>23.7037037037037</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
         <v>1114</v>
       </c>
-      <c r="B28" t="n">
+      <c r="C28" t="n">
         <v>39</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>28.56410256410257</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
         <v>1290</v>
       </c>
-      <c r="B29" t="n">
+      <c r="C29" t="n">
         <v>34</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>37.94117647058823</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
         <v>1300</v>
       </c>
-      <c r="B30" t="n">
+      <c r="C30" t="n">
         <v>28</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>46.42857142857143</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
         <v>1300</v>
       </c>
-      <c r="B31" t="n">
+      <c r="C31" t="n">
         <v>32</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>40.625</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
         <v>1304</v>
       </c>
-      <c r="B32" t="n">
+      <c r="C32" t="n">
         <v>40</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>32.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
         <v>1340</v>
       </c>
-      <c r="B33" t="n">
+      <c r="C33" t="n">
         <v>42</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>31.90476190476191</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
         <v>1344</v>
       </c>
-      <c r="B34" t="n">
+      <c r="C34" t="n">
         <v>31</v>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>43.35483870967742</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
         <v>1290</v>
       </c>
-      <c r="B35" t="n">
+      <c r="C35" t="n">
         <v>33</v>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>39.09090909090909</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
         <v>1364</v>
       </c>
-      <c r="B36" t="n">
+      <c r="C36" t="n">
         <v>39</v>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>34.97435897435897</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
         <v>1400</v>
       </c>
-      <c r="B37" t="n">
+      <c r="C37" t="n">
         <v>47</v>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>29.78723404255319</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
         <v>1400</v>
       </c>
-      <c r="B38" t="n">
+      <c r="C38" t="n">
         <v>33</v>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>42.42424242424242</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
         <v>1420</v>
       </c>
-      <c r="B39" t="n">
+      <c r="C39" t="n">
         <v>37</v>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>38.37837837837838</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
         <v>1420</v>
       </c>
-      <c r="B40" t="n">
+      <c r="C40" t="n">
         <v>42</v>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>33.80952380952381</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
         <v>1445</v>
       </c>
-      <c r="B41" t="n">
+      <c r="C41" t="n">
         <v>46</v>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>31.41304347826087</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
         <v>1500</v>
       </c>
-      <c r="B42" t="n">
+      <c r="C42" t="n">
         <v>37</v>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>40.54054054054054</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
         <v>1544</v>
       </c>
-      <c r="B43" t="n">
+      <c r="C43" t="n">
         <v>46</v>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>33.56521739130435</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
         <v>1550</v>
       </c>
-      <c r="B44" t="n">
+      <c r="C44" t="n">
         <v>42</v>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>36.90476190476191</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
         <v>1500</v>
       </c>
-      <c r="B45" t="n">
+      <c r="C45" t="n">
         <v>49</v>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>30.61224489795918</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
         <v>1612</v>
       </c>
-      <c r="B46" t="n">
+      <c r="C46" t="n">
         <v>48</v>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>33.58333333333334</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
         <v>1650</v>
       </c>
-      <c r="B47" t="n">
+      <c r="C47" t="n">
         <v>50</v>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
         <v>1533</v>
       </c>
-      <c r="B48" t="n">
+      <c r="C48" t="n">
         <v>54</v>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>28.38888888888889</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
         <v>1663</v>
       </c>
-      <c r="B49" t="n">
+      <c r="C49" t="n">
         <v>54</v>
       </c>
-      <c r="C49" t="n">
+      <c r="D49" t="n">
         <v>30.7962962962963</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
         <v>1584</v>
       </c>
-      <c r="B50" t="n">
+      <c r="C50" t="n">
         <v>45</v>
       </c>
-      <c r="C50" t="n">
+      <c r="D50" t="n">
         <v>35.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
         <v>1680</v>
       </c>
-      <c r="B51" t="n">
+      <c r="C51" t="n">
         <v>53</v>
       </c>
-      <c r="C51" t="n">
+      <c r="D51" t="n">
         <v>31.69811320754717</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
         <v>1700</v>
       </c>
-      <c r="B52" t="n">
+      <c r="C52" t="n">
         <v>40</v>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>42.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
         <v>1700</v>
       </c>
-      <c r="B53" t="n">
+      <c r="C53" t="n">
         <v>35</v>
       </c>
-      <c r="C53" t="n">
+      <c r="D53" t="n">
         <v>48.57142857142857</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
         <v>1700</v>
       </c>
-      <c r="B54" t="n">
+      <c r="C54" t="n">
         <v>40</v>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>42.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
         <v>1700</v>
       </c>
-      <c r="B55" t="n">
+      <c r="C55" t="n">
         <v>35</v>
       </c>
-      <c r="C55" t="n">
+      <c r="D55" t="n">
         <v>48.57142857142857</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
         <v>1700</v>
       </c>
-      <c r="B56" t="n">
+      <c r="C56" t="n">
         <v>60</v>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>28.33333333333333</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
         <v>1600</v>
       </c>
-      <c r="B57" t="n">
+      <c r="C57" t="n">
         <v>30</v>
       </c>
-      <c r="C57" t="n">
+      <c r="D57" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
         <v>1700</v>
       </c>
-      <c r="B58" t="n">
+      <c r="C58" t="n">
         <v>34</v>
       </c>
-      <c r="C58" t="n">
+      <c r="D58" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
         <v>1710</v>
       </c>
-      <c r="B59" t="n">
+      <c r="C59" t="n">
         <v>64</v>
       </c>
-      <c r="C59" t="n">
+      <c r="D59" t="n">
         <v>26.71875</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
         <v>1600</v>
       </c>
-      <c r="B60" t="n">
+      <c r="C60" t="n">
         <v>47</v>
       </c>
-      <c r="C60" t="n">
+      <c r="D60" t="n">
         <v>34.04255319148936</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
         <v>1750</v>
       </c>
-      <c r="B61" t="n">
+      <c r="C61" t="n">
         <v>43</v>
       </c>
-      <c r="C61" t="n">
+      <c r="D61" t="n">
         <v>40.69767441860465</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
         <v>1765</v>
       </c>
-      <c r="B62" t="n">
+      <c r="C62" t="n">
         <v>62</v>
       </c>
-      <c r="C62" t="n">
+      <c r="D62" t="n">
         <v>28.46774193548387</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
         <v>1790</v>
       </c>
-      <c r="B63" t="n">
+      <c r="C63" t="n">
         <v>50</v>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>35.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
         <v>1689</v>
       </c>
-      <c r="B64" t="n">
+      <c r="C64" t="n">
         <v>53</v>
       </c>
-      <c r="C64" t="n">
+      <c r="D64" t="n">
         <v>31.86792452830189</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
         <v>1795</v>
       </c>
-      <c r="B65" t="n">
+      <c r="C65" t="n">
         <v>50</v>
       </c>
-      <c r="C65" t="n">
+      <c r="D65" t="n">
         <v>35.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
         <v>1800</v>
       </c>
-      <c r="B66" t="n">
+      <c r="C66" t="n">
         <v>50</v>
       </c>
-      <c r="C66" t="n">
+      <c r="D66" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
         <v>1700</v>
       </c>
-      <c r="B67" t="n">
+      <c r="C67" t="n">
         <v>60</v>
       </c>
-      <c r="C67" t="n">
+      <c r="D67" t="n">
         <v>28.33333333333333</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
         <v>1800</v>
       </c>
-      <c r="B68" t="n">
+      <c r="C68" t="n">
         <v>42</v>
       </c>
-      <c r="C68" t="n">
+      <c r="D68" t="n">
         <v>42.85714285714285</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
         <v>1850</v>
       </c>
-      <c r="B69" t="n">
+      <c r="C69" t="n">
         <v>52</v>
       </c>
-      <c r="C69" t="n">
+      <c r="D69" t="n">
         <v>35.57692307692308</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
         <v>1850</v>
       </c>
-      <c r="B70" t="n">
+      <c r="C70" t="n">
         <v>45</v>
       </c>
-      <c r="C70" t="n">
+      <c r="D70" t="n">
         <v>41.11111111111111</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
         <v>1750</v>
       </c>
-      <c r="B71" t="n">
+      <c r="C71" t="n">
         <v>41</v>
       </c>
-      <c r="C71" t="n">
+      <c r="D71" t="n">
         <v>42.68292682926829</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
         <v>1850</v>
       </c>
-      <c r="B72" t="n">
+      <c r="C72" t="n">
         <v>63</v>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
         <v>29.36507936507936</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
         <v>1850</v>
       </c>
-      <c r="B73" t="n">
+      <c r="C73" t="n">
         <v>53</v>
       </c>
-      <c r="C73" t="n">
+      <c r="D73" t="n">
         <v>34.90566037735849</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
         <v>1850</v>
       </c>
-      <c r="B74" t="n">
+      <c r="C74" t="n">
         <v>45</v>
       </c>
-      <c r="C74" t="n">
+      <c r="D74" t="n">
         <v>41.11111111111111</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
         <v>1875</v>
       </c>
-      <c r="B75" t="n">
+      <c r="C75" t="n">
         <v>53</v>
       </c>
-      <c r="C75" t="n">
+      <c r="D75" t="n">
         <v>35.37735849056604</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
         <v>1900</v>
       </c>
-      <c r="B76" t="n">
+      <c r="C76" t="n">
         <v>55</v>
       </c>
-      <c r="C76" t="n">
+      <c r="D76" t="n">
         <v>34.54545454545455</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
         <v>1950</v>
       </c>
-      <c r="B77" t="n">
+      <c r="C77" t="n">
         <v>46</v>
       </c>
-      <c r="C77" t="n">
+      <c r="D77" t="n">
         <v>42.39130434782609</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
         <v>1750</v>
       </c>
-      <c r="B78" t="n">
+      <c r="C78" t="n">
         <v>73</v>
       </c>
-      <c r="C78" t="n">
+      <c r="D78" t="n">
         <v>23.97260273972603</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
         <v>2000</v>
       </c>
-      <c r="B79" t="n">
+      <c r="C79" t="n">
         <v>53</v>
       </c>
-      <c r="C79" t="n">
+      <c r="D79" t="n">
         <v>37.73584905660378</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
         <v>2044</v>
       </c>
-      <c r="B80" t="n">
+      <c r="C80" t="n">
         <v>64</v>
       </c>
-      <c r="C80" t="n">
+      <c r="D80" t="n">
         <v>31.9375</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
         <v>2100</v>
       </c>
-      <c r="B81" t="n">
+      <c r="C81" t="n">
         <v>38</v>
       </c>
-      <c r="C81" t="n">
+      <c r="D81" t="n">
         <v>55.26315789473684</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
         <v>2100</v>
       </c>
-      <c r="B82" t="n">
+      <c r="C82" t="n">
         <v>65</v>
       </c>
-      <c r="C82" t="n">
+      <c r="D82" t="n">
         <v>32.30769230769231</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
         <v>2100</v>
       </c>
-      <c r="B83" t="n">
+      <c r="C83" t="n">
         <v>59</v>
       </c>
-      <c r="C83" t="n">
+      <c r="D83" t="n">
         <v>35.59322033898305</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
         <v>2100</v>
       </c>
-      <c r="B84" t="n">
+      <c r="C84" t="n">
         <v>47</v>
       </c>
-      <c r="C84" t="n">
+      <c r="D84" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
         <v>2107</v>
       </c>
-      <c r="B85" t="n">
+      <c r="C85" t="n">
         <v>75</v>
       </c>
-      <c r="C85" t="n">
+      <c r="D85" t="n">
         <v>28.09333333333333</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
         <v>2116</v>
       </c>
-      <c r="B86" t="n">
+      <c r="C86" t="n">
         <v>83</v>
       </c>
-      <c r="C86" t="n">
+      <c r="D86" t="n">
         <v>25.49397590361446</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
         <v>2132</v>
       </c>
-      <c r="B87" t="n">
+      <c r="C87" t="n">
         <v>69</v>
       </c>
-      <c r="C87" t="n">
+      <c r="D87" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
         <v>2000</v>
       </c>
-      <c r="B88" t="n">
+      <c r="C88" t="n">
         <v>68</v>
       </c>
-      <c r="C88" t="n">
+      <c r="D88" t="n">
         <v>29.41176470588235</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
         <v>2180</v>
       </c>
-      <c r="B89" t="n">
+      <c r="C89" t="n">
         <v>69</v>
       </c>
-      <c r="C89" t="n">
+      <c r="D89" t="n">
         <v>31.59420289855073</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
         <v>2100</v>
       </c>
-      <c r="B90" t="n">
+      <c r="C90" t="n">
         <v>72</v>
       </c>
-      <c r="C90" t="n">
+      <c r="D90" t="n">
         <v>29.16666666666667</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
         <v>2200</v>
       </c>
-      <c r="B91" t="n">
+      <c r="C91" t="n">
         <v>40</v>
       </c>
-      <c r="C91" t="n">
+      <c r="D91" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
         <v>2200</v>
       </c>
-      <c r="B92" t="n">
+      <c r="C92" t="n">
         <v>50</v>
       </c>
-      <c r="C92" t="n">
+      <c r="D92" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
         <v>2200</v>
       </c>
-      <c r="B93" t="n">
+      <c r="C93" t="n">
         <v>60</v>
       </c>
-      <c r="C93" t="n">
+      <c r="D93" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
         <v>2216</v>
       </c>
-      <c r="B94" t="n">
+      <c r="C94" t="n">
         <v>68</v>
       </c>
-      <c r="C94" t="n">
+      <c r="D94" t="n">
         <v>32.58823529411764</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
         <v>2240</v>
       </c>
-      <c r="B95" t="n">
+      <c r="C95" t="n">
         <v>69</v>
       </c>
-      <c r="C95" t="n">
+      <c r="D95" t="n">
         <v>32.46376811594203</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
         <v>2249</v>
       </c>
-      <c r="B96" t="n">
+      <c r="C96" t="n">
         <v>35</v>
       </c>
-      <c r="C96" t="n">
+      <c r="D96" t="n">
         <v>64.25714285714285</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
         <v>2282</v>
       </c>
-      <c r="B97" t="n">
+      <c r="C97" t="n">
         <v>78</v>
       </c>
-      <c r="C97" t="n">
+      <c r="D97" t="n">
         <v>29.25641025641026</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
         <v>2300</v>
       </c>
-      <c r="B98" t="n">
+      <c r="C98" t="n">
         <v>65</v>
       </c>
-      <c r="C98" t="n">
+      <c r="D98" t="n">
         <v>35.38461538461539</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
         <v>2300</v>
       </c>
-      <c r="B99" t="n">
+      <c r="C99" t="n">
         <v>54</v>
       </c>
-      <c r="C99" t="n">
+      <c r="D99" t="n">
         <v>42.5925925925926</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
         <v>2320</v>
       </c>
-      <c r="B100" t="n">
+      <c r="C100" t="n">
         <v>60</v>
       </c>
-      <c r="C100" t="n">
+      <c r="D100" t="n">
         <v>38.66666666666666</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
         <v>2324</v>
       </c>
-      <c r="B101" t="n">
+      <c r="C101" t="n">
         <v>64</v>
       </c>
-      <c r="C101" t="n">
+      <c r="D101" t="n">
         <v>36.3125</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
         <v>2324</v>
       </c>
-      <c r="B102" t="n">
+      <c r="C102" t="n">
         <v>64</v>
       </c>
-      <c r="C102" t="n">
+      <c r="D102" t="n">
         <v>36.3125</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
         <v>2367</v>
       </c>
-      <c r="B103" t="n">
+      <c r="C103" t="n">
         <v>76</v>
       </c>
-      <c r="C103" t="n">
+      <c r="D103" t="n">
         <v>31.14473684210526</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
         <v>2400</v>
       </c>
-      <c r="B104" t="n">
+      <c r="C104" t="n">
         <v>70</v>
       </c>
-      <c r="C104" t="n">
+      <c r="D104" t="n">
         <v>34.28571428571428</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
         <v>2400</v>
       </c>
-      <c r="B105" t="n">
+      <c r="C105" t="n">
         <v>70</v>
       </c>
-      <c r="C105" t="n">
+      <c r="D105" t="n">
         <v>34.28571428571428</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
         <v>2445</v>
       </c>
-      <c r="B106" t="n">
+      <c r="C106" t="n">
         <v>71</v>
       </c>
-      <c r="C106" t="n">
+      <c r="D106" t="n">
         <v>34.43661971830986</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
         <v>2450</v>
       </c>
-      <c r="B107" t="n">
+      <c r="C107" t="n">
         <v>84</v>
       </c>
-      <c r="C107" t="n">
+      <c r="D107" t="n">
         <v>29.16666666666667</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
         <v>2450</v>
       </c>
-      <c r="B108" t="n">
+      <c r="C108" t="n">
         <v>90</v>
       </c>
-      <c r="C108" t="n">
+      <c r="D108" t="n">
         <v>27.22222222222222</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
         <v>2280</v>
       </c>
-      <c r="B109" t="n">
+      <c r="C109" t="n">
         <v>96</v>
       </c>
-      <c r="C109" t="n">
+      <c r="D109" t="n">
         <v>23.75</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
         <v>2250</v>
       </c>
-      <c r="B110" t="n">
+      <c r="C110" t="n">
         <v>89</v>
       </c>
-      <c r="C110" t="n">
+      <c r="D110" t="n">
         <v>25.28089887640449</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
         <v>2415</v>
       </c>
-      <c r="B111" t="n">
+      <c r="C111" t="n">
         <v>75</v>
       </c>
-      <c r="C111" t="n">
+      <c r="D111" t="n">
         <v>32.2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
         <v>2470</v>
       </c>
-      <c r="B112" t="n">
+      <c r="C112" t="n">
         <v>55</v>
       </c>
-      <c r="C112" t="n">
+      <c r="D112" t="n">
         <v>44.90909090909091</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
         <v>2600</v>
       </c>
-      <c r="B113" t="n">
+      <c r="C113" t="n">
         <v>56</v>
       </c>
-      <c r="C113" t="n">
+      <c r="D113" t="n">
         <v>46.42857142857143</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
         <v>2650</v>
       </c>
-      <c r="B114" t="n">
+      <c r="C114" t="n">
         <v>56</v>
       </c>
-      <c r="C114" t="n">
+      <c r="D114" t="n">
         <v>47.32142857142857</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
         <v>2650</v>
       </c>
-      <c r="B115" t="n">
+      <c r="C115" t="n">
         <v>56</v>
       </c>
-      <c r="C115" t="n">
+      <c r="D115" t="n">
         <v>47.32142857142857</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
         <v>2675</v>
       </c>
-      <c r="B116" t="n">
+      <c r="C116" t="n">
         <v>91</v>
       </c>
-      <c r="C116" t="n">
+      <c r="D116" t="n">
         <v>29.39560439560439</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
         <v>2550</v>
       </c>
-      <c r="B117" t="n">
+      <c r="C117" t="n">
         <v>100</v>
       </c>
-      <c r="C117" t="n">
+      <c r="D117" t="n">
         <v>25.5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
         <v>2700</v>
       </c>
-      <c r="B118" t="n">
+      <c r="C118" t="n">
         <v>73</v>
       </c>
-      <c r="C118" t="n">
+      <c r="D118" t="n">
         <v>36.98630136986301</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
         <v>2780</v>
       </c>
-      <c r="B119" t="n">
+      <c r="C119" t="n">
         <v>94</v>
       </c>
-      <c r="C119" t="n">
+      <c r="D119" t="n">
         <v>29.57446808510638</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
         <v>2800</v>
       </c>
-      <c r="B120" t="n">
+      <c r="C120" t="n">
         <v>50</v>
       </c>
-      <c r="C120" t="n">
+      <c r="D120" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
         <v>2800</v>
       </c>
-      <c r="B121" t="n">
+      <c r="C121" t="n">
         <v>60</v>
       </c>
-      <c r="C121" t="n">
+      <c r="D121" t="n">
         <v>46.66666666666666</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
         <v>2850</v>
       </c>
-      <c r="B122" t="n">
+      <c r="C122" t="n">
         <v>90</v>
       </c>
-      <c r="C122" t="n">
+      <c r="D122" t="n">
         <v>31.66666666666667</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
         <v>2941</v>
       </c>
-      <c r="B123" t="n">
+      <c r="C123" t="n">
         <v>96</v>
       </c>
-      <c r="C123" t="n">
+      <c r="D123" t="n">
         <v>30.63541666666667</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
         <v>2941</v>
       </c>
-      <c r="B124" t="n">
+      <c r="C124" t="n">
         <v>96</v>
       </c>
-      <c r="C124" t="n">
+      <c r="D124" t="n">
         <v>30.63541666666667</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
         <v>3000</v>
       </c>
-      <c r="B125" t="n">
+      <c r="C125" t="n">
         <v>50</v>
       </c>
-      <c r="C125" t="n">
+      <c r="D125" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
         <v>2800</v>
       </c>
-      <c r="B126" t="n">
+      <c r="C126" t="n">
         <v>83</v>
       </c>
-      <c r="C126" t="n">
+      <c r="D126" t="n">
         <v>33.73493975903614</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
         <v>3000</v>
       </c>
-      <c r="B127" t="n">
+      <c r="C127" t="n">
         <v>99</v>
       </c>
-      <c r="C127" t="n">
+      <c r="D127" t="n">
         <v>30.3030303030303</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
         <v>3000</v>
       </c>
-      <c r="B128" t="n">
+      <c r="C128" t="n">
         <v>88</v>
       </c>
-      <c r="C128" t="n">
+      <c r="D128" t="n">
         <v>34.09090909090909</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
         <v>3010</v>
       </c>
-      <c r="B129" t="n">
+      <c r="C129" t="n">
         <v>104</v>
       </c>
-      <c r="C129" t="n">
+      <c r="D129" t="n">
         <v>28.94230769230769</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
         <v>2950</v>
       </c>
-      <c r="B130" t="n">
+      <c r="C130" t="n">
         <v>85</v>
       </c>
-      <c r="C130" t="n">
+      <c r="D130" t="n">
         <v>34.70588235294117</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
         <v>3200</v>
       </c>
-      <c r="B131" t="n">
+      <c r="C131" t="n">
         <v>70</v>
       </c>
-      <c r="C131" t="n">
+      <c r="D131" t="n">
         <v>45.71428571428572</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
         <v>3200</v>
       </c>
-      <c r="B132" t="n">
+      <c r="C132" t="n">
         <v>60</v>
       </c>
-      <c r="C132" t="n">
+      <c r="D132" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
         <v>3200</v>
       </c>
-      <c r="B133" t="n">
+      <c r="C133" t="n">
         <v>84</v>
       </c>
-      <c r="C133" t="n">
+      <c r="D133" t="n">
         <v>38.09523809523809</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
         <v>3234</v>
       </c>
-      <c r="B134" t="n">
+      <c r="C134" t="n">
         <v>103</v>
       </c>
-      <c r="C134" t="n">
+      <c r="D134" t="n">
         <v>31.39805825242718</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
         <v>3300</v>
       </c>
-      <c r="B135" t="n">
+      <c r="C135" t="n">
         <v>108</v>
       </c>
-      <c r="C135" t="n">
+      <c r="D135" t="n">
         <v>30.55555555555556</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
         <v>3420</v>
       </c>
-      <c r="B136" t="n">
+      <c r="C136" t="n">
         <v>70</v>
       </c>
-      <c r="C136" t="n">
+      <c r="D136" t="n">
         <v>48.85714285714285</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
         <v>3350</v>
       </c>
-      <c r="B137" t="n">
+      <c r="C137" t="n">
         <v>88</v>
       </c>
-      <c r="C137" t="n">
+      <c r="D137" t="n">
         <v>38.06818181818182</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
         <v>3130</v>
       </c>
-      <c r="B138" t="n">
+      <c r="C138" t="n">
         <v>101</v>
       </c>
-      <c r="C138" t="n">
+      <c r="D138" t="n">
         <v>30.99009900990099</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
         <v>3500</v>
       </c>
-      <c r="B139" t="n">
+      <c r="C139" t="n">
         <v>103</v>
       </c>
-      <c r="C139" t="n">
+      <c r="D139" t="n">
         <v>33.98058252427185</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
         <v>3700</v>
       </c>
-      <c r="B140" t="n">
+      <c r="C140" t="n">
         <v>70</v>
       </c>
-      <c r="C140" t="n">
+      <c r="D140" t="n">
         <v>52.85714285714285</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
         <v>3705</v>
       </c>
-      <c r="B141" t="n">
+      <c r="C141" t="n">
         <v>53</v>
       </c>
-      <c r="C141" t="n">
+      <c r="D141" t="n">
         <v>69.90566037735849</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
         <v>3705</v>
       </c>
-      <c r="B142" t="n">
+      <c r="C142" t="n">
         <v>53</v>
       </c>
-      <c r="C142" t="n">
+      <c r="D142" t="n">
         <v>69.90566037735849</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
         <v>3800</v>
       </c>
-      <c r="B143" t="n">
+      <c r="C143" t="n">
         <v>72</v>
       </c>
-      <c r="C143" t="n">
+      <c r="D143" t="n">
         <v>52.77777777777778</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
         <v>3900</v>
       </c>
-      <c r="B144" t="n">
+      <c r="C144" t="n">
         <v>91</v>
       </c>
-      <c r="C144" t="n">
+      <c r="D144" t="n">
         <v>42.85714285714285</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
         <v>3700</v>
       </c>
-      <c r="B145" t="n">
+      <c r="C145" t="n">
         <v>97</v>
       </c>
-      <c r="C145" t="n">
+      <c r="D145" t="n">
         <v>38.14432989690722</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
         <v>4000</v>
       </c>
-      <c r="B146" t="n">
+      <c r="C146" t="n">
         <v>135</v>
       </c>
-      <c r="C146" t="n">
+      <c r="D146" t="n">
         <v>29.62962962962963</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
         <v>4000</v>
       </c>
-      <c r="B147" t="n">
+      <c r="C147" t="n">
         <v>80</v>
       </c>
-      <c r="C147" t="n">
+      <c r="D147" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
         <v>3850</v>
       </c>
-      <c r="B148" t="n">
+      <c r="C148" t="n">
         <v>116</v>
       </c>
-      <c r="C148" t="n">
+      <c r="D148" t="n">
         <v>33.18965517241379</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
         <v>4407</v>
       </c>
-      <c r="B149" t="n">
+      <c r="C149" t="n">
         <v>152</v>
       </c>
-      <c r="C149" t="n">
+      <c r="D149" t="n">
         <v>28.99342105263158</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
         <v>5000</v>
       </c>
-      <c r="B150" t="n">
+      <c r="C150" t="n">
         <v>159</v>
       </c>
-      <c r="C150" t="n">
+      <c r="D150" t="n">
         <v>31.44654088050314</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
         <v>5233</v>
       </c>
-      <c r="B151" t="n">
+      <c r="C151" t="n">
         <v>162</v>
       </c>
-      <c r="C151" t="n">
+      <c r="D151" t="n">
         <v>32.30246913580247</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
         <v>5249</v>
       </c>
-      <c r="B152" t="n">
+      <c r="C152" t="n">
         <v>137</v>
       </c>
-      <c r="C152" t="n">
+      <c r="D152" t="n">
         <v>38.31386861313869</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
         <v>5500</v>
       </c>
-      <c r="B153" t="n">
+      <c r="C153" t="n">
         <v>160</v>
       </c>
-      <c r="C153" t="n">
+      <c r="D153" t="n">
         <v>34.375</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
         <v>5600</v>
       </c>
-      <c r="B154" t="n">
+      <c r="C154" t="n">
         <v>157</v>
       </c>
-      <c r="C154" t="n">
+      <c r="D154" t="n">
         <v>35.6687898089172</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
         <v>5970</v>
       </c>
-      <c r="B155" t="n">
+      <c r="C155" t="n">
         <v>160</v>
       </c>
-      <c r="C155" t="n">
+      <c r="D155" t="n">
         <v>37.3125</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
         <v>6000</v>
       </c>
-      <c r="B156" t="n">
+      <c r="C156" t="n">
         <v>152</v>
       </c>
-      <c r="C156" t="n">
+      <c r="D156" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
         <v>6000</v>
       </c>
-      <c r="B157" t="n">
+      <c r="C157" t="n">
         <v>152</v>
       </c>
-      <c r="C157" t="n">
+      <c r="D157" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
         <v>7450</v>
       </c>
-      <c r="B158" t="n">
+      <c r="C158" t="n">
         <v>180</v>
       </c>
-      <c r="C158" t="n">
+      <c r="D158" t="n">
         <v>41.38888888888889</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
         <v>7280</v>
       </c>
-      <c r="B159" t="n">
+      <c r="C159" t="n">
         <v>182</v>
       </c>
-      <c r="C159" t="n">
+      <c r="D159" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
         <v>10000</v>
       </c>
-      <c r="B160" t="n">
+      <c r="C160" t="n">
         <v>220</v>
       </c>
-      <c r="C160" t="n">
+      <c r="D160" t="n">
         <v>45.45454545454545</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
         <v>14300</v>
       </c>
-      <c r="B161" t="n">
+      <c r="C161" t="n">
         <v>347</v>
       </c>
-      <c r="C161" t="n">
+      <c r="D161" t="n">
         <v>41.21037463976946</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
         <v>15000</v>
       </c>
-      <c r="B162" t="n">
+      <c r="C162" t="n">
         <v>347</v>
       </c>
-      <c r="C162" t="n">
+      <c r="D162" t="n">
         <v>43.22766570605187</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="n">
         <v>775</v>
       </c>
-      <c r="B163" t="n">
+      <c r="C163" t="n">
         <v>20</v>
       </c>
-      <c r="C163" t="n">
+      <c r="D163" t="n">
         <v>38.75</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="n">
         <v>816</v>
       </c>
-      <c r="B164" t="n">
+      <c r="C164" t="n">
         <v>19</v>
       </c>
-      <c r="C164" t="n">
+      <c r="D164" t="n">
         <v>42.94736842105263</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="n">
         <v>800</v>
       </c>
-      <c r="B165" t="n">
+      <c r="C165" t="n">
         <v>19</v>
       </c>
-      <c r="C165" t="n">
+      <c r="D165" t="n">
         <v>42.10526315789474</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" t="n">
         <v>900</v>
       </c>
-      <c r="B166" t="n">
+      <c r="C166" t="n">
         <v>18</v>
       </c>
-      <c r="C166" t="n">
+      <c r="D166" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" t="n">
         <v>900</v>
       </c>
-      <c r="B167" t="n">
+      <c r="C167" t="n">
         <v>28</v>
       </c>
-      <c r="C167" t="n">
+      <c r="D167" t="n">
         <v>32.14285714285715</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" t="n">
         <v>888</v>
       </c>
-      <c r="B168" t="n">
+      <c r="C168" t="n">
         <v>24</v>
       </c>
-      <c r="C168" t="n">
+      <c r="D168" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" t="n">
         <v>960</v>
       </c>
-      <c r="B169" t="n">
+      <c r="C169" t="n">
         <v>21</v>
       </c>
-      <c r="C169" t="n">
+      <c r="D169" t="n">
         <v>45.71428571428572</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" t="n">
         <v>966</v>
       </c>
-      <c r="B170" t="n">
+      <c r="C170" t="n">
         <v>30</v>
       </c>
-      <c r="C170" t="n">
+      <c r="D170" t="n">
         <v>32.2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="n">
         <v>1000</v>
       </c>
-      <c r="B171" t="n">
+      <c r="C171" t="n">
         <v>19</v>
       </c>
-      <c r="C171" t="n">
+      <c r="D171" t="n">
         <v>52.63157894736842</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="n">
         <v>1040</v>
       </c>
-      <c r="B172" t="n">
+      <c r="C172" t="n">
         <v>26</v>
       </c>
-      <c r="C172" t="n">
+      <c r="D172" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="n">
         <v>1048</v>
       </c>
-      <c r="B173" t="n">
+      <c r="C173" t="n">
         <v>31</v>
       </c>
-      <c r="C173" t="n">
+      <c r="D173" t="n">
         <v>33.80645161290322</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="n">
         <v>1072</v>
       </c>
-      <c r="B174" t="n">
+      <c r="C174" t="n">
         <v>32</v>
       </c>
-      <c r="C174" t="n">
+      <c r="D174" t="n">
         <v>33.5</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="n">
         <v>1090</v>
       </c>
-      <c r="B175" t="n">
+      <c r="C175" t="n">
         <v>20</v>
       </c>
-      <c r="C175" t="n">
+      <c r="D175" t="n">
         <v>54.5</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="n">
         <v>1100</v>
       </c>
-      <c r="B176" t="n">
+      <c r="C176" t="n">
         <v>26</v>
       </c>
-      <c r="C176" t="n">
+      <c r="D176" t="n">
         <v>42.30769230769231</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="n">
         <v>1150</v>
       </c>
-      <c r="B177" t="n">
+      <c r="C177" t="n">
         <v>21</v>
       </c>
-      <c r="C177" t="n">
+      <c r="D177" t="n">
         <v>54.76190476190476</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="n">
         <v>1180</v>
       </c>
-      <c r="B178" t="n">
+      <c r="C178" t="n">
         <v>23</v>
       </c>
-      <c r="C178" t="n">
+      <c r="D178" t="n">
         <v>51.30434782608695</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="n">
         <v>1200</v>
       </c>
-      <c r="B179" t="n">
+      <c r="C179" t="n">
         <v>30</v>
       </c>
-      <c r="C179" t="n">
+      <c r="D179" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="n">
         <v>1200</v>
       </c>
-      <c r="B180" t="n">
+      <c r="C180" t="n">
         <v>32</v>
       </c>
-      <c r="C180" t="n">
+      <c r="D180" t="n">
         <v>37.5</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="n">
         <v>1200</v>
       </c>
-      <c r="B181" t="n">
+      <c r="C181" t="n">
         <v>20</v>
       </c>
-      <c r="C181" t="n">
+      <c r="D181" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="n">
         <v>1200</v>
       </c>
-      <c r="B182" t="n">
+      <c r="C182" t="n">
         <v>20</v>
       </c>
-      <c r="C182" t="n">
+      <c r="D182" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="n">
         <v>1218</v>
       </c>
-      <c r="B183" t="n">
+      <c r="C183" t="n">
         <v>28</v>
       </c>
-      <c r="C183" t="n">
+      <c r="D183" t="n">
         <v>43.5</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="n">
         <v>1250</v>
       </c>
-      <c r="B184" t="n">
+      <c r="C184" t="n">
         <v>21</v>
       </c>
-      <c r="C184" t="n">
+      <c r="D184" t="n">
         <v>59.52380952380953</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="n">
         <v>1250</v>
       </c>
-      <c r="B185" t="n">
+      <c r="C185" t="n">
         <v>34</v>
       </c>
-      <c r="C185" t="n">
+      <c r="D185" t="n">
         <v>36.76470588235294</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="n">
         <v>1300</v>
       </c>
-      <c r="B186" t="n">
+      <c r="C186" t="n">
         <v>22</v>
       </c>
-      <c r="C186" t="n">
+      <c r="D186" t="n">
         <v>59.09090909090909</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="n">
         <v>1329</v>
       </c>
-      <c r="B187" t="n">
+      <c r="C187" t="n">
         <v>35</v>
       </c>
-      <c r="C187" t="n">
+      <c r="D187" t="n">
         <v>37.97142857142857</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="n">
         <v>1340</v>
       </c>
-      <c r="B188" t="n">
+      <c r="C188" t="n">
         <v>30</v>
       </c>
-      <c r="C188" t="n">
+      <c r="D188" t="n">
         <v>44.66666666666666</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" t="n">
         <v>1500</v>
       </c>
-      <c r="B189" t="n">
+      <c r="C189" t="n">
         <v>32</v>
       </c>
-      <c r="C189" t="n">
+      <c r="D189" t="n">
         <v>46.875</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="n">
         <v>1500</v>
       </c>
-      <c r="B190" t="n">
+      <c r="C190" t="n">
         <v>32</v>
       </c>
-      <c r="C190" t="n">
+      <c r="D190" t="n">
         <v>46.875</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="n">
         <v>1550</v>
       </c>
-      <c r="B191" t="n">
+      <c r="C191" t="n">
         <v>59</v>
       </c>
-      <c r="C191" t="n">
+      <c r="D191" t="n">
         <v>26.27118644067797</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="n">
         <v>1900</v>
       </c>
-      <c r="B192" t="n">
+      <c r="C192" t="n">
         <v>50</v>
       </c>
-      <c r="C192" t="n">
+      <c r="D192" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="n">
         <v>1910</v>
       </c>
-      <c r="B193" t="n">
+      <c r="C193" t="n">
         <v>71</v>
       </c>
-      <c r="C193" t="n">
+      <c r="D193" t="n">
         <v>26.90140845070422</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="n">
         <v>2700</v>
       </c>
-      <c r="B194" t="n">
+      <c r="C194" t="n">
         <v>50</v>
       </c>
-      <c r="C194" t="n">
+      <c r="D194" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="n">
         <v>2950</v>
       </c>
-      <c r="B195" t="n">
+      <c r="C195" t="n">
         <v>82</v>
       </c>
-      <c r="C195" t="n">
+      <c r="D195" t="n">
         <v>35.97560975609756</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="n">
         <v>2700</v>
       </c>
-      <c r="B196" t="n">
+      <c r="C196" t="n">
         <v>50</v>
       </c>
-      <c r="C196" t="n">
+      <c r="D196" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="n">
         <v>6500</v>
       </c>
-      <c r="B197" t="n">
+      <c r="C197" t="n">
         <v>161</v>
       </c>
-      <c r="C197" t="n">
+      <c r="D197" t="n">
         <v>40.37267080745342</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="n">
         <v>7500</v>
       </c>
-      <c r="B198" t="n">
+      <c r="C198" t="n">
         <v>150</v>
       </c>
-      <c r="C198" t="n">
+      <c r="D198" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="n">
         <v>1048</v>
       </c>
-      <c r="B199" t="n">
+      <c r="C199" t="n">
         <v>31</v>
       </c>
-      <c r="C199" t="n">
+      <c r="D199" t="n">
         <v>33.80645161290322</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="n">
         <v>1650</v>
       </c>
-      <c r="B200" t="n">
+      <c r="C200" t="n">
         <v>45</v>
       </c>
-      <c r="C200" t="n">
+      <c r="D200" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="n">
         <v>1100</v>
       </c>
-      <c r="B201" t="n">
+      <c r="C201" t="n">
         <v>29</v>
       </c>
-      <c r="C201" t="n">
+      <c r="D201" t="n">
         <v>37.93103448275862</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" t="n">
         <v>1133</v>
       </c>
-      <c r="B202" t="n">
+      <c r="C202" t="n">
         <v>33</v>
       </c>
-      <c r="C202" t="n">
+      <c r="D202" t="n">
         <v>34.33333333333334</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" t="n">
         <v>1500</v>
       </c>
-      <c r="B203" t="n">
+      <c r="C203" t="n">
         <v>45</v>
       </c>
-      <c r="C203" t="n">
+      <c r="D203" t="n">
         <v>33.33333333333334</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" t="n">
         <v>1530</v>
       </c>
-      <c r="B204" t="n">
+      <c r="C204" t="n">
         <v>35</v>
       </c>
-      <c r="C204" t="n">
+      <c r="D204" t="n">
         <v>43.71428571428572</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="n">
         <v>1520</v>
       </c>
-      <c r="B205" t="n">
+      <c r="C205" t="n">
         <v>55</v>
       </c>
-      <c r="C205" t="n">
+      <c r="D205" t="n">
         <v>27.63636363636364</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" t="n">
         <v>1600</v>
       </c>
-      <c r="B206" t="n">
+      <c r="C206" t="n">
         <v>32</v>
       </c>
-      <c r="C206" t="n">
+      <c r="D206" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" t="n">
         <v>1620</v>
       </c>
-      <c r="B207" t="n">
+      <c r="C207" t="n">
         <v>54</v>
       </c>
-      <c r="C207" t="n">
+      <c r="D207" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" t="n">
         <v>1700</v>
       </c>
-      <c r="B208" t="n">
+      <c r="C208" t="n">
         <v>60</v>
       </c>
-      <c r="C208" t="n">
+      <c r="D208" t="n">
         <v>28.33333333333333</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" t="n">
         <v>1820</v>
       </c>
-      <c r="B209" t="n">
+      <c r="C209" t="n">
         <v>46</v>
       </c>
-      <c r="C209" t="n">
+      <c r="D209" t="n">
         <v>39.56521739130435</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" t="n">
         <v>1850</v>
       </c>
-      <c r="B210" t="n">
+      <c r="C210" t="n">
         <v>66</v>
       </c>
-      <c r="C210" t="n">
+      <c r="D210" t="n">
         <v>28.03030303030303</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" t="n">
         <v>1939</v>
       </c>
-      <c r="B211" t="n">
+      <c r="C211" t="n">
         <v>71</v>
       </c>
-      <c r="C211" t="n">
+      <c r="D211" t="n">
         <v>27.30985915492958</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" t="n">
         <v>1958</v>
       </c>
-      <c r="B212" t="n">
+      <c r="C212" t="n">
         <v>74</v>
       </c>
-      <c r="C212" t="n">
+      <c r="D212" t="n">
         <v>26.45945945945946</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" t="n">
         <v>1750</v>
       </c>
-      <c r="B213" t="n">
+      <c r="C213" t="n">
         <v>87</v>
       </c>
-      <c r="C213" t="n">
+      <c r="D213" t="n">
         <v>20.11494252873563</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" t="n">
         <v>2090</v>
       </c>
-      <c r="B214" t="n">
+      <c r="C214" t="n">
         <v>62</v>
       </c>
-      <c r="C214" t="n">
+      <c r="D214" t="n">
         <v>33.70967741935484</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" t="n">
         <v>2102</v>
       </c>
-      <c r="B215" t="n">
+      <c r="C215" t="n">
         <v>68</v>
       </c>
-      <c r="C215" t="n">
+      <c r="D215" t="n">
         <v>30.91176470588235</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" t="n">
         <v>2162</v>
       </c>
-      <c r="B216" t="n">
+      <c r="C216" t="n">
         <v>75</v>
       </c>
-      <c r="C216" t="n">
+      <c r="D216" t="n">
         <v>28.82666666666667</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" t="n">
         <v>2150</v>
       </c>
-      <c r="B217" t="n">
+      <c r="C217" t="n">
         <v>80</v>
       </c>
-      <c r="C217" t="n">
+      <c r="D217" t="n">
         <v>26.875</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" t="n">
         <v>2250</v>
       </c>
-      <c r="B218" t="n">
+      <c r="C218" t="n">
         <v>74</v>
       </c>
-      <c r="C218" t="n">
+      <c r="D218" t="n">
         <v>30.40540540540541</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" t="n">
         <v>2359</v>
       </c>
-      <c r="B219" t="n">
+      <c r="C219" t="n">
         <v>80</v>
       </c>
-      <c r="C219" t="n">
+      <c r="D219" t="n">
         <v>29.4875</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" t="n">
         <v>2400</v>
       </c>
-      <c r="B220" t="n">
+      <c r="C220" t="n">
         <v>112</v>
       </c>
-      <c r="C220" t="n">
+      <c r="D220" t="n">
         <v>21.42857142857143</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" t="n">
         <v>2459</v>
       </c>
-      <c r="B221" t="n">
+      <c r="C221" t="n">
         <v>96</v>
       </c>
-      <c r="C221" t="n">
+      <c r="D221" t="n">
         <v>25.61458333333333</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" t="n">
         <v>2400</v>
       </c>
-      <c r="B222" t="n">
+      <c r="C222" t="n">
         <v>112</v>
       </c>
-      <c r="C222" t="n">
+      <c r="D222" t="n">
         <v>21.42857142857143</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" t="n">
         <v>2459</v>
       </c>
-      <c r="B223" t="n">
+      <c r="C223" t="n">
         <v>96</v>
       </c>
-      <c r="C223" t="n">
+      <c r="D223" t="n">
         <v>25.61458333333333</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" t="n">
         <v>2535</v>
       </c>
-      <c r="B224" t="n">
+      <c r="C224" t="n">
         <v>86</v>
       </c>
-      <c r="C224" t="n">
+      <c r="D224" t="n">
         <v>29.47674418604651</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" t="n">
         <v>2650</v>
       </c>
-      <c r="B225" t="n">
+      <c r="C225" t="n">
         <v>90</v>
       </c>
-      <c r="C225" t="n">
+      <c r="D225" t="n">
         <v>29.44444444444444</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" t="n">
         <v>2650</v>
       </c>
-      <c r="B226" t="n">
+      <c r="C226" t="n">
         <v>98</v>
       </c>
-      <c r="C226" t="n">
+      <c r="D226" t="n">
         <v>27.04081632653061</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" t="n">
         <v>2900</v>
       </c>
-      <c r="B227" t="n">
+      <c r="C227" t="n">
         <v>105</v>
       </c>
-      <c r="C227" t="n">
+      <c r="D227" t="n">
         <v>27.61904761904762</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" t="n">
         <v>2950</v>
       </c>
-      <c r="B228" t="n">
+      <c r="C228" t="n">
         <v>70</v>
       </c>
-      <c r="C228" t="n">
+      <c r="D228" t="n">
         <v>42.14285714285715</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" t="n">
         <v>3000</v>
       </c>
-      <c r="B229" t="n">
+      <c r="C229" t="n">
         <v>88</v>
       </c>
-      <c r="C229" t="n">
+      <c r="D229" t="n">
         <v>34.09090909090909</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" t="n">
         <v>3234</v>
       </c>
-      <c r="B230" t="n">
+      <c r="C230" t="n">
         <v>105</v>
       </c>
-      <c r="C230" t="n">
+      <c r="D230" t="n">
         <v>30.8</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" t="n">
         <v>3243</v>
       </c>
-      <c r="B231" t="n">
+      <c r="C231" t="n">
         <v>120</v>
       </c>
-      <c r="C231" t="n">
+      <c r="D231" t="n">
         <v>27.025</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" t="n">
         <v>4200</v>
       </c>
-      <c r="B232" t="n">
+      <c r="C232" t="n">
         <v>117</v>
       </c>
-      <c r="C232" t="n">
+      <c r="D232" t="n">
         <v>35.8974358974359</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
+        <v>231</v>
+      </c>
+      <c r="B233" t="n">
         <v>4938</v>
       </c>
-      <c r="B233" t="n">
+      <c r="C233" t="n">
         <v>173</v>
       </c>
-      <c r="C233" t="n">
+      <c r="D233" t="n">
         <v>28.54335260115607</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
+        <v>232</v>
+      </c>
+      <c r="B234" t="n">
         <v>1100</v>
       </c>
-      <c r="B234" t="n">
+      <c r="C234" t="n">
         <v>31</v>
       </c>
-      <c r="C234" t="n">
+      <c r="D234" t="n">
         <v>35.48387096774194</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" t="n">
         <v>700</v>
       </c>
-      <c r="B235" t="n">
+      <c r="C235" t="n">
         <v>23</v>
       </c>
-      <c r="C235" t="n">
+      <c r="D235" t="n">
         <v>30.43478260869565</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" t="n">
         <v>880</v>
       </c>
-      <c r="B236" t="n">
+      <c r="C236" t="n">
         <v>21</v>
       </c>
-      <c r="C236" t="n">
+      <c r="D236" t="n">
         <v>41.90476190476191</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
+        <v>235</v>
+      </c>
+      <c r="B237" t="n">
         <v>930</v>
       </c>
-      <c r="B237" t="n">
+      <c r="C237" t="n">
         <v>15</v>
       </c>
-      <c r="C237" t="n">
+      <c r="D237" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
+        <v>236</v>
+      </c>
+      <c r="B238" t="n">
         <v>940</v>
       </c>
-      <c r="B238" t="n">
+      <c r="C238" t="n">
         <v>27</v>
       </c>
-      <c r="C238" t="n">
+      <c r="D238" t="n">
         <v>34.81481481481482</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
+        <v>237</v>
+      </c>
+      <c r="B239" t="n">
         <v>950</v>
       </c>
-      <c r="B239" t="n">
+      <c r="C239" t="n">
         <v>21</v>
       </c>
-      <c r="C239" t="n">
+      <c r="D239" t="n">
         <v>45.23809523809524</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
+        <v>238</v>
+      </c>
+      <c r="B240" t="n">
         <v>950</v>
       </c>
-      <c r="B240" t="n">
+      <c r="C240" t="n">
         <v>21</v>
       </c>
-      <c r="C240" t="n">
+      <c r="D240" t="n">
         <v>45.23809523809524</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
+        <v>239</v>
+      </c>
+      <c r="B241" t="n">
         <v>1000</v>
       </c>
-      <c r="B241" t="n">
+      <c r="C241" t="n">
         <v>21</v>
       </c>
-      <c r="C241" t="n">
+      <c r="D241" t="n">
         <v>47.61904761904762</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
+        <v>240</v>
+      </c>
+      <c r="B242" t="n">
         <v>1380</v>
       </c>
-      <c r="B242" t="n">
+      <c r="C242" t="n">
         <v>36</v>
       </c>
-      <c r="C242" t="n">
+      <c r="D242" t="n">
         <v>38.33333333333334</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
+        <v>241</v>
+      </c>
+      <c r="B243" t="n">
         <v>1700</v>
       </c>
-      <c r="B243" t="n">
+      <c r="C243" t="n">
         <v>57</v>
       </c>
-      <c r="C243" t="n">
+      <c r="D243" t="n">
         <v>29.82456140350877</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" t="n">
         <v>1740</v>
       </c>
-      <c r="B244" t="n">
+      <c r="C244" t="n">
         <v>49</v>
       </c>
-      <c r="C244" t="n">
+      <c r="D244" t="n">
         <v>35.51020408163265</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
+        <v>243</v>
+      </c>
+      <c r="B245" t="n">
         <v>2367</v>
       </c>
-      <c r="B245" t="n">
+      <c r="C245" t="n">
         <v>76</v>
       </c>
-      <c r="C245" t="n">
+      <c r="D245" t="n">
         <v>31.14473684210526</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
+        <v>244</v>
+      </c>
+      <c r="B246" t="n">
         <v>2800</v>
       </c>
-      <c r="B246" t="n">
+      <c r="C246" t="n">
         <v>83</v>
       </c>
-      <c r="C246" t="n">
+      <c r="D246" t="n">
         <v>33.73493975903614</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
+        <v>245</v>
+      </c>
+      <c r="B247" t="n">
         <v>3000</v>
       </c>
-      <c r="B247" t="n">
+      <c r="C247" t="n">
         <v>104</v>
       </c>
-      <c r="C247" t="n">
+      <c r="D247" t="n">
         <v>28.84615384615385</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
+        <v>246</v>
+      </c>
+      <c r="B248" t="n">
         <v>1365</v>
       </c>
-      <c r="B248" t="n">
+      <c r="C248" t="n">
         <v>44</v>
       </c>
-      <c r="C248" t="n">
+      <c r="D248" t="n">
         <v>31.02272727272727</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
+        <v>247</v>
+      </c>
+      <c r="B249" t="n">
         <v>855</v>
       </c>
-      <c r="B249" t="n">
+      <c r="C249" t="n">
         <v>20</v>
       </c>
-      <c r="C249" t="n">
+      <c r="D249" t="n">
         <v>42.75</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
+        <v>248</v>
+      </c>
+      <c r="B250" t="n">
         <v>1250</v>
       </c>
-      <c r="B250" t="n">
+      <c r="C250" t="n">
         <v>30</v>
       </c>
-      <c r="C250" t="n">
+      <c r="D250" t="n">
         <v>41.66666666666666</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" t="n">
         <v>2132</v>
       </c>
-      <c r="B251" t="n">
+      <c r="C251" t="n">
         <v>69</v>
       </c>
-      <c r="C251" t="n">
+      <c r="D251" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
+        <v>250</v>
+      </c>
+      <c r="B252" t="n">
         <v>2840</v>
       </c>
-      <c r="B252" t="n">
+      <c r="C252" t="n">
         <v>77</v>
       </c>
-      <c r="C252" t="n">
+      <c r="D252" t="n">
         <v>36.88311688311688</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
+        <v>251</v>
+      </c>
+      <c r="B253" t="n">
         <v>2614</v>
       </c>
-      <c r="B253" t="n">
+      <c r="C253" t="n">
         <v>96</v>
       </c>
-      <c r="C253" t="n">
+      <c r="D253" t="n">
         <v>27.22916666666667</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
+        <v>252</v>
+      </c>
+      <c r="B254" t="n">
         <v>693</v>
       </c>
-      <c r="B254" t="n">
+      <c r="C254" t="n">
         <v>19</v>
       </c>
-      <c r="C254" t="n">
+      <c r="D254" t="n">
         <v>36.47368421052632</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
+        <v>253</v>
+      </c>
+      <c r="B255" t="n">
         <v>1000</v>
       </c>
-      <c r="B255" t="n">
+      <c r="C255" t="n">
         <v>20</v>
       </c>
-      <c r="C255" t="n">
+      <c r="D255" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
+        <v>254</v>
+      </c>
+      <c r="B256" t="n">
         <v>2200</v>
       </c>
-      <c r="B256" t="n">
+      <c r="C256" t="n">
         <v>27</v>
       </c>
-      <c r="C256" t="n">
+      <c r="D256" t="n">
         <v>81.48148148148148</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
+        <v>255</v>
+      </c>
+      <c r="B257" t="n">
         <v>1900</v>
       </c>
-      <c r="B257" t="n">
+      <c r="C257" t="n">
         <v>60</v>
       </c>
-      <c r="C257" t="n">
+      <c r="D257" t="n">
         <v>31.66666666666667</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
+        <v>256</v>
+      </c>
+      <c r="B258" t="n">
         <v>2347</v>
       </c>
-      <c r="B258" t="n">
+      <c r="C258" t="n">
         <v>72</v>
       </c>
-      <c r="C258" t="n">
+      <c r="D258" t="n">
         <v>32.59722222222222</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
+        <v>257</v>
+      </c>
+      <c r="B259" t="n">
         <v>3460</v>
       </c>
-      <c r="B259" t="n">
+      <c r="C259" t="n">
         <v>103</v>
       </c>
-      <c r="C259" t="n">
+      <c r="D259" t="n">
         <v>33.59223300970874</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
+        <v>258</v>
+      </c>
+      <c r="B260" t="n">
         <v>1100</v>
       </c>
-      <c r="B260" t="n">
+      <c r="C260" t="n">
         <v>25</v>
       </c>
-      <c r="C260" t="n">
+      <c r="D260" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
+        <v>259</v>
+      </c>
+      <c r="B261" t="n">
         <v>1200</v>
       </c>
-      <c r="B261" t="n">
+      <c r="C261" t="n">
         <v>30</v>
       </c>
-      <c r="C261" t="n">
+      <c r="D261" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
+        <v>260</v>
+      </c>
+      <c r="B262" t="n">
         <v>1313</v>
       </c>
-      <c r="B262" t="n">
+      <c r="C262" t="n">
         <v>40</v>
       </c>
-      <c r="C262" t="n">
+      <c r="D262" t="n">
         <v>32.825</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
+        <v>261</v>
+      </c>
+      <c r="B263" t="n">
         <v>1490</v>
       </c>
-      <c r="B263" t="n">
+      <c r="C263" t="n">
         <v>54</v>
       </c>
-      <c r="C263" t="n">
+      <c r="D263" t="n">
         <v>27.59259259259259</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
+        <v>262</v>
+      </c>
+      <c r="B264" t="n">
         <v>1850</v>
       </c>
-      <c r="B264" t="n">
+      <c r="C264" t="n">
         <v>59</v>
       </c>
-      <c r="C264" t="n">
+      <c r="D264" t="n">
         <v>31.35593220338983</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
+        <v>263</v>
+      </c>
+      <c r="B265" t="n">
         <v>1880</v>
       </c>
-      <c r="B265" t="n">
+      <c r="C265" t="n">
         <v>62</v>
       </c>
-      <c r="C265" t="n">
+      <c r="D265" t="n">
         <v>30.32258064516129</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
+        <v>264</v>
+      </c>
+      <c r="B266" t="n">
         <v>1900</v>
       </c>
-      <c r="B266" t="n">
+      <c r="C266" t="n">
         <v>64</v>
       </c>
-      <c r="C266" t="n">
+      <c r="D266" t="n">
         <v>29.6875</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
+        <v>265</v>
+      </c>
+      <c r="B267" t="n">
         <v>1900</v>
       </c>
-      <c r="B267" t="n">
+      <c r="C267" t="n">
         <v>48</v>
       </c>
-      <c r="C267" t="n">
+      <c r="D267" t="n">
         <v>39.58333333333334</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
+        <v>266</v>
+      </c>
+      <c r="B268" t="n">
         <v>2008</v>
       </c>
-      <c r="B268" t="n">
+      <c r="C268" t="n">
         <v>87</v>
       </c>
-      <c r="C268" t="n">
+      <c r="D268" t="n">
         <v>23.08045977011494</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
+        <v>267</v>
+      </c>
+      <c r="B269" t="n">
         <v>2960</v>
       </c>
-      <c r="B269" t="n">
+      <c r="C269" t="n">
         <v>106</v>
       </c>
-      <c r="C269" t="n">
+      <c r="D269" t="n">
         <v>27.92452830188679</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
+        <v>268</v>
+      </c>
+      <c r="B270" t="n">
         <v>3200</v>
       </c>
-      <c r="B270" t="n">
+      <c r="C270" t="n">
         <v>114</v>
       </c>
-      <c r="C270" t="n">
+      <c r="D270" t="n">
         <v>28.07017543859649</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
+        <v>269</v>
+      </c>
+      <c r="B271" t="n">
         <v>3220</v>
       </c>
-      <c r="B271" t="n">
+      <c r="C271" t="n">
         <v>110</v>
       </c>
-      <c r="C271" t="n">
+      <c r="D271" t="n">
         <v>29.27272727272727</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
+        <v>270</v>
+      </c>
+      <c r="B272" t="n">
         <v>3380</v>
       </c>
-      <c r="B272" t="n">
+      <c r="C272" t="n">
         <v>129</v>
       </c>
-      <c r="C272" t="n">
+      <c r="D272" t="n">
         <v>26.2015503875969</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
+        <v>271</v>
+      </c>
+      <c r="B273" t="n">
         <v>3950</v>
       </c>
-      <c r="B273" t="n">
+      <c r="C273" t="n">
         <v>125</v>
       </c>
-      <c r="C273" t="n">
+      <c r="D273" t="n">
         <v>31.6</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
+        <v>272</v>
+      </c>
+      <c r="B274" t="n">
         <v>645</v>
       </c>
-      <c r="B274" t="n">
+      <c r="C274" t="n">
         <v>15</v>
       </c>
-      <c r="C274" t="n">
+      <c r="D274" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
+        <v>273</v>
+      </c>
+      <c r="B275" t="n">
         <v>682</v>
       </c>
-      <c r="B275" t="n">
+      <c r="C275" t="n">
         <v>17</v>
       </c>
-      <c r="C275" t="n">
+      <c r="D275" t="n">
         <v>40.11764705882353</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
+        <v>274</v>
+      </c>
+      <c r="B276" t="n">
         <v>745</v>
       </c>
-      <c r="B276" t="n">
+      <c r="C276" t="n">
         <v>20</v>
       </c>
-      <c r="C276" t="n">
+      <c r="D276" t="n">
         <v>37.25</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
+        <v>275</v>
+      </c>
+      <c r="B277" t="n">
         <v>1780</v>
       </c>
-      <c r="B277" t="n">
+      <c r="C277" t="n">
         <v>45</v>
       </c>
-      <c r="C277" t="n">
+      <c r="D277" t="n">
         <v>39.55555555555556</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
+        <v>276</v>
+      </c>
+      <c r="B278" t="n">
         <v>1595</v>
       </c>
-      <c r="B278" t="n">
+      <c r="C278" t="n">
         <v>54</v>
       </c>
-      <c r="C278" t="n">
+      <c r="D278" t="n">
         <v>29.53703703703704</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
+        <v>277</v>
+      </c>
+      <c r="B279" t="n">
         <v>4200</v>
       </c>
-      <c r="B279" t="n">
+      <c r="C279" t="n">
         <v>105</v>
       </c>
-      <c r="C279" t="n">
+      <c r="D279" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
+        <v>278</v>
+      </c>
+      <c r="B280" t="n">
         <v>9500</v>
       </c>
-      <c r="B280" t="n">
+      <c r="C280" t="n">
         <v>150</v>
       </c>
-      <c r="C280" t="n">
+      <c r="D280" t="n">
         <v>63.33333333333334</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
+        <v>279</v>
+      </c>
+      <c r="B281" t="n">
         <v>973</v>
       </c>
-      <c r="B281" t="n">
+      <c r="C281" t="n">
         <v>29</v>
       </c>
-      <c r="C281" t="n">
+      <c r="D281" t="n">
         <v>33.55172413793103</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
+        <v>280</v>
+      </c>
+      <c r="B282" t="n">
         <v>1100</v>
       </c>
-      <c r="B282" t="n">
+      <c r="C282" t="n">
         <v>36</v>
       </c>
-      <c r="C282" t="n">
+      <c r="D282" t="n">
         <v>30.55555555555556</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
+        <v>281</v>
+      </c>
+      <c r="B283" t="n">
         <v>1851</v>
       </c>
-      <c r="B283" t="n">
+      <c r="C283" t="n">
         <v>50</v>
       </c>
-      <c r="C283" t="n">
+      <c r="D283" t="n">
         <v>37.02</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
+        <v>282</v>
+      </c>
+      <c r="B284" t="n">
         <v>1105</v>
       </c>
-      <c r="B284" t="n">
+      <c r="C284" t="n">
         <v>33</v>
       </c>
-      <c r="C284" t="n">
+      <c r="D284" t="n">
         <v>33.48484848484848</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
+        <v>283</v>
+      </c>
+      <c r="B285" t="n">
         <v>1200</v>
       </c>
-      <c r="B285" t="n">
+      <c r="C285" t="n">
         <v>40</v>
       </c>
-      <c r="C285" t="n">
+      <c r="D285" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
+        <v>284</v>
+      </c>
+      <c r="B286" t="n">
         <v>1704</v>
       </c>
-      <c r="B286" t="n">
+      <c r="C286" t="n">
         <v>56</v>
       </c>
-      <c r="C286" t="n">
+      <c r="D286" t="n">
         <v>30.42857142857143</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
+        <v>285</v>
+      </c>
+      <c r="B287" t="n">
         <v>800</v>
       </c>
-      <c r="B287" t="n">
+      <c r="C287" t="n">
         <v>15</v>
       </c>
-      <c r="C287" t="n">
+      <c r="D287" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
+        <v>286</v>
+      </c>
+      <c r="B288" t="n">
         <v>985</v>
       </c>
-      <c r="B288" t="n">
+      <c r="C288" t="n">
         <v>34</v>
       </c>
-      <c r="C288" t="n">
+      <c r="D288" t="n">
         <v>28.97058823529412</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
+        <v>287</v>
+      </c>
+      <c r="B289" t="n">
         <v>1000</v>
       </c>
-      <c r="B289" t="n">
+      <c r="C289" t="n">
         <v>29</v>
       </c>
-      <c r="C289" t="n">
+      <c r="D289" t="n">
         <v>34.48275862068966</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
+        <v>288</v>
+      </c>
+      <c r="B290" t="n">
         <v>1006</v>
       </c>
-      <c r="B290" t="n">
+      <c r="C290" t="n">
         <v>26</v>
       </c>
-      <c r="C290" t="n">
+      <c r="D290" t="n">
         <v>38.69230769230769</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
+        <v>289</v>
+      </c>
+      <c r="B291" t="n">
         <v>1100</v>
       </c>
-      <c r="B291" t="n">
+      <c r="C291" t="n">
         <v>37</v>
       </c>
-      <c r="C291" t="n">
+      <c r="D291" t="n">
         <v>29.72972972972973</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
+        <v>290</v>
+      </c>
+      <c r="B292" t="n">
         <v>1220</v>
       </c>
-      <c r="B292" t="n">
+      <c r="C292" t="n">
         <v>32</v>
       </c>
-      <c r="C292" t="n">
+      <c r="D292" t="n">
         <v>38.125</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
+        <v>291</v>
+      </c>
+      <c r="B293" t="n">
         <v>1230</v>
       </c>
-      <c r="B293" t="n">
+      <c r="C293" t="n">
         <v>35</v>
       </c>
-      <c r="C293" t="n">
+      <c r="D293" t="n">
         <v>35.14285714285715</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
+        <v>292</v>
+      </c>
+      <c r="B294" t="n">
         <v>1270</v>
       </c>
-      <c r="B294" t="n">
+      <c r="C294" t="n">
         <v>30</v>
       </c>
-      <c r="C294" t="n">
+      <c r="D294" t="n">
         <v>42.33333333333334</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
+        <v>293</v>
+      </c>
+      <c r="B295" t="n">
         <v>1280</v>
       </c>
-      <c r="B295" t="n">
+      <c r="C295" t="n">
         <v>31</v>
       </c>
-      <c r="C295" t="n">
+      <c r="D295" t="n">
         <v>41.29032258064516</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
+        <v>294</v>
+      </c>
+      <c r="B296" t="n">
         <v>1290</v>
       </c>
-      <c r="B296" t="n">
+      <c r="C296" t="n">
         <v>38</v>
       </c>
-      <c r="C296" t="n">
+      <c r="D296" t="n">
         <v>33.94736842105263</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
+        <v>295</v>
+      </c>
+      <c r="B297" t="n">
         <v>1300</v>
       </c>
-      <c r="B297" t="n">
+      <c r="C297" t="n">
         <v>39</v>
       </c>
-      <c r="C297" t="n">
+      <c r="D297" t="n">
         <v>33.33333333333334</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
+        <v>296</v>
+      </c>
+      <c r="B298" t="n">
         <v>1340</v>
       </c>
-      <c r="B298" t="n">
+      <c r="C298" t="n">
         <v>34</v>
       </c>
-      <c r="C298" t="n">
+      <c r="D298" t="n">
         <v>39.41176470588236</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
+        <v>297</v>
+      </c>
+      <c r="B299" t="n">
         <v>1350</v>
       </c>
-      <c r="B299" t="n">
+      <c r="C299" t="n">
         <v>39</v>
       </c>
-      <c r="C299" t="n">
+      <c r="D299" t="n">
         <v>34.61538461538461</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
+        <v>298</v>
+      </c>
+      <c r="B300" t="n">
         <v>1380</v>
       </c>
-      <c r="B300" t="n">
+      <c r="C300" t="n">
         <v>40</v>
       </c>
-      <c r="C300" t="n">
+      <c r="D300" t="n">
         <v>34.5</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
+        <v>299</v>
+      </c>
+      <c r="B301" t="n">
         <v>1390</v>
       </c>
-      <c r="B301" t="n">
+      <c r="C301" t="n">
         <v>47</v>
       </c>
-      <c r="C301" t="n">
+      <c r="D301" t="n">
         <v>29.57446808510638</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
+        <v>300</v>
+      </c>
+      <c r="B302" t="n">
         <v>1390</v>
       </c>
-      <c r="B302" t="n">
+      <c r="C302" t="n">
         <v>40</v>
       </c>
-      <c r="C302" t="n">
+      <c r="D302" t="n">
         <v>34.75</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
+        <v>301</v>
+      </c>
+      <c r="B303" t="n">
         <v>1400</v>
       </c>
-      <c r="B303" t="n">
+      <c r="C303" t="n">
         <v>52</v>
       </c>
-      <c r="C303" t="n">
+      <c r="D303" t="n">
         <v>26.92307692307692</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
+        <v>302</v>
+      </c>
+      <c r="B304" t="n">
         <v>1400</v>
       </c>
-      <c r="B304" t="n">
+      <c r="C304" t="n">
         <v>40</v>
       </c>
-      <c r="C304" t="n">
+      <c r="D304" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
+        <v>303</v>
+      </c>
+      <c r="B305" t="n">
         <v>1400</v>
       </c>
-      <c r="B305" t="n">
+      <c r="C305" t="n">
         <v>33</v>
       </c>
-      <c r="C305" t="n">
+      <c r="D305" t="n">
         <v>42.42424242424242</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
+        <v>304</v>
+      </c>
+      <c r="B306" t="n">
         <v>1500</v>
       </c>
-      <c r="B306" t="n">
+      <c r="C306" t="n">
         <v>40</v>
       </c>
-      <c r="C306" t="n">
+      <c r="D306" t="n">
         <v>37.5</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
+        <v>305</v>
+      </c>
+      <c r="B307" t="n">
         <v>1550</v>
       </c>
-      <c r="B307" t="n">
+      <c r="C307" t="n">
         <v>50</v>
       </c>
-      <c r="C307" t="n">
+      <c r="D307" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
+        <v>306</v>
+      </c>
+      <c r="B308" t="n">
         <v>1570</v>
       </c>
-      <c r="B308" t="n">
+      <c r="C308" t="n">
         <v>51</v>
       </c>
-      <c r="C308" t="n">
+      <c r="D308" t="n">
         <v>30.7843137254902</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
+        <v>307</v>
+      </c>
+      <c r="B309" t="n">
         <v>1590</v>
       </c>
-      <c r="B309" t="n">
+      <c r="C309" t="n">
         <v>45</v>
       </c>
-      <c r="C309" t="n">
+      <c r="D309" t="n">
         <v>35.33333333333334</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
+        <v>308</v>
+      </c>
+      <c r="B310" t="n">
         <v>1600</v>
       </c>
-      <c r="B310" t="n">
+      <c r="C310" t="n">
         <v>35</v>
       </c>
-      <c r="C310" t="n">
+      <c r="D310" t="n">
         <v>45.71428571428572</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
+        <v>309</v>
+      </c>
+      <c r="B311" t="n">
         <v>1600</v>
       </c>
-      <c r="B311" t="n">
+      <c r="C311" t="n">
         <v>37</v>
       </c>
-      <c r="C311" t="n">
+      <c r="D311" t="n">
         <v>43.24324324324324</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
+        <v>310</v>
+      </c>
+      <c r="B312" t="n">
         <v>1627</v>
       </c>
-      <c r="B312" t="n">
+      <c r="C312" t="n">
         <v>46</v>
       </c>
-      <c r="C312" t="n">
+      <c r="D312" t="n">
         <v>35.3695652173913</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
+        <v>311</v>
+      </c>
+      <c r="B313" t="n">
         <v>1690</v>
       </c>
-      <c r="B313" t="n">
+      <c r="C313" t="n">
         <v>56</v>
       </c>
-      <c r="C313" t="n">
+      <c r="D313" t="n">
         <v>30.17857142857143</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
+        <v>312</v>
+      </c>
+      <c r="B314" t="n">
         <v>1696</v>
       </c>
-      <c r="B314" t="n">
+      <c r="C314" t="n">
         <v>57</v>
       </c>
-      <c r="C314" t="n">
+      <c r="D314" t="n">
         <v>29.75438596491228</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
+        <v>313</v>
+      </c>
+      <c r="B315" t="n">
         <v>1700</v>
       </c>
-      <c r="B315" t="n">
+      <c r="C315" t="n">
         <v>45</v>
       </c>
-      <c r="C315" t="n">
+      <c r="D315" t="n">
         <v>37.77777777777778</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
+        <v>314</v>
+      </c>
+      <c r="B316" t="n">
         <v>1700</v>
       </c>
-      <c r="B316" t="n">
+      <c r="C316" t="n">
         <v>47</v>
       </c>
-      <c r="C316" t="n">
+      <c r="D316" t="n">
         <v>36.17021276595744</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
+        <v>315</v>
+      </c>
+      <c r="B317" t="n">
         <v>1705</v>
       </c>
-      <c r="B317" t="n">
+      <c r="C317" t="n">
         <v>75</v>
       </c>
-      <c r="C317" t="n">
+      <c r="D317" t="n">
         <v>22.73333333333333</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
+        <v>316</v>
+      </c>
+      <c r="B318" t="n">
         <v>1750</v>
       </c>
-      <c r="B318" t="n">
+      <c r="C318" t="n">
         <v>51</v>
       </c>
-      <c r="C318" t="n">
+      <c r="D318" t="n">
         <v>34.31372549019608</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
+        <v>317</v>
+      </c>
+      <c r="B319" t="n">
         <v>1750</v>
       </c>
-      <c r="B319" t="n">
+      <c r="C319" t="n">
         <v>49</v>
       </c>
-      <c r="C319" t="n">
+      <c r="D319" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
+        <v>318</v>
+      </c>
+      <c r="B320" t="n">
         <v>1800</v>
       </c>
-      <c r="B320" t="n">
+      <c r="C320" t="n">
         <v>40</v>
       </c>
-      <c r="C320" t="n">
+      <c r="D320" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
+        <v>319</v>
+      </c>
+      <c r="B321" t="n">
         <v>1830</v>
       </c>
-      <c r="B321" t="n">
+      <c r="C321" t="n">
         <v>64</v>
       </c>
-      <c r="C321" t="n">
+      <c r="D321" t="n">
         <v>28.59375</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
+        <v>320</v>
+      </c>
+      <c r="B322" t="n">
         <v>1726</v>
       </c>
-      <c r="B322" t="n">
+      <c r="C322" t="n">
         <v>62</v>
       </c>
-      <c r="C322" t="n">
+      <c r="D322" t="n">
         <v>27.83870967741936</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
+        <v>321</v>
+      </c>
+      <c r="B323" t="n">
         <v>1850</v>
       </c>
-      <c r="B323" t="n">
+      <c r="C323" t="n">
         <v>35</v>
       </c>
-      <c r="C323" t="n">
+      <c r="D323" t="n">
         <v>52.85714285714285</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
+        <v>322</v>
+      </c>
+      <c r="B324" t="n">
         <v>1875</v>
       </c>
-      <c r="B324" t="n">
+      <c r="C324" t="n">
         <v>42</v>
       </c>
-      <c r="C324" t="n">
+      <c r="D324" t="n">
         <v>44.64285714285715</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
+        <v>323</v>
+      </c>
+      <c r="B325" t="n">
         <v>1900</v>
       </c>
-      <c r="B325" t="n">
+      <c r="C325" t="n">
         <v>45</v>
       </c>
-      <c r="C325" t="n">
+      <c r="D325" t="n">
         <v>42.22222222222222</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
+        <v>324</v>
+      </c>
+      <c r="B326" t="n">
         <v>1930</v>
       </c>
-      <c r="B326" t="n">
+      <c r="C326" t="n">
         <v>64</v>
       </c>
-      <c r="C326" t="n">
+      <c r="D326" t="n">
         <v>30.15625</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
+        <v>325</v>
+      </c>
+      <c r="B327" t="n">
         <v>1990</v>
       </c>
-      <c r="B327" t="n">
+      <c r="C327" t="n">
         <v>61</v>
       </c>
-      <c r="C327" t="n">
+      <c r="D327" t="n">
         <v>32.62295081967213</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
+        <v>326</v>
+      </c>
+      <c r="B328" t="n">
         <v>2000</v>
       </c>
-      <c r="B328" t="n">
+      <c r="C328" t="n">
         <v>50</v>
       </c>
-      <c r="C328" t="n">
+      <c r="D328" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
+        <v>327</v>
+      </c>
+      <c r="B329" t="n">
         <v>2044</v>
       </c>
-      <c r="B329" t="n">
+      <c r="C329" t="n">
         <v>64</v>
       </c>
-      <c r="C329" t="n">
+      <c r="D329" t="n">
         <v>31.9375</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
+        <v>328</v>
+      </c>
+      <c r="B330" t="n">
         <v>2060</v>
       </c>
-      <c r="B330" t="n">
+      <c r="C330" t="n">
         <v>69</v>
       </c>
-      <c r="C330" t="n">
+      <c r="D330" t="n">
         <v>29.85507246376812</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
+        <v>329</v>
+      </c>
+      <c r="B331" t="n">
         <v>2100</v>
       </c>
-      <c r="B331" t="n">
+      <c r="C331" t="n">
         <v>50</v>
       </c>
-      <c r="C331" t="n">
+      <c r="D331" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
+        <v>330</v>
+      </c>
+      <c r="B332" t="n">
         <v>1922</v>
       </c>
-      <c r="B332" t="n">
+      <c r="C332" t="n">
         <v>73</v>
       </c>
-      <c r="C332" t="n">
+      <c r="D332" t="n">
         <v>26.32876712328767</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
+        <v>331</v>
+      </c>
+      <c r="B333" t="n">
         <v>2190</v>
       </c>
-      <c r="B333" t="n">
+      <c r="C333" t="n">
         <v>70</v>
       </c>
-      <c r="C333" t="n">
+      <c r="D333" t="n">
         <v>31.28571428571428</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
+        <v>332</v>
+      </c>
+      <c r="B334" t="n">
         <v>2250</v>
       </c>
-      <c r="B334" t="n">
+      <c r="C334" t="n">
         <v>66</v>
       </c>
-      <c r="C334" t="n">
+      <c r="D334" t="n">
         <v>34.09090909090909</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
+        <v>333</v>
+      </c>
+      <c r="B335" t="n">
         <v>2250</v>
       </c>
-      <c r="B335" t="n">
+      <c r="C335" t="n">
         <v>55</v>
       </c>
-      <c r="C335" t="n">
+      <c r="D335" t="n">
         <v>40.90909090909091</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
+        <v>334</v>
+      </c>
+      <c r="B336" t="n">
         <v>2300</v>
       </c>
-      <c r="B336" t="n">
+      <c r="C336" t="n">
         <v>65</v>
       </c>
-      <c r="C336" t="n">
+      <c r="D336" t="n">
         <v>35.38461538461539</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
+        <v>335</v>
+      </c>
+      <c r="B337" t="n">
         <v>2300</v>
       </c>
-      <c r="B337" t="n">
+      <c r="C337" t="n">
         <v>80</v>
       </c>
-      <c r="C337" t="n">
+      <c r="D337" t="n">
         <v>28.75</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
+        <v>336</v>
+      </c>
+      <c r="B338" t="n">
         <v>2309</v>
       </c>
-      <c r="B338" t="n">
+      <c r="C338" t="n">
         <v>88</v>
       </c>
-      <c r="C338" t="n">
+      <c r="D338" t="n">
         <v>26.23863636363636</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
+        <v>337</v>
+      </c>
+      <c r="B339" t="n">
         <v>2450</v>
       </c>
-      <c r="B339" t="n">
+      <c r="C339" t="n">
         <v>54</v>
       </c>
-      <c r="C339" t="n">
+      <c r="D339" t="n">
         <v>45.37037037037037</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
+        <v>338</v>
+      </c>
+      <c r="B340" t="n">
         <v>2471</v>
       </c>
-      <c r="B340" t="n">
+      <c r="C340" t="n">
         <v>89</v>
       </c>
-      <c r="C340" t="n">
+      <c r="D340" t="n">
         <v>27.76404494382022</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
+        <v>339</v>
+      </c>
+      <c r="B341" t="n">
         <v>2500</v>
       </c>
-      <c r="B341" t="n">
+      <c r="C341" t="n">
         <v>52</v>
       </c>
-      <c r="C341" t="n">
+      <c r="D341" t="n">
         <v>48.07692307692308</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
+        <v>340</v>
+      </c>
+      <c r="B342" t="n">
         <v>2500</v>
       </c>
-      <c r="B342" t="n">
+      <c r="C342" t="n">
         <v>32</v>
       </c>
-      <c r="C342" t="n">
+      <c r="D342" t="n">
         <v>78.125</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
+        <v>341</v>
+      </c>
+      <c r="B343" t="n">
         <v>2500</v>
       </c>
-      <c r="B343" t="n">
+      <c r="C343" t="n">
         <v>63</v>
       </c>
-      <c r="C343" t="n">
+      <c r="D343" t="n">
         <v>39.68253968253968</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
+        <v>342</v>
+      </c>
+      <c r="B344" t="n">
         <v>2500</v>
       </c>
-      <c r="B344" t="n">
+      <c r="C344" t="n">
         <v>76</v>
       </c>
-      <c r="C344" t="n">
+      <c r="D344" t="n">
         <v>32.89473684210526</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
+        <v>343</v>
+      </c>
+      <c r="B345" t="n">
         <v>2587</v>
       </c>
-      <c r="B345" t="n">
+      <c r="C345" t="n">
         <v>73</v>
       </c>
-      <c r="C345" t="n">
+      <c r="D345" t="n">
         <v>35.43835616438356</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
+        <v>344</v>
+      </c>
+      <c r="B346" t="n">
         <v>2700</v>
       </c>
-      <c r="B346" t="n">
+      <c r="C346" t="n">
         <v>101</v>
       </c>
-      <c r="C346" t="n">
+      <c r="D346" t="n">
         <v>26.73267326732673</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
+        <v>345</v>
+      </c>
+      <c r="B347" t="n">
         <v>2700</v>
       </c>
-      <c r="B347" t="n">
+      <c r="C347" t="n">
         <v>84</v>
       </c>
-      <c r="C347" t="n">
+      <c r="D347" t="n">
         <v>32.14285714285715</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
+        <v>346</v>
+      </c>
+      <c r="B348" t="n">
         <v>2750</v>
       </c>
-      <c r="B348" t="n">
+      <c r="C348" t="n">
         <v>81</v>
       </c>
-      <c r="C348" t="n">
+      <c r="D348" t="n">
         <v>33.95061728395062</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
+        <v>347</v>
+      </c>
+      <c r="B349" t="n">
         <v>2800</v>
       </c>
-      <c r="B349" t="n">
+      <c r="C349" t="n">
         <v>68</v>
       </c>
-      <c r="C349" t="n">
+      <c r="D349" t="n">
         <v>41.1764705882353</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
+        <v>348</v>
+      </c>
+      <c r="B350" t="n">
         <v>2800</v>
       </c>
-      <c r="B350" t="n">
+      <c r="C350" t="n">
         <v>60</v>
       </c>
-      <c r="C350" t="n">
+      <c r="D350" t="n">
         <v>46.66666666666666</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
+        <v>349</v>
+      </c>
+      <c r="B351" t="n">
         <v>2886</v>
       </c>
-      <c r="B351" t="n">
+      <c r="C351" t="n">
         <v>85</v>
       </c>
-      <c r="C351" t="n">
+      <c r="D351" t="n">
         <v>33.95294117647059</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
+        <v>350</v>
+      </c>
+      <c r="B352" t="n">
         <v>2900</v>
       </c>
-      <c r="B352" t="n">
+      <c r="C352" t="n">
         <v>110</v>
       </c>
-      <c r="C352" t="n">
+      <c r="D352" t="n">
         <v>26.36363636363636</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
+        <v>351</v>
+      </c>
+      <c r="B353" t="n">
         <v>3000</v>
       </c>
-      <c r="B353" t="n">
+      <c r="C353" t="n">
         <v>95</v>
       </c>
-      <c r="C353" t="n">
+      <c r="D353" t="n">
         <v>31.57894736842105</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
+        <v>352</v>
+      </c>
+      <c r="B354" t="n">
         <v>3000</v>
       </c>
-      <c r="B354" t="n">
+      <c r="C354" t="n">
         <v>101</v>
       </c>
-      <c r="C354" t="n">
+      <c r="D354" t="n">
         <v>29.7029702970297</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
+        <v>353</v>
+      </c>
+      <c r="B355" t="n">
         <v>3000</v>
       </c>
-      <c r="B355" t="n">
+      <c r="C355" t="n">
         <v>90</v>
       </c>
-      <c r="C355" t="n">
+      <c r="D355" t="n">
         <v>33.33333333333334</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
+        <v>354</v>
+      </c>
+      <c r="B356" t="n">
         <v>2840</v>
       </c>
-      <c r="B356" t="n">
+      <c r="C356" t="n">
         <v>100</v>
       </c>
-      <c r="C356" t="n">
+      <c r="D356" t="n">
         <v>28.4</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
+        <v>355</v>
+      </c>
+      <c r="B357" t="n">
         <v>3100</v>
       </c>
-      <c r="B357" t="n">
+      <c r="C357" t="n">
         <v>100</v>
       </c>
-      <c r="C357" t="n">
+      <c r="D357" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
+        <v>356</v>
+      </c>
+      <c r="B358" t="n">
         <v>3179</v>
       </c>
-      <c r="B358" t="n">
+      <c r="C358" t="n">
         <v>72</v>
       </c>
-      <c r="C358" t="n">
+      <c r="D358" t="n">
         <v>44.15277777777778</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
+        <v>357</v>
+      </c>
+      <c r="B359" t="n">
         <v>3200</v>
       </c>
-      <c r="B359" t="n">
+      <c r="C359" t="n">
         <v>114</v>
       </c>
-      <c r="C359" t="n">
+      <c r="D359" t="n">
         <v>28.07017543859649</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
+        <v>358</v>
+      </c>
+      <c r="B360" t="n">
         <v>3200</v>
       </c>
-      <c r="B360" t="n">
+      <c r="C360" t="n">
         <v>110</v>
       </c>
-      <c r="C360" t="n">
+      <c r="D360" t="n">
         <v>29.09090909090909</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
+        <v>359</v>
+      </c>
+      <c r="B361" t="n">
         <v>3000</v>
       </c>
-      <c r="B361" t="n">
+      <c r="C361" t="n">
         <v>110</v>
       </c>
-      <c r="C361" t="n">
+      <c r="D361" t="n">
         <v>27.27272727272727</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
+        <v>360</v>
+      </c>
+      <c r="B362" t="n">
         <v>3200</v>
       </c>
-      <c r="B362" t="n">
+      <c r="C362" t="n">
         <v>105</v>
       </c>
-      <c r="C362" t="n">
+      <c r="D362" t="n">
         <v>30.47619047619047</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
+        <v>361</v>
+      </c>
+      <c r="B363" t="n">
         <v>3300</v>
       </c>
-      <c r="B363" t="n">
+      <c r="C363" t="n">
         <v>101</v>
       </c>
-      <c r="C363" t="n">
+      <c r="D363" t="n">
         <v>32.67326732673267</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
+        <v>362</v>
+      </c>
+      <c r="B364" t="n">
         <v>3300</v>
       </c>
-      <c r="B364" t="n">
+      <c r="C364" t="n">
         <v>95</v>
       </c>
-      <c r="C364" t="n">
+      <c r="D364" t="n">
         <v>34.73684210526316</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
+        <v>363</v>
+      </c>
+      <c r="B365" t="n">
         <v>3300</v>
       </c>
-      <c r="B365" t="n">
+      <c r="C365" t="n">
         <v>108</v>
       </c>
-      <c r="C365" t="n">
+      <c r="D365" t="n">
         <v>30.55555555555556</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
+        <v>364</v>
+      </c>
+      <c r="B366" t="n">
         <v>3460</v>
       </c>
-      <c r="B366" t="n">
+      <c r="C366" t="n">
         <v>103</v>
       </c>
-      <c r="C366" t="n">
+      <c r="D366" t="n">
         <v>33.59223300970874</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
+        <v>365</v>
+      </c>
+      <c r="B367" t="n">
         <v>3500</v>
       </c>
-      <c r="B367" t="n">
+      <c r="C367" t="n">
         <v>78</v>
       </c>
-      <c r="C367" t="n">
+      <c r="D367" t="n">
         <v>44.87179487179487</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
+        <v>366</v>
+      </c>
+      <c r="B368" t="n">
         <v>3650</v>
       </c>
-      <c r="B368" t="n">
+      <c r="C368" t="n">
         <v>120</v>
       </c>
-      <c r="C368" t="n">
+      <c r="D368" t="n">
         <v>30.41666666666667</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
+        <v>367</v>
+      </c>
+      <c r="B369" t="n">
         <v>3660</v>
       </c>
-      <c r="B369" t="n">
+      <c r="C369" t="n">
         <v>100</v>
       </c>
-      <c r="C369" t="n">
+      <c r="D369" t="n">
         <v>36.6</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
+        <v>368</v>
+      </c>
+      <c r="B370" t="n">
         <v>3680</v>
       </c>
-      <c r="B370" t="n">
+      <c r="C370" t="n">
         <v>112</v>
       </c>
-      <c r="C370" t="n">
+      <c r="D370" t="n">
         <v>32.85714285714285</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
+        <v>369</v>
+      </c>
+      <c r="B371" t="n">
         <v>3700</v>
       </c>
-      <c r="B371" t="n">
+      <c r="C371" t="n">
         <v>145</v>
       </c>
-      <c r="C371" t="n">
+      <c r="D371" t="n">
         <v>25.51724137931035</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
+        <v>370</v>
+      </c>
+      <c r="B372" t="n">
         <v>4500</v>
       </c>
-      <c r="B372" t="n">
+      <c r="C372" t="n">
         <v>117</v>
       </c>
-      <c r="C372" t="n">
+      <c r="D372" t="n">
         <v>38.46153846153846</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
+        <v>371</v>
+      </c>
+      <c r="B373" t="n">
         <v>4600</v>
       </c>
-      <c r="B373" t="n">
+      <c r="C373" t="n">
         <v>131</v>
       </c>
-      <c r="C373" t="n">
+      <c r="D373" t="n">
         <v>35.11450381679389</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
+        <v>372</v>
+      </c>
+      <c r="B374" t="n">
         <v>4930</v>
       </c>
-      <c r="B374" t="n">
+      <c r="C374" t="n">
         <v>117</v>
       </c>
-      <c r="C374" t="n">
+      <c r="D374" t="n">
         <v>42.13675213675214</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
+        <v>373</v>
+      </c>
+      <c r="B375" t="n">
         <v>4937</v>
       </c>
-      <c r="B375" t="n">
+      <c r="C375" t="n">
         <v>173</v>
       </c>
-      <c r="C375" t="n">
+      <c r="D375" t="n">
         <v>28.53757225433526</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
+        <v>374</v>
+      </c>
+      <c r="B376" t="n">
         <v>5100</v>
       </c>
-      <c r="B376" t="n">
+      <c r="C376" t="n">
         <v>100</v>
       </c>
-      <c r="C376" t="n">
+      <c r="D376" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
+        <v>375</v>
+      </c>
+      <c r="B377" t="n">
         <v>5233</v>
       </c>
-      <c r="B377" t="n">
+      <c r="C377" t="n">
         <v>162</v>
       </c>
-      <c r="C377" t="n">
+      <c r="D377" t="n">
         <v>32.30246913580247</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
+        <v>376</v>
+      </c>
+      <c r="B378" t="n">
         <v>5249</v>
       </c>
-      <c r="B378" t="n">
+      <c r="C378" t="n">
         <v>162</v>
       </c>
-      <c r="C378" t="n">
+      <c r="D378" t="n">
         <v>32.40123456790123</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
+        <v>377</v>
+      </c>
+      <c r="B379" t="n">
         <v>5000</v>
       </c>
-      <c r="B379" t="n">
+      <c r="C379" t="n">
         <v>152</v>
       </c>
-      <c r="C379" t="n">
+      <c r="D379" t="n">
         <v>32.89473684210526</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
+        <v>378</v>
+      </c>
+      <c r="B380" t="n">
         <v>5307</v>
       </c>
-      <c r="B380" t="n">
+      <c r="C380" t="n">
         <v>175</v>
       </c>
-      <c r="C380" t="n">
+      <c r="D380" t="n">
         <v>30.32571428571429</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
+        <v>379</v>
+      </c>
+      <c r="B381" t="n">
         <v>5950</v>
       </c>
-      <c r="B381" t="n">
+      <c r="C381" t="n">
         <v>235</v>
       </c>
-      <c r="C381" t="n">
+      <c r="D381" t="n">
         <v>25.31914893617021</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
+        <v>380</v>
+      </c>
+      <c r="B382" t="n">
         <v>7450</v>
       </c>
-      <c r="B382" t="n">
+      <c r="C382" t="n">
         <v>180</v>
       </c>
-      <c r="C382" t="n">
+      <c r="D382" t="n">
         <v>41.38888888888889</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
+        <v>381</v>
+      </c>
+      <c r="B383" t="n">
         <v>25000</v>
       </c>
-      <c r="B383" t="n">
+      <c r="C383" t="n">
         <v>415</v>
       </c>
-      <c r="C383" t="n">
+      <c r="D383" t="n">
         <v>60.24096385542169</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
+        <v>382</v>
+      </c>
+      <c r="B384" t="n">
         <v>730</v>
       </c>
-      <c r="B384" t="n">
+      <c r="C384" t="n">
         <v>11</v>
       </c>
-      <c r="C384" t="n">
+      <c r="D384" t="n">
         <v>66.36363636363636</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
+        <v>383</v>
+      </c>
+      <c r="B385" t="n">
         <v>738</v>
       </c>
-      <c r="B385" t="n">
+      <c r="C385" t="n">
         <v>14</v>
       </c>
-      <c r="C385" t="n">
+      <c r="D385" t="n">
         <v>52.71428571428572</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
+        <v>384</v>
+      </c>
+      <c r="B386" t="n">
         <v>821</v>
       </c>
-      <c r="B386" t="n">
+      <c r="C386" t="n">
         <v>18</v>
       </c>
-      <c r="C386" t="n">
+      <c r="D386" t="n">
         <v>45.61111111111111</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
+        <v>385</v>
+      </c>
+      <c r="B387" t="n">
         <v>850</v>
       </c>
-      <c r="B387" t="n">
+      <c r="C387" t="n">
         <v>16</v>
       </c>
-      <c r="C387" t="n">
+      <c r="D387" t="n">
         <v>53.125</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
+        <v>386</v>
+      </c>
+      <c r="B388" t="n">
         <v>854</v>
       </c>
-      <c r="B388" t="n">
+      <c r="C388" t="n">
         <v>25</v>
       </c>
-      <c r="C388" t="n">
+      <c r="D388" t="n">
         <v>34.16</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
+        <v>387</v>
+      </c>
+      <c r="B389" t="n">
         <v>910</v>
       </c>
-      <c r="B389" t="n">
+      <c r="C389" t="n">
         <v>24</v>
       </c>
-      <c r="C389" t="n">
+      <c r="D389" t="n">
         <v>37.91666666666666</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
+        <v>388</v>
+      </c>
+      <c r="B390" t="n">
         <v>940</v>
       </c>
-      <c r="B390" t="n">
+      <c r="C390" t="n">
         <v>19</v>
       </c>
-      <c r="C390" t="n">
+      <c r="D390" t="n">
         <v>49.47368421052632</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
+        <v>389</v>
+      </c>
+      <c r="B391" t="n">
         <v>950</v>
       </c>
-      <c r="B391" t="n">
+      <c r="C391" t="n">
         <v>20</v>
       </c>
-      <c r="C391" t="n">
+      <c r="D391" t="n">
         <v>47.5</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
+        <v>390</v>
+      </c>
+      <c r="B392" t="n">
         <v>950</v>
       </c>
-      <c r="B392" t="n">
+      <c r="C392" t="n">
         <v>21</v>
       </c>
-      <c r="C392" t="n">
+      <c r="D392" t="n">
         <v>45.23809523809524</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
+        <v>391</v>
+      </c>
+      <c r="B393" t="n">
         <v>976</v>
       </c>
-      <c r="B393" t="n">
+      <c r="C393" t="n">
         <v>23</v>
       </c>
-      <c r="C393" t="n">
+      <c r="D393" t="n">
         <v>42.43478260869565</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
+        <v>392</v>
+      </c>
+      <c r="B394" t="n">
         <v>990</v>
       </c>
-      <c r="B394" t="n">
+      <c r="C394" t="n">
         <v>27</v>
       </c>
-      <c r="C394" t="n">
+      <c r="D394" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
+        <v>393</v>
+      </c>
+      <c r="B395" t="n">
         <v>1190</v>
       </c>
-      <c r="B395" t="n">
+      <c r="C395" t="n">
         <v>29</v>
       </c>
-      <c r="C395" t="n">
+      <c r="D395" t="n">
         <v>41.03448275862069</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
+        <v>394</v>
+      </c>
+      <c r="B396" t="n">
         <v>1095</v>
       </c>
-      <c r="B396" t="n">
+      <c r="C396" t="n">
         <v>30</v>
       </c>
-      <c r="C396" t="n">
+      <c r="D396" t="n">
         <v>36.5</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
+        <v>395</v>
+      </c>
+      <c r="B397" t="n">
         <v>1210</v>
       </c>
-      <c r="B397" t="n">
+      <c r="C397" t="n">
         <v>40</v>
       </c>
-      <c r="C397" t="n">
+      <c r="D397" t="n">
         <v>30.25</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
+        <v>396</v>
+      </c>
+      <c r="B398" t="n">
         <v>1250</v>
       </c>
-      <c r="B398" t="n">
+      <c r="C398" t="n">
         <v>28</v>
       </c>
-      <c r="C398" t="n">
+      <c r="D398" t="n">
         <v>44.64285714285715</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
+        <v>397</v>
+      </c>
+      <c r="B399" t="n">
         <v>1255</v>
       </c>
-      <c r="B399" t="n">
+      <c r="C399" t="n">
         <v>24</v>
       </c>
-      <c r="C399" t="n">
+      <c r="D399" t="n">
         <v>52.29166666666666</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
+        <v>398</v>
+      </c>
+      <c r="B400" t="n">
         <v>1255</v>
       </c>
-      <c r="B400" t="n">
+      <c r="C400" t="n">
         <v>24</v>
       </c>
-      <c r="C400" t="n">
+      <c r="D400" t="n">
         <v>52.29166666666666</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
+        <v>399</v>
+      </c>
+      <c r="B401" t="n">
         <v>1300</v>
       </c>
-      <c r="B401" t="n">
+      <c r="C401" t="n">
         <v>32</v>
       </c>
-      <c r="C401" t="n">
+      <c r="D401" t="n">
         <v>40.625</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
+        <v>400</v>
+      </c>
+      <c r="B402" t="n">
         <v>1380</v>
       </c>
-      <c r="B402" t="n">
+      <c r="C402" t="n">
         <v>32</v>
       </c>
-      <c r="C402" t="n">
+      <c r="D402" t="n">
         <v>43.125</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
+        <v>401</v>
+      </c>
+      <c r="B403" t="n">
         <v>1500</v>
       </c>
-      <c r="B403" t="n">
+      <c r="C403" t="n">
         <v>42</v>
       </c>
-      <c r="C403" t="n">
+      <c r="D403" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
+        <v>402</v>
+      </c>
+      <c r="B404" t="n">
         <v>1500</v>
       </c>
-      <c r="B404" t="n">
+      <c r="C404" t="n">
         <v>34</v>
       </c>
-      <c r="C404" t="n">
+      <c r="D404" t="n">
         <v>44.11764705882353</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
+        <v>403</v>
+      </c>
+      <c r="B405" t="n">
         <v>1510</v>
       </c>
-      <c r="B405" t="n">
+      <c r="C405" t="n">
         <v>29</v>
       </c>
-      <c r="C405" t="n">
+      <c r="D405" t="n">
         <v>52.06896551724138</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
+        <v>404</v>
+      </c>
+      <c r="B406" t="n">
         <v>1550</v>
       </c>
-      <c r="B406" t="n">
+      <c r="C406" t="n">
         <v>30</v>
       </c>
-      <c r="C406" t="n">
+      <c r="D406" t="n">
         <v>51.66666666666666</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
+        <v>405</v>
+      </c>
+      <c r="B407" t="n">
         <v>1560</v>
       </c>
-      <c r="B407" t="n">
+      <c r="C407" t="n">
         <v>50</v>
       </c>
-      <c r="C407" t="n">
+      <c r="D407" t="n">
         <v>31.2</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
+        <v>406</v>
+      </c>
+      <c r="B408" t="n">
         <v>1580</v>
       </c>
-      <c r="B408" t="n">
+      <c r="C408" t="n">
         <v>35</v>
       </c>
-      <c r="C408" t="n">
+      <c r="D408" t="n">
         <v>45.14285714285715</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
+        <v>407</v>
+      </c>
+      <c r="B409" t="n">
         <v>1640</v>
       </c>
-      <c r="B409" t="n">
+      <c r="C409" t="n">
         <v>47</v>
       </c>
-      <c r="C409" t="n">
+      <c r="D409" t="n">
         <v>34.8936170212766</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
+        <v>408</v>
+      </c>
+      <c r="B410" t="n">
         <v>1650</v>
       </c>
-      <c r="B410" t="n">
+      <c r="C410" t="n">
         <v>40</v>
       </c>
-      <c r="C410" t="n">
+      <c r="D410" t="n">
         <v>41.25</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
+        <v>409</v>
+      </c>
+      <c r="B411" t="n">
         <v>1665</v>
       </c>
-      <c r="B411" t="n">
+      <c r="C411" t="n">
         <v>34</v>
       </c>
-      <c r="C411" t="n">
+      <c r="D411" t="n">
         <v>48.97058823529412</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
+        <v>410</v>
+      </c>
+      <c r="B412" t="n">
         <v>1865</v>
       </c>
-      <c r="B412" t="n">
+      <c r="C412" t="n">
         <v>55</v>
       </c>
-      <c r="C412" t="n">
+      <c r="D412" t="n">
         <v>33.90909090909091</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
+        <v>411</v>
+      </c>
+      <c r="B413" t="n">
         <v>1920</v>
       </c>
-      <c r="B413" t="n">
+      <c r="C413" t="n">
         <v>64</v>
       </c>
-      <c r="C413" t="n">
+      <c r="D413" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
+        <v>412</v>
+      </c>
+      <c r="B414" t="n">
         <v>2000</v>
       </c>
-      <c r="B414" t="n">
+      <c r="C414" t="n">
         <v>42</v>
       </c>
-      <c r="C414" t="n">
+      <c r="D414" t="n">
         <v>47.61904761904762</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
+        <v>413</v>
+      </c>
+      <c r="B415" t="n">
         <v>2000</v>
       </c>
-      <c r="B415" t="n">
+      <c r="C415" t="n">
         <v>41</v>
       </c>
-      <c r="C415" t="n">
+      <c r="D415" t="n">
         <v>48.78048780487805</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
+        <v>414</v>
+      </c>
+      <c r="B416" t="n">
         <v>2130</v>
       </c>
-      <c r="B416" t="n">
+      <c r="C416" t="n">
         <v>73</v>
       </c>
-      <c r="C416" t="n">
+      <c r="D416" t="n">
         <v>29.17808219178082</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
+        <v>415</v>
+      </c>
+      <c r="B417" t="n">
         <v>2200</v>
       </c>
-      <c r="B417" t="n">
+      <c r="C417" t="n">
         <v>57</v>
       </c>
-      <c r="C417" t="n">
+      <c r="D417" t="n">
         <v>38.59649122807018</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
+        <v>416</v>
+      </c>
+      <c r="B418" t="n">
         <v>2300</v>
       </c>
-      <c r="B418" t="n">
+      <c r="C418" t="n">
         <v>80</v>
       </c>
-      <c r="C418" t="n">
+      <c r="D418" t="n">
         <v>28.75</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
+        <v>417</v>
+      </c>
+      <c r="B419" t="n">
         <v>2500</v>
       </c>
-      <c r="B419" t="n">
+      <c r="C419" t="n">
         <v>60</v>
       </c>
-      <c r="C419" t="n">
+      <c r="D419" t="n">
         <v>41.66666666666666</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
+        <v>418</v>
+      </c>
+      <c r="B420" t="n">
         <v>3750</v>
       </c>
-      <c r="B420" t="n">
+      <c r="C420" t="n">
         <v>70</v>
       </c>
-      <c r="C420" t="n">
+      <c r="D420" t="n">
         <v>53.57142857142857</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
+        <v>419</v>
+      </c>
+      <c r="B421" t="n">
         <v>3800</v>
       </c>
-      <c r="B421" t="n">
+      <c r="C421" t="n">
         <v>138</v>
       </c>
-      <c r="C421" t="n">
+      <c r="D421" t="n">
         <v>27.53623188405797</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
+        <v>420</v>
+      </c>
+      <c r="B422" t="n">
         <v>4100</v>
       </c>
-      <c r="B422" t="n">
+      <c r="C422" t="n">
         <v>127</v>
       </c>
-      <c r="C422" t="n">
+      <c r="D422" t="n">
         <v>32.28346456692913</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
+        <v>421</v>
+      </c>
+      <c r="B423" t="n">
         <v>4300</v>
       </c>
-      <c r="B423" t="n">
+      <c r="C423" t="n">
         <v>148</v>
       </c>
-      <c r="C423" t="n">
+      <c r="D423" t="n">
         <v>29.05405405405405</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
+        <v>422</v>
+      </c>
+      <c r="B424" t="n">
         <v>4500</v>
       </c>
-      <c r="B424" t="n">
+      <c r="C424" t="n">
         <v>115</v>
       </c>
-      <c r="C424" t="n">
+      <c r="D424" t="n">
         <v>39.1304347826087</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
+        <v>423</v>
+      </c>
+      <c r="B425" t="n">
         <v>15000</v>
       </c>
-      <c r="B425" t="n">
+      <c r="C425" t="n">
         <v>347</v>
       </c>
-      <c r="C425" t="n">
+      <c r="D425" t="n">
         <v>43.22766570605187</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
+        <v>424</v>
+      </c>
+      <c r="B426" t="n">
         <v>637</v>
       </c>
-      <c r="B426" t="n">
+      <c r="C426" t="n">
         <v>14</v>
       </c>
-      <c r="C426" t="n">
+      <c r="D426" t="n">
         <v>45.5</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
+        <v>425</v>
+      </c>
+      <c r="B427" t="n">
         <v>680</v>
       </c>
-      <c r="B427" t="n">
+      <c r="C427" t="n">
         <v>14</v>
       </c>
-      <c r="C427" t="n">
+      <c r="D427" t="n">
         <v>48.57142857142857</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
+        <v>426</v>
+      </c>
+      <c r="B428" t="n">
         <v>700</v>
       </c>
-      <c r="B428" t="n">
+      <c r="C428" t="n">
         <v>18</v>
       </c>
-      <c r="C428" t="n">
+      <c r="D428" t="n">
         <v>38.88888888888889</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
+        <v>427</v>
+      </c>
+      <c r="B429" t="n">
         <v>960</v>
       </c>
-      <c r="B429" t="n">
+      <c r="C429" t="n">
         <v>20</v>
       </c>
-      <c r="C429" t="n">
+      <c r="D429" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
+        <v>428</v>
+      </c>
+      <c r="B430" t="n">
         <v>775</v>
       </c>
-      <c r="B430" t="n">
+      <c r="C430" t="n">
         <v>20</v>
       </c>
-      <c r="C430" t="n">
+      <c r="D430" t="n">
         <v>38.75</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
+        <v>429</v>
+      </c>
+      <c r="B431" t="n">
         <v>1250</v>
       </c>
-      <c r="B431" t="n">
+      <c r="C431" t="n">
         <v>40</v>
       </c>
-      <c r="C431" t="n">
+      <c r="D431" t="n">
         <v>31.25</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
+        <v>430</v>
+      </c>
+      <c r="B432" t="n">
         <v>1380</v>
       </c>
-      <c r="B432" t="n">
+      <c r="C432" t="n">
         <v>30</v>
       </c>
-      <c r="C432" t="n">
+      <c r="D432" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
+        <v>431</v>
+      </c>
+      <c r="B433" t="n">
         <v>1630</v>
       </c>
-      <c r="B433" t="n">
+      <c r="C433" t="n">
         <v>54</v>
       </c>
-      <c r="C433" t="n">
+      <c r="D433" t="n">
         <v>30.18518518518519</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
+        <v>432</v>
+      </c>
+      <c r="B434" t="n">
         <v>1650</v>
       </c>
-      <c r="B434" t="n">
+      <c r="C434" t="n">
         <v>50</v>
       </c>
-      <c r="C434" t="n">
+      <c r="D434" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
+        <v>433</v>
+      </c>
+      <c r="B435" t="n">
         <v>1765</v>
       </c>
-      <c r="B435" t="n">
+      <c r="C435" t="n">
         <v>62</v>
       </c>
-      <c r="C435" t="n">
+      <c r="D435" t="n">
         <v>28.46774193548387</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
+        <v>434</v>
+      </c>
+      <c r="B436" t="n">
         <v>1900</v>
       </c>
-      <c r="B436" t="n">
+      <c r="C436" t="n">
         <v>64</v>
       </c>
-      <c r="C436" t="n">
+      <c r="D436" t="n">
         <v>29.6875</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
+        <v>435</v>
+      </c>
+      <c r="B437" t="n">
         <v>1787</v>
       </c>
-      <c r="B437" t="n">
+      <c r="C437" t="n">
         <v>77</v>
       </c>
-      <c r="C437" t="n">
+      <c r="D437" t="n">
         <v>23.20779220779221</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
+        <v>436</v>
+      </c>
+      <c r="B438" t="n">
         <v>1920</v>
       </c>
-      <c r="B438" t="n">
+      <c r="C438" t="n">
         <v>64</v>
       </c>
-      <c r="C438" t="n">
+      <c r="D438" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
+        <v>437</v>
+      </c>
+      <c r="B439" t="n">
         <v>2132</v>
       </c>
-      <c r="B439" t="n">
+      <c r="C439" t="n">
         <v>69</v>
       </c>
-      <c r="C439" t="n">
+      <c r="D439" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
+        <v>438</v>
+      </c>
+      <c r="B440" t="n">
         <v>2132</v>
       </c>
-      <c r="B440" t="n">
+      <c r="C440" t="n">
         <v>69</v>
       </c>
-      <c r="C440" t="n">
+      <c r="D440" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
+        <v>439</v>
+      </c>
+      <c r="B441" t="n">
         <v>2200</v>
       </c>
-      <c r="B441" t="n">
+      <c r="C441" t="n">
         <v>60</v>
       </c>
-      <c r="C441" t="n">
+      <c r="D441" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
+        <v>440</v>
+      </c>
+      <c r="B442" t="n">
         <v>2272</v>
       </c>
-      <c r="B442" t="n">
+      <c r="C442" t="n">
         <v>69</v>
       </c>
-      <c r="C442" t="n">
+      <c r="D442" t="n">
         <v>32.92753623188405</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
+        <v>441</v>
+      </c>
+      <c r="B443" t="n">
         <v>2400</v>
       </c>
-      <c r="B443" t="n">
+      <c r="C443" t="n">
         <v>70</v>
       </c>
-      <c r="C443" t="n">
+      <c r="D443" t="n">
         <v>34.28571428571428</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
+        <v>442</v>
+      </c>
+      <c r="B444" t="n">
         <v>2350</v>
       </c>
-      <c r="B444" t="n">
+      <c r="C444" t="n">
         <v>70</v>
       </c>
-      <c r="C444" t="n">
+      <c r="D444" t="n">
         <v>33.57142857142857</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
+        <v>443</v>
+      </c>
+      <c r="B445" t="n">
         <v>2657</v>
       </c>
-      <c r="B445" t="n">
+      <c r="C445" t="n">
         <v>40</v>
       </c>
-      <c r="C445" t="n">
+      <c r="D445" t="n">
         <v>66.425</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
+        <v>444</v>
+      </c>
+      <c r="B446" t="n">
         <v>2999</v>
       </c>
-      <c r="B446" t="n">
+      <c r="C446" t="n">
         <v>76</v>
       </c>
-      <c r="C446" t="n">
+      <c r="D446" t="n">
         <v>39.46052631578947</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
+        <v>445</v>
+      </c>
+      <c r="B447" t="n">
         <v>3000</v>
       </c>
-      <c r="B447" t="n">
+      <c r="C447" t="n">
         <v>80</v>
       </c>
-      <c r="C447" t="n">
+      <c r="D447" t="n">
         <v>37.5</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
+        <v>446</v>
+      </c>
+      <c r="B448" t="n">
         <v>3460</v>
       </c>
-      <c r="B448" t="n">
+      <c r="C448" t="n">
         <v>103</v>
       </c>
-      <c r="C448" t="n">
+      <c r="D448" t="n">
         <v>33.59223300970874</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
+        <v>447</v>
+      </c>
+      <c r="B449" t="n">
         <v>3600</v>
       </c>
-      <c r="B449" t="n">
+      <c r="C449" t="n">
         <v>124</v>
       </c>
-      <c r="C449" t="n">
+      <c r="D449" t="n">
         <v>29.03225806451613</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
+        <v>448</v>
+      </c>
+      <c r="B450" t="n">
         <v>16000</v>
       </c>
-      <c r="B450" t="n">
+      <c r="C450" t="n">
         <v>347</v>
       </c>
-      <c r="C450" t="n">
+      <c r="D450" t="n">
         <v>46.10951008645533</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
+        <v>449</v>
+      </c>
+      <c r="B451" t="n">
         <v>20000</v>
       </c>
-      <c r="B451" t="n">
+      <c r="C451" t="n">
         <v>180</v>
       </c>
-      <c r="C451" t="n">
+      <c r="D451" t="n">
         <v>111.1111111111111</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
+        <v>450</v>
+      </c>
+      <c r="B452" t="n">
         <v>2290</v>
       </c>
-      <c r="B452" t="n">
+      <c r="C452" t="n">
         <v>70</v>
       </c>
-      <c r="C452" t="n">
+      <c r="D452" t="n">
         <v>32.71428571428572</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
+        <v>451</v>
+      </c>
+      <c r="B453" t="n">
         <v>2927</v>
       </c>
-      <c r="B453" t="n">
+      <c r="C453" t="n">
         <v>116</v>
       </c>
-      <c r="C453" t="n">
+      <c r="D453" t="n">
         <v>25.23275862068965</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
+        <v>452</v>
+      </c>
+      <c r="B454" t="n">
         <v>700</v>
       </c>
-      <c r="B454" t="n">
+      <c r="C454" t="n">
         <v>14</v>
       </c>
-      <c r="C454" t="n">
+      <c r="D454" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
+        <v>453</v>
+      </c>
+      <c r="B455" t="n">
         <v>755</v>
       </c>
-      <c r="B455" t="n">
+      <c r="C455" t="n">
         <v>19</v>
       </c>
-      <c r="C455" t="n">
+      <c r="D455" t="n">
         <v>39.73684210526316</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
+        <v>454</v>
+      </c>
+      <c r="B456" t="n">
         <v>990</v>
       </c>
-      <c r="B456" t="n">
+      <c r="C456" t="n">
         <v>24</v>
       </c>
-      <c r="C456" t="n">
+      <c r="D456" t="n">
         <v>41.25</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
+        <v>455</v>
+      </c>
+      <c r="B457" t="n">
         <v>1058</v>
       </c>
-      <c r="B457" t="n">
+      <c r="C457" t="n">
         <v>21</v>
       </c>
-      <c r="C457" t="n">
+      <c r="D457" t="n">
         <v>50.38095238095238</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
+        <v>456</v>
+      </c>
+      <c r="B458" t="n">
         <v>1095</v>
       </c>
-      <c r="B458" t="n">
+      <c r="C458" t="n">
         <v>20</v>
       </c>
-      <c r="C458" t="n">
+      <c r="D458" t="n">
         <v>54.75</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
+        <v>457</v>
+      </c>
+      <c r="B459" t="n">
         <v>1100</v>
       </c>
-      <c r="B459" t="n">
+      <c r="C459" t="n">
         <v>37</v>
       </c>
-      <c r="C459" t="n">
+      <c r="D459" t="n">
         <v>29.72972972972973</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
+        <v>458</v>
+      </c>
+      <c r="B460" t="n">
         <v>1280</v>
       </c>
-      <c r="B460" t="n">
+      <c r="C460" t="n">
         <v>29</v>
       </c>
-      <c r="C460" t="n">
+      <c r="D460" t="n">
         <v>44.13793103448276</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
+        <v>459</v>
+      </c>
+      <c r="B461" t="n">
         <v>1350</v>
       </c>
-      <c r="B461" t="n">
+      <c r="C461" t="n">
         <v>35</v>
       </c>
-      <c r="C461" t="n">
+      <c r="D461" t="n">
         <v>38.57142857142857</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
+        <v>460</v>
+      </c>
+      <c r="B462" t="n">
         <v>1400</v>
       </c>
-      <c r="B462" t="n">
+      <c r="C462" t="n">
         <v>45</v>
       </c>
-      <c r="C462" t="n">
+      <c r="D462" t="n">
         <v>31.11111111111111</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
+        <v>461</v>
+      </c>
+      <c r="B463" t="n">
         <v>1550</v>
       </c>
-      <c r="B463" t="n">
+      <c r="C463" t="n">
         <v>33</v>
       </c>
-      <c r="C463" t="n">
+      <c r="D463" t="n">
         <v>46.96969696969697</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
+        <v>462</v>
+      </c>
+      <c r="B464" t="n">
         <v>1900</v>
       </c>
-      <c r="B464" t="n">
+      <c r="C464" t="n">
         <v>64</v>
       </c>
-      <c r="C464" t="n">
+      <c r="D464" t="n">
         <v>29.6875</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
+        <v>463</v>
+      </c>
+      <c r="B465" t="n">
         <v>2200</v>
       </c>
-      <c r="B465" t="n">
+      <c r="C465" t="n">
         <v>55</v>
       </c>
-      <c r="C465" t="n">
+      <c r="D465" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
+        <v>464</v>
+      </c>
+      <c r="B466" t="n">
         <v>3140</v>
       </c>
-      <c r="B466" t="n">
+      <c r="C466" t="n">
         <v>100</v>
       </c>
-      <c r="C466" t="n">
+      <c r="D466" t="n">
         <v>31.4</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
+        <v>465</v>
+      </c>
+      <c r="B467" t="n">
         <v>600</v>
       </c>
-      <c r="B467" t="n">
+      <c r="C467" t="n">
         <v>20</v>
       </c>
-      <c r="C467" t="n">
+      <c r="D467" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
+        <v>466</v>
+      </c>
+      <c r="B468" t="n">
         <v>600</v>
       </c>
-      <c r="B468" t="n">
+      <c r="C468" t="n">
         <v>16</v>
       </c>
-      <c r="C468" t="n">
+      <c r="D468" t="n">
         <v>37.5</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
+        <v>467</v>
+      </c>
+      <c r="B469" t="n">
         <v>890</v>
       </c>
-      <c r="B469" t="n">
+      <c r="C469" t="n">
         <v>20</v>
       </c>
-      <c r="C469" t="n">
+      <c r="D469" t="n">
         <v>44.5</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
+        <v>468</v>
+      </c>
+      <c r="B470" t="n">
         <v>1050</v>
       </c>
-      <c r="B470" t="n">
+      <c r="C470" t="n">
         <v>30</v>
       </c>
-      <c r="C470" t="n">
+      <c r="D470" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
+        <v>469</v>
+      </c>
+      <c r="B471" t="n">
         <v>1100</v>
       </c>
-      <c r="B471" t="n">
+      <c r="C471" t="n">
         <v>31</v>
       </c>
-      <c r="C471" t="n">
+      <c r="D471" t="n">
         <v>35.48387096774194</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
+        <v>470</v>
+      </c>
+      <c r="B472" t="n">
         <v>1650</v>
       </c>
-      <c r="B472" t="n">
+      <c r="C472" t="n">
         <v>49</v>
       </c>
-      <c r="C472" t="n">
+      <c r="D472" t="n">
         <v>33.67346938775511</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
+        <v>471</v>
+      </c>
+      <c r="B473" t="n">
         <v>2090</v>
       </c>
-      <c r="B473" t="n">
+      <c r="C473" t="n">
         <v>73</v>
       </c>
-      <c r="C473" t="n">
+      <c r="D473" t="n">
         <v>28.63013698630137</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
+        <v>472</v>
+      </c>
+      <c r="B474" t="n">
         <v>6300</v>
       </c>
-      <c r="B474" t="n">
+      <c r="C474" t="n">
         <v>112</v>
       </c>
-      <c r="C474" t="n">
+      <c r="D474" t="n">
         <v>56.25</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
+        <v>473</v>
+      </c>
+      <c r="B475" t="n">
         <v>930</v>
       </c>
-      <c r="B475" t="n">
+      <c r="C475" t="n">
         <v>16</v>
       </c>
-      <c r="C475" t="n">
+      <c r="D475" t="n">
         <v>58.125</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
+        <v>474</v>
+      </c>
+      <c r="B476" t="n">
         <v>1980</v>
       </c>
-      <c r="B476" t="n">
+      <c r="C476" t="n">
         <v>84</v>
       </c>
-      <c r="C476" t="n">
+      <c r="D476" t="n">
         <v>23.57142857142857</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
+        <v>475</v>
+      </c>
+      <c r="B477" t="n">
         <v>885</v>
       </c>
-      <c r="B477" t="n">
+      <c r="C477" t="n">
         <v>23</v>
       </c>
-      <c r="C477" t="n">
+      <c r="D477" t="n">
         <v>38.47826086956522</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
+        <v>476</v>
+      </c>
+      <c r="B478" t="n">
         <v>1060</v>
       </c>
-      <c r="B478" t="n">
+      <c r="C478" t="n">
         <v>47</v>
       </c>
-      <c r="C478" t="n">
+      <c r="D478" t="n">
         <v>22.5531914893617</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
+        <v>477</v>
+      </c>
+      <c r="B479" t="n">
         <v>1200</v>
       </c>
-      <c r="B479" t="n">
+      <c r="C479" t="n">
         <v>48</v>
       </c>
-      <c r="C479" t="n">
+      <c r="D479" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
+        <v>478</v>
+      </c>
+      <c r="B480" t="n">
         <v>1500</v>
       </c>
-      <c r="B480" t="n">
+      <c r="C480" t="n">
         <v>38</v>
       </c>
-      <c r="C480" t="n">
+      <c r="D480" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
+        <v>479</v>
+      </c>
+      <c r="B481" t="n">
         <v>890</v>
       </c>
-      <c r="B481" t="n">
+      <c r="C481" t="n">
         <v>20</v>
       </c>
-      <c r="C481" t="n">
+      <c r="D481" t="n">
         <v>44.5</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
+        <v>480</v>
+      </c>
+      <c r="B482" t="n">
         <v>1300</v>
       </c>
-      <c r="B482" t="n">
+      <c r="C482" t="n">
         <v>42</v>
       </c>
-      <c r="C482" t="n">
+      <c r="D482" t="n">
         <v>30.95238095238095</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
+        <v>481</v>
+      </c>
+      <c r="B483" t="n">
         <v>900</v>
       </c>
-      <c r="B483" t="n">
+      <c r="C483" t="n">
         <v>29</v>
       </c>
-      <c r="C483" t="n">
+      <c r="D483" t="n">
         <v>31.03448275862069</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
+        <v>482</v>
+      </c>
+      <c r="B484" t="n">
         <v>1150</v>
       </c>
-      <c r="B484" t="n">
+      <c r="C484" t="n">
         <v>24</v>
       </c>
-      <c r="C484" t="n">
+      <c r="D484" t="n">
         <v>47.91666666666666</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
+        <v>483</v>
+      </c>
+      <c r="B485" t="n">
         <v>840</v>
       </c>
-      <c r="B485" t="n">
+      <c r="C485" t="n">
         <v>22</v>
       </c>
-      <c r="C485" t="n">
+      <c r="D485" t="n">
         <v>38.18181818181818</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
+        <v>484</v>
+      </c>
+      <c r="B486" t="n">
         <v>928</v>
       </c>
-      <c r="B486" t="n">
+      <c r="C486" t="n">
         <v>29</v>
       </c>
-      <c r="C486" t="n">
+      <c r="D486" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
+        <v>485</v>
+      </c>
+      <c r="B487" t="n">
         <v>981</v>
       </c>
-      <c r="B487" t="n">
+      <c r="C487" t="n">
         <v>30</v>
       </c>
-      <c r="C487" t="n">
+      <c r="D487" t="n">
         <v>32.7</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
+        <v>486</v>
+      </c>
+      <c r="B488" t="n">
         <v>1180</v>
       </c>
-      <c r="B488" t="n">
+      <c r="C488" t="n">
         <v>31</v>
       </c>
-      <c r="C488" t="n">
+      <c r="D488" t="n">
         <v>38.06451612903226</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
+        <v>487</v>
+      </c>
+      <c r="B489" t="n">
         <v>1198</v>
       </c>
-      <c r="B489" t="n">
+      <c r="C489" t="n">
         <v>33</v>
       </c>
-      <c r="C489" t="n">
+      <c r="D489" t="n">
         <v>36.3030303030303</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
+        <v>488</v>
+      </c>
+      <c r="B490" t="n">
         <v>1450</v>
       </c>
-      <c r="B490" t="n">
+      <c r="C490" t="n">
         <v>47</v>
       </c>
-      <c r="C490" t="n">
+      <c r="D490" t="n">
         <v>30.85106382978723</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
+        <v>489</v>
+      </c>
+      <c r="B491" t="n">
         <v>3000</v>
       </c>
-      <c r="B491" t="n">
+      <c r="C491" t="n">
         <v>50</v>
       </c>
-      <c r="C491" t="n">
+      <c r="D491" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
+        <v>490</v>
+      </c>
+      <c r="B492" t="n">
         <v>875</v>
       </c>
-      <c r="B492" t="n">
+      <c r="C492" t="n">
         <v>18</v>
       </c>
-      <c r="C492" t="n">
+      <c r="D492" t="n">
         <v>48.61111111111111</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
+        <v>491</v>
+      </c>
+      <c r="B493" t="n">
         <v>998</v>
       </c>
-      <c r="B493" t="n">
+      <c r="C493" t="n">
         <v>34</v>
       </c>
-      <c r="C493" t="n">
+      <c r="D493" t="n">
         <v>29.35294117647059</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
+        <v>492</v>
+      </c>
+      <c r="B494" t="n">
         <v>1000</v>
       </c>
-      <c r="B494" t="n">
+      <c r="C494" t="n">
         <v>25</v>
       </c>
-      <c r="C494" t="n">
+      <c r="D494" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
+        <v>493</v>
+      </c>
+      <c r="B495" t="n">
         <v>1250</v>
       </c>
-      <c r="B495" t="n">
+      <c r="C495" t="n">
         <v>31</v>
       </c>
-      <c r="C495" t="n">
+      <c r="D495" t="n">
         <v>40.32258064516129</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
+        <v>494</v>
+      </c>
+      <c r="B496" t="n">
         <v>1480</v>
       </c>
-      <c r="B496" t="n">
+      <c r="C496" t="n">
         <v>40</v>
       </c>
-      <c r="C496" t="n">
+      <c r="D496" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
+        <v>495</v>
+      </c>
+      <c r="B497" t="n">
         <v>1900</v>
       </c>
-      <c r="B497" t="n">
+      <c r="C497" t="n">
         <v>46</v>
       </c>
-      <c r="C497" t="n">
+      <c r="D497" t="n">
         <v>41.30434782608695</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
+        <v>496</v>
+      </c>
+      <c r="B498" t="n">
         <v>2500</v>
       </c>
-      <c r="B498" t="n">
+      <c r="C498" t="n">
         <v>70</v>
       </c>
-      <c r="C498" t="n">
+      <c r="D498" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
+        <v>497</v>
+      </c>
+      <c r="B499" t="n">
         <v>950</v>
       </c>
-      <c r="B499" t="n">
+      <c r="C499" t="n">
         <v>28</v>
       </c>
-      <c r="C499" t="n">
+      <c r="D499" t="n">
         <v>33.92857142857143</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
+        <v>498</v>
+      </c>
+      <c r="B500" t="n">
         <v>1180</v>
       </c>
-      <c r="B500" t="n">
+      <c r="C500" t="n">
         <v>27</v>
       </c>
-      <c r="C500" t="n">
+      <c r="D500" t="n">
         <v>43.7037037037037</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
+        <v>499</v>
+      </c>
+      <c r="B501" t="n">
         <v>1550</v>
       </c>
-      <c r="B501" t="n">
+      <c r="C501" t="n">
         <v>40</v>
       </c>
-      <c r="C501" t="n">
+      <c r="D501" t="n">
         <v>38.75</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
+        <v>500</v>
+      </c>
+      <c r="B502" t="n">
         <v>1333</v>
       </c>
-      <c r="B502" t="n">
+      <c r="C502" t="n">
         <v>41</v>
       </c>
-      <c r="C502" t="n">
+      <c r="D502" t="n">
         <v>32.51219512195122</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
+        <v>501</v>
+      </c>
+      <c r="B503" t="n">
         <v>1580</v>
       </c>
-      <c r="B503" t="n">
+      <c r="C503" t="n">
         <v>40</v>
       </c>
-      <c r="C503" t="n">
+      <c r="D503" t="n">
         <v>39.5</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
+        <v>502</v>
+      </c>
+      <c r="B504" t="n">
         <v>850</v>
       </c>
-      <c r="B504" t="n">
+      <c r="C504" t="n">
         <v>27</v>
       </c>
-      <c r="C504" t="n">
+      <c r="D504" t="n">
         <v>31.48148148148148</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
+        <v>503</v>
+      </c>
+      <c r="B505" t="n">
         <v>488</v>
       </c>
-      <c r="B505" t="n">
+      <c r="C505" t="n">
         <v>13</v>
       </c>
-      <c r="C505" t="n">
+      <c r="D505" t="n">
         <v>37.53846153846154</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
+        <v>504</v>
+      </c>
+      <c r="B506" t="n">
         <v>619</v>
       </c>
-      <c r="B506" t="n">
+      <c r="C506" t="n">
         <v>18</v>
       </c>
-      <c r="C506" t="n">
+      <c r="D506" t="n">
         <v>34.38888888888889</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
+        <v>505</v>
+      </c>
+      <c r="B507" t="n">
         <v>820</v>
       </c>
-      <c r="B507" t="n">
+      <c r="C507" t="n">
         <v>23</v>
       </c>
-      <c r="C507" t="n">
+      <c r="D507" t="n">
         <v>35.65217391304348</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
+        <v>506</v>
+      </c>
+      <c r="B508" t="n">
         <v>1350</v>
       </c>
-      <c r="B508" t="n">
+      <c r="C508" t="n">
         <v>32</v>
       </c>
-      <c r="C508" t="n">
+      <c r="D508" t="n">
         <v>42.1875</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
+        <v>507</v>
+      </c>
+      <c r="B509" t="n">
         <v>1475</v>
       </c>
-      <c r="B509" t="n">
+      <c r="C509" t="n">
         <v>57</v>
       </c>
-      <c r="C509" t="n">
+      <c r="D509" t="n">
         <v>25.87719298245614</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
+        <v>508</v>
+      </c>
+      <c r="B510" t="n">
         <v>1397</v>
       </c>
-      <c r="B510" t="n">
+      <c r="C510" t="n">
         <v>38</v>
       </c>
-      <c r="C510" t="n">
+      <c r="D510" t="n">
         <v>36.76315789473684</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
+        <v>509</v>
+      </c>
+      <c r="B511" t="n">
         <v>1460</v>
       </c>
-      <c r="B511" t="n">
+      <c r="C511" t="n">
         <v>52</v>
       </c>
-      <c r="C511" t="n">
+      <c r="D511" t="n">
         <v>28.07692307692308</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
+        <v>510</v>
+      </c>
+      <c r="B512" t="n">
         <v>3200</v>
       </c>
-      <c r="B512" t="n">
+      <c r="C512" t="n">
         <v>114</v>
       </c>
-      <c r="C512" t="n">
+      <c r="D512" t="n">
         <v>28.07017543859649</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
+        <v>511</v>
+      </c>
+      <c r="B513" t="n">
         <v>5000</v>
       </c>
-      <c r="B513" t="n">
+      <c r="C513" t="n">
         <v>136</v>
       </c>
-      <c r="C513" t="n">
+      <c r="D513" t="n">
         <v>36.76470588235294</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
+        <v>512</v>
+      </c>
+      <c r="B514" t="n">
         <v>790</v>
       </c>
-      <c r="B514" t="n">
+      <c r="C514" t="n">
         <v>22</v>
       </c>
-      <c r="C514" t="n">
+      <c r="D514" t="n">
         <v>35.90909090909091</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
+        <v>513</v>
+      </c>
+      <c r="B515" t="n">
         <v>800</v>
       </c>
-      <c r="B515" t="n">
+      <c r="C515" t="n">
         <v>14</v>
       </c>
-      <c r="C515" t="n">
+      <c r="D515" t="n">
         <v>57.14285714285715</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
+        <v>514</v>
+      </c>
+      <c r="B516" t="n">
         <v>810</v>
       </c>
-      <c r="B516" t="n">
+      <c r="C516" t="n">
         <v>18</v>
       </c>
-      <c r="C516" t="n">
+      <c r="D516" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
+        <v>515</v>
+      </c>
+      <c r="B517" t="n">
         <v>940</v>
       </c>
-      <c r="B517" t="n">
+      <c r="C517" t="n">
         <v>26</v>
       </c>
-      <c r="C517" t="n">
+      <c r="D517" t="n">
         <v>36.15384615384615</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
+        <v>516</v>
+      </c>
+      <c r="B518" t="n">
         <v>898</v>
       </c>
-      <c r="B518" t="n">
+      <c r="C518" t="n">
         <v>27</v>
       </c>
-      <c r="C518" t="n">
+      <c r="D518" t="n">
         <v>33.25925925925926</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
+        <v>517</v>
+      </c>
+      <c r="B519" t="n">
         <v>1137</v>
       </c>
-      <c r="B519" t="n">
+      <c r="C519" t="n">
         <v>33</v>
       </c>
-      <c r="C519" t="n">
+      <c r="D519" t="n">
         <v>34.45454545454545</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
+        <v>518</v>
+      </c>
+      <c r="B520" t="n">
         <v>810</v>
       </c>
-      <c r="B520" t="n">
+      <c r="C520" t="n">
         <v>18</v>
       </c>
-      <c r="C520" t="n">
+      <c r="D520" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
+        <v>519</v>
+      </c>
+      <c r="B521" t="n">
         <v>940</v>
       </c>
-      <c r="B521" t="n">
+      <c r="C521" t="n">
         <v>26</v>
       </c>
-      <c r="C521" t="n">
+      <c r="D521" t="n">
         <v>36.15384615384615</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
+        <v>520</v>
+      </c>
+      <c r="B522" t="n">
         <v>898</v>
       </c>
-      <c r="B522" t="n">
+      <c r="C522" t="n">
         <v>27</v>
       </c>
-      <c r="C522" t="n">
+      <c r="D522" t="n">
         <v>33.25925925925926</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
+        <v>521</v>
+      </c>
+      <c r="B523" t="n">
         <v>1137</v>
       </c>
-      <c r="B523" t="n">
+      <c r="C523" t="n">
         <v>33</v>
       </c>
-      <c r="C523" t="n">
+      <c r="D523" t="n">
         <v>34.45454545454545</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
+        <v>522</v>
+      </c>
+      <c r="B524" t="n">
         <v>1600</v>
       </c>
-      <c r="B524" t="n">
+      <c r="C524" t="n">
         <v>60</v>
       </c>
-      <c r="C524" t="n">
+      <c r="D524" t="n">
         <v>26.66666666666667</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
+        <v>523</v>
+      </c>
+      <c r="B525" t="n">
         <v>2097</v>
       </c>
-      <c r="B525" t="n">
+      <c r="C525" t="n">
         <v>58</v>
       </c>
-      <c r="C525" t="n">
+      <c r="D525" t="n">
         <v>36.1551724137931</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
+        <v>524</v>
+      </c>
+      <c r="B526" t="n">
         <v>733</v>
       </c>
-      <c r="B526" t="n">
+      <c r="C526" t="n">
         <v>20</v>
       </c>
-      <c r="C526" t="n">
+      <c r="D526" t="n">
         <v>36.65</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
+        <v>525</v>
+      </c>
+      <c r="B527" t="n">
         <v>12000</v>
       </c>
-      <c r="B527" t="n">
+      <c r="C527" t="n">
         <v>230</v>
       </c>
-      <c r="C527" t="n">
+      <c r="D527" t="n">
         <v>52.17391304347826</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
+        <v>526</v>
+      </c>
+      <c r="B528" t="n">
         <v>1166</v>
       </c>
-      <c r="B528" t="n">
+      <c r="C528" t="n">
         <v>27</v>
       </c>
-      <c r="C528" t="n">
+      <c r="D528" t="n">
         <v>43.18518518518518</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
+        <v>527</v>
+      </c>
+      <c r="B529" t="n">
         <v>1500</v>
       </c>
-      <c r="B529" t="n">
+      <c r="C529" t="n">
         <v>38</v>
       </c>
-      <c r="C529" t="n">
+      <c r="D529" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
+        <v>528</v>
+      </c>
+      <c r="B530" t="n">
         <v>1900</v>
       </c>
-      <c r="B530" t="n">
+      <c r="C530" t="n">
         <v>45</v>
       </c>
-      <c r="C530" t="n">
+      <c r="D530" t="n">
         <v>42.22222222222222</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
+        <v>529</v>
+      </c>
+      <c r="B531" t="n">
         <v>1900</v>
       </c>
-      <c r="B531" t="n">
+      <c r="C531" t="n">
         <v>64</v>
       </c>
-      <c r="C531" t="n">
+      <c r="D531" t="n">
         <v>29.6875</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
+        <v>530</v>
+      </c>
+      <c r="B532" t="n">
         <v>1950</v>
       </c>
-      <c r="B532" t="n">
+      <c r="C532" t="n">
         <v>45</v>
       </c>
-      <c r="C532" t="n">
+      <c r="D532" t="n">
         <v>43.33333333333334</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
+        <v>531</v>
+      </c>
+      <c r="B533" t="n">
         <v>2000</v>
       </c>
-      <c r="B533" t="n">
+      <c r="C533" t="n">
         <v>65</v>
       </c>
-      <c r="C533" t="n">
+      <c r="D533" t="n">
         <v>30.76923076923077</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
+        <v>532</v>
+      </c>
+      <c r="B534" t="n">
         <v>2950</v>
       </c>
-      <c r="B534" t="n">
+      <c r="C534" t="n">
         <v>95</v>
       </c>
-      <c r="C534" t="n">
+      <c r="D534" t="n">
         <v>31.05263157894737</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
+        <v>533</v>
+      </c>
+      <c r="B535" t="n">
         <v>1200</v>
       </c>
-      <c r="B535" t="n">
+      <c r="C535" t="n">
         <v>20</v>
       </c>
-      <c r="C535" t="n">
+      <c r="D535" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
+        <v>534</v>
+      </c>
+      <c r="B536" t="n">
         <v>1300</v>
       </c>
-      <c r="B536" t="n">
+      <c r="C536" t="n">
         <v>20</v>
       </c>
-      <c r="C536" t="n">
+      <c r="D536" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
+        <v>535</v>
+      </c>
+      <c r="B537" t="n">
         <v>1400</v>
       </c>
-      <c r="B537" t="n">
+      <c r="C537" t="n">
         <v>20</v>
       </c>
-      <c r="C537" t="n">
+      <c r="D537" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
+        <v>536</v>
+      </c>
+      <c r="B538" t="n">
         <v>1690</v>
       </c>
-      <c r="B538" t="n">
+      <c r="C538" t="n">
         <v>58</v>
       </c>
-      <c r="C538" t="n">
+      <c r="D538" t="n">
         <v>29.13793103448276</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
+        <v>537</v>
+      </c>
+      <c r="B539" t="n">
         <v>1940</v>
       </c>
-      <c r="B539" t="n">
+      <c r="C539" t="n">
         <v>40</v>
       </c>
-      <c r="C539" t="n">
+      <c r="D539" t="n">
         <v>48.5</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
+        <v>538</v>
+      </c>
+      <c r="B540" t="n">
         <v>2100</v>
       </c>
-      <c r="B540" t="n">
+      <c r="C540" t="n">
         <v>70</v>
       </c>
-      <c r="C540" t="n">
+      <c r="D540" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
+        <v>539</v>
+      </c>
+      <c r="B541" t="n">
         <v>2490</v>
       </c>
-      <c r="B541" t="n">
+      <c r="C541" t="n">
         <v>70</v>
       </c>
-      <c r="C541" t="n">
+      <c r="D541" t="n">
         <v>35.57142857142857</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
+        <v>540</v>
+      </c>
+      <c r="B542" t="n">
         <v>1490</v>
       </c>
-      <c r="B542" t="n">
+      <c r="C542" t="n">
         <v>48</v>
       </c>
-      <c r="C542" t="n">
+      <c r="D542" t="n">
         <v>31.04166666666667</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
+        <v>541</v>
+      </c>
+      <c r="B543" t="n">
         <v>2020</v>
       </c>
-      <c r="B543" t="n">
+      <c r="C543" t="n">
         <v>58</v>
       </c>
-      <c r="C543" t="n">
+      <c r="D543" t="n">
         <v>34.82758620689656</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
+        <v>542</v>
+      </c>
+      <c r="B544" t="n">
         <v>2050</v>
       </c>
-      <c r="B544" t="n">
+      <c r="C544" t="n">
         <v>70</v>
       </c>
-      <c r="C544" t="n">
+      <c r="D544" t="n">
         <v>29.28571428571428</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
+        <v>543</v>
+      </c>
+      <c r="B545" t="n">
         <v>1220</v>
       </c>
-      <c r="B545" t="n">
+      <c r="C545" t="n">
         <v>42</v>
       </c>
-      <c r="C545" t="n">
+      <c r="D545" t="n">
         <v>29.04761904761905</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
+        <v>544</v>
+      </c>
+      <c r="B546" t="n">
         <v>1610</v>
       </c>
-      <c r="B546" t="n">
+      <c r="C546" t="n">
         <v>44</v>
       </c>
-      <c r="C546" t="n">
+      <c r="D546" t="n">
         <v>36.59090909090909</v>
       </c>
     </row>

--- a/data/house/house.xlsx
+++ b/data/house/house.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D546"/>
+  <dimension ref="A1:F546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,16 @@
           <t>loyer_m2</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sin</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mask</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -446,6 +456,12 @@
       <c r="D2" t="n">
         <v>35.94594594594594</v>
       </c>
+      <c r="E2" t="n">
+        <v>-0.9834167079457684</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -459,6 +475,12 @@
       </c>
       <c r="D3" t="n">
         <v>43.75</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.2302135780707541</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -474,6 +496,12 @@
       <c r="D4" t="n">
         <v>34.76923076923077</v>
       </c>
+      <c r="E4" t="n">
+        <v>-0.2101335715883806</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -488,6 +516,12 @@
       <c r="D5" t="n">
         <v>31.83333333333333</v>
       </c>
+      <c r="E5" t="n">
+        <v>0.405391260099164</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -502,6 +536,12 @@
       <c r="D6" t="n">
         <v>36.35714285714285</v>
       </c>
+      <c r="E6" t="n">
+        <v>-0.9739330654121445</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -516,6 +556,12 @@
       <c r="D7" t="n">
         <v>40.41666666666666</v>
       </c>
+      <c r="E7" t="n">
+        <v>0.411444016884261</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -530,6 +576,12 @@
       <c r="D8" t="n">
         <v>38.04878048780488</v>
       </c>
+      <c r="E8" t="n">
+        <v>0.3425865225353109</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -544,6 +596,12 @@
       <c r="D9" t="n">
         <v>29.25373134328358</v>
       </c>
+      <c r="E9" t="n">
+        <v>-0.8301615919329036</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -558,6 +616,12 @@
       <c r="D10" t="n">
         <v>31.74603174603175</v>
       </c>
+      <c r="E10" t="n">
+        <v>0.3241425598427976</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -572,6 +636,12 @@
       <c r="D11" t="n">
         <v>37.14285714285715</v>
       </c>
+      <c r="E11" t="n">
+        <v>-0.5280092554170536</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -586,6 +656,12 @@
       <c r="D12" t="n">
         <v>40.49382716049383</v>
       </c>
+      <c r="E12" t="n">
+        <v>0.3399627952306745</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -600,6 +676,12 @@
       <c r="D13" t="n">
         <v>46.10951008645533</v>
       </c>
+      <c r="E13" t="n">
+        <v>0.849153114903015</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -614,6 +696,12 @@
       <c r="D14" t="n">
         <v>37.69230769230769</v>
       </c>
+      <c r="E14" t="n">
+        <v>-0.00680409826858927</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -628,6 +716,12 @@
       <c r="D15" t="n">
         <v>34.72222222222222</v>
       </c>
+      <c r="E15" t="n">
+        <v>-0.1639593897904862</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -642,6 +736,12 @@
       <c r="D16" t="n">
         <v>39.57894736842105</v>
       </c>
+      <c r="E16" t="n">
+        <v>0.9526262310529627</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -656,6 +756,12 @@
       <c r="D17" t="n">
         <v>40.75</v>
       </c>
+      <c r="E17" t="n">
+        <v>0.09058017221711874</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -670,6 +776,12 @@
       <c r="D18" t="n">
         <v>45.88</v>
       </c>
+      <c r="E18" t="n">
+        <v>0.9470402349818713</v>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -684,6 +796,12 @@
       <c r="D19" t="n">
         <v>42.85714285714285</v>
       </c>
+      <c r="E19" t="n">
+        <v>-0.9023341109265443</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -698,6 +816,12 @@
       <c r="D20" t="n">
         <v>29.89166666666667</v>
       </c>
+      <c r="E20" t="n">
+        <v>-0.9989173744614732</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -712,6 +836,12 @@
       <c r="D21" t="n">
         <v>33.875</v>
       </c>
+      <c r="E21" t="n">
+        <v>0.630749879707115</v>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -726,6 +856,12 @@
       <c r="D22" t="n">
         <v>41.5</v>
       </c>
+      <c r="E22" t="n">
+        <v>-0.6125601529754698</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -740,6 +876,12 @@
       <c r="D23" t="n">
         <v>44</v>
       </c>
+      <c r="E23" t="n">
+        <v>0.01770192510541358</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -754,6 +896,12 @@
       <c r="D24" t="n">
         <v>53.33333333333334</v>
       </c>
+      <c r="E24" t="n">
+        <v>0.07367496307722743</v>
+      </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -768,6 +916,12 @@
       <c r="D25" t="n">
         <v>27.84090909090909</v>
       </c>
+      <c r="E25" t="n">
+        <v>0.4199813696478868</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -782,6 +936,12 @@
       <c r="D26" t="n">
         <v>35.71428571428572</v>
       </c>
+      <c r="E26" t="n">
+        <v>-0.9155070638063744</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -796,6 +956,12 @@
       <c r="D27" t="n">
         <v>23.7037037037037</v>
       </c>
+      <c r="E27" t="n">
+        <v>-0.9899690361020956</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -810,6 +976,12 @@
       <c r="D28" t="n">
         <v>28.56410256410257</v>
       </c>
+      <c r="E28" t="n">
+        <v>-0.285730558202645</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -824,6 +996,12 @@
       <c r="D29" t="n">
         <v>37.94117647058823</v>
       </c>
+      <c r="E29" t="n">
+        <v>0.2397075694817074</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -838,6 +1016,12 @@
       <c r="D30" t="n">
         <v>46.42857142857143</v>
       </c>
+      <c r="E30" t="n">
+        <v>0.6406299363802627</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -852,6 +1036,12 @@
       <c r="D31" t="n">
         <v>40.625</v>
       </c>
+      <c r="E31" t="n">
+        <v>0.2140356519137885</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -866,6 +1056,12 @@
       <c r="D32" t="n">
         <v>32.6</v>
       </c>
+      <c r="E32" t="n">
+        <v>0.9261500206805285</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -880,6 +1076,12 @@
       <c r="D33" t="n">
         <v>31.90476190476191</v>
       </c>
+      <c r="E33" t="n">
+        <v>0.4695979769136132</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -894,6 +1096,12 @@
       <c r="D34" t="n">
         <v>43.35483870967742</v>
       </c>
+      <c r="E34" t="n">
+        <v>-0.5870892074311692</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -908,6 +1116,12 @@
       <c r="D35" t="n">
         <v>39.09090909090909</v>
       </c>
+      <c r="E35" t="n">
+        <v>0.9840223943960513</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -922,6 +1136,12 @@
       <c r="D36" t="n">
         <v>34.97435897435897</v>
       </c>
+      <c r="E36" t="n">
+        <v>-0.404872864237582</v>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -936,6 +1156,12 @@
       <c r="D37" t="n">
         <v>29.78723404255319</v>
       </c>
+      <c r="E37" t="n">
+        <v>-0.9983244850503094</v>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -950,6 +1176,12 @@
       <c r="D38" t="n">
         <v>42.42424242424242</v>
       </c>
+      <c r="E38" t="n">
+        <v>-0.9999188269029812</v>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -964,6 +1196,12 @@
       <c r="D39" t="n">
         <v>38.37837837837838</v>
       </c>
+      <c r="E39" t="n">
+        <v>0.6282225327933564</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -978,6 +1216,12 @@
       <c r="D40" t="n">
         <v>33.80952380952381</v>
       </c>
+      <c r="E40" t="n">
+        <v>0.6801706332562436</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -992,6 +1236,12 @@
       <c r="D41" t="n">
         <v>31.41304347826087</v>
       </c>
+      <c r="E41" t="n">
+        <v>-0.002883053643056989</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1006,6 +1256,12 @@
       <c r="D42" t="n">
         <v>40.54054054054054</v>
       </c>
+      <c r="E42" t="n">
+        <v>0.2956768359591289</v>
+      </c>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1020,6 +1276,12 @@
       <c r="D43" t="n">
         <v>33.56521739130435</v>
       </c>
+      <c r="E43" t="n">
+        <v>0.8372867360628385</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1034,6 +1296,12 @@
       <c r="D44" t="n">
         <v>36.90476190476191</v>
       </c>
+      <c r="E44" t="n">
+        <v>-0.713408225840231</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1048,6 +1316,12 @@
       <c r="D45" t="n">
         <v>30.61224489795918</v>
       </c>
+      <c r="E45" t="n">
+        <v>-0.7199162452772808</v>
+      </c>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1062,6 +1336,12 @@
       <c r="D46" t="n">
         <v>33.58333333333334</v>
       </c>
+      <c r="E46" t="n">
+        <v>0.8272447423876894</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1076,6 +1356,12 @@
       <c r="D47" t="n">
         <v>33</v>
       </c>
+      <c r="E47" t="n">
+        <v>0.9999118601072672</v>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1090,6 +1376,12 @@
       <c r="D48" t="n">
         <v>28.38888888888889</v>
       </c>
+      <c r="E48" t="n">
+        <v>-0.1143046229054958</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1104,6 +1396,12 @@
       <c r="D49" t="n">
         <v>30.7962962962963</v>
       </c>
+      <c r="E49" t="n">
+        <v>-0.5807341808014436</v>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1118,6 +1416,12 @@
       <c r="D50" t="n">
         <v>35.2</v>
       </c>
+      <c r="E50" t="n">
+        <v>-0.5991834492142653</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1132,6 +1436,12 @@
       <c r="D51" t="n">
         <v>31.69811320754717</v>
       </c>
+      <c r="E51" t="n">
+        <v>0.278456498868122</v>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1146,6 +1456,12 @@
       <c r="D52" t="n">
         <v>42.5</v>
       </c>
+      <c r="E52" t="n">
+        <v>-0.996086503119594</v>
+      </c>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1160,6 +1476,12 @@
       <c r="D53" t="n">
         <v>48.57142857142857</v>
       </c>
+      <c r="E53" t="n">
+        <v>-0.9924133992546977</v>
+      </c>
+      <c r="F53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1174,6 +1496,12 @@
       <c r="D54" t="n">
         <v>42.5</v>
       </c>
+      <c r="E54" t="n">
+        <v>-0.996086503119594</v>
+      </c>
+      <c r="F54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1188,6 +1516,12 @@
       <c r="D55" t="n">
         <v>48.57142857142857</v>
       </c>
+      <c r="E55" t="n">
+        <v>-0.9924133992546977</v>
+      </c>
+      <c r="F55" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1202,6 +1536,12 @@
       <c r="D56" t="n">
         <v>28.33333333333333</v>
       </c>
+      <c r="E56" t="n">
+        <v>-0.05896522810427303</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1216,6 +1556,12 @@
       <c r="D57" t="n">
         <v>53.33333333333334</v>
       </c>
+      <c r="E57" t="n">
+        <v>0.07367496307722743</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1230,6 +1576,12 @@
       <c r="D58" t="n">
         <v>50</v>
       </c>
+      <c r="E58" t="n">
+        <v>-0.2623748537039288</v>
+      </c>
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1244,6 +1596,12 @@
       <c r="D59" t="n">
         <v>26.71875</v>
       </c>
+      <c r="E59" t="n">
+        <v>0.9998842929977892</v>
+      </c>
+      <c r="F59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1258,6 +1616,12 @@
       <c r="D60" t="n">
         <v>34.04255319148936</v>
       </c>
+      <c r="E60" t="n">
+        <v>0.4925052570568287</v>
+      </c>
+      <c r="F60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1272,6 +1636,12 @@
       <c r="D61" t="n">
         <v>40.69767441860465</v>
       </c>
+      <c r="E61" t="n">
+        <v>0.1425429012221065</v>
+      </c>
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1286,6 +1656,12 @@
       <c r="D62" t="n">
         <v>28.46774193548387</v>
       </c>
+      <c r="E62" t="n">
+        <v>-0.1922045143693956</v>
+      </c>
+      <c r="F62" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1300,6 +1676,12 @@
       <c r="D63" t="n">
         <v>35.8</v>
       </c>
+      <c r="E63" t="n">
+        <v>-0.9465868462849605</v>
+      </c>
+      <c r="F63" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1314,6 +1696,12 @@
       <c r="D64" t="n">
         <v>31.86792452830189</v>
       </c>
+      <c r="E64" t="n">
+        <v>0.4367637511997248</v>
+      </c>
+      <c r="F64" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1328,6 +1716,12 @@
       <c r="D65" t="n">
         <v>35.9</v>
       </c>
+      <c r="E65" t="n">
+        <v>-0.9740490378683264</v>
+      </c>
+      <c r="F65" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1342,6 +1736,12 @@
       <c r="D66" t="n">
         <v>36</v>
       </c>
+      <c r="E66" t="n">
+        <v>-0.9917788534431158</v>
+      </c>
+      <c r="F66" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1356,6 +1756,12 @@
       <c r="D67" t="n">
         <v>28.33333333333333</v>
       </c>
+      <c r="E67" t="n">
+        <v>-0.05896522810427303</v>
+      </c>
+      <c r="F67" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1370,6 +1776,12 @@
       <c r="D68" t="n">
         <v>42.85714285714285</v>
       </c>
+      <c r="E68" t="n">
+        <v>-0.9023341109265443</v>
+      </c>
+      <c r="F68" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1384,6 +1796,12 @@
       <c r="D69" t="n">
         <v>35.57692307692308</v>
       </c>
+      <c r="E69" t="n">
+        <v>-0.8517958855500224</v>
+      </c>
+      <c r="F69" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1398,6 +1816,12 @@
       <c r="D70" t="n">
         <v>41.11111111111111</v>
       </c>
+      <c r="E70" t="n">
+        <v>-0.2671232977949494</v>
+      </c>
+      <c r="F70" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1412,6 +1836,12 @@
       <c r="D71" t="n">
         <v>42.68292682926829</v>
       </c>
+      <c r="E71" t="n">
+        <v>-0.9633895560071108</v>
+      </c>
+      <c r="F71" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1426,6 +1856,12 @@
       <c r="D72" t="n">
         <v>29.36507936507936</v>
       </c>
+      <c r="E72" t="n">
+        <v>-0.88697144292147</v>
+      </c>
+      <c r="F72" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1440,6 +1876,12 @@
       <c r="D73" t="n">
         <v>34.90566037735849</v>
       </c>
+      <c r="E73" t="n">
+        <v>-0.3411510986813802</v>
+      </c>
+      <c r="F73" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1454,6 +1896,12 @@
       <c r="D74" t="n">
         <v>41.11111111111111</v>
       </c>
+      <c r="E74" t="n">
+        <v>-0.2671232977949494</v>
+      </c>
+      <c r="F74" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1468,6 +1916,12 @@
       <c r="D75" t="n">
         <v>35.37735849056604</v>
       </c>
+      <c r="E75" t="n">
+        <v>-0.7310361880743972</v>
+      </c>
+      <c r="F75" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1482,6 +1936,12 @@
       <c r="D76" t="n">
         <v>34.54545454545455</v>
       </c>
+      <c r="E76" t="n">
+        <v>0.01206435135582041</v>
+      </c>
+      <c r="F76" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1496,6 +1956,12 @@
       <c r="D77" t="n">
         <v>42.39130434782609</v>
       </c>
+      <c r="E77" t="n">
+        <v>-0.9997960581183652</v>
+      </c>
+      <c r="F77" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1510,6 +1976,12 @@
       <c r="D78" t="n">
         <v>23.97260273972603</v>
       </c>
+      <c r="E78" t="n">
+        <v>-0.9168584041088347</v>
+      </c>
+      <c r="F78" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1524,6 +1996,12 @@
       <c r="D79" t="n">
         <v>37.73584905660378</v>
       </c>
+      <c r="E79" t="n">
+        <v>0.03672895052002344</v>
+      </c>
+      <c r="F79" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1538,6 +2016,12 @@
       <c r="D80" t="n">
         <v>31.9375</v>
       </c>
+      <c r="E80" t="n">
+        <v>0.4982450045214716</v>
+      </c>
+      <c r="F80" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1552,6 +2036,12 @@
       <c r="D81" t="n">
         <v>55.26315789473684</v>
       </c>
+      <c r="E81" t="n">
+        <v>-0.959581073788497</v>
+      </c>
+      <c r="F81" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1566,6 +2056,12 @@
       <c r="D82" t="n">
         <v>32.30769230769231</v>
       </c>
+      <c r="E82" t="n">
+        <v>0.778181933517716</v>
+      </c>
+      <c r="F82" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1580,6 +2076,12 @@
       <c r="D83" t="n">
         <v>35.59322033898305</v>
       </c>
+      <c r="E83" t="n">
+        <v>-0.8602201000850204</v>
+      </c>
+      <c r="F83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1594,6 +2096,12 @@
       <c r="D84" t="n">
         <v>44.68085106382978</v>
       </c>
+      <c r="E84" t="n">
+        <v>0.6431109861341677</v>
+      </c>
+      <c r="F84" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1608,6 +2116,12 @@
       <c r="D85" t="n">
         <v>28.09333333333333</v>
       </c>
+      <c r="E85" t="n">
+        <v>0.180013867446679</v>
+      </c>
+      <c r="F85" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1622,6 +2136,12 @@
       <c r="D86" t="n">
         <v>25.49397590361446</v>
       </c>
+      <c r="E86" t="n">
+        <v>0.3534294927877724</v>
+      </c>
+      <c r="F86" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1636,6 +2156,12 @@
       <c r="D87" t="n">
         <v>30.89855072463768</v>
       </c>
+      <c r="E87" t="n">
+        <v>-0.4946011082896373</v>
+      </c>
+      <c r="F87" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1650,6 +2176,12 @@
       <c r="D88" t="n">
         <v>29.41176470588235</v>
       </c>
+      <c r="E88" t="n">
+        <v>-0.9075576245489081</v>
+      </c>
+      <c r="F88" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1664,6 +2196,12 @@
       <c r="D89" t="n">
         <v>31.59420289855073</v>
       </c>
+      <c r="E89" t="n">
+        <v>0.177333518591084</v>
+      </c>
+      <c r="F89" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1678,6 +2216,12 @@
       <c r="D90" t="n">
         <v>29.16666666666667</v>
       </c>
+      <c r="E90" t="n">
+        <v>-0.7785379143600272</v>
+      </c>
+      <c r="F90" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1692,6 +2236,12 @@
       <c r="D91" t="n">
         <v>55</v>
       </c>
+      <c r="E91" t="n">
+        <v>-0.9997551733586199</v>
+      </c>
+      <c r="F91" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1706,6 +2256,12 @@
       <c r="D92" t="n">
         <v>44</v>
       </c>
+      <c r="E92" t="n">
+        <v>0.01770192510541358</v>
+      </c>
+      <c r="F92" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1720,6 +2276,12 @@
       <c r="D93" t="n">
         <v>36.66666666666666</v>
       </c>
+      <c r="E93" t="n">
+        <v>-0.8585552479838888</v>
+      </c>
+      <c r="F93" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1734,6 +2296,12 @@
       <c r="D94" t="n">
         <v>32.58823529411764</v>
       </c>
+      <c r="E94" t="n">
+        <v>0.9216489088769145</v>
+      </c>
+      <c r="F94" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1748,6 +2316,12 @@
       <c r="D95" t="n">
         <v>32.46376811594203</v>
       </c>
+      <c r="E95" t="n">
+        <v>0.8663472385838897</v>
+      </c>
+      <c r="F95" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1762,6 +2336,12 @@
       <c r="D96" t="n">
         <v>64.25714285714285</v>
       </c>
+      <c r="E96" t="n">
+        <v>0.9894325875251604</v>
+      </c>
+      <c r="F96" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1776,6 +2356,12 @@
       <c r="D97" t="n">
         <v>29.25641025641026</v>
       </c>
+      <c r="E97" t="n">
+        <v>-0.8316521665780727</v>
+      </c>
+      <c r="F97" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1790,6 +2376,12 @@
       <c r="D98" t="n">
         <v>35.38461538461539</v>
       </c>
+      <c r="E98" t="n">
+        <v>-0.7359685551967111</v>
+      </c>
+      <c r="F98" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1804,6 +2396,12 @@
       <c r="D99" t="n">
         <v>42.5925925925926</v>
       </c>
+      <c r="E99" t="n">
+        <v>-0.9836476475142345</v>
+      </c>
+      <c r="F99" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1818,6 +2416,12 @@
       <c r="D100" t="n">
         <v>38.66666666666666</v>
       </c>
+      <c r="E100" t="n">
+        <v>0.8235009916888967</v>
+      </c>
+      <c r="F100" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -1832,6 +2436,12 @@
       <c r="D101" t="n">
         <v>36.3125</v>
       </c>
+      <c r="E101" t="n">
+        <v>-0.9830859351477087</v>
+      </c>
+      <c r="F101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -1846,6 +2456,12 @@
       <c r="D102" t="n">
         <v>36.3125</v>
       </c>
+      <c r="E102" t="n">
+        <v>-0.9830859351477087</v>
+      </c>
+      <c r="F102" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -1860,6 +2476,12 @@
       <c r="D103" t="n">
         <v>31.14473684210526</v>
       </c>
+      <c r="E103" t="n">
+        <v>-0.2678778399093261</v>
+      </c>
+      <c r="F103" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -1874,6 +2496,12 @@
       <c r="D104" t="n">
         <v>34.28571428571428</v>
       </c>
+      <c r="E104" t="n">
+        <v>0.2684705150095526</v>
+      </c>
+      <c r="F104" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -1888,6 +2516,12 @@
       <c r="D105" t="n">
         <v>34.28571428571428</v>
       </c>
+      <c r="E105" t="n">
+        <v>0.2684705150095526</v>
+      </c>
+      <c r="F105" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -1902,6 +2536,12 @@
       <c r="D106" t="n">
         <v>34.43661971830986</v>
       </c>
+      <c r="E106" t="n">
+        <v>0.1206051614951143</v>
+      </c>
+      <c r="F106" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -1916,6 +2556,12 @@
       <c r="D107" t="n">
         <v>29.16666666666667</v>
       </c>
+      <c r="E107" t="n">
+        <v>-0.7785379143600272</v>
+      </c>
+      <c r="F107" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -1930,6 +2576,12 @@
       <c r="D108" t="n">
         <v>27.22222222222222</v>
       </c>
+      <c r="E108" t="n">
+        <v>0.8684719917685516</v>
+      </c>
+      <c r="F108" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -1944,6 +2596,12 @@
       <c r="D109" t="n">
         <v>23.75</v>
       </c>
+      <c r="E109" t="n">
+        <v>-0.9823696896284233</v>
+      </c>
+      <c r="F109" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -1958,6 +2616,12 @@
       <c r="D110" t="n">
         <v>25.28089887640449</v>
       </c>
+      <c r="E110" t="n">
+        <v>0.1476162152048078</v>
+      </c>
+      <c r="F110" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -1972,6 +2636,12 @@
       <c r="D111" t="n">
         <v>32.2</v>
       </c>
+      <c r="E111" t="n">
+        <v>0.7061694571803344</v>
+      </c>
+      <c r="F111" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -1986,6 +2656,12 @@
       <c r="D112" t="n">
         <v>44.90909090909091</v>
       </c>
+      <c r="E112" t="n">
+        <v>0.7996990239274064</v>
+      </c>
+      <c r="F112" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2000,6 +2676,12 @@
       <c r="D113" t="n">
         <v>46.42857142857143</v>
       </c>
+      <c r="E113" t="n">
+        <v>0.6406299363802627</v>
+      </c>
+      <c r="F113" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2014,6 +2696,12 @@
       <c r="D114" t="n">
         <v>47.32142857142857</v>
       </c>
+      <c r="E114" t="n">
+        <v>-0.1962565598610875</v>
+      </c>
+      <c r="F114" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2028,6 +2716,12 @@
       <c r="D115" t="n">
         <v>47.32142857142857</v>
       </c>
+      <c r="E115" t="n">
+        <v>-0.1962565598610875</v>
+      </c>
+      <c r="F115" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2042,6 +2736,12 @@
       <c r="D116" t="n">
         <v>29.39560439560439</v>
       </c>
+      <c r="E116" t="n">
+        <v>-0.9006532558957377</v>
+      </c>
+      <c r="F116" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2056,6 +2756,12 @@
       <c r="D117" t="n">
         <v>25.5</v>
       </c>
+      <c r="E117" t="n">
+        <v>0.3590583540221683</v>
+      </c>
+      <c r="F117" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2070,6 +2776,12 @@
       <c r="D118" t="n">
         <v>36.98630136986301</v>
       </c>
+      <c r="E118" t="n">
+        <v>-0.6539625496176034</v>
+      </c>
+      <c r="F118" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2084,6 +2796,12 @@
       <c r="D119" t="n">
         <v>29.57446808510638</v>
       </c>
+      <c r="E119" t="n">
+        <v>-0.9635940758313835</v>
+      </c>
+      <c r="F119" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2098,6 +2816,12 @@
       <c r="D120" t="n">
         <v>56</v>
       </c>
+      <c r="E120" t="n">
+        <v>-0.5215510020869119</v>
+      </c>
+      <c r="F120" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2112,6 +2836,12 @@
       <c r="D121" t="n">
         <v>46.66666666666666</v>
       </c>
+      <c r="E121" t="n">
+        <v>0.4414581836648109</v>
+      </c>
+      <c r="F121" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2126,6 +2856,12 @@
       <c r="D122" t="n">
         <v>31.66666666666667</v>
       </c>
+      <c r="E122" t="n">
+        <v>0.2481210133214244</v>
+      </c>
+      <c r="F122" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2140,6 +2876,12 @@
       <c r="D123" t="n">
         <v>30.63541666666667</v>
       </c>
+      <c r="E123" t="n">
+        <v>-0.7036418007092375</v>
+      </c>
+      <c r="F123" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2154,6 +2896,12 @@
       <c r="D124" t="n">
         <v>30.63541666666667</v>
       </c>
+      <c r="E124" t="n">
+        <v>-0.7036418007092375</v>
+      </c>
+      <c r="F124" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2168,6 +2916,12 @@
       <c r="D125" t="n">
         <v>60</v>
       </c>
+      <c r="E125" t="n">
+        <v>-0.3048106211022167</v>
+      </c>
+      <c r="F125" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2182,6 +2936,12 @@
       <c r="D126" t="n">
         <v>33.73493975903614</v>
       </c>
+      <c r="E126" t="n">
+        <v>0.732903137608343</v>
+      </c>
+      <c r="F126" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2196,6 +2956,12 @@
       <c r="D127" t="n">
         <v>30.3030303030303</v>
       </c>
+      <c r="E127" t="n">
+        <v>-0.8969827705478868</v>
+      </c>
+      <c r="F127" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2210,6 +2976,12 @@
       <c r="D128" t="n">
         <v>34.09090909090909</v>
       </c>
+      <c r="E128" t="n">
+        <v>0.4498613604067414</v>
+      </c>
+      <c r="F128" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2224,6 +2996,12 @@
       <c r="D129" t="n">
         <v>28.94230769230769</v>
       </c>
+      <c r="E129" t="n">
+        <v>-0.6193965417899544</v>
+      </c>
+      <c r="F129" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2238,6 +3016,12 @@
       <c r="D130" t="n">
         <v>34.70588235294117</v>
       </c>
+      <c r="E130" t="n">
+        <v>-0.147819476369955</v>
+      </c>
+      <c r="F130" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2252,6 +3036,12 @@
       <c r="D131" t="n">
         <v>45.71428571428572</v>
       </c>
+      <c r="E131" t="n">
+        <v>0.9870366366857232</v>
+      </c>
+      <c r="F131" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2266,6 +3056,12 @@
       <c r="D132" t="n">
         <v>53.33333333333334</v>
       </c>
+      <c r="E132" t="n">
+        <v>0.07367496307722743</v>
+      </c>
+      <c r="F132" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2280,6 +3076,12 @@
       <c r="D133" t="n">
         <v>38.09523809523809</v>
       </c>
+      <c r="E133" t="n">
+        <v>0.38584747140952</v>
+      </c>
+      <c r="F133" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2294,6 +3096,12 @@
       <c r="D134" t="n">
         <v>31.39805825242718</v>
       </c>
+      <c r="E134" t="n">
+        <v>-0.01786733266824247</v>
+      </c>
+      <c r="F134" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2308,6 +3116,12 @@
       <c r="D135" t="n">
         <v>30.55555555555556</v>
       </c>
+      <c r="E135" t="n">
+        <v>-0.7580845522154663</v>
+      </c>
+      <c r="F135" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2322,6 +3136,12 @@
       <c r="D136" t="n">
         <v>48.85714285714285</v>
       </c>
+      <c r="E136" t="n">
+        <v>-0.9868329033028999</v>
+      </c>
+      <c r="F136" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2336,6 +3156,12 @@
       <c r="D137" t="n">
         <v>38.06818181818182</v>
       </c>
+      <c r="E137" t="n">
+        <v>0.3607481880586501</v>
+      </c>
+      <c r="F137" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2350,6 +3176,12 @@
       <c r="D138" t="n">
         <v>30.99009900990099</v>
       </c>
+      <c r="E138" t="n">
+        <v>-0.4130745487146406</v>
+      </c>
+      <c r="F138" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2364,6 +3196,12 @@
       <c r="D139" t="n">
         <v>33.98058252427185</v>
       </c>
+      <c r="E139" t="n">
+        <v>0.5454590043365362</v>
+      </c>
+      <c r="F139" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2378,6 +3216,12 @@
       <c r="D140" t="n">
         <v>52.85714285714285</v>
       </c>
+      <c r="E140" t="n">
+        <v>0.5226294725057784</v>
+      </c>
+      <c r="F140" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2392,6 +3236,12 @@
       <c r="D141" t="n">
         <v>69.90566037735849</v>
       </c>
+      <c r="E141" t="n">
+        <v>0.710790925626183</v>
+      </c>
+      <c r="F141" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2406,6 +3256,12 @@
       <c r="D142" t="n">
         <v>69.90566037735849</v>
       </c>
+      <c r="E142" t="n">
+        <v>0.710790925626183</v>
+      </c>
+      <c r="F142" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2420,6 +3276,12 @@
       <c r="D143" t="n">
         <v>52.77777777777778</v>
       </c>
+      <c r="E143" t="n">
+        <v>0.5885768384824438</v>
+      </c>
+      <c r="F143" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2434,6 +3296,12 @@
       <c r="D144" t="n">
         <v>42.85714285714285</v>
       </c>
+      <c r="E144" t="n">
+        <v>-0.9023341109265443</v>
+      </c>
+      <c r="F144" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2448,6 +3316,12 @@
       <c r="D145" t="n">
         <v>38.14432989690722</v>
       </c>
+      <c r="E145" t="n">
+        <v>0.4306546877780721</v>
+      </c>
+      <c r="F145" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2462,6 +3336,12 @@
       <c r="D146" t="n">
         <v>29.62962962962963</v>
       </c>
+      <c r="E146" t="n">
+        <v>-0.9768694744627346</v>
+      </c>
+      <c r="F146" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2476,6 +3356,12 @@
       <c r="D147" t="n">
         <v>50</v>
       </c>
+      <c r="E147" t="n">
+        <v>-0.2623748537039288</v>
+      </c>
+      <c r="F147" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2490,6 +3376,12 @@
       <c r="D148" t="n">
         <v>33.18965517241379</v>
       </c>
+      <c r="E148" t="n">
+        <v>0.9794798051471841</v>
+      </c>
+      <c r="F148" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2504,6 +3396,12 @@
       <c r="D149" t="n">
         <v>28.99342105263158</v>
       </c>
+      <c r="E149" t="n">
+        <v>-0.6586981267674484</v>
+      </c>
+      <c r="F149" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2518,6 +3416,12 @@
       <c r="D150" t="n">
         <v>31.44654088050314</v>
       </c>
+      <c r="E150" t="n">
+        <v>0.0306095626743005</v>
+      </c>
+      <c r="F150" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2532,6 +3436,12 @@
       <c r="D151" t="n">
         <v>32.30246913580247</v>
       </c>
+      <c r="E151" t="n">
+        <v>0.7748909782577089</v>
+      </c>
+      <c r="F151" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2546,6 +3456,12 @@
       <c r="D152" t="n">
         <v>38.31386861313869</v>
       </c>
+      <c r="E152" t="n">
+        <v>0.5767598414651622</v>
+      </c>
+      <c r="F152" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2560,6 +3476,12 @@
       <c r="D153" t="n">
         <v>34.375</v>
       </c>
+      <c r="E153" t="n">
+        <v>0.1815074914039231</v>
+      </c>
+      <c r="F153" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2574,6 +3496,12 @@
       <c r="D154" t="n">
         <v>35.6687898089172</v>
       </c>
+      <c r="E154" t="n">
+        <v>-0.8962629580498255</v>
+      </c>
+      <c r="F154" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2588,6 +3516,12 @@
       <c r="D155" t="n">
         <v>37.3125</v>
       </c>
+      <c r="E155" t="n">
+        <v>-0.3770525018802441</v>
+      </c>
+      <c r="F155" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2602,6 +3536,12 @@
       <c r="D156" t="n">
         <v>39.47368421052632</v>
       </c>
+      <c r="E156" t="n">
+        <v>0.9793094090311945</v>
+      </c>
+      <c r="F156" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2616,6 +3556,12 @@
       <c r="D157" t="n">
         <v>39.47368421052632</v>
       </c>
+      <c r="E157" t="n">
+        <v>0.9793094090311945</v>
+      </c>
+      <c r="F157" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2630,6 +3576,12 @@
       <c r="D158" t="n">
         <v>41.38888888888889</v>
       </c>
+      <c r="E158" t="n">
+        <v>-0.5211385181263918</v>
+      </c>
+      <c r="F158" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2644,6 +3596,12 @@
       <c r="D159" t="n">
         <v>40</v>
       </c>
+      <c r="E159" t="n">
+        <v>0.7451131604793488</v>
+      </c>
+      <c r="F159" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -2658,6 +3616,12 @@
       <c r="D160" t="n">
         <v>45.45454545454545</v>
       </c>
+      <c r="E160" t="n">
+        <v>0.9951480722482271</v>
+      </c>
+      <c r="F160" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -2672,6 +3636,12 @@
       <c r="D161" t="n">
         <v>41.21037463976946</v>
       </c>
+      <c r="E161" t="n">
+        <v>-0.361307877691643</v>
+      </c>
+      <c r="F161" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -2686,6 +3656,12 @@
       <c r="D162" t="n">
         <v>43.22766570605187</v>
       </c>
+      <c r="E162" t="n">
+        <v>-0.6850202134235917</v>
+      </c>
+      <c r="F162" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -2700,6 +3676,12 @@
       <c r="D163" t="n">
         <v>38.75</v>
       </c>
+      <c r="E163" t="n">
+        <v>0.8678648045849774</v>
+      </c>
+      <c r="F163" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -2714,6 +3696,12 @@
       <c r="D164" t="n">
         <v>42.94736842105263</v>
       </c>
+      <c r="E164" t="n">
+        <v>-0.8598259686998618</v>
+      </c>
+      <c r="F164" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -2728,6 +3716,12 @@
       <c r="D165" t="n">
         <v>42.10526315789474</v>
       </c>
+      <c r="E165" t="n">
+        <v>-0.9534745595805655</v>
+      </c>
+      <c r="F165" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -2742,6 +3736,12 @@
       <c r="D166" t="n">
         <v>50</v>
       </c>
+      <c r="E166" t="n">
+        <v>-0.2623748537039288</v>
+      </c>
+      <c r="F166" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -2756,6 +3756,12 @@
       <c r="D167" t="n">
         <v>32.14285714285715</v>
       </c>
+      <c r="E167" t="n">
+        <v>0.6645792641255234</v>
+      </c>
+      <c r="F167" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -2770,6 +3776,12 @@
       <c r="D168" t="n">
         <v>37</v>
       </c>
+      <c r="E168" t="n">
+        <v>-0.6435381333569995</v>
+      </c>
+      <c r="F168" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -2784,6 +3796,12 @@
       <c r="D169" t="n">
         <v>45.71428571428572</v>
       </c>
+      <c r="E169" t="n">
+        <v>0.9870366366857232</v>
+      </c>
+      <c r="F169" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -2798,6 +3816,12 @@
       <c r="D170" t="n">
         <v>32.2</v>
       </c>
+      <c r="E170" t="n">
+        <v>0.7061694571803344</v>
+      </c>
+      <c r="F170" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -2812,6 +3836,12 @@
       <c r="D171" t="n">
         <v>52.63157894736842</v>
       </c>
+      <c r="E171" t="n">
+        <v>0.7000704589582356</v>
+      </c>
+      <c r="F171" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -2826,6 +3856,12 @@
       <c r="D172" t="n">
         <v>40</v>
       </c>
+      <c r="E172" t="n">
+        <v>0.7451131604793488</v>
+      </c>
+      <c r="F172" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -2840,6 +3876,12 @@
       <c r="D173" t="n">
         <v>33.80645161290322</v>
       </c>
+      <c r="E173" t="n">
+        <v>0.6824195053399589</v>
+      </c>
+      <c r="F173" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -2854,6 +3896,12 @@
       <c r="D174" t="n">
         <v>33.5</v>
       </c>
+      <c r="E174" t="n">
+        <v>0.8711400001691764</v>
+      </c>
+      <c r="F174" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -2868,6 +3916,12 @@
       <c r="D175" t="n">
         <v>54.5</v>
       </c>
+      <c r="E175" t="n">
+        <v>-0.8879758383376634</v>
+      </c>
+      <c r="F175" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -2882,6 +3936,12 @@
       <c r="D176" t="n">
         <v>42.30769230769231</v>
       </c>
+      <c r="E176" t="n">
+        <v>-0.9946167328998345</v>
+      </c>
+      <c r="F176" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -2896,6 +3956,12 @@
       <c r="D177" t="n">
         <v>54.76190476190476</v>
       </c>
+      <c r="E177" t="n">
+        <v>-0.9767696999443887</v>
+      </c>
+      <c r="F177" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -2910,6 +3976,12 @@
       <c r="D178" t="n">
         <v>51.30434782608695</v>
       </c>
+      <c r="E178" t="n">
+        <v>0.8618292988683534</v>
+      </c>
+      <c r="F178" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -2924,6 +3996,12 @@
       <c r="D179" t="n">
         <v>40</v>
       </c>
+      <c r="E179" t="n">
+        <v>0.7451131604793488</v>
+      </c>
+      <c r="F179" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -2938,6 +4016,12 @@
       <c r="D180" t="n">
         <v>37.5</v>
       </c>
+      <c r="E180" t="n">
+        <v>-0.1977987996364623</v>
+      </c>
+      <c r="F180" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -2952,6 +4036,12 @@
       <c r="D181" t="n">
         <v>60</v>
       </c>
+      <c r="E181" t="n">
+        <v>-0.3048106211022167</v>
+      </c>
+      <c r="F181" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -2966,6 +4056,12 @@
       <c r="D182" t="n">
         <v>60</v>
       </c>
+      <c r="E182" t="n">
+        <v>-0.3048106211022167</v>
+      </c>
+      <c r="F182" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -2980,6 +4076,12 @@
       <c r="D183" t="n">
         <v>43.5</v>
       </c>
+      <c r="E183" t="n">
+        <v>-0.4638155159838274</v>
+      </c>
+      <c r="F183" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -2994,6 +4096,12 @@
       <c r="D184" t="n">
         <v>59.52380952380953</v>
       </c>
+      <c r="E184" t="n">
+        <v>0.1656833464694588</v>
+      </c>
+      <c r="F184" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -3008,6 +4116,12 @@
       <c r="D185" t="n">
         <v>36.76470588235294</v>
       </c>
+      <c r="E185" t="n">
+        <v>-0.8042461847004519</v>
+      </c>
+      <c r="F185" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -3022,6 +4136,12 @@
       <c r="D186" t="n">
         <v>59.09090909090909</v>
       </c>
+      <c r="E186" t="n">
+        <v>0.5641069819542825</v>
+      </c>
+      <c r="F186" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -3036,6 +4156,12 @@
       <c r="D187" t="n">
         <v>37.97142857142857</v>
       </c>
+      <c r="E187" t="n">
+        <v>0.2689635142468394</v>
+      </c>
+      <c r="F187" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -3050,6 +4176,12 @@
       <c r="D188" t="n">
         <v>44.66666666666666</v>
       </c>
+      <c r="E188" t="n">
+        <v>0.6321846273006374</v>
+      </c>
+      <c r="F188" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -3064,6 +4196,12 @@
       <c r="D189" t="n">
         <v>46.875</v>
       </c>
+      <c r="E189" t="n">
+        <v>0.2463281241651517</v>
+      </c>
+      <c r="F189" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -3078,6 +4216,12 @@
       <c r="D190" t="n">
         <v>46.875</v>
       </c>
+      <c r="E190" t="n">
+        <v>0.2463281241651517</v>
+      </c>
+      <c r="F190" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -3092,6 +4236,12 @@
       <c r="D191" t="n">
         <v>26.27118644067797</v>
       </c>
+      <c r="E191" t="n">
+        <v>0.9079831271874169</v>
+      </c>
+      <c r="F191" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -3106,6 +4256,12 @@
       <c r="D192" t="n">
         <v>38</v>
       </c>
+      <c r="E192" t="n">
+        <v>0.2963685787093853</v>
+      </c>
+      <c r="F192" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -3120,6 +4276,12 @@
       <c r="D193" t="n">
         <v>26.90140845070422</v>
       </c>
+      <c r="E193" t="n">
+        <v>0.980487343986435</v>
+      </c>
+      <c r="F193" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -3134,6 +4296,12 @@
       <c r="D194" t="n">
         <v>54</v>
       </c>
+      <c r="E194" t="n">
+        <v>-0.5587890488516163</v>
+      </c>
+      <c r="F194" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -3148,6 +4316,12 @@
       <c r="D195" t="n">
         <v>35.97560975609756</v>
       </c>
+      <c r="E195" t="n">
+        <v>-0.9883631152178051</v>
+      </c>
+      <c r="F195" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -3162,6 +4336,12 @@
       <c r="D196" t="n">
         <v>54</v>
       </c>
+      <c r="E196" t="n">
+        <v>-0.5587890488516163</v>
+      </c>
+      <c r="F196" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -3176,6 +4356,12 @@
       <c r="D197" t="n">
         <v>40.37267080745342</v>
       </c>
+      <c r="E197" t="n">
+        <v>0.4511323106526043</v>
+      </c>
+      <c r="F197" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -3190,6 +4376,12 @@
       <c r="D198" t="n">
         <v>50</v>
       </c>
+      <c r="E198" t="n">
+        <v>-0.2623748537039288</v>
+      </c>
+      <c r="F198" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -3204,6 +4396,12 @@
       <c r="D199" t="n">
         <v>33.80645161290322</v>
       </c>
+      <c r="E199" t="n">
+        <v>0.6824195053399589</v>
+      </c>
+      <c r="F199" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -3218,6 +4416,12 @@
       <c r="D200" t="n">
         <v>36.66666666666666</v>
       </c>
+      <c r="E200" t="n">
+        <v>-0.8585552479838888</v>
+      </c>
+      <c r="F200" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -3232,6 +4436,12 @@
       <c r="D201" t="n">
         <v>37.93103448275862</v>
       </c>
+      <c r="E201" t="n">
+        <v>0.2298491106647837</v>
+      </c>
+      <c r="F201" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -3246,6 +4456,12 @@
       <c r="D202" t="n">
         <v>34.33333333333334</v>
       </c>
+      <c r="E202" t="n">
+        <v>0.2223126656555978</v>
+      </c>
+      <c r="F202" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -3260,6 +4476,12 @@
       <c r="D203" t="n">
         <v>33.33333333333334</v>
       </c>
+      <c r="E203" t="n">
+        <v>0.9405295766287635</v>
+      </c>
+      <c r="F203" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -3274,6 +4496,12 @@
       <c r="D204" t="n">
         <v>43.71428571428572</v>
       </c>
+      <c r="E204" t="n">
+        <v>-0.2648143904361316</v>
+      </c>
+      <c r="F204" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -3288,6 +4516,12 @@
       <c r="D205" t="n">
         <v>27.63636363636364</v>
       </c>
+      <c r="E205" t="n">
+        <v>0.595566155170052</v>
+      </c>
+      <c r="F205" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -3302,6 +4536,12 @@
       <c r="D206" t="n">
         <v>50</v>
       </c>
+      <c r="E206" t="n">
+        <v>-0.2623748537039288</v>
+      </c>
+      <c r="F206" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -3316,6 +4556,12 @@
       <c r="D207" t="n">
         <v>30</v>
       </c>
+      <c r="E207" t="n">
+        <v>-0.9880316240928618</v>
+      </c>
+      <c r="F207" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -3330,6 +4576,12 @@
       <c r="D208" t="n">
         <v>28.33333333333333</v>
       </c>
+      <c r="E208" t="n">
+        <v>-0.05896522810427303</v>
+      </c>
+      <c r="F208" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -3344,6 +4596,12 @@
       <c r="D209" t="n">
         <v>39.56521739130435</v>
       </c>
+      <c r="E209" t="n">
+        <v>0.956712193585968</v>
+      </c>
+      <c r="F209" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -3358,6 +4616,12 @@
       <c r="D210" t="n">
         <v>28.03030303030303</v>
       </c>
+      <c r="E210" t="n">
+        <v>0.2416160043822434</v>
+      </c>
+      <c r="F210" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -3372,6 +4636,12 @@
       <c r="D211" t="n">
         <v>27.30985915492958</v>
       </c>
+      <c r="E211" t="n">
+        <v>0.8217497039219137</v>
+      </c>
+      <c r="F211" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -3386,6 +4656,12 @@
       <c r="D212" t="n">
         <v>26.45945945945946</v>
       </c>
+      <c r="E212" t="n">
+        <v>0.9703605263107955</v>
+      </c>
+      <c r="F212" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -3400,6 +4676,12 @@
       <c r="D213" t="n">
         <v>20.11494252873563</v>
       </c>
+      <c r="E213" t="n">
+        <v>0.9537238365109195</v>
+      </c>
+      <c r="F213" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -3414,6 +4696,12 @@
       <c r="D214" t="n">
         <v>33.70967741935484</v>
       </c>
+      <c r="E214" t="n">
+        <v>0.7498542611939305</v>
+      </c>
+      <c r="F214" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -3428,6 +4716,12 @@
       <c r="D215" t="n">
         <v>30.91176470588235</v>
       </c>
+      <c r="E215" t="n">
+        <v>-0.4830737254899058</v>
+      </c>
+      <c r="F215" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -3442,6 +4736,12 @@
       <c r="D216" t="n">
         <v>28.82666666666667</v>
       </c>
+      <c r="E216" t="n">
+        <v>-0.5246745607965275</v>
+      </c>
+      <c r="F216" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -3456,6 +4756,12 @@
       <c r="D217" t="n">
         <v>26.875</v>
       </c>
+      <c r="E217" t="n">
+        <v>0.9853362932476007</v>
+      </c>
+      <c r="F217" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -3470,6 +4776,12 @@
       <c r="D218" t="n">
         <v>30.40540540540541</v>
       </c>
+      <c r="E218" t="n">
+        <v>-0.8471088984551353</v>
+      </c>
+      <c r="F218" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -3484,6 +4796,12 @@
       <c r="D219" t="n">
         <v>29.4875</v>
       </c>
+      <c r="E219" t="n">
+        <v>-0.9367290112133916</v>
+      </c>
+      <c r="F219" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -3498,6 +4816,12 @@
       <c r="D220" t="n">
         <v>21.42857142857143</v>
       </c>
+      <c r="E220" t="n">
+        <v>0.5333679321116596</v>
+      </c>
+      <c r="F220" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -3512,6 +4836,12 @@
       <c r="D221" t="n">
         <v>25.61458333333333</v>
       </c>
+      <c r="E221" t="n">
+        <v>0.4634123285692919</v>
+      </c>
+      <c r="F221" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -3526,6 +4856,12 @@
       <c r="D222" t="n">
         <v>21.42857142857143</v>
       </c>
+      <c r="E222" t="n">
+        <v>0.5333679321116596</v>
+      </c>
+      <c r="F222" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -3540,6 +4876,12 @@
       <c r="D223" t="n">
         <v>25.61458333333333</v>
       </c>
+      <c r="E223" t="n">
+        <v>0.4634123285692919</v>
+      </c>
+      <c r="F223" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -3554,6 +4896,12 @@
       <c r="D224" t="n">
         <v>29.47674418604651</v>
       </c>
+      <c r="E224" t="n">
+        <v>-0.9329097700026979</v>
+      </c>
+      <c r="F224" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -3568,6 +4916,12 @@
       <c r="D225" t="n">
         <v>29.44444444444444</v>
       </c>
+      <c r="E225" t="n">
+        <v>-0.9207937281121261</v>
+      </c>
+      <c r="F225" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -3582,6 +4936,12 @@
       <c r="D226" t="n">
         <v>27.04081632653061</v>
       </c>
+      <c r="E226" t="n">
+        <v>0.9436586685607121</v>
+      </c>
+      <c r="F226" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -3596,6 +4956,12 @@
       <c r="D227" t="n">
         <v>27.61904761904762</v>
       </c>
+      <c r="E227" t="n">
+        <v>0.6093862388526794</v>
+      </c>
+      <c r="F227" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -3610,6 +4976,12 @@
       <c r="D228" t="n">
         <v>42.14285714285715</v>
       </c>
+      <c r="E228" t="n">
+        <v>-0.9641317827983479</v>
+      </c>
+      <c r="F228" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -3624,6 +4996,12 @@
       <c r="D229" t="n">
         <v>34.09090909090909</v>
       </c>
+      <c r="E229" t="n">
+        <v>0.4498613604067414</v>
+      </c>
+      <c r="F229" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -3638,6 +5016,12 @@
       <c r="D230" t="n">
         <v>30.8</v>
       </c>
+      <c r="E230" t="n">
+        <v>-0.5777150444457317</v>
+      </c>
+      <c r="F230" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -3652,6 +5036,12 @@
       <c r="D231" t="n">
         <v>27.025</v>
       </c>
+      <c r="E231" t="n">
+        <v>0.9487743670285951</v>
+      </c>
+      <c r="F231" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -3666,6 +5056,12 @@
       <c r="D232" t="n">
         <v>35.8974358974359</v>
       </c>
+      <c r="E232" t="n">
+        <v>-0.9734654850278111</v>
+      </c>
+      <c r="F232" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -3680,6 +5076,12 @@
       <c r="D233" t="n">
         <v>28.54335260115607</v>
       </c>
+      <c r="E233" t="n">
+        <v>-0.2657855782055563</v>
+      </c>
+      <c r="F233" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -3694,6 +5096,12 @@
       <c r="D234" t="n">
         <v>35.48387096774194</v>
       </c>
+      <c r="E234" t="n">
+        <v>-0.799433580204136</v>
+      </c>
+      <c r="F234" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -3708,6 +5116,12 @@
       <c r="D235" t="n">
         <v>30.43478260869565</v>
       </c>
+      <c r="E235" t="n">
+        <v>-0.8311340202148491</v>
+      </c>
+      <c r="F235" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -3722,6 +5136,12 @@
       <c r="D236" t="n">
         <v>41.90476190476191</v>
       </c>
+      <c r="E236" t="n">
+        <v>-0.8743318498521788</v>
+      </c>
+      <c r="F236" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -3736,6 +5156,12 @@
       <c r="D237" t="n">
         <v>62</v>
       </c>
+      <c r="E237" t="n">
+        <v>-0.7391806966492228</v>
+      </c>
+      <c r="F237" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -3750,6 +5176,12 @@
       <c r="D238" t="n">
         <v>34.81481481481482</v>
       </c>
+      <c r="E238" t="n">
+        <v>-0.2544661343997753</v>
+      </c>
+      <c r="F238" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -3764,6 +5196,12 @@
       <c r="D239" t="n">
         <v>45.23809523809524</v>
       </c>
+      <c r="E239" t="n">
+        <v>0.9507969245127809</v>
+      </c>
+      <c r="F239" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -3778,6 +5216,12 @@
       <c r="D240" t="n">
         <v>45.23809523809524</v>
       </c>
+      <c r="E240" t="n">
+        <v>0.9507969245127809</v>
+      </c>
+      <c r="F240" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -3792,6 +5236,12 @@
       <c r="D241" t="n">
         <v>47.61904761904762</v>
       </c>
+      <c r="E241" t="n">
+        <v>-0.475170517793463</v>
+      </c>
+      <c r="F241" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -3806,6 +5256,12 @@
       <c r="D242" t="n">
         <v>38.33333333333334</v>
       </c>
+      <c r="E242" t="n">
+        <v>0.5925505785029125</v>
+      </c>
+      <c r="F242" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -3820,6 +5276,12 @@
       <c r="D243" t="n">
         <v>29.82456140350877</v>
       </c>
+      <c r="E243" t="n">
+        <v>-0.9997884695761534</v>
+      </c>
+      <c r="F243" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -3834,6 +5296,12 @@
       <c r="D244" t="n">
         <v>35.51020408163265</v>
       </c>
+      <c r="E244" t="n">
+        <v>-0.8149743274603717</v>
+      </c>
+      <c r="F244" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -3848,6 +5316,12 @@
       <c r="D245" t="n">
         <v>31.14473684210526</v>
       </c>
+      <c r="E245" t="n">
+        <v>-0.2678778399093261</v>
+      </c>
+      <c r="F245" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -3862,6 +5336,12 @@
       <c r="D246" t="n">
         <v>33.73493975903614</v>
       </c>
+      <c r="E246" t="n">
+        <v>0.732903137608343</v>
+      </c>
+      <c r="F246" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -3876,6 +5356,12 @@
       <c r="D247" t="n">
         <v>28.84615384615385</v>
       </c>
+      <c r="E247" t="n">
+        <v>-0.541163383521727</v>
+      </c>
+      <c r="F247" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -3890,6 +5376,12 @@
       <c r="D248" t="n">
         <v>31.02272727272727</v>
       </c>
+      <c r="E248" t="n">
+        <v>-0.3831454919001258</v>
+      </c>
+      <c r="F248" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -3904,6 +5396,12 @@
       <c r="D249" t="n">
         <v>42.75</v>
       </c>
+      <c r="E249" t="n">
+        <v>-0.943254108829076</v>
+      </c>
+      <c r="F249" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -3918,6 +5416,12 @@
       <c r="D250" t="n">
         <v>41.66666666666666</v>
       </c>
+      <c r="E250" t="n">
+        <v>-0.7352003292894852</v>
+      </c>
+      <c r="F250" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -3932,6 +5436,12 @@
       <c r="D251" t="n">
         <v>30.89855072463768</v>
       </c>
+      <c r="E251" t="n">
+        <v>-0.4946011082896373</v>
+      </c>
+      <c r="F251" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -3946,6 +5456,12 @@
       <c r="D252" t="n">
         <v>36.88311688311688</v>
       </c>
+      <c r="E252" t="n">
+        <v>-0.7284076498724666</v>
+      </c>
+      <c r="F252" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -3960,6 +5476,12 @@
       <c r="D253" t="n">
         <v>27.22916666666667</v>
       </c>
+      <c r="E253" t="n">
+        <v>0.8650084517129446</v>
+      </c>
+      <c r="F253" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -3974,6 +5496,12 @@
       <c r="D254" t="n">
         <v>36.47368421052632</v>
       </c>
+      <c r="E254" t="n">
+        <v>-0.9409506974784461</v>
+      </c>
+      <c r="F254" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -3988,6 +5516,12 @@
       <c r="D255" t="n">
         <v>50</v>
       </c>
+      <c r="E255" t="n">
+        <v>-0.2623748537039288</v>
+      </c>
+      <c r="F255" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -4002,6 +5536,12 @@
       <c r="D256" t="n">
         <v>81.48148148148148</v>
       </c>
+      <c r="E256" t="n">
+        <v>-0.1985982870631424</v>
+      </c>
+      <c r="F256" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -4016,6 +5556,12 @@
       <c r="D257" t="n">
         <v>31.66666666666667</v>
       </c>
+      <c r="E257" t="n">
+        <v>0.2481210133214244</v>
+      </c>
+      <c r="F257" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -4030,6 +5576,12 @@
       <c r="D258" t="n">
         <v>32.59722222222222</v>
       </c>
+      <c r="E258" t="n">
+        <v>0.9250987952398479</v>
+      </c>
+      <c r="F258" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -4044,6 +5596,12 @@
       <c r="D259" t="n">
         <v>33.59223300970874</v>
       </c>
+      <c r="E259" t="n">
+        <v>0.8222118383409271</v>
+      </c>
+      <c r="F259" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -4058,6 +5616,12 @@
       <c r="D260" t="n">
         <v>44</v>
       </c>
+      <c r="E260" t="n">
+        <v>0.01770192510541358</v>
+      </c>
+      <c r="F260" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -4072,6 +5636,12 @@
       <c r="D261" t="n">
         <v>40</v>
       </c>
+      <c r="E261" t="n">
+        <v>0.7451131604793488</v>
+      </c>
+      <c r="F261" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -4086,6 +5656,12 @@
       <c r="D262" t="n">
         <v>32.825</v>
       </c>
+      <c r="E262" t="n">
+        <v>0.9869513349457315</v>
+      </c>
+      <c r="F262" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -4100,6 +5676,12 @@
       <c r="D263" t="n">
         <v>27.59259259259259</v>
       </c>
+      <c r="E263" t="n">
+        <v>0.6301460494342492</v>
+      </c>
+      <c r="F263" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -4114,6 +5696,12 @@
       <c r="D264" t="n">
         <v>31.35593220338983</v>
       </c>
+      <c r="E264" t="n">
+        <v>-0.05995834918500887</v>
+      </c>
+      <c r="F264" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -4128,6 +5716,12 @@
       <c r="D265" t="n">
         <v>30.32258064516129</v>
       </c>
+      <c r="E265" t="n">
+        <v>-0.8881693741843197</v>
+      </c>
+      <c r="F265" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -4142,6 +5736,12 @@
       <c r="D266" t="n">
         <v>29.6875</v>
       </c>
+      <c r="E266" t="n">
+        <v>-0.9876020617700564</v>
+      </c>
+      <c r="F266" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -4156,6 +5756,12 @@
       <c r="D267" t="n">
         <v>39.58333333333334</v>
       </c>
+      <c r="E267" t="n">
+        <v>0.9512831099720535</v>
+      </c>
+      <c r="F267" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -4170,6 +5776,12 @@
       <c r="D268" t="n">
         <v>23.08045977011494</v>
       </c>
+      <c r="E268" t="n">
+        <v>-0.8863081419041505</v>
+      </c>
+      <c r="F268" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -4184,6 +5796,12 @@
       <c r="D269" t="n">
         <v>27.92452830188679</v>
       </c>
+      <c r="E269" t="n">
+        <v>0.3427151685289802</v>
+      </c>
+      <c r="F269" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -4198,6 +5816,12 @@
       <c r="D270" t="n">
         <v>28.07017543859649</v>
       </c>
+      <c r="E270" t="n">
+        <v>0.2027431529889751</v>
+      </c>
+      <c r="F270" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -4212,6 +5836,12 @@
       <c r="D271" t="n">
         <v>29.27272727272727</v>
       </c>
+      <c r="E271" t="n">
+        <v>-0.8406018443203209</v>
+      </c>
+      <c r="F271" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -4226,6 +5856,12 @@
       <c r="D272" t="n">
         <v>26.2015503875969</v>
       </c>
+      <c r="E272" t="n">
+        <v>0.8766281307544114</v>
+      </c>
+      <c r="F272" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -4240,6 +5876,12 @@
       <c r="D273" t="n">
         <v>31.6</v>
       </c>
+      <c r="E273" t="n">
+        <v>0.183035728980588</v>
+      </c>
+      <c r="F273" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -4254,6 +5896,12 @@
       <c r="D274" t="n">
         <v>43</v>
       </c>
+      <c r="E274" t="n">
+        <v>-0.8317747426285983</v>
+      </c>
+      <c r="F274" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -4268,6 +5916,12 @@
       <c r="D275" t="n">
         <v>40.11764705882353</v>
       </c>
+      <c r="E275" t="n">
+        <v>0.6616801857405195</v>
+      </c>
+      <c r="F275" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -4282,6 +5936,12 @@
       <c r="D276" t="n">
         <v>37.25</v>
       </c>
+      <c r="E276" t="n">
+        <v>-0.4341656243337532</v>
+      </c>
+      <c r="F276" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -4296,6 +5956,12 @@
       <c r="D277" t="n">
         <v>39.55555555555556</v>
       </c>
+      <c r="E277" t="n">
+        <v>0.9594794342604003</v>
+      </c>
+      <c r="F277" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -4310,6 +5976,12 @@
       <c r="D278" t="n">
         <v>29.53703703703704</v>
       </c>
+      <c r="E278" t="n">
+        <v>-0.9529135325242237</v>
+      </c>
+      <c r="F278" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -4324,6 +5996,12 @@
       <c r="D279" t="n">
         <v>40</v>
       </c>
+      <c r="E279" t="n">
+        <v>0.7451131604793488</v>
+      </c>
+      <c r="F279" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -4338,6 +6016,12 @@
       <c r="D280" t="n">
         <v>63.33333333333334</v>
       </c>
+      <c r="E280" t="n">
+        <v>0.4807240645897722</v>
+      </c>
+      <c r="F280" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -4352,6 +6036,12 @@
       <c r="D281" t="n">
         <v>33.55172413793103</v>
       </c>
+      <c r="E281" t="n">
+        <v>0.8445879176399634</v>
+      </c>
+      <c r="F281" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -4366,6 +6056,12 @@
       <c r="D282" t="n">
         <v>30.55555555555556</v>
       </c>
+      <c r="E282" t="n">
+        <v>-0.7580845522154663</v>
+      </c>
+      <c r="F282" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -4380,6 +6076,12 @@
       <c r="D283" t="n">
         <v>37.02</v>
       </c>
+      <c r="E283" t="n">
+        <v>-0.6281021695132742</v>
+      </c>
+      <c r="F283" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -4394,6 +6096,12 @@
       <c r="D284" t="n">
         <v>33.48484848484848</v>
       </c>
+      <c r="E284" t="n">
+        <v>0.8784796443701782</v>
+      </c>
+      <c r="F284" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -4408,6 +6116,12 @@
       <c r="D285" t="n">
         <v>30</v>
       </c>
+      <c r="E285" t="n">
+        <v>-0.9880316240928618</v>
+      </c>
+      <c r="F285" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -4422,6 +6136,12 @@
       <c r="D286" t="n">
         <v>30.42857142857143</v>
       </c>
+      <c r="E286" t="n">
+        <v>-0.8345718303099512</v>
+      </c>
+      <c r="F286" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -4436,6 +6156,12 @@
       <c r="D287" t="n">
         <v>53.33333333333334</v>
       </c>
+      <c r="E287" t="n">
+        <v>0.07367496307722743</v>
+      </c>
+      <c r="F287" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -4450,6 +6176,12 @@
       <c r="D288" t="n">
         <v>28.97058823529412</v>
       </c>
+      <c r="E288" t="n">
+        <v>-0.64134834594113</v>
+      </c>
+      <c r="F288" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -4464,6 +6196,12 @@
       <c r="D289" t="n">
         <v>34.48275862068966</v>
       </c>
+      <c r="E289" t="n">
+        <v>0.07469094700999017</v>
+      </c>
+      <c r="F289" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -4478,6 +6216,12 @@
       <c r="D290" t="n">
         <v>38.69230769230769</v>
       </c>
+      <c r="E290" t="n">
+        <v>0.8377752363320395</v>
+      </c>
+      <c r="F290" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -4492,6 +6236,12 @@
       <c r="D291" t="n">
         <v>29.72972972972973</v>
       </c>
+      <c r="E291" t="n">
+        <v>-0.9933487509714088</v>
+      </c>
+      <c r="F291" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -4506,6 +6256,12 @@
       <c r="D292" t="n">
         <v>38.125</v>
       </c>
+      <c r="E292" t="n">
+        <v>0.4131297643703782</v>
+      </c>
+      <c r="F292" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -4520,6 +6276,12 @@
       <c r="D293" t="n">
         <v>35.14285714285715</v>
       </c>
+      <c r="E293" t="n">
+        <v>-0.5524811065993861</v>
+      </c>
+      <c r="F293" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -4534,6 +6296,12 @@
       <c r="D294" t="n">
         <v>42.33333333333334</v>
       </c>
+      <c r="E294" t="n">
+        <v>-0.9969464770105411</v>
+      </c>
+      <c r="F294" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -4548,6 +6316,12 @@
       <c r="D295" t="n">
         <v>41.29032258064516</v>
       </c>
+      <c r="E295" t="n">
+        <v>-0.4346216072220985</v>
+      </c>
+      <c r="F295" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -4562,6 +6336,12 @@
       <c r="D296" t="n">
         <v>33.94736842105263</v>
       </c>
+      <c r="E296" t="n">
+        <v>0.572991030638033</v>
+      </c>
+      <c r="F296" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -4576,6 +6356,12 @@
       <c r="D297" t="n">
         <v>33.33333333333334</v>
       </c>
+      <c r="E297" t="n">
+        <v>0.9405295766287635</v>
+      </c>
+      <c r="F297" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -4590,6 +6376,12 @@
       <c r="D298" t="n">
         <v>39.41176470588236</v>
       </c>
+      <c r="E298" t="n">
+        <v>0.989955223043085</v>
+      </c>
+      <c r="F298" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -4604,6 +6396,12 @@
       <c r="D299" t="n">
         <v>34.61538461538461</v>
       </c>
+      <c r="E299" t="n">
+        <v>-0.05783313846512109</v>
+      </c>
+      <c r="F299" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -4618,6 +6416,12 @@
       <c r="D300" t="n">
         <v>34.5</v>
       </c>
+      <c r="E300" t="n">
+        <v>0.05748747810492456</v>
+      </c>
+      <c r="F300" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -4632,6 +6436,12 @@
       <c r="D301" t="n">
         <v>29.57446808510638</v>
       </c>
+      <c r="E301" t="n">
+        <v>-0.9635940758313835</v>
+      </c>
+      <c r="F301" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -4646,6 +6456,12 @@
       <c r="D302" t="n">
         <v>34.75</v>
       </c>
+      <c r="E302" t="n">
+        <v>-0.1912944777489552</v>
+      </c>
+      <c r="F302" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -4660,6 +6476,12 @@
       <c r="D303" t="n">
         <v>26.92307692307692</v>
       </c>
+      <c r="E303" t="n">
+        <v>0.9759978694359551</v>
+      </c>
+      <c r="F303" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -4674,6 +6496,12 @@
       <c r="D304" t="n">
         <v>35</v>
       </c>
+      <c r="E304" t="n">
+        <v>-0.428182669496151</v>
+      </c>
+      <c r="F304" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -4688,6 +6516,12 @@
       <c r="D305" t="n">
         <v>42.42424242424242</v>
       </c>
+      <c r="E305" t="n">
+        <v>-0.9999188269029812</v>
+      </c>
+      <c r="F305" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -4702,6 +6536,12 @@
       <c r="D306" t="n">
         <v>37.5</v>
       </c>
+      <c r="E306" t="n">
+        <v>-0.1977987996364623</v>
+      </c>
+      <c r="F306" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -4716,6 +6556,12 @@
       <c r="D307" t="n">
         <v>31</v>
       </c>
+      <c r="E307" t="n">
+        <v>-0.404037645323065</v>
+      </c>
+      <c r="F307" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -4730,6 +6576,12 @@
       <c r="D308" t="n">
         <v>30.7843137254902</v>
       </c>
+      <c r="E308" t="n">
+        <v>-0.5904471863234821</v>
+      </c>
+      <c r="F308" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -4744,6 +6596,12 @@
       <c r="D309" t="n">
         <v>35.33333333333334</v>
       </c>
+      <c r="E309" t="n">
+        <v>-0.7002974848739389</v>
+      </c>
+      <c r="F309" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -4758,6 +6616,12 @@
       <c r="D310" t="n">
         <v>45.71428571428572</v>
       </c>
+      <c r="E310" t="n">
+        <v>0.9870366366857232</v>
+      </c>
+      <c r="F310" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -4772,6 +6636,12 @@
       <c r="D311" t="n">
         <v>43.24324324324324</v>
       </c>
+      <c r="E311" t="n">
+        <v>-0.6735889500336615</v>
+      </c>
+      <c r="F311" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -4786,6 +6656,12 @@
       <c r="D312" t="n">
         <v>35.3695652173913</v>
       </c>
+      <c r="E312" t="n">
+        <v>-0.7256963904032744</v>
+      </c>
+      <c r="F312" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -4800,6 +6676,12 @@
       <c r="D313" t="n">
         <v>30.17857142857143</v>
       </c>
+      <c r="E313" t="n">
+        <v>-0.9449216410441829</v>
+      </c>
+      <c r="F313" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -4814,6 +6696,12 @@
       <c r="D314" t="n">
         <v>29.75438596491228</v>
       </c>
+      <c r="E314" t="n">
+        <v>-0.9958855656012497</v>
+      </c>
+      <c r="F314" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -4828,6 +6716,12 @@
       <c r="D315" t="n">
         <v>37.77777777777778</v>
       </c>
+      <c r="E315" t="n">
+        <v>0.07858482468323198</v>
+      </c>
+      <c r="F315" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -4842,6 +6736,12 @@
       <c r="D316" t="n">
         <v>36.17021276595744</v>
       </c>
+      <c r="E316" t="n">
+        <v>-0.9991224386172179</v>
+      </c>
+      <c r="F316" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -4856,6 +6756,12 @@
       <c r="D317" t="n">
         <v>22.73333333333333</v>
       </c>
+      <c r="E317" t="n">
+        <v>-0.6758996763430772</v>
+      </c>
+      <c r="F317" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -4870,6 +6776,12 @@
       <c r="D318" t="n">
         <v>34.31372549019608</v>
       </c>
+      <c r="E318" t="n">
+        <v>0.2413858712508038</v>
+      </c>
+      <c r="F318" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -4884,6 +6796,12 @@
       <c r="D319" t="n">
         <v>35.71428571428572</v>
       </c>
+      <c r="E319" t="n">
+        <v>-0.9155070638063744</v>
+      </c>
+      <c r="F319" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -4898,6 +6816,12 @@
       <c r="D320" t="n">
         <v>45</v>
       </c>
+      <c r="E320" t="n">
+        <v>0.8509035245341184</v>
+      </c>
+      <c r="F320" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -4912,6 +6836,12 @@
       <c r="D321" t="n">
         <v>28.59375</v>
       </c>
+      <c r="E321" t="n">
+        <v>-0.314012265259946</v>
+      </c>
+      <c r="F321" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -4926,6 +6856,12 @@
       <c r="D322" t="n">
         <v>27.83870967741936</v>
       </c>
+      <c r="E322" t="n">
+        <v>0.4219763919463504</v>
+      </c>
+      <c r="F322" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -4940,6 +6876,12 @@
       <c r="D323" t="n">
         <v>52.85714285714285</v>
       </c>
+      <c r="E323" t="n">
+        <v>0.5226294725057784</v>
+      </c>
+      <c r="F323" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -4954,6 +6896,12 @@
       <c r="D324" t="n">
         <v>44.64285714285715</v>
       </c>
+      <c r="E324" t="n">
+        <v>0.613559145619861</v>
+      </c>
+      <c r="F324" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -4968,6 +6916,12 @@
       <c r="D325" t="n">
         <v>42.22222222222222</v>
       </c>
+      <c r="E325" t="n">
+        <v>-0.9821402221526757</v>
+      </c>
+      <c r="F325" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -4982,6 +6936,12 @@
       <c r="D326" t="n">
         <v>30.15625</v>
       </c>
+      <c r="E326" t="n">
+        <v>-0.9519913709924333</v>
+      </c>
+      <c r="F326" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -4996,6 +6956,12 @@
       <c r="D327" t="n">
         <v>32.62295081967213</v>
       </c>
+      <c r="E327" t="n">
+        <v>0.9345613751595228</v>
+      </c>
+      <c r="F327" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -5010,6 +6976,12 @@
       <c r="D328" t="n">
         <v>40</v>
       </c>
+      <c r="E328" t="n">
+        <v>0.7451131604793488</v>
+      </c>
+      <c r="F328" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -5024,6 +6996,12 @@
       <c r="D329" t="n">
         <v>31.9375</v>
       </c>
+      <c r="E329" t="n">
+        <v>0.4982450045214716</v>
+      </c>
+      <c r="F329" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -5038,6 +7016,12 @@
       <c r="D330" t="n">
         <v>29.85507246376812</v>
       </c>
+      <c r="E330" t="n">
+        <v>-0.9999505761932115</v>
+      </c>
+      <c r="F330" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -5052,6 +7036,12 @@
       <c r="D331" t="n">
         <v>42</v>
       </c>
+      <c r="E331" t="n">
+        <v>-0.9165215479156338</v>
+      </c>
+      <c r="F331" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -5066,6 +7056,12 @@
       <c r="D332" t="n">
         <v>26.32876712328767</v>
       </c>
+      <c r="E332" t="n">
+        <v>0.9305916817614029</v>
+      </c>
+      <c r="F332" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -5080,6 +7076,12 @@
       <c r="D333" t="n">
         <v>31.28571428571428</v>
       </c>
+      <c r="E333" t="n">
+        <v>-0.1298445988921355</v>
+      </c>
+      <c r="F333" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -5094,6 +7096,12 @@
       <c r="D334" t="n">
         <v>34.09090909090909</v>
       </c>
+      <c r="E334" t="n">
+        <v>0.4498613604067414</v>
+      </c>
+      <c r="F334" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -5108,6 +7116,12 @@
       <c r="D335" t="n">
         <v>40.90909090909091</v>
       </c>
+      <c r="E335" t="n">
+        <v>-0.0683331210813377</v>
+      </c>
+      <c r="F335" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -5122,6 +7136,12 @@
       <c r="D336" t="n">
         <v>35.38461538461539</v>
       </c>
+      <c r="E336" t="n">
+        <v>-0.7359685551967111</v>
+      </c>
+      <c r="F336" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -5136,6 +7156,12 @@
       <c r="D337" t="n">
         <v>28.75</v>
       </c>
+      <c r="E337" t="n">
+        <v>-0.4579307192868114</v>
+      </c>
+      <c r="F337" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -5150,6 +7176,12 @@
       <c r="D338" t="n">
         <v>26.23863636363636</v>
       </c>
+      <c r="E338" t="n">
+        <v>0.8938658690588137</v>
+      </c>
+      <c r="F338" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -5164,6 +7196,12 @@
       <c r="D339" t="n">
         <v>45.37037037037037</v>
       </c>
+      <c r="E339" t="n">
+        <v>0.9833525290122983</v>
+      </c>
+      <c r="F339" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -5178,6 +7216,12 @@
       <c r="D340" t="n">
         <v>27.76404494382022</v>
       </c>
+      <c r="E340" t="n">
+        <v>0.4884293959799259</v>
+      </c>
+      <c r="F340" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -5192,6 +7236,12 @@
       <c r="D341" t="n">
         <v>48.07692307692308</v>
       </c>
+      <c r="E341" t="n">
+        <v>-0.8151761637262019</v>
+      </c>
+      <c r="F341" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -5206,6 +7256,12 @@
       <c r="D342" t="n">
         <v>78.125</v>
       </c>
+      <c r="E342" t="n">
+        <v>0.4030218530896224</v>
+      </c>
+      <c r="F342" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -5220,6 +7276,12 @@
       <c r="D343" t="n">
         <v>39.68253968253968</v>
       </c>
+      <c r="E343" t="n">
+        <v>0.9160687030670338</v>
+      </c>
+      <c r="F343" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -5234,6 +7296,12 @@
       <c r="D344" t="n">
         <v>32.89473684210526</v>
       </c>
+      <c r="E344" t="n">
+        <v>0.99577226832378</v>
+      </c>
+      <c r="F344" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -5248,6 +7316,12 @@
       <c r="D345" t="n">
         <v>35.43835616438356</v>
       </c>
+      <c r="E345" t="n">
+        <v>-0.7712718883875826</v>
+      </c>
+      <c r="F345" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -5262,6 +7336,12 @@
       <c r="D346" t="n">
         <v>26.73267326732673</v>
       </c>
+      <c r="E346" t="n">
+        <v>0.999575585173283</v>
+      </c>
+      <c r="F346" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -5276,6 +7356,12 @@
       <c r="D347" t="n">
         <v>32.14285714285715</v>
       </c>
+      <c r="E347" t="n">
+        <v>0.6645792641255234</v>
+      </c>
+      <c r="F347" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -5290,6 +7376,12 @@
       <c r="D348" t="n">
         <v>33.95061728395062</v>
       </c>
+      <c r="E348" t="n">
+        <v>0.5703253679340939</v>
+      </c>
+      <c r="F348" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -5304,6 +7396,12 @@
       <c r="D349" t="n">
         <v>41.1764705882353</v>
       </c>
+      <c r="E349" t="n">
+        <v>-0.329492578101362</v>
+      </c>
+      <c r="F349" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -5318,6 +7416,12 @@
       <c r="D350" t="n">
         <v>46.66666666666666</v>
       </c>
+      <c r="E350" t="n">
+        <v>0.4414581836648109</v>
+      </c>
+      <c r="F350" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -5332,6 +7436,12 @@
       <c r="D351" t="n">
         <v>33.95294117647059</v>
       </c>
+      <c r="E351" t="n">
+        <v>0.5684149404500352</v>
+      </c>
+      <c r="F351" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -5346,6 +7456,12 @@
       <c r="D352" t="n">
         <v>26.36363636363636</v>
       </c>
+      <c r="E352" t="n">
+        <v>0.9427876121598738</v>
+      </c>
+      <c r="F352" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -5360,6 +7476,12 @@
       <c r="D353" t="n">
         <v>31.57894736842105</v>
       </c>
+      <c r="E353" t="n">
+        <v>0.1622997234409144</v>
+      </c>
+      <c r="F353" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -5374,6 +7496,12 @@
       <c r="D354" t="n">
         <v>29.7029702970297</v>
       </c>
+      <c r="E354" t="n">
+        <v>-0.9899122858019986</v>
+      </c>
+      <c r="F354" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -5388,6 +7516,12 @@
       <c r="D355" t="n">
         <v>33.33333333333334</v>
       </c>
+      <c r="E355" t="n">
+        <v>0.9405295766287635</v>
+      </c>
+      <c r="F355" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -5402,6 +7536,12 @@
       <c r="D356" t="n">
         <v>28.4</v>
       </c>
+      <c r="E356" t="n">
+        <v>-0.1253356260964291</v>
+      </c>
+      <c r="F356" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -5416,6 +7556,12 @@
       <c r="D357" t="n">
         <v>31</v>
       </c>
+      <c r="E357" t="n">
+        <v>-0.404037645323065</v>
+      </c>
+      <c r="F357" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -5430,6 +7576,12 @@
       <c r="D358" t="n">
         <v>44.15277777777778</v>
       </c>
+      <c r="E358" t="n">
+        <v>0.1696560286708925</v>
+      </c>
+      <c r="F358" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -5444,6 +7596,12 @@
       <c r="D359" t="n">
         <v>28.07017543859649</v>
       </c>
+      <c r="E359" t="n">
+        <v>0.2027431529889751</v>
+      </c>
+      <c r="F359" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -5458,6 +7616,12 @@
       <c r="D360" t="n">
         <v>29.09090909090909</v>
       </c>
+      <c r="E360" t="n">
+        <v>-0.7288050810991762</v>
+      </c>
+      <c r="F360" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -5472,6 +7636,12 @@
       <c r="D361" t="n">
         <v>27.27272727272727</v>
       </c>
+      <c r="E361" t="n">
+        <v>0.8423379532957915</v>
+      </c>
+      <c r="F361" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -5486,6 +7656,12 @@
       <c r="D362" t="n">
         <v>30.47619047619047</v>
       </c>
+      <c r="E362" t="n">
+        <v>-0.8074024034540006</v>
+      </c>
+      <c r="F362" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -5500,6 +7676,12 @@
       <c r="D363" t="n">
         <v>32.67326732673267</v>
       </c>
+      <c r="E363" t="n">
+        <v>0.9512737451226221</v>
+      </c>
+      <c r="F363" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -5514,6 +7696,12 @@
       <c r="D364" t="n">
         <v>34.73684210526316</v>
       </c>
+      <c r="E364" t="n">
+        <v>-0.1783633873954648</v>
+      </c>
+      <c r="F364" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -5528,6 +7716,12 @@
       <c r="D365" t="n">
         <v>30.55555555555556</v>
       </c>
+      <c r="E365" t="n">
+        <v>-0.7580845522154663</v>
+      </c>
+      <c r="F365" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -5542,6 +7736,12 @@
       <c r="D366" t="n">
         <v>33.59223300970874</v>
       </c>
+      <c r="E366" t="n">
+        <v>0.8222118383409271</v>
+      </c>
+      <c r="F366" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -5556,6 +7756,12 @@
       <c r="D367" t="n">
         <v>44.87179487179487</v>
       </c>
+      <c r="E367" t="n">
+        <v>0.7767555094140483</v>
+      </c>
+      <c r="F367" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -5570,6 +7776,12 @@
       <c r="D368" t="n">
         <v>30.41666666666667</v>
       </c>
+      <c r="E368" t="n">
+        <v>-0.8410708600072342</v>
+      </c>
+      <c r="F368" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -5584,6 +7796,12 @@
       <c r="D369" t="n">
         <v>36.6</v>
       </c>
+      <c r="E369" t="n">
+        <v>-0.8908041440768614</v>
+      </c>
+      <c r="F369" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -5598,6 +7816,12 @@
       <c r="D370" t="n">
         <v>32.85714285714285</v>
       </c>
+      <c r="E370" t="n">
+        <v>0.991616251880175</v>
+      </c>
+      <c r="F370" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -5612,6 +7836,12 @@
       <c r="D371" t="n">
         <v>25.51724137931035</v>
       </c>
+      <c r="E371" t="n">
+        <v>0.3750958302022671</v>
+      </c>
+      <c r="F371" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -5626,6 +7856,12 @@
       <c r="D372" t="n">
         <v>38.46153846153846</v>
       </c>
+      <c r="E372" t="n">
+        <v>0.6906783154810628</v>
+      </c>
+      <c r="F372" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -5640,6 +7876,12 @@
       <c r="D373" t="n">
         <v>35.11450381679389</v>
       </c>
+      <c r="E373" t="n">
+        <v>-0.5286289969698663</v>
+      </c>
+      <c r="F373" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -5654,6 +7896,12 @@
       <c r="D374" t="n">
         <v>42.13675213675214</v>
       </c>
+      <c r="E374" t="n">
+        <v>-0.9624934105890127</v>
+      </c>
+      <c r="F374" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -5668,6 +7916,12 @@
       <c r="D375" t="n">
         <v>28.53757225433526</v>
       </c>
+      <c r="E375" t="n">
+        <v>-0.2602087286871549</v>
+      </c>
+      <c r="F375" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -5682,6 +7936,12 @@
       <c r="D376" t="n">
         <v>51</v>
       </c>
+      <c r="E376" t="n">
+        <v>0.6702291758433747</v>
+      </c>
+      <c r="F376" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -5696,6 +7956,12 @@
       <c r="D377" t="n">
         <v>32.30246913580247</v>
       </c>
+      <c r="E377" t="n">
+        <v>0.7748909782577089</v>
+      </c>
+      <c r="F377" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -5710,6 +7976,12 @@
       <c r="D378" t="n">
         <v>32.40123456790123</v>
       </c>
+      <c r="E378" t="n">
+        <v>0.8334423504237026</v>
+      </c>
+      <c r="F378" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -5724,6 +7996,12 @@
       <c r="D379" t="n">
         <v>32.89473684210526</v>
       </c>
+      <c r="E379" t="n">
+        <v>0.99577226832378</v>
+      </c>
+      <c r="F379" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -5738,6 +8016,12 @@
       <c r="D380" t="n">
         <v>30.32571428571429</v>
       </c>
+      <c r="E380" t="n">
+        <v>-0.8867250570814692</v>
+      </c>
+      <c r="F380" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -5752,6 +8036,12 @@
       <c r="D381" t="n">
         <v>25.31914893617021</v>
       </c>
+      <c r="E381" t="n">
+        <v>0.1853300374978686</v>
+      </c>
+      <c r="F381" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -5766,6 +8056,12 @@
       <c r="D382" t="n">
         <v>41.38888888888889</v>
       </c>
+      <c r="E382" t="n">
+        <v>-0.5211385181263918</v>
+      </c>
+      <c r="F382" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -5780,6 +8076,12 @@
       <c r="D383" t="n">
         <v>60.24096385542169</v>
       </c>
+      <c r="E383" t="n">
+        <v>-0.52328679703818</v>
+      </c>
+      <c r="F383" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -5794,6 +8096,12 @@
       <c r="D384" t="n">
         <v>66.36363636363636</v>
       </c>
+      <c r="E384" t="n">
+        <v>-0.3803647312587399</v>
+      </c>
+      <c r="F384" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -5808,6 +8116,12 @@
       <c r="D385" t="n">
         <v>52.71428571428572</v>
       </c>
+      <c r="E385" t="n">
+        <v>0.6386860141910382</v>
+      </c>
+      <c r="F385" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -5822,6 +8136,12 @@
       <c r="D386" t="n">
         <v>45.61111111111111</v>
       </c>
+      <c r="E386" t="n">
+        <v>0.9983174491104893</v>
+      </c>
+      <c r="F386" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -5836,6 +8156,12 @@
       <c r="D387" t="n">
         <v>53.125</v>
       </c>
+      <c r="E387" t="n">
+        <v>0.2783493488645977</v>
+      </c>
+      <c r="F387" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -5850,6 +8176,12 @@
       <c r="D388" t="n">
         <v>34.16</v>
       </c>
+      <c r="E388" t="n">
+        <v>0.3871321685345126</v>
+      </c>
+      <c r="F388" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -5864,6 +8196,12 @@
       <c r="D389" t="n">
         <v>37.91666666666666</v>
       </c>
+      <c r="E389" t="n">
+        <v>0.2158427316513198</v>
+      </c>
+      <c r="F389" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -5878,6 +8216,12 @@
       <c r="D390" t="n">
         <v>49.47368421052632</v>
       </c>
+      <c r="E390" t="n">
+        <v>-0.711617810868202</v>
+      </c>
+      <c r="F390" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -5892,6 +8236,12 @@
       <c r="D391" t="n">
         <v>47.5</v>
       </c>
+      <c r="E391" t="n">
+        <v>-0.3673053491341913</v>
+      </c>
+      <c r="F391" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -5906,6 +8256,12 @@
       <c r="D392" t="n">
         <v>45.23809523809524</v>
       </c>
+      <c r="E392" t="n">
+        <v>0.9507969245127809</v>
+      </c>
+      <c r="F392" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -5920,6 +8276,12 @@
       <c r="D393" t="n">
         <v>42.43478260869565</v>
       </c>
+      <c r="E393" t="n">
+        <v>-0.9997289914799931</v>
+      </c>
+      <c r="F393" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -5934,6 +8296,12 @@
       <c r="D394" t="n">
         <v>36.66666666666666</v>
       </c>
+      <c r="E394" t="n">
+        <v>-0.8585552479838888</v>
+      </c>
+      <c r="F394" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -5948,6 +8316,12 @@
       <c r="D395" t="n">
         <v>41.03448275862069</v>
       </c>
+      <c r="E395" t="n">
+        <v>-0.1925678073849641</v>
+      </c>
+      <c r="F395" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -5962,6 +8336,12 @@
       <c r="D396" t="n">
         <v>36.5</v>
       </c>
+      <c r="E396" t="n">
+        <v>-0.9317168878547055</v>
+      </c>
+      <c r="F396" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -5976,6 +8356,12 @@
       <c r="D397" t="n">
         <v>30.25</v>
       </c>
+      <c r="E397" t="n">
+        <v>-0.9191536942035773</v>
+      </c>
+      <c r="F397" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -5990,6 +8376,12 @@
       <c r="D398" t="n">
         <v>44.64285714285715</v>
       </c>
+      <c r="E398" t="n">
+        <v>0.613559145619861</v>
+      </c>
+      <c r="F398" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -6004,6 +8396,12 @@
       <c r="D399" t="n">
         <v>52.29166666666666</v>
       </c>
+      <c r="E399" t="n">
+        <v>0.8980905008974973</v>
+      </c>
+      <c r="F399" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -6018,6 +8416,12 @@
       <c r="D400" t="n">
         <v>52.29166666666666</v>
       </c>
+      <c r="E400" t="n">
+        <v>0.8980905008974973</v>
+      </c>
+      <c r="F400" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -6032,6 +8436,12 @@
       <c r="D401" t="n">
         <v>40.625</v>
       </c>
+      <c r="E401" t="n">
+        <v>0.2140356519137885</v>
+      </c>
+      <c r="F401" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -6046,6 +8456,12 @@
       <c r="D402" t="n">
         <v>43.125</v>
       </c>
+      <c r="E402" t="n">
+        <v>-0.7560763564306933</v>
+      </c>
+      <c r="F402" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -6060,6 +8476,12 @@
       <c r="D403" t="n">
         <v>35.71428571428572</v>
       </c>
+      <c r="E403" t="n">
+        <v>-0.9155070638063744</v>
+      </c>
+      <c r="F403" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -6074,6 +8496,12 @@
       <c r="D404" t="n">
         <v>44.11764705882353</v>
       </c>
+      <c r="E404" t="n">
+        <v>0.1349370276251922</v>
+      </c>
+      <c r="F404" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -6088,6 +8516,12 @@
       <c r="D405" t="n">
         <v>52.06896551724138</v>
       </c>
+      <c r="E405" t="n">
+        <v>0.9730503667843077</v>
+      </c>
+      <c r="F405" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -6102,6 +8536,12 @@
       <c r="D406" t="n">
         <v>51.66666666666666</v>
       </c>
+      <c r="E406" t="n">
+        <v>0.9856503156274583</v>
+      </c>
+      <c r="F406" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -6116,6 +8556,12 @@
       <c r="D407" t="n">
         <v>31.2</v>
       </c>
+      <c r="E407" t="n">
+        <v>-0.2142525402958877</v>
+      </c>
+      <c r="F407" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -6130,6 +8576,12 @@
       <c r="D408" t="n">
         <v>45.14285714285715</v>
       </c>
+      <c r="E408" t="n">
+        <v>0.9170265921905256</v>
+      </c>
+      <c r="F408" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -6144,6 +8596,12 @@
       <c r="D409" t="n">
         <v>34.8936170212766</v>
       </c>
+      <c r="E409" t="n">
+        <v>-0.3298057752033151</v>
+      </c>
+      <c r="F409" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -6158,6 +8616,12 @@
       <c r="D410" t="n">
         <v>41.25</v>
       </c>
+      <c r="E410" t="n">
+        <v>-0.397963120556671</v>
+      </c>
+      <c r="F410" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -6172,6 +8636,12 @@
       <c r="D411" t="n">
         <v>48.97058823529412</v>
       </c>
+      <c r="E411" t="n">
+        <v>-0.9621798422989879</v>
+      </c>
+      <c r="F411" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -6186,6 +8656,12 @@
       <c r="D412" t="n">
         <v>33.90909090909091</v>
       </c>
+      <c r="E412" t="n">
+        <v>0.6039344382426391</v>
+      </c>
+      <c r="F412" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -6200,6 +8676,12 @@
       <c r="D413" t="n">
         <v>30</v>
       </c>
+      <c r="E413" t="n">
+        <v>-0.9880316240928618</v>
+      </c>
+      <c r="F413" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -6214,6 +8696,12 @@
       <c r="D414" t="n">
         <v>47.61904761904762</v>
       </c>
+      <c r="E414" t="n">
+        <v>-0.475170517793463</v>
+      </c>
+      <c r="F414" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -6228,6 +8716,12 @@
       <c r="D415" t="n">
         <v>48.78048780487805</v>
       </c>
+      <c r="E415" t="n">
+        <v>-0.9963212940439318</v>
+      </c>
+      <c r="F415" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -6242,6 +8736,12 @@
       <c r="D416" t="n">
         <v>29.17808219178082</v>
       </c>
+      <c r="E416" t="n">
+        <v>-0.7856513879077592</v>
+      </c>
+      <c r="F416" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -6256,6 +8756,12 @@
       <c r="D417" t="n">
         <v>38.59649122807018</v>
       </c>
+      <c r="E417" t="n">
+        <v>0.7816952212850625</v>
+      </c>
+      <c r="F417" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -6270,6 +8776,12 @@
       <c r="D418" t="n">
         <v>28.75</v>
       </c>
+      <c r="E418" t="n">
+        <v>-0.4579307192868114</v>
+      </c>
+      <c r="F418" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -6284,6 +8796,12 @@
       <c r="D419" t="n">
         <v>41.66666666666666</v>
       </c>
+      <c r="E419" t="n">
+        <v>-0.7352003292894852</v>
+      </c>
+      <c r="F419" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -6298,6 +8816,12 @@
       <c r="D420" t="n">
         <v>53.57142857142857</v>
       </c>
+      <c r="E420" t="n">
+        <v>-0.1636145381782299</v>
+      </c>
+      <c r="F420" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -6312,6 +8836,12 @@
       <c r="D421" t="n">
         <v>27.53623188405797</v>
       </c>
+      <c r="E421" t="n">
+        <v>0.6728850833224013</v>
+      </c>
+      <c r="F421" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -6326,6 +8856,12 @@
       <c r="D422" t="n">
         <v>32.28346456692913</v>
       </c>
+      <c r="E422" t="n">
+        <v>0.7627390792707407</v>
+      </c>
+      <c r="F422" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -6340,6 +8876,12 @@
       <c r="D423" t="n">
         <v>29.05405405405405</v>
       </c>
+      <c r="E423" t="n">
+        <v>-0.7030804579741144</v>
+      </c>
+      <c r="F423" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -6354,6 +8896,12 @@
       <c r="D424" t="n">
         <v>39.1304347826087</v>
       </c>
+      <c r="E424" t="n">
+        <v>0.9902893440868434</v>
+      </c>
+      <c r="F424" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -6368,6 +8916,12 @@
       <c r="D425" t="n">
         <v>43.22766570605187</v>
       </c>
+      <c r="E425" t="n">
+        <v>-0.6850202134235917</v>
+      </c>
+      <c r="F425" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -6382,6 +8936,12 @@
       <c r="D426" t="n">
         <v>45.5</v>
       </c>
+      <c r="E426" t="n">
+        <v>0.9985908724117705</v>
+      </c>
+      <c r="F426" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -6396,6 +8956,12 @@
       <c r="D427" t="n">
         <v>48.57142857142857</v>
       </c>
+      <c r="E427" t="n">
+        <v>-0.9924133992546977</v>
+      </c>
+      <c r="F427" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -6410,6 +8976,12 @@
       <c r="D428" t="n">
         <v>38.88888888888889</v>
       </c>
+      <c r="E428" t="n">
+        <v>0.9282860810506389</v>
+      </c>
+      <c r="F428" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -6424,6 +8996,12 @@
       <c r="D429" t="n">
         <v>48</v>
       </c>
+      <c r="E429" t="n">
+        <v>-0.7682546613236668</v>
+      </c>
+      <c r="F429" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -6438,6 +9016,12 @@
       <c r="D430" t="n">
         <v>38.75</v>
       </c>
+      <c r="E430" t="n">
+        <v>0.8678648045849774</v>
+      </c>
+      <c r="F430" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -6452,6 +9036,12 @@
       <c r="D431" t="n">
         <v>31.25</v>
       </c>
+      <c r="E431" t="n">
+        <v>-0.165166212373579</v>
+      </c>
+      <c r="F431" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -6466,6 +9056,12 @@
       <c r="D432" t="n">
         <v>46</v>
       </c>
+      <c r="E432" t="n">
+        <v>0.9017883476488092</v>
+      </c>
+      <c r="F432" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -6480,6 +9076,12 @@
       <c r="D433" t="n">
         <v>30.18518518518519</v>
       </c>
+      <c r="E433" t="n">
+        <v>-0.9427363302899051</v>
+      </c>
+      <c r="F433" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -6494,6 +9096,12 @@
       <c r="D434" t="n">
         <v>33</v>
       </c>
+      <c r="E434" t="n">
+        <v>0.9999118601072672</v>
+      </c>
+      <c r="F434" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -6508,6 +9116,12 @@
       <c r="D435" t="n">
         <v>28.46774193548387</v>
       </c>
+      <c r="E435" t="n">
+        <v>-0.1922045143693956</v>
+      </c>
+      <c r="F435" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -6522,6 +9136,12 @@
       <c r="D436" t="n">
         <v>29.6875</v>
       </c>
+      <c r="E436" t="n">
+        <v>-0.9876020617700564</v>
+      </c>
+      <c r="F436" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -6536,6 +9156,12 @@
       <c r="D437" t="n">
         <v>23.20779220779221</v>
       </c>
+      <c r="E437" t="n">
+        <v>-0.9379406675595412</v>
+      </c>
+      <c r="F437" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -6550,6 +9176,12 @@
       <c r="D438" t="n">
         <v>30</v>
       </c>
+      <c r="E438" t="n">
+        <v>-0.9880316240928618</v>
+      </c>
+      <c r="F438" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -6564,6 +9196,12 @@
       <c r="D439" t="n">
         <v>30.89855072463768</v>
       </c>
+      <c r="E439" t="n">
+        <v>-0.4946011082896373</v>
+      </c>
+      <c r="F439" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -6578,6 +9216,12 @@
       <c r="D440" t="n">
         <v>30.89855072463768</v>
       </c>
+      <c r="E440" t="n">
+        <v>-0.4946011082896373</v>
+      </c>
+      <c r="F440" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -6592,6 +9236,12 @@
       <c r="D441" t="n">
         <v>36.66666666666666</v>
       </c>
+      <c r="E441" t="n">
+        <v>-0.8585552479838888</v>
+      </c>
+      <c r="F441" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -6606,6 +9256,12 @@
       <c r="D442" t="n">
         <v>32.92753623188405</v>
       </c>
+      <c r="E442" t="n">
+        <v>0.9982489826158107</v>
+      </c>
+      <c r="F442" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -6620,6 +9276,12 @@
       <c r="D443" t="n">
         <v>34.28571428571428</v>
       </c>
+      <c r="E443" t="n">
+        <v>0.2684705150095526</v>
+      </c>
+      <c r="F443" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -6634,6 +9296,12 @@
       <c r="D444" t="n">
         <v>33.57142857142857</v>
       </c>
+      <c r="E444" t="n">
+        <v>0.8338745572362449</v>
+      </c>
+      <c r="F444" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -6648,6 +9316,12 @@
       <c r="D445" t="n">
         <v>66.425</v>
       </c>
+      <c r="E445" t="n">
+        <v>-0.4363645502323307</v>
+      </c>
+      <c r="F445" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -6662,6 +9336,12 @@
       <c r="D446" t="n">
         <v>39.46052631578947</v>
       </c>
+      <c r="E446" t="n">
+        <v>0.9818873051558241</v>
+      </c>
+      <c r="F446" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -6676,6 +9356,12 @@
       <c r="D447" t="n">
         <v>37.5</v>
       </c>
+      <c r="E447" t="n">
+        <v>-0.1977987996364623</v>
+      </c>
+      <c r="F447" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -6690,6 +9376,12 @@
       <c r="D448" t="n">
         <v>33.59223300970874</v>
       </c>
+      <c r="E448" t="n">
+        <v>0.8222118383409271</v>
+      </c>
+      <c r="F448" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -6704,6 +9396,12 @@
       <c r="D449" t="n">
         <v>29.03225806451613</v>
       </c>
+      <c r="E449" t="n">
+        <v>-0.6874153344163036</v>
+      </c>
+      <c r="F449" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -6718,6 +9416,12 @@
       <c r="D450" t="n">
         <v>46.10951008645533</v>
       </c>
+      <c r="E450" t="n">
+        <v>0.849153114903015</v>
+      </c>
+      <c r="F450" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -6732,6 +9436,12 @@
       <c r="D451" t="n">
         <v>111.1111111111111</v>
       </c>
+      <c r="E451" t="n">
+        <v>-0.9149436345346486</v>
+      </c>
+      <c r="F451" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -6746,6 +9456,12 @@
       <c r="D452" t="n">
         <v>32.71428571428572</v>
       </c>
+      <c r="E452" t="n">
+        <v>0.9631179706634697</v>
+      </c>
+      <c r="F452" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -6760,6 +9476,12 @@
       <c r="D453" t="n">
         <v>25.23275862068965</v>
       </c>
+      <c r="E453" t="n">
+        <v>0.09985072171562319</v>
+      </c>
+      <c r="F453" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -6774,6 +9496,12 @@
       <c r="D454" t="n">
         <v>50</v>
       </c>
+      <c r="E454" t="n">
+        <v>-0.2623748537039288</v>
+      </c>
+      <c r="F454" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -6788,6 +9516,12 @@
       <c r="D455" t="n">
         <v>39.73684210526316</v>
       </c>
+      <c r="E455" t="n">
+        <v>0.89295267392835</v>
+      </c>
+      <c r="F455" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -6802,6 +9536,12 @@
       <c r="D456" t="n">
         <v>41.25</v>
       </c>
+      <c r="E456" t="n">
+        <v>-0.397963120556671</v>
+      </c>
+      <c r="F456" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -6816,6 +9556,12 @@
       <c r="D457" t="n">
         <v>50.38095238095238</v>
       </c>
+      <c r="E457" t="n">
+        <v>0.1152134952763465</v>
+      </c>
+      <c r="F457" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -6830,6 +9576,12 @@
       <c r="D458" t="n">
         <v>54.75</v>
       </c>
+      <c r="E458" t="n">
+        <v>-0.9741494532413135</v>
+      </c>
+      <c r="F458" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -6844,6 +9596,12 @@
       <c r="D459" t="n">
         <v>29.72972972972973</v>
       </c>
+      <c r="E459" t="n">
+        <v>-0.9933487509714088</v>
+      </c>
+      <c r="F459" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -6858,6 +9616,12 @@
       <c r="D460" t="n">
         <v>44.13793103448276</v>
       </c>
+      <c r="E460" t="n">
+        <v>0.1550063531576545</v>
+      </c>
+      <c r="F460" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -6872,6 +9636,12 @@
       <c r="D461" t="n">
         <v>38.57142857142857</v>
       </c>
+      <c r="E461" t="n">
+        <v>0.7658207724688868</v>
+      </c>
+      <c r="F461" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -6886,6 +9656,12 @@
       <c r="D462" t="n">
         <v>31.11111111111111</v>
       </c>
+      <c r="E462" t="n">
+        <v>-0.3001171135904562</v>
+      </c>
+      <c r="F462" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -6900,6 +9676,12 @@
       <c r="D463" t="n">
         <v>46.96969696969697</v>
       </c>
+      <c r="E463" t="n">
+        <v>0.1535825599200187</v>
+      </c>
+      <c r="F463" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -6914,6 +9696,12 @@
       <c r="D464" t="n">
         <v>29.6875</v>
       </c>
+      <c r="E464" t="n">
+        <v>-0.9876020617700564</v>
+      </c>
+      <c r="F464" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -6928,6 +9716,12 @@
       <c r="D465" t="n">
         <v>40</v>
       </c>
+      <c r="E465" t="n">
+        <v>0.7451131604793488</v>
+      </c>
+      <c r="F465" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -6942,6 +9736,12 @@
       <c r="D466" t="n">
         <v>31.4</v>
       </c>
+      <c r="E466" t="n">
+        <v>-0.0159258626001018</v>
+      </c>
+      <c r="F466" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -6956,6 +9756,12 @@
       <c r="D467" t="n">
         <v>30</v>
       </c>
+      <c r="E467" t="n">
+        <v>-0.9880316240928618</v>
+      </c>
+      <c r="F467" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -6970,6 +9776,12 @@
       <c r="D468" t="n">
         <v>37.5</v>
       </c>
+      <c r="E468" t="n">
+        <v>-0.1977987996364623</v>
+      </c>
+      <c r="F468" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -6984,6 +9796,12 @@
       <c r="D469" t="n">
         <v>44.5</v>
       </c>
+      <c r="E469" t="n">
+        <v>0.4948853175526281</v>
+      </c>
+      <c r="F469" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -6998,6 +9816,12 @@
       <c r="D470" t="n">
         <v>35</v>
       </c>
+      <c r="E470" t="n">
+        <v>-0.428182669496151</v>
+      </c>
+      <c r="F470" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -7012,6 +9836,12 @@
       <c r="D471" t="n">
         <v>35.48387096774194</v>
       </c>
+      <c r="E471" t="n">
+        <v>-0.799433580204136</v>
+      </c>
+      <c r="F471" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -7026,6 +9856,12 @@
       <c r="D472" t="n">
         <v>33.67346938775511</v>
       </c>
+      <c r="E472" t="n">
+        <v>0.773312887258672</v>
+      </c>
+      <c r="F472" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -7040,6 +9876,12 @@
       <c r="D473" t="n">
         <v>28.63013698630137</v>
       </c>
+      <c r="E473" t="n">
+        <v>-0.3483432807005264</v>
+      </c>
+      <c r="F473" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -7054,6 +9896,12 @@
       <c r="D474" t="n">
         <v>56.25</v>
       </c>
+      <c r="E474" t="n">
+        <v>-0.2942472117115055</v>
+      </c>
+      <c r="F474" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -7068,6 +9916,12 @@
       <c r="D475" t="n">
         <v>58.125</v>
       </c>
+      <c r="E475" t="n">
+        <v>0.9999846768971812</v>
+      </c>
+      <c r="F475" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -7082,6 +9936,12 @@
       <c r="D476" t="n">
         <v>23.57142857142857</v>
       </c>
+      <c r="E476" t="n">
+        <v>-0.9999550303434078</v>
+      </c>
+      <c r="F476" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -7096,6 +9956,12 @@
       <c r="D477" t="n">
         <v>38.47826086956522</v>
       </c>
+      <c r="E477" t="n">
+        <v>0.7026741960410798</v>
+      </c>
+      <c r="F477" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -7110,6 +9976,12 @@
       <c r="D478" t="n">
         <v>22.5531914893617</v>
       </c>
+      <c r="E478" t="n">
+        <v>-0.5329159577902858</v>
+      </c>
+      <c r="F478" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -7124,6 +9996,12 @@
       <c r="D479" t="n">
         <v>25</v>
       </c>
+      <c r="E479" t="n">
+        <v>-0.132351750097773</v>
+      </c>
+      <c r="F479" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -7138,6 +10016,12 @@
       <c r="D480" t="n">
         <v>39.47368421052632</v>
       </c>
+      <c r="E480" t="n">
+        <v>0.9793094090311945</v>
+      </c>
+      <c r="F480" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -7152,6 +10036,12 @@
       <c r="D481" t="n">
         <v>44.5</v>
       </c>
+      <c r="E481" t="n">
+        <v>0.4948853175526281</v>
+      </c>
+      <c r="F481" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -7166,6 +10056,12 @@
       <c r="D482" t="n">
         <v>30.95238095238095</v>
       </c>
+      <c r="E482" t="n">
+        <v>-0.4471223388056394</v>
+      </c>
+      <c r="F482" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -7180,6 +10076,12 @@
       <c r="D483" t="n">
         <v>31.03448275862069</v>
       </c>
+      <c r="E483" t="n">
+        <v>-0.3722608672557353</v>
+      </c>
+      <c r="F483" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -7194,6 +10096,12 @@
       <c r="D484" t="n">
         <v>47.91666666666666</v>
       </c>
+      <c r="E484" t="n">
+        <v>-0.7123050130400819</v>
+      </c>
+      <c r="F484" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -7208,6 +10116,12 @@
       <c r="D485" t="n">
         <v>38.18181818181818</v>
       </c>
+      <c r="E485" t="n">
+        <v>0.4641779902369369</v>
+      </c>
+      <c r="F485" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -7222,6 +10136,12 @@
       <c r="D486" t="n">
         <v>32</v>
       </c>
+      <c r="E486" t="n">
+        <v>0.5514266812416906</v>
+      </c>
+      <c r="F486" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -7236,6 +10156,12 @@
       <c r="D487" t="n">
         <v>32.7</v>
       </c>
+      <c r="E487" t="n">
+        <v>0.9591758329530804</v>
+      </c>
+      <c r="F487" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -7250,6 +10176,12 @@
       <c r="D488" t="n">
         <v>38.06451612903226</v>
       </c>
+      <c r="E488" t="n">
+        <v>0.35732691841208</v>
+      </c>
+      <c r="F488" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -7264,6 +10196,12 @@
       <c r="D489" t="n">
         <v>36.3030303030303</v>
       </c>
+      <c r="E489" t="n">
+        <v>-0.9847761568003609</v>
+      </c>
+      <c r="F489" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -7278,6 +10216,12 @@
       <c r="D490" t="n">
         <v>30.85106382978723</v>
       </c>
+      <c r="E490" t="n">
+        <v>-0.5352998541115467</v>
+      </c>
+      <c r="F490" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -7292,6 +10236,12 @@
       <c r="D491" t="n">
         <v>60</v>
       </c>
+      <c r="E491" t="n">
+        <v>-0.3048106211022167</v>
+      </c>
+      <c r="F491" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -7306,6 +10256,12 @@
       <c r="D492" t="n">
         <v>48.61111111111111</v>
       </c>
+      <c r="E492" t="n">
+        <v>-0.9965096403822424</v>
+      </c>
+      <c r="F492" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -7320,6 +10276,12 @@
       <c r="D493" t="n">
         <v>29.35294117647059</v>
       </c>
+      <c r="E493" t="n">
+        <v>-0.8813005299973875</v>
+      </c>
+      <c r="F493" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -7334,6 +10296,12 @@
       <c r="D494" t="n">
         <v>40</v>
       </c>
+      <c r="E494" t="n">
+        <v>0.7451131604793488</v>
+      </c>
+      <c r="F494" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -7348,6 +10316,12 @@
       <c r="D495" t="n">
         <v>40.32258064516129</v>
       </c>
+      <c r="E495" t="n">
+        <v>0.4952511066597252</v>
+      </c>
+      <c r="F495" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -7362,6 +10336,12 @@
       <c r="D496" t="n">
         <v>37</v>
       </c>
+      <c r="E496" t="n">
+        <v>-0.6435381333569995</v>
+      </c>
+      <c r="F496" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -7376,6 +10356,12 @@
       <c r="D497" t="n">
         <v>41.30434782608695</v>
       </c>
+      <c r="E497" t="n">
+        <v>-0.4472097677221027</v>
+      </c>
+      <c r="F497" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -7390,6 +10376,12 @@
       <c r="D498" t="n">
         <v>35.71428571428572</v>
       </c>
+      <c r="E498" t="n">
+        <v>-0.9155070638063744</v>
+      </c>
+      <c r="F498" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -7404,6 +10396,12 @@
       <c r="D499" t="n">
         <v>33.92857142857143</v>
       </c>
+      <c r="E499" t="n">
+        <v>0.5882941938216167</v>
+      </c>
+      <c r="F499" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -7418,6 +10416,12 @@
       <c r="D500" t="n">
         <v>43.7037037037037</v>
       </c>
+      <c r="E500" t="n">
+        <v>-0.275003599800771</v>
+      </c>
+      <c r="F500" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -7432,6 +10436,12 @@
       <c r="D501" t="n">
         <v>38.75</v>
       </c>
+      <c r="E501" t="n">
+        <v>0.8678648045849774</v>
+      </c>
+      <c r="F501" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -7446,6 +10456,12 @@
       <c r="D502" t="n">
         <v>32.51219512195122</v>
       </c>
+      <c r="E502" t="n">
+        <v>0.8895086047620938</v>
+      </c>
+      <c r="F502" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -7460,6 +10476,12 @@
       <c r="D503" t="n">
         <v>39.5</v>
       </c>
+      <c r="E503" t="n">
+        <v>0.9736454556949781</v>
+      </c>
+      <c r="F503" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -7474,6 +10496,12 @@
       <c r="D504" t="n">
         <v>31.48148148148148</v>
       </c>
+      <c r="E504" t="n">
+        <v>0.06550800247825639</v>
+      </c>
+      <c r="F504" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -7488,6 +10516,12 @@
       <c r="D505" t="n">
         <v>37.53846153846154</v>
       </c>
+      <c r="E505" t="n">
+        <v>-0.1599601713408731</v>
+      </c>
+      <c r="F505" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -7502,6 +10536,12 @@
       <c r="D506" t="n">
         <v>34.38888888888889</v>
       </c>
+      <c r="E506" t="n">
+        <v>0.1678322359245849</v>
+      </c>
+      <c r="F506" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -7516,6 +10556,12 @@
       <c r="D507" t="n">
         <v>35.65217391304348</v>
       </c>
+      <c r="E507" t="n">
+        <v>-0.8887700431950436</v>
+      </c>
+      <c r="F507" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -7530,6 +10576,12 @@
       <c r="D508" t="n">
         <v>42.1875</v>
       </c>
+      <c r="E508" t="n">
+        <v>-0.9750165430796872</v>
+      </c>
+      <c r="F508" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -7544,6 +10596,12 @@
       <c r="D509" t="n">
         <v>25.87719298245614</v>
       </c>
+      <c r="E509" t="n">
+        <v>0.6775686993906961</v>
+      </c>
+      <c r="F509" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -7558,6 +10616,12 @@
       <c r="D510" t="n">
         <v>36.76315789473684</v>
       </c>
+      <c r="E510" t="n">
+        <v>-0.8051651840289875</v>
+      </c>
+      <c r="F510" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -7572,6 +10636,12 @@
       <c r="D511" t="n">
         <v>28.07692307692308</v>
       </c>
+      <c r="E511" t="n">
+        <v>0.1961310845925819</v>
+      </c>
+      <c r="F511" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -7586,6 +10656,12 @@
       <c r="D512" t="n">
         <v>28.07017543859649</v>
       </c>
+      <c r="E512" t="n">
+        <v>0.2027431529889751</v>
+      </c>
+      <c r="F512" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -7600,6 +10676,12 @@
       <c r="D513" t="n">
         <v>36.76470588235294</v>
       </c>
+      <c r="E513" t="n">
+        <v>-0.8042461847004519</v>
+      </c>
+      <c r="F513" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -7614,6 +10696,12 @@
       <c r="D514" t="n">
         <v>35.90909090909091</v>
       </c>
+      <c r="E514" t="n">
+        <v>-0.9760663696225885</v>
+      </c>
+      <c r="F514" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -7628,6 +10716,12 @@
       <c r="D515" t="n">
         <v>57.14285714285715</v>
       </c>
+      <c r="E515" t="n">
+        <v>0.5598372552220318</v>
+      </c>
+      <c r="F515" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -7642,6 +10736,12 @@
       <c r="D516" t="n">
         <v>45</v>
       </c>
+      <c r="E516" t="n">
+        <v>0.8509035245341184</v>
+      </c>
+      <c r="F516" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -7656,6 +10756,12 @@
       <c r="D517" t="n">
         <v>36.15384615384615</v>
       </c>
+      <c r="E517" t="n">
+        <v>-0.9996741109749476</v>
+      </c>
+      <c r="F517" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -7670,6 +10776,12 @@
       <c r="D518" t="n">
         <v>33.25925925925926</v>
       </c>
+      <c r="E518" t="n">
+        <v>0.9630912602754822</v>
+      </c>
+      <c r="F518" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -7684,6 +10796,12 @@
       <c r="D519" t="n">
         <v>34.45454545454545</v>
       </c>
+      <c r="E519" t="n">
+        <v>0.1027918495217874</v>
+      </c>
+      <c r="F519" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -7698,6 +10816,12 @@
       <c r="D520" t="n">
         <v>45</v>
       </c>
+      <c r="E520" t="n">
+        <v>0.8509035245341184</v>
+      </c>
+      <c r="F520" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -7712,6 +10836,12 @@
       <c r="D521" t="n">
         <v>36.15384615384615</v>
       </c>
+      <c r="E521" t="n">
+        <v>-0.9996741109749476</v>
+      </c>
+      <c r="F521" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -7726,6 +10856,12 @@
       <c r="D522" t="n">
         <v>33.25925925925926</v>
       </c>
+      <c r="E522" t="n">
+        <v>0.9630912602754822</v>
+      </c>
+      <c r="F522" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -7740,6 +10876,12 @@
       <c r="D523" t="n">
         <v>34.45454545454545</v>
       </c>
+      <c r="E523" t="n">
+        <v>0.1027918495217874</v>
+      </c>
+      <c r="F523" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -7754,6 +10896,12 @@
       <c r="D524" t="n">
         <v>26.66666666666667</v>
       </c>
+      <c r="E524" t="n">
+        <v>0.999320345780098</v>
+      </c>
+      <c r="F524" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -7768,6 +10916,12 @@
       <c r="D525" t="n">
         <v>36.1551724137931</v>
       </c>
+      <c r="E525" t="n">
+        <v>-0.9996393752051809</v>
+      </c>
+      <c r="F525" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -7782,6 +10936,12 @@
       <c r="D526" t="n">
         <v>36.65</v>
       </c>
+      <c r="E526" t="n">
+        <v>-0.8669809623599548</v>
+      </c>
+      <c r="F526" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -7796,6 +10956,12 @@
       <c r="D527" t="n">
         <v>52.17391304347826</v>
       </c>
+      <c r="E527" t="n">
+        <v>0.9435409706269111</v>
+      </c>
+      <c r="F527" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -7810,6 +10976,12 @@
       <c r="D528" t="n">
         <v>43.18518518518518</v>
       </c>
+      <c r="E528" t="n">
+        <v>-0.715340988745086</v>
+      </c>
+      <c r="F528" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -7824,6 +10996,12 @@
       <c r="D529" t="n">
         <v>39.47368421052632</v>
       </c>
+      <c r="E529" t="n">
+        <v>0.9793094090311945</v>
+      </c>
+      <c r="F529" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -7838,6 +11016,12 @@
       <c r="D530" t="n">
         <v>42.22222222222222</v>
       </c>
+      <c r="E530" t="n">
+        <v>-0.9821402221526757</v>
+      </c>
+      <c r="F530" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -7852,6 +11036,12 @@
       <c r="D531" t="n">
         <v>29.6875</v>
       </c>
+      <c r="E531" t="n">
+        <v>-0.9876020617700564</v>
+      </c>
+      <c r="F531" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -7866,6 +11056,12 @@
       <c r="D532" t="n">
         <v>43.33333333333334</v>
       </c>
+      <c r="E532" t="n">
+        <v>-0.6043611924374931</v>
+      </c>
+      <c r="F532" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -7880,6 +11076,12 @@
       <c r="D533" t="n">
         <v>30.76923076923077</v>
       </c>
+      <c r="E533" t="n">
+        <v>-0.6025526602028074</v>
+      </c>
+      <c r="F533" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -7894,6 +11096,12 @@
       <c r="D534" t="n">
         <v>31.05263157894737</v>
       </c>
+      <c r="E534" t="n">
+        <v>-0.3553560551660062</v>
+      </c>
+      <c r="F534" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -7908,6 +11116,12 @@
       <c r="D535" t="n">
         <v>60</v>
       </c>
+      <c r="E535" t="n">
+        <v>-0.3048106211022167</v>
+      </c>
+      <c r="F535" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -7922,6 +11136,12 @@
       <c r="D536" t="n">
         <v>65</v>
       </c>
+      <c r="E536" t="n">
+        <v>0.8268286794901034</v>
+      </c>
+      <c r="F536" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -7936,6 +11156,12 @@
       <c r="D537" t="n">
         <v>70</v>
       </c>
+      <c r="E537" t="n">
+        <v>0.7738906815578891</v>
+      </c>
+      <c r="F537" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -7950,6 +11176,12 @@
       <c r="D538" t="n">
         <v>29.13793103448276</v>
       </c>
+      <c r="E538" t="n">
+        <v>-0.7601845716433042</v>
+      </c>
+      <c r="F538" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -7964,6 +11196,12 @@
       <c r="D539" t="n">
         <v>48.5</v>
       </c>
+      <c r="E539" t="n">
+        <v>-0.981108438603097</v>
+      </c>
+      <c r="F539" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -7978,6 +11216,12 @@
       <c r="D540" t="n">
         <v>30</v>
       </c>
+      <c r="E540" t="n">
+        <v>-0.9880316240928618</v>
+      </c>
+      <c r="F540" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -7992,6 +11236,12 @@
       <c r="D541" t="n">
         <v>35.57142857142857</v>
       </c>
+      <c r="E541" t="n">
+        <v>-0.8489046148505054</v>
+      </c>
+      <c r="F541" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -8006,6 +11256,12 @@
       <c r="D542" t="n">
         <v>31.04166666666667</v>
       </c>
+      <c r="E542" t="n">
+        <v>-0.3655837315065439</v>
+      </c>
+      <c r="F542" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -8020,6 +11276,12 @@
       <c r="D543" t="n">
         <v>34.82758620689656</v>
       </c>
+      <c r="E543" t="n">
+        <v>-0.2667960255179727</v>
+      </c>
+      <c r="F543" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -8034,6 +11296,12 @@
       <c r="D544" t="n">
         <v>29.28571428571428</v>
       </c>
+      <c r="E544" t="n">
+        <v>-0.8475652199115747</v>
+      </c>
+      <c r="F544" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -8048,6 +11316,12 @@
       <c r="D545" t="n">
         <v>29.04761904761905</v>
       </c>
+      <c r="E545" t="n">
+        <v>-0.6984899331626387</v>
+      </c>
+      <c r="F545" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -8061,6 +11335,12 @@
       </c>
       <c r="D546" t="n">
         <v>36.59090909090909</v>
+      </c>
+      <c r="E546" t="n">
+        <v>-0.8948980725658613</v>
+      </c>
+      <c r="F546" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/house/house.xlsx
+++ b/data/house/house.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C546"/>
+  <dimension ref="A1:D546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>toto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>surface</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>loyer_m2</t>
         </is>
@@ -450,9 +455,12 @@
         <v>1330</v>
       </c>
       <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
         <v>37</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>35.94594594594594</v>
       </c>
     </row>
@@ -461,9 +469,12 @@
         <v>1400</v>
       </c>
       <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
         <v>32</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>43.75</v>
       </c>
     </row>
@@ -472,9 +483,12 @@
         <v>904</v>
       </c>
       <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
         <v>26</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>34.76923076923077</v>
       </c>
     </row>
@@ -483,9 +497,12 @@
         <v>955</v>
       </c>
       <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
         <v>30</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>31.83333333333333</v>
       </c>
     </row>
@@ -494,9 +511,12 @@
         <v>2545</v>
       </c>
       <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
         <v>70</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>36.35714285714285</v>
       </c>
     </row>
@@ -505,9 +525,12 @@
         <v>970</v>
       </c>
       <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
         <v>24</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>40.41666666666666</v>
       </c>
     </row>
@@ -516,9 +539,12 @@
         <v>1560</v>
       </c>
       <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
         <v>41</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>38.04878048780488</v>
       </c>
     </row>
@@ -527,9 +553,12 @@
         <v>1960</v>
       </c>
       <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
         <v>67</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>29.25373134328358</v>
       </c>
     </row>
@@ -538,9 +567,12 @@
         <v>2000</v>
       </c>
       <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
         <v>63</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>31.74603174603175</v>
       </c>
     </row>
@@ -549,9 +581,12 @@
         <v>2600</v>
       </c>
       <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
         <v>70</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>37.14285714285715</v>
       </c>
     </row>
@@ -560,9 +595,12 @@
         <v>3280</v>
       </c>
       <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
         <v>81</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>40.49382716049383</v>
       </c>
     </row>
@@ -571,9 +609,12 @@
         <v>16000</v>
       </c>
       <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
         <v>347</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>46.10951008645533</v>
       </c>
     </row>
@@ -582,9 +623,12 @@
         <v>980</v>
       </c>
       <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
         <v>26</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>37.69230769230769</v>
       </c>
     </row>
@@ -593,9 +637,12 @@
         <v>1250</v>
       </c>
       <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
         <v>36</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>34.72222222222222</v>
       </c>
     </row>
@@ -604,9 +651,12 @@
         <v>752</v>
       </c>
       <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
         <v>19</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>39.57894736842105</v>
       </c>
     </row>
@@ -615,9 +665,12 @@
         <v>815</v>
       </c>
       <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
         <v>20</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>40.75</v>
       </c>
     </row>
@@ -626,9 +679,12 @@
         <v>1147</v>
       </c>
       <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
         <v>25</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>45.88</v>
       </c>
     </row>
@@ -637,9 +693,12 @@
         <v>1500</v>
       </c>
       <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
         <v>35</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>42.85714285714285</v>
       </c>
     </row>
@@ -648,9 +707,12 @@
         <v>3587</v>
       </c>
       <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
         <v>120</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>29.89166666666667</v>
       </c>
     </row>
@@ -659,9 +721,12 @@
         <v>1355</v>
       </c>
       <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
         <v>40</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>33.875</v>
       </c>
     </row>
@@ -670,9 +735,12 @@
         <v>1245</v>
       </c>
       <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
         <v>30</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>41.5</v>
       </c>
     </row>
@@ -681,9 +749,12 @@
         <v>1100</v>
       </c>
       <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="n">
         <v>25</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>44</v>
       </c>
     </row>
@@ -692,9 +763,12 @@
         <v>1120</v>
       </c>
       <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
         <v>21</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
@@ -703,9 +777,12 @@
         <v>1225</v>
       </c>
       <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="n">
         <v>44</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>27.84090909090909</v>
       </c>
     </row>
@@ -714,9 +791,12 @@
         <v>1250</v>
       </c>
       <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
         <v>35</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
@@ -725,9 +805,12 @@
         <v>1280</v>
       </c>
       <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="n">
         <v>54</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>23.7037037037037</v>
       </c>
     </row>
@@ -736,9 +819,12 @@
         <v>1114</v>
       </c>
       <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
         <v>39</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>28.56410256410257</v>
       </c>
     </row>
@@ -747,9 +833,12 @@
         <v>1290</v>
       </c>
       <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="n">
         <v>34</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>37.94117647058823</v>
       </c>
     </row>
@@ -758,9 +847,12 @@
         <v>1300</v>
       </c>
       <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="n">
         <v>28</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>46.42857142857143</v>
       </c>
     </row>
@@ -769,9 +861,12 @@
         <v>1300</v>
       </c>
       <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="n">
         <v>32</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>40.625</v>
       </c>
     </row>
@@ -780,9 +875,12 @@
         <v>1304</v>
       </c>
       <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="n">
         <v>40</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>32.6</v>
       </c>
     </row>
@@ -791,9 +889,12 @@
         <v>1340</v>
       </c>
       <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="n">
         <v>42</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>31.90476190476191</v>
       </c>
     </row>
@@ -802,9 +903,12 @@
         <v>1344</v>
       </c>
       <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
         <v>31</v>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>43.35483870967742</v>
       </c>
     </row>
@@ -813,9 +917,12 @@
         <v>1290</v>
       </c>
       <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="n">
         <v>33</v>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>39.09090909090909</v>
       </c>
     </row>
@@ -824,9 +931,12 @@
         <v>1364</v>
       </c>
       <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
         <v>39</v>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>34.97435897435897</v>
       </c>
     </row>
@@ -835,9 +945,12 @@
         <v>1400</v>
       </c>
       <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" t="n">
         <v>47</v>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>29.78723404255319</v>
       </c>
     </row>
@@ -846,9 +959,12 @@
         <v>1400</v>
       </c>
       <c r="B38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" t="n">
         <v>33</v>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>42.42424242424242</v>
       </c>
     </row>
@@ -857,9 +973,12 @@
         <v>1420</v>
       </c>
       <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="n">
         <v>37</v>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>38.37837837837838</v>
       </c>
     </row>
@@ -868,9 +987,12 @@
         <v>1420</v>
       </c>
       <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
         <v>42</v>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>33.80952380952381</v>
       </c>
     </row>
@@ -879,9 +1001,12 @@
         <v>1445</v>
       </c>
       <c r="B41" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" t="n">
         <v>46</v>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>31.41304347826087</v>
       </c>
     </row>
@@ -890,9 +1015,12 @@
         <v>1500</v>
       </c>
       <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="n">
         <v>37</v>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>40.54054054054054</v>
       </c>
     </row>
@@ -901,9 +1029,12 @@
         <v>1544</v>
       </c>
       <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="n">
         <v>46</v>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>33.56521739130435</v>
       </c>
     </row>
@@ -912,9 +1043,12 @@
         <v>1550</v>
       </c>
       <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="n">
         <v>42</v>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>36.90476190476191</v>
       </c>
     </row>
@@ -923,9 +1057,12 @@
         <v>1500</v>
       </c>
       <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="n">
         <v>49</v>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>30.61224489795918</v>
       </c>
     </row>
@@ -934,9 +1071,12 @@
         <v>1612</v>
       </c>
       <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="n">
         <v>48</v>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>33.58333333333334</v>
       </c>
     </row>
@@ -945,9 +1085,12 @@
         <v>1650</v>
       </c>
       <c r="B47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" t="n">
         <v>50</v>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>33</v>
       </c>
     </row>
@@ -956,9 +1099,12 @@
         <v>1533</v>
       </c>
       <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="n">
         <v>54</v>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>28.38888888888889</v>
       </c>
     </row>
@@ -967,9 +1113,12 @@
         <v>1663</v>
       </c>
       <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="n">
         <v>54</v>
       </c>
-      <c r="C49" t="n">
+      <c r="D49" t="n">
         <v>30.7962962962963</v>
       </c>
     </row>
@@ -978,9 +1127,12 @@
         <v>1584</v>
       </c>
       <c r="B50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="n">
         <v>45</v>
       </c>
-      <c r="C50" t="n">
+      <c r="D50" t="n">
         <v>35.2</v>
       </c>
     </row>
@@ -989,9 +1141,12 @@
         <v>1680</v>
       </c>
       <c r="B51" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" t="n">
         <v>53</v>
       </c>
-      <c r="C51" t="n">
+      <c r="D51" t="n">
         <v>31.69811320754717</v>
       </c>
     </row>
@@ -1000,9 +1155,12 @@
         <v>1700</v>
       </c>
       <c r="B52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" t="n">
         <v>40</v>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>42.5</v>
       </c>
     </row>
@@ -1011,9 +1169,12 @@
         <v>1700</v>
       </c>
       <c r="B53" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" t="n">
         <v>35</v>
       </c>
-      <c r="C53" t="n">
+      <c r="D53" t="n">
         <v>48.57142857142857</v>
       </c>
     </row>
@@ -1022,9 +1183,12 @@
         <v>1700</v>
       </c>
       <c r="B54" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" t="n">
         <v>40</v>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>42.5</v>
       </c>
     </row>
@@ -1033,9 +1197,12 @@
         <v>1700</v>
       </c>
       <c r="B55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" t="n">
         <v>35</v>
       </c>
-      <c r="C55" t="n">
+      <c r="D55" t="n">
         <v>48.57142857142857</v>
       </c>
     </row>
@@ -1044,9 +1211,12 @@
         <v>1700</v>
       </c>
       <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="n">
         <v>60</v>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>28.33333333333333</v>
       </c>
     </row>
@@ -1055,9 +1225,12 @@
         <v>1600</v>
       </c>
       <c r="B57" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" t="n">
         <v>30</v>
       </c>
-      <c r="C57" t="n">
+      <c r="D57" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
@@ -1066,9 +1239,12 @@
         <v>1700</v>
       </c>
       <c r="B58" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" t="n">
         <v>34</v>
       </c>
-      <c r="C58" t="n">
+      <c r="D58" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1077,9 +1253,12 @@
         <v>1710</v>
       </c>
       <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="n">
         <v>64</v>
       </c>
-      <c r="C59" t="n">
+      <c r="D59" t="n">
         <v>26.71875</v>
       </c>
     </row>
@@ -1088,9 +1267,12 @@
         <v>1600</v>
       </c>
       <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="n">
         <v>47</v>
       </c>
-      <c r="C60" t="n">
+      <c r="D60" t="n">
         <v>34.04255319148936</v>
       </c>
     </row>
@@ -1099,9 +1281,12 @@
         <v>1750</v>
       </c>
       <c r="B61" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" t="n">
         <v>43</v>
       </c>
-      <c r="C61" t="n">
+      <c r="D61" t="n">
         <v>40.69767441860465</v>
       </c>
     </row>
@@ -1110,9 +1295,12 @@
         <v>1765</v>
       </c>
       <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="n">
         <v>62</v>
       </c>
-      <c r="C62" t="n">
+      <c r="D62" t="n">
         <v>28.46774193548387</v>
       </c>
     </row>
@@ -1121,9 +1309,12 @@
         <v>1790</v>
       </c>
       <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="n">
         <v>50</v>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>35.8</v>
       </c>
     </row>
@@ -1132,9 +1323,12 @@
         <v>1689</v>
       </c>
       <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="n">
         <v>53</v>
       </c>
-      <c r="C64" t="n">
+      <c r="D64" t="n">
         <v>31.86792452830189</v>
       </c>
     </row>
@@ -1143,9 +1337,12 @@
         <v>1795</v>
       </c>
       <c r="B65" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" t="n">
         <v>50</v>
       </c>
-      <c r="C65" t="n">
+      <c r="D65" t="n">
         <v>35.9</v>
       </c>
     </row>
@@ -1154,9 +1351,12 @@
         <v>1800</v>
       </c>
       <c r="B66" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" t="n">
         <v>50</v>
       </c>
-      <c r="C66" t="n">
+      <c r="D66" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1165,9 +1365,12 @@
         <v>1700</v>
       </c>
       <c r="B67" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" t="n">
         <v>60</v>
       </c>
-      <c r="C67" t="n">
+      <c r="D67" t="n">
         <v>28.33333333333333</v>
       </c>
     </row>
@@ -1176,9 +1379,12 @@
         <v>1800</v>
       </c>
       <c r="B68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="n">
         <v>42</v>
       </c>
-      <c r="C68" t="n">
+      <c r="D68" t="n">
         <v>42.85714285714285</v>
       </c>
     </row>
@@ -1187,9 +1393,12 @@
         <v>1850</v>
       </c>
       <c r="B69" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" t="n">
         <v>52</v>
       </c>
-      <c r="C69" t="n">
+      <c r="D69" t="n">
         <v>35.57692307692308</v>
       </c>
     </row>
@@ -1198,9 +1407,12 @@
         <v>1850</v>
       </c>
       <c r="B70" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" t="n">
         <v>45</v>
       </c>
-      <c r="C70" t="n">
+      <c r="D70" t="n">
         <v>41.11111111111111</v>
       </c>
     </row>
@@ -1209,9 +1421,12 @@
         <v>1750</v>
       </c>
       <c r="B71" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" t="n">
         <v>41</v>
       </c>
-      <c r="C71" t="n">
+      <c r="D71" t="n">
         <v>42.68292682926829</v>
       </c>
     </row>
@@ -1220,9 +1435,12 @@
         <v>1850</v>
       </c>
       <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" t="n">
         <v>63</v>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
         <v>29.36507936507936</v>
       </c>
     </row>
@@ -1231,9 +1449,12 @@
         <v>1850</v>
       </c>
       <c r="B73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="n">
         <v>53</v>
       </c>
-      <c r="C73" t="n">
+      <c r="D73" t="n">
         <v>34.90566037735849</v>
       </c>
     </row>
@@ -1242,9 +1463,12 @@
         <v>1850</v>
       </c>
       <c r="B74" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" t="n">
         <v>45</v>
       </c>
-      <c r="C74" t="n">
+      <c r="D74" t="n">
         <v>41.11111111111111</v>
       </c>
     </row>
@@ -1253,9 +1477,12 @@
         <v>1875</v>
       </c>
       <c r="B75" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" t="n">
         <v>53</v>
       </c>
-      <c r="C75" t="n">
+      <c r="D75" t="n">
         <v>35.37735849056604</v>
       </c>
     </row>
@@ -1264,9 +1491,12 @@
         <v>1900</v>
       </c>
       <c r="B76" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" t="n">
         <v>55</v>
       </c>
-      <c r="C76" t="n">
+      <c r="D76" t="n">
         <v>34.54545454545455</v>
       </c>
     </row>
@@ -1275,9 +1505,12 @@
         <v>1950</v>
       </c>
       <c r="B77" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" t="n">
         <v>46</v>
       </c>
-      <c r="C77" t="n">
+      <c r="D77" t="n">
         <v>42.39130434782609</v>
       </c>
     </row>
@@ -1286,9 +1519,12 @@
         <v>1750</v>
       </c>
       <c r="B78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" t="n">
         <v>73</v>
       </c>
-      <c r="C78" t="n">
+      <c r="D78" t="n">
         <v>23.97260273972603</v>
       </c>
     </row>
@@ -1297,9 +1533,12 @@
         <v>2000</v>
       </c>
       <c r="B79" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" t="n">
         <v>53</v>
       </c>
-      <c r="C79" t="n">
+      <c r="D79" t="n">
         <v>37.73584905660378</v>
       </c>
     </row>
@@ -1308,9 +1547,12 @@
         <v>2044</v>
       </c>
       <c r="B80" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" t="n">
         <v>64</v>
       </c>
-      <c r="C80" t="n">
+      <c r="D80" t="n">
         <v>31.9375</v>
       </c>
     </row>
@@ -1319,9 +1561,12 @@
         <v>2100</v>
       </c>
       <c r="B81" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" t="n">
         <v>38</v>
       </c>
-      <c r="C81" t="n">
+      <c r="D81" t="n">
         <v>55.26315789473684</v>
       </c>
     </row>
@@ -1330,9 +1575,12 @@
         <v>2100</v>
       </c>
       <c r="B82" t="n">
+        <v>3</v>
+      </c>
+      <c r="C82" t="n">
         <v>65</v>
       </c>
-      <c r="C82" t="n">
+      <c r="D82" t="n">
         <v>32.30769230769231</v>
       </c>
     </row>
@@ -1341,9 +1589,12 @@
         <v>2100</v>
       </c>
       <c r="B83" t="n">
+        <v>3</v>
+      </c>
+      <c r="C83" t="n">
         <v>59</v>
       </c>
-      <c r="C83" t="n">
+      <c r="D83" t="n">
         <v>35.59322033898305</v>
       </c>
     </row>
@@ -1352,9 +1603,12 @@
         <v>2100</v>
       </c>
       <c r="B84" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" t="n">
         <v>47</v>
       </c>
-      <c r="C84" t="n">
+      <c r="D84" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -1363,9 +1617,12 @@
         <v>2107</v>
       </c>
       <c r="B85" t="n">
+        <v>3</v>
+      </c>
+      <c r="C85" t="n">
         <v>75</v>
       </c>
-      <c r="C85" t="n">
+      <c r="D85" t="n">
         <v>28.09333333333333</v>
       </c>
     </row>
@@ -1374,9 +1631,12 @@
         <v>2116</v>
       </c>
       <c r="B86" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" t="n">
         <v>83</v>
       </c>
-      <c r="C86" t="n">
+      <c r="D86" t="n">
         <v>25.49397590361446</v>
       </c>
     </row>
@@ -1385,9 +1645,12 @@
         <v>2132</v>
       </c>
       <c r="B87" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" t="n">
         <v>69</v>
       </c>
-      <c r="C87" t="n">
+      <c r="D87" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
@@ -1396,9 +1659,12 @@
         <v>2000</v>
       </c>
       <c r="B88" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" t="n">
         <v>68</v>
       </c>
-      <c r="C88" t="n">
+      <c r="D88" t="n">
         <v>29.41176470588235</v>
       </c>
     </row>
@@ -1407,9 +1673,12 @@
         <v>2180</v>
       </c>
       <c r="B89" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" t="n">
         <v>69</v>
       </c>
-      <c r="C89" t="n">
+      <c r="D89" t="n">
         <v>31.59420289855073</v>
       </c>
     </row>
@@ -1418,9 +1687,12 @@
         <v>2100</v>
       </c>
       <c r="B90" t="n">
+        <v>3</v>
+      </c>
+      <c r="C90" t="n">
         <v>72</v>
       </c>
-      <c r="C90" t="n">
+      <c r="D90" t="n">
         <v>29.16666666666667</v>
       </c>
     </row>
@@ -1429,9 +1701,12 @@
         <v>2200</v>
       </c>
       <c r="B91" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" t="n">
         <v>40</v>
       </c>
-      <c r="C91" t="n">
+      <c r="D91" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1440,9 +1715,12 @@
         <v>2200</v>
       </c>
       <c r="B92" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" t="n">
         <v>50</v>
       </c>
-      <c r="C92" t="n">
+      <c r="D92" t="n">
         <v>44</v>
       </c>
     </row>
@@ -1451,9 +1729,12 @@
         <v>2200</v>
       </c>
       <c r="B93" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" t="n">
         <v>60</v>
       </c>
-      <c r="C93" t="n">
+      <c r="D93" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
@@ -1462,9 +1743,12 @@
         <v>2216</v>
       </c>
       <c r="B94" t="n">
+        <v>3</v>
+      </c>
+      <c r="C94" t="n">
         <v>68</v>
       </c>
-      <c r="C94" t="n">
+      <c r="D94" t="n">
         <v>32.58823529411764</v>
       </c>
     </row>
@@ -1473,9 +1757,12 @@
         <v>2240</v>
       </c>
       <c r="B95" t="n">
+        <v>3</v>
+      </c>
+      <c r="C95" t="n">
         <v>69</v>
       </c>
-      <c r="C95" t="n">
+      <c r="D95" t="n">
         <v>32.46376811594203</v>
       </c>
     </row>
@@ -1484,9 +1771,12 @@
         <v>2249</v>
       </c>
       <c r="B96" t="n">
+        <v>3</v>
+      </c>
+      <c r="C96" t="n">
         <v>35</v>
       </c>
-      <c r="C96" t="n">
+      <c r="D96" t="n">
         <v>64.25714285714285</v>
       </c>
     </row>
@@ -1495,9 +1785,12 @@
         <v>2282</v>
       </c>
       <c r="B97" t="n">
+        <v>3</v>
+      </c>
+      <c r="C97" t="n">
         <v>78</v>
       </c>
-      <c r="C97" t="n">
+      <c r="D97" t="n">
         <v>29.25641025641026</v>
       </c>
     </row>
@@ -1506,9 +1799,12 @@
         <v>2300</v>
       </c>
       <c r="B98" t="n">
+        <v>3</v>
+      </c>
+      <c r="C98" t="n">
         <v>65</v>
       </c>
-      <c r="C98" t="n">
+      <c r="D98" t="n">
         <v>35.38461538461539</v>
       </c>
     </row>
@@ -1517,9 +1813,12 @@
         <v>2300</v>
       </c>
       <c r="B99" t="n">
+        <v>3</v>
+      </c>
+      <c r="C99" t="n">
         <v>54</v>
       </c>
-      <c r="C99" t="n">
+      <c r="D99" t="n">
         <v>42.5925925925926</v>
       </c>
     </row>
@@ -1528,9 +1827,12 @@
         <v>2320</v>
       </c>
       <c r="B100" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" t="n">
         <v>60</v>
       </c>
-      <c r="C100" t="n">
+      <c r="D100" t="n">
         <v>38.66666666666666</v>
       </c>
     </row>
@@ -1539,9 +1841,12 @@
         <v>2324</v>
       </c>
       <c r="B101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C101" t="n">
         <v>64</v>
       </c>
-      <c r="C101" t="n">
+      <c r="D101" t="n">
         <v>36.3125</v>
       </c>
     </row>
@@ -1550,9 +1855,12 @@
         <v>2324</v>
       </c>
       <c r="B102" t="n">
+        <v>3</v>
+      </c>
+      <c r="C102" t="n">
         <v>64</v>
       </c>
-      <c r="C102" t="n">
+      <c r="D102" t="n">
         <v>36.3125</v>
       </c>
     </row>
@@ -1561,9 +1869,12 @@
         <v>2367</v>
       </c>
       <c r="B103" t="n">
+        <v>3</v>
+      </c>
+      <c r="C103" t="n">
         <v>76</v>
       </c>
-      <c r="C103" t="n">
+      <c r="D103" t="n">
         <v>31.14473684210526</v>
       </c>
     </row>
@@ -1572,9 +1883,12 @@
         <v>2400</v>
       </c>
       <c r="B104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C104" t="n">
         <v>70</v>
       </c>
-      <c r="C104" t="n">
+      <c r="D104" t="n">
         <v>34.28571428571428</v>
       </c>
     </row>
@@ -1583,9 +1897,12 @@
         <v>2400</v>
       </c>
       <c r="B105" t="n">
+        <v>3</v>
+      </c>
+      <c r="C105" t="n">
         <v>70</v>
       </c>
-      <c r="C105" t="n">
+      <c r="D105" t="n">
         <v>34.28571428571428</v>
       </c>
     </row>
@@ -1594,9 +1911,12 @@
         <v>2445</v>
       </c>
       <c r="B106" t="n">
+        <v>3</v>
+      </c>
+      <c r="C106" t="n">
         <v>71</v>
       </c>
-      <c r="C106" t="n">
+      <c r="D106" t="n">
         <v>34.43661971830986</v>
       </c>
     </row>
@@ -1605,9 +1925,12 @@
         <v>2450</v>
       </c>
       <c r="B107" t="n">
+        <v>3</v>
+      </c>
+      <c r="C107" t="n">
         <v>84</v>
       </c>
-      <c r="C107" t="n">
+      <c r="D107" t="n">
         <v>29.16666666666667</v>
       </c>
     </row>
@@ -1616,9 +1939,12 @@
         <v>2450</v>
       </c>
       <c r="B108" t="n">
+        <v>3</v>
+      </c>
+      <c r="C108" t="n">
         <v>90</v>
       </c>
-      <c r="C108" t="n">
+      <c r="D108" t="n">
         <v>27.22222222222222</v>
       </c>
     </row>
@@ -1627,9 +1953,12 @@
         <v>2280</v>
       </c>
       <c r="B109" t="n">
+        <v>3</v>
+      </c>
+      <c r="C109" t="n">
         <v>96</v>
       </c>
-      <c r="C109" t="n">
+      <c r="D109" t="n">
         <v>23.75</v>
       </c>
     </row>
@@ -1638,9 +1967,12 @@
         <v>2250</v>
       </c>
       <c r="B110" t="n">
+        <v>3</v>
+      </c>
+      <c r="C110" t="n">
         <v>89</v>
       </c>
-      <c r="C110" t="n">
+      <c r="D110" t="n">
         <v>25.28089887640449</v>
       </c>
     </row>
@@ -1649,9 +1981,12 @@
         <v>2415</v>
       </c>
       <c r="B111" t="n">
+        <v>3</v>
+      </c>
+      <c r="C111" t="n">
         <v>75</v>
       </c>
-      <c r="C111" t="n">
+      <c r="D111" t="n">
         <v>32.2</v>
       </c>
     </row>
@@ -1660,9 +1995,12 @@
         <v>2470</v>
       </c>
       <c r="B112" t="n">
+        <v>3</v>
+      </c>
+      <c r="C112" t="n">
         <v>55</v>
       </c>
-      <c r="C112" t="n">
+      <c r="D112" t="n">
         <v>44.90909090909091</v>
       </c>
     </row>
@@ -1671,9 +2009,12 @@
         <v>2600</v>
       </c>
       <c r="B113" t="n">
+        <v>3</v>
+      </c>
+      <c r="C113" t="n">
         <v>56</v>
       </c>
-      <c r="C113" t="n">
+      <c r="D113" t="n">
         <v>46.42857142857143</v>
       </c>
     </row>
@@ -1682,9 +2023,12 @@
         <v>2650</v>
       </c>
       <c r="B114" t="n">
+        <v>3</v>
+      </c>
+      <c r="C114" t="n">
         <v>56</v>
       </c>
-      <c r="C114" t="n">
+      <c r="D114" t="n">
         <v>47.32142857142857</v>
       </c>
     </row>
@@ -1693,9 +2037,12 @@
         <v>2650</v>
       </c>
       <c r="B115" t="n">
+        <v>3</v>
+      </c>
+      <c r="C115" t="n">
         <v>56</v>
       </c>
-      <c r="C115" t="n">
+      <c r="D115" t="n">
         <v>47.32142857142857</v>
       </c>
     </row>
@@ -1704,9 +2051,12 @@
         <v>2675</v>
       </c>
       <c r="B116" t="n">
+        <v>3</v>
+      </c>
+      <c r="C116" t="n">
         <v>91</v>
       </c>
-      <c r="C116" t="n">
+      <c r="D116" t="n">
         <v>29.39560439560439</v>
       </c>
     </row>
@@ -1715,9 +2065,12 @@
         <v>2550</v>
       </c>
       <c r="B117" t="n">
+        <v>3</v>
+      </c>
+      <c r="C117" t="n">
         <v>100</v>
       </c>
-      <c r="C117" t="n">
+      <c r="D117" t="n">
         <v>25.5</v>
       </c>
     </row>
@@ -1726,9 +2079,12 @@
         <v>2700</v>
       </c>
       <c r="B118" t="n">
+        <v>3</v>
+      </c>
+      <c r="C118" t="n">
         <v>73</v>
       </c>
-      <c r="C118" t="n">
+      <c r="D118" t="n">
         <v>36.98630136986301</v>
       </c>
     </row>
@@ -1737,9 +2093,12 @@
         <v>2780</v>
       </c>
       <c r="B119" t="n">
+        <v>3</v>
+      </c>
+      <c r="C119" t="n">
         <v>94</v>
       </c>
-      <c r="C119" t="n">
+      <c r="D119" t="n">
         <v>29.57446808510638</v>
       </c>
     </row>
@@ -1748,9 +2107,12 @@
         <v>2800</v>
       </c>
       <c r="B120" t="n">
+        <v>3</v>
+      </c>
+      <c r="C120" t="n">
         <v>50</v>
       </c>
-      <c r="C120" t="n">
+      <c r="D120" t="n">
         <v>56</v>
       </c>
     </row>
@@ -1759,9 +2121,12 @@
         <v>2800</v>
       </c>
       <c r="B121" t="n">
+        <v>3</v>
+      </c>
+      <c r="C121" t="n">
         <v>60</v>
       </c>
-      <c r="C121" t="n">
+      <c r="D121" t="n">
         <v>46.66666666666666</v>
       </c>
     </row>
@@ -1770,9 +2135,12 @@
         <v>2850</v>
       </c>
       <c r="B122" t="n">
+        <v>3</v>
+      </c>
+      <c r="C122" t="n">
         <v>90</v>
       </c>
-      <c r="C122" t="n">
+      <c r="D122" t="n">
         <v>31.66666666666667</v>
       </c>
     </row>
@@ -1781,9 +2149,12 @@
         <v>2941</v>
       </c>
       <c r="B123" t="n">
+        <v>3</v>
+      </c>
+      <c r="C123" t="n">
         <v>96</v>
       </c>
-      <c r="C123" t="n">
+      <c r="D123" t="n">
         <v>30.63541666666667</v>
       </c>
     </row>
@@ -1792,9 +2163,12 @@
         <v>2941</v>
       </c>
       <c r="B124" t="n">
+        <v>3</v>
+      </c>
+      <c r="C124" t="n">
         <v>96</v>
       </c>
-      <c r="C124" t="n">
+      <c r="D124" t="n">
         <v>30.63541666666667</v>
       </c>
     </row>
@@ -1803,9 +2177,12 @@
         <v>3000</v>
       </c>
       <c r="B125" t="n">
+        <v>3</v>
+      </c>
+      <c r="C125" t="n">
         <v>50</v>
       </c>
-      <c r="C125" t="n">
+      <c r="D125" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1814,9 +2191,12 @@
         <v>2800</v>
       </c>
       <c r="B126" t="n">
+        <v>3</v>
+      </c>
+      <c r="C126" t="n">
         <v>83</v>
       </c>
-      <c r="C126" t="n">
+      <c r="D126" t="n">
         <v>33.73493975903614</v>
       </c>
     </row>
@@ -1825,9 +2205,12 @@
         <v>3000</v>
       </c>
       <c r="B127" t="n">
+        <v>3</v>
+      </c>
+      <c r="C127" t="n">
         <v>99</v>
       </c>
-      <c r="C127" t="n">
+      <c r="D127" t="n">
         <v>30.3030303030303</v>
       </c>
     </row>
@@ -1836,9 +2219,12 @@
         <v>3000</v>
       </c>
       <c r="B128" t="n">
+        <v>3</v>
+      </c>
+      <c r="C128" t="n">
         <v>88</v>
       </c>
-      <c r="C128" t="n">
+      <c r="D128" t="n">
         <v>34.09090909090909</v>
       </c>
     </row>
@@ -1847,9 +2233,12 @@
         <v>3010</v>
       </c>
       <c r="B129" t="n">
+        <v>3</v>
+      </c>
+      <c r="C129" t="n">
         <v>104</v>
       </c>
-      <c r="C129" t="n">
+      <c r="D129" t="n">
         <v>28.94230769230769</v>
       </c>
     </row>
@@ -1858,9 +2247,12 @@
         <v>2950</v>
       </c>
       <c r="B130" t="n">
+        <v>3</v>
+      </c>
+      <c r="C130" t="n">
         <v>85</v>
       </c>
-      <c r="C130" t="n">
+      <c r="D130" t="n">
         <v>34.70588235294117</v>
       </c>
     </row>
@@ -1869,9 +2261,12 @@
         <v>3200</v>
       </c>
       <c r="B131" t="n">
+        <v>3</v>
+      </c>
+      <c r="C131" t="n">
         <v>70</v>
       </c>
-      <c r="C131" t="n">
+      <c r="D131" t="n">
         <v>45.71428571428572</v>
       </c>
     </row>
@@ -1880,9 +2275,12 @@
         <v>3200</v>
       </c>
       <c r="B132" t="n">
+        <v>3</v>
+      </c>
+      <c r="C132" t="n">
         <v>60</v>
       </c>
-      <c r="C132" t="n">
+      <c r="D132" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
@@ -1891,9 +2289,12 @@
         <v>3200</v>
       </c>
       <c r="B133" t="n">
+        <v>3</v>
+      </c>
+      <c r="C133" t="n">
         <v>84</v>
       </c>
-      <c r="C133" t="n">
+      <c r="D133" t="n">
         <v>38.09523809523809</v>
       </c>
     </row>
@@ -1902,9 +2303,12 @@
         <v>3234</v>
       </c>
       <c r="B134" t="n">
+        <v>3</v>
+      </c>
+      <c r="C134" t="n">
         <v>103</v>
       </c>
-      <c r="C134" t="n">
+      <c r="D134" t="n">
         <v>31.39805825242718</v>
       </c>
     </row>
@@ -1913,9 +2317,12 @@
         <v>3300</v>
       </c>
       <c r="B135" t="n">
+        <v>3</v>
+      </c>
+      <c r="C135" t="n">
         <v>108</v>
       </c>
-      <c r="C135" t="n">
+      <c r="D135" t="n">
         <v>30.55555555555556</v>
       </c>
     </row>
@@ -1924,9 +2331,12 @@
         <v>3420</v>
       </c>
       <c r="B136" t="n">
+        <v>3</v>
+      </c>
+      <c r="C136" t="n">
         <v>70</v>
       </c>
-      <c r="C136" t="n">
+      <c r="D136" t="n">
         <v>48.85714285714285</v>
       </c>
     </row>
@@ -1935,9 +2345,12 @@
         <v>3350</v>
       </c>
       <c r="B137" t="n">
+        <v>3</v>
+      </c>
+      <c r="C137" t="n">
         <v>88</v>
       </c>
-      <c r="C137" t="n">
+      <c r="D137" t="n">
         <v>38.06818181818182</v>
       </c>
     </row>
@@ -1946,9 +2359,12 @@
         <v>3130</v>
       </c>
       <c r="B138" t="n">
+        <v>3</v>
+      </c>
+      <c r="C138" t="n">
         <v>101</v>
       </c>
-      <c r="C138" t="n">
+      <c r="D138" t="n">
         <v>30.99009900990099</v>
       </c>
     </row>
@@ -1957,9 +2373,12 @@
         <v>3500</v>
       </c>
       <c r="B139" t="n">
+        <v>3</v>
+      </c>
+      <c r="C139" t="n">
         <v>103</v>
       </c>
-      <c r="C139" t="n">
+      <c r="D139" t="n">
         <v>33.98058252427185</v>
       </c>
     </row>
@@ -1968,9 +2387,12 @@
         <v>3700</v>
       </c>
       <c r="B140" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" t="n">
         <v>70</v>
       </c>
-      <c r="C140" t="n">
+      <c r="D140" t="n">
         <v>52.85714285714285</v>
       </c>
     </row>
@@ -1979,9 +2401,12 @@
         <v>3705</v>
       </c>
       <c r="B141" t="n">
+        <v>3</v>
+      </c>
+      <c r="C141" t="n">
         <v>53</v>
       </c>
-      <c r="C141" t="n">
+      <c r="D141" t="n">
         <v>69.90566037735849</v>
       </c>
     </row>
@@ -1990,9 +2415,12 @@
         <v>3705</v>
       </c>
       <c r="B142" t="n">
+        <v>3</v>
+      </c>
+      <c r="C142" t="n">
         <v>53</v>
       </c>
-      <c r="C142" t="n">
+      <c r="D142" t="n">
         <v>69.90566037735849</v>
       </c>
     </row>
@@ -2001,9 +2429,12 @@
         <v>3800</v>
       </c>
       <c r="B143" t="n">
+        <v>3</v>
+      </c>
+      <c r="C143" t="n">
         <v>72</v>
       </c>
-      <c r="C143" t="n">
+      <c r="D143" t="n">
         <v>52.77777777777778</v>
       </c>
     </row>
@@ -2012,9 +2443,12 @@
         <v>3900</v>
       </c>
       <c r="B144" t="n">
+        <v>3</v>
+      </c>
+      <c r="C144" t="n">
         <v>91</v>
       </c>
-      <c r="C144" t="n">
+      <c r="D144" t="n">
         <v>42.85714285714285</v>
       </c>
     </row>
@@ -2023,9 +2457,12 @@
         <v>3700</v>
       </c>
       <c r="B145" t="n">
+        <v>3</v>
+      </c>
+      <c r="C145" t="n">
         <v>97</v>
       </c>
-      <c r="C145" t="n">
+      <c r="D145" t="n">
         <v>38.14432989690722</v>
       </c>
     </row>
@@ -2034,9 +2471,12 @@
         <v>4000</v>
       </c>
       <c r="B146" t="n">
+        <v>3</v>
+      </c>
+      <c r="C146" t="n">
         <v>135</v>
       </c>
-      <c r="C146" t="n">
+      <c r="D146" t="n">
         <v>29.62962962962963</v>
       </c>
     </row>
@@ -2045,9 +2485,12 @@
         <v>4000</v>
       </c>
       <c r="B147" t="n">
+        <v>3</v>
+      </c>
+      <c r="C147" t="n">
         <v>80</v>
       </c>
-      <c r="C147" t="n">
+      <c r="D147" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2056,9 +2499,12 @@
         <v>3850</v>
       </c>
       <c r="B148" t="n">
+        <v>3</v>
+      </c>
+      <c r="C148" t="n">
         <v>116</v>
       </c>
-      <c r="C148" t="n">
+      <c r="D148" t="n">
         <v>33.18965517241379</v>
       </c>
     </row>
@@ -2067,9 +2513,12 @@
         <v>4407</v>
       </c>
       <c r="B149" t="n">
+        <v>3</v>
+      </c>
+      <c r="C149" t="n">
         <v>152</v>
       </c>
-      <c r="C149" t="n">
+      <c r="D149" t="n">
         <v>28.99342105263158</v>
       </c>
     </row>
@@ -2078,9 +2527,12 @@
         <v>5000</v>
       </c>
       <c r="B150" t="n">
+        <v>3</v>
+      </c>
+      <c r="C150" t="n">
         <v>159</v>
       </c>
-      <c r="C150" t="n">
+      <c r="D150" t="n">
         <v>31.44654088050314</v>
       </c>
     </row>
@@ -2089,9 +2541,12 @@
         <v>5233</v>
       </c>
       <c r="B151" t="n">
+        <v>3</v>
+      </c>
+      <c r="C151" t="n">
         <v>162</v>
       </c>
-      <c r="C151" t="n">
+      <c r="D151" t="n">
         <v>32.30246913580247</v>
       </c>
     </row>
@@ -2100,9 +2555,12 @@
         <v>5249</v>
       </c>
       <c r="B152" t="n">
+        <v>3</v>
+      </c>
+      <c r="C152" t="n">
         <v>137</v>
       </c>
-      <c r="C152" t="n">
+      <c r="D152" t="n">
         <v>38.31386861313869</v>
       </c>
     </row>
@@ -2111,9 +2569,12 @@
         <v>5500</v>
       </c>
       <c r="B153" t="n">
+        <v>3</v>
+      </c>
+      <c r="C153" t="n">
         <v>160</v>
       </c>
-      <c r="C153" t="n">
+      <c r="D153" t="n">
         <v>34.375</v>
       </c>
     </row>
@@ -2122,9 +2583,12 @@
         <v>5600</v>
       </c>
       <c r="B154" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" t="n">
         <v>157</v>
       </c>
-      <c r="C154" t="n">
+      <c r="D154" t="n">
         <v>35.6687898089172</v>
       </c>
     </row>
@@ -2133,9 +2597,12 @@
         <v>5970</v>
       </c>
       <c r="B155" t="n">
+        <v>3</v>
+      </c>
+      <c r="C155" t="n">
         <v>160</v>
       </c>
-      <c r="C155" t="n">
+      <c r="D155" t="n">
         <v>37.3125</v>
       </c>
     </row>
@@ -2144,9 +2611,12 @@
         <v>6000</v>
       </c>
       <c r="B156" t="n">
+        <v>3</v>
+      </c>
+      <c r="C156" t="n">
         <v>152</v>
       </c>
-      <c r="C156" t="n">
+      <c r="D156" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
@@ -2155,9 +2625,12 @@
         <v>6000</v>
       </c>
       <c r="B157" t="n">
+        <v>3</v>
+      </c>
+      <c r="C157" t="n">
         <v>152</v>
       </c>
-      <c r="C157" t="n">
+      <c r="D157" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
@@ -2166,9 +2639,12 @@
         <v>7450</v>
       </c>
       <c r="B158" t="n">
+        <v>3</v>
+      </c>
+      <c r="C158" t="n">
         <v>180</v>
       </c>
-      <c r="C158" t="n">
+      <c r="D158" t="n">
         <v>41.38888888888889</v>
       </c>
     </row>
@@ -2177,9 +2653,12 @@
         <v>7280</v>
       </c>
       <c r="B159" t="n">
+        <v>3</v>
+      </c>
+      <c r="C159" t="n">
         <v>182</v>
       </c>
-      <c r="C159" t="n">
+      <c r="D159" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2188,9 +2667,12 @@
         <v>10000</v>
       </c>
       <c r="B160" t="n">
+        <v>3</v>
+      </c>
+      <c r="C160" t="n">
         <v>220</v>
       </c>
-      <c r="C160" t="n">
+      <c r="D160" t="n">
         <v>45.45454545454545</v>
       </c>
     </row>
@@ -2199,9 +2681,12 @@
         <v>14300</v>
       </c>
       <c r="B161" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" t="n">
         <v>347</v>
       </c>
-      <c r="C161" t="n">
+      <c r="D161" t="n">
         <v>41.21037463976946</v>
       </c>
     </row>
@@ -2210,9 +2695,12 @@
         <v>15000</v>
       </c>
       <c r="B162" t="n">
+        <v>3</v>
+      </c>
+      <c r="C162" t="n">
         <v>347</v>
       </c>
-      <c r="C162" t="n">
+      <c r="D162" t="n">
         <v>43.22766570605187</v>
       </c>
     </row>
@@ -2221,9 +2709,12 @@
         <v>775</v>
       </c>
       <c r="B163" t="n">
+        <v>3</v>
+      </c>
+      <c r="C163" t="n">
         <v>20</v>
       </c>
-      <c r="C163" t="n">
+      <c r="D163" t="n">
         <v>38.75</v>
       </c>
     </row>
@@ -2232,9 +2723,12 @@
         <v>816</v>
       </c>
       <c r="B164" t="n">
+        <v>3</v>
+      </c>
+      <c r="C164" t="n">
         <v>19</v>
       </c>
-      <c r="C164" t="n">
+      <c r="D164" t="n">
         <v>42.94736842105263</v>
       </c>
     </row>
@@ -2243,9 +2737,12 @@
         <v>800</v>
       </c>
       <c r="B165" t="n">
+        <v>3</v>
+      </c>
+      <c r="C165" t="n">
         <v>19</v>
       </c>
-      <c r="C165" t="n">
+      <c r="D165" t="n">
         <v>42.10526315789474</v>
       </c>
     </row>
@@ -2254,9 +2751,12 @@
         <v>900</v>
       </c>
       <c r="B166" t="n">
+        <v>3</v>
+      </c>
+      <c r="C166" t="n">
         <v>18</v>
       </c>
-      <c r="C166" t="n">
+      <c r="D166" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2265,9 +2765,12 @@
         <v>900</v>
       </c>
       <c r="B167" t="n">
+        <v>3</v>
+      </c>
+      <c r="C167" t="n">
         <v>28</v>
       </c>
-      <c r="C167" t="n">
+      <c r="D167" t="n">
         <v>32.14285714285715</v>
       </c>
     </row>
@@ -2276,9 +2779,12 @@
         <v>888</v>
       </c>
       <c r="B168" t="n">
+        <v>3</v>
+      </c>
+      <c r="C168" t="n">
         <v>24</v>
       </c>
-      <c r="C168" t="n">
+      <c r="D168" t="n">
         <v>37</v>
       </c>
     </row>
@@ -2287,9 +2793,12 @@
         <v>960</v>
       </c>
       <c r="B169" t="n">
+        <v>3</v>
+      </c>
+      <c r="C169" t="n">
         <v>21</v>
       </c>
-      <c r="C169" t="n">
+      <c r="D169" t="n">
         <v>45.71428571428572</v>
       </c>
     </row>
@@ -2298,9 +2807,12 @@
         <v>966</v>
       </c>
       <c r="B170" t="n">
+        <v>3</v>
+      </c>
+      <c r="C170" t="n">
         <v>30</v>
       </c>
-      <c r="C170" t="n">
+      <c r="D170" t="n">
         <v>32.2</v>
       </c>
     </row>
@@ -2309,9 +2821,12 @@
         <v>1000</v>
       </c>
       <c r="B171" t="n">
+        <v>3</v>
+      </c>
+      <c r="C171" t="n">
         <v>19</v>
       </c>
-      <c r="C171" t="n">
+      <c r="D171" t="n">
         <v>52.63157894736842</v>
       </c>
     </row>
@@ -2320,9 +2835,12 @@
         <v>1040</v>
       </c>
       <c r="B172" t="n">
+        <v>3</v>
+      </c>
+      <c r="C172" t="n">
         <v>26</v>
       </c>
-      <c r="C172" t="n">
+      <c r="D172" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2331,9 +2849,12 @@
         <v>1048</v>
       </c>
       <c r="B173" t="n">
+        <v>3</v>
+      </c>
+      <c r="C173" t="n">
         <v>31</v>
       </c>
-      <c r="C173" t="n">
+      <c r="D173" t="n">
         <v>33.80645161290322</v>
       </c>
     </row>
@@ -2342,9 +2863,12 @@
         <v>1072</v>
       </c>
       <c r="B174" t="n">
+        <v>3</v>
+      </c>
+      <c r="C174" t="n">
         <v>32</v>
       </c>
-      <c r="C174" t="n">
+      <c r="D174" t="n">
         <v>33.5</v>
       </c>
     </row>
@@ -2353,9 +2877,12 @@
         <v>1090</v>
       </c>
       <c r="B175" t="n">
+        <v>3</v>
+      </c>
+      <c r="C175" t="n">
         <v>20</v>
       </c>
-      <c r="C175" t="n">
+      <c r="D175" t="n">
         <v>54.5</v>
       </c>
     </row>
@@ -2364,9 +2891,12 @@
         <v>1100</v>
       </c>
       <c r="B176" t="n">
+        <v>3</v>
+      </c>
+      <c r="C176" t="n">
         <v>26</v>
       </c>
-      <c r="C176" t="n">
+      <c r="D176" t="n">
         <v>42.30769230769231</v>
       </c>
     </row>
@@ -2375,9 +2905,12 @@
         <v>1150</v>
       </c>
       <c r="B177" t="n">
+        <v>3</v>
+      </c>
+      <c r="C177" t="n">
         <v>21</v>
       </c>
-      <c r="C177" t="n">
+      <c r="D177" t="n">
         <v>54.76190476190476</v>
       </c>
     </row>
@@ -2386,9 +2919,12 @@
         <v>1180</v>
       </c>
       <c r="B178" t="n">
+        <v>3</v>
+      </c>
+      <c r="C178" t="n">
         <v>23</v>
       </c>
-      <c r="C178" t="n">
+      <c r="D178" t="n">
         <v>51.30434782608695</v>
       </c>
     </row>
@@ -2397,9 +2933,12 @@
         <v>1200</v>
       </c>
       <c r="B179" t="n">
+        <v>3</v>
+      </c>
+      <c r="C179" t="n">
         <v>30</v>
       </c>
-      <c r="C179" t="n">
+      <c r="D179" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2408,9 +2947,12 @@
         <v>1200</v>
       </c>
       <c r="B180" t="n">
+        <v>3</v>
+      </c>
+      <c r="C180" t="n">
         <v>32</v>
       </c>
-      <c r="C180" t="n">
+      <c r="D180" t="n">
         <v>37.5</v>
       </c>
     </row>
@@ -2419,9 +2961,12 @@
         <v>1200</v>
       </c>
       <c r="B181" t="n">
+        <v>3</v>
+      </c>
+      <c r="C181" t="n">
         <v>20</v>
       </c>
-      <c r="C181" t="n">
+      <c r="D181" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2430,9 +2975,12 @@
         <v>1200</v>
       </c>
       <c r="B182" t="n">
+        <v>3</v>
+      </c>
+      <c r="C182" t="n">
         <v>20</v>
       </c>
-      <c r="C182" t="n">
+      <c r="D182" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2441,9 +2989,12 @@
         <v>1218</v>
       </c>
       <c r="B183" t="n">
+        <v>3</v>
+      </c>
+      <c r="C183" t="n">
         <v>28</v>
       </c>
-      <c r="C183" t="n">
+      <c r="D183" t="n">
         <v>43.5</v>
       </c>
     </row>
@@ -2452,9 +3003,12 @@
         <v>1250</v>
       </c>
       <c r="B184" t="n">
+        <v>3</v>
+      </c>
+      <c r="C184" t="n">
         <v>21</v>
       </c>
-      <c r="C184" t="n">
+      <c r="D184" t="n">
         <v>59.52380952380953</v>
       </c>
     </row>
@@ -2463,9 +3017,12 @@
         <v>1250</v>
       </c>
       <c r="B185" t="n">
+        <v>3</v>
+      </c>
+      <c r="C185" t="n">
         <v>34</v>
       </c>
-      <c r="C185" t="n">
+      <c r="D185" t="n">
         <v>36.76470588235294</v>
       </c>
     </row>
@@ -2474,9 +3031,12 @@
         <v>1300</v>
       </c>
       <c r="B186" t="n">
+        <v>3</v>
+      </c>
+      <c r="C186" t="n">
         <v>22</v>
       </c>
-      <c r="C186" t="n">
+      <c r="D186" t="n">
         <v>59.09090909090909</v>
       </c>
     </row>
@@ -2485,9 +3045,12 @@
         <v>1329</v>
       </c>
       <c r="B187" t="n">
+        <v>3</v>
+      </c>
+      <c r="C187" t="n">
         <v>35</v>
       </c>
-      <c r="C187" t="n">
+      <c r="D187" t="n">
         <v>37.97142857142857</v>
       </c>
     </row>
@@ -2496,9 +3059,12 @@
         <v>1340</v>
       </c>
       <c r="B188" t="n">
+        <v>3</v>
+      </c>
+      <c r="C188" t="n">
         <v>30</v>
       </c>
-      <c r="C188" t="n">
+      <c r="D188" t="n">
         <v>44.66666666666666</v>
       </c>
     </row>
@@ -2507,9 +3073,12 @@
         <v>1500</v>
       </c>
       <c r="B189" t="n">
+        <v>3</v>
+      </c>
+      <c r="C189" t="n">
         <v>32</v>
       </c>
-      <c r="C189" t="n">
+      <c r="D189" t="n">
         <v>46.875</v>
       </c>
     </row>
@@ -2518,9 +3087,12 @@
         <v>1500</v>
       </c>
       <c r="B190" t="n">
+        <v>3</v>
+      </c>
+      <c r="C190" t="n">
         <v>32</v>
       </c>
-      <c r="C190" t="n">
+      <c r="D190" t="n">
         <v>46.875</v>
       </c>
     </row>
@@ -2529,9 +3101,12 @@
         <v>1550</v>
       </c>
       <c r="B191" t="n">
+        <v>3</v>
+      </c>
+      <c r="C191" t="n">
         <v>59</v>
       </c>
-      <c r="C191" t="n">
+      <c r="D191" t="n">
         <v>26.27118644067797</v>
       </c>
     </row>
@@ -2540,9 +3115,12 @@
         <v>1900</v>
       </c>
       <c r="B192" t="n">
+        <v>3</v>
+      </c>
+      <c r="C192" t="n">
         <v>50</v>
       </c>
-      <c r="C192" t="n">
+      <c r="D192" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2551,9 +3129,12 @@
         <v>1910</v>
       </c>
       <c r="B193" t="n">
+        <v>3</v>
+      </c>
+      <c r="C193" t="n">
         <v>71</v>
       </c>
-      <c r="C193" t="n">
+      <c r="D193" t="n">
         <v>26.90140845070422</v>
       </c>
     </row>
@@ -2562,9 +3143,12 @@
         <v>2700</v>
       </c>
       <c r="B194" t="n">
+        <v>3</v>
+      </c>
+      <c r="C194" t="n">
         <v>50</v>
       </c>
-      <c r="C194" t="n">
+      <c r="D194" t="n">
         <v>54</v>
       </c>
     </row>
@@ -2573,9 +3157,12 @@
         <v>2950</v>
       </c>
       <c r="B195" t="n">
+        <v>3</v>
+      </c>
+      <c r="C195" t="n">
         <v>82</v>
       </c>
-      <c r="C195" t="n">
+      <c r="D195" t="n">
         <v>35.97560975609756</v>
       </c>
     </row>
@@ -2584,9 +3171,12 @@
         <v>2700</v>
       </c>
       <c r="B196" t="n">
+        <v>3</v>
+      </c>
+      <c r="C196" t="n">
         <v>50</v>
       </c>
-      <c r="C196" t="n">
+      <c r="D196" t="n">
         <v>54</v>
       </c>
     </row>
@@ -2595,9 +3185,12 @@
         <v>6500</v>
       </c>
       <c r="B197" t="n">
+        <v>3</v>
+      </c>
+      <c r="C197" t="n">
         <v>161</v>
       </c>
-      <c r="C197" t="n">
+      <c r="D197" t="n">
         <v>40.37267080745342</v>
       </c>
     </row>
@@ -2606,9 +3199,12 @@
         <v>7500</v>
       </c>
       <c r="B198" t="n">
+        <v>3</v>
+      </c>
+      <c r="C198" t="n">
         <v>150</v>
       </c>
-      <c r="C198" t="n">
+      <c r="D198" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2617,9 +3213,12 @@
         <v>1048</v>
       </c>
       <c r="B199" t="n">
+        <v>3</v>
+      </c>
+      <c r="C199" t="n">
         <v>31</v>
       </c>
-      <c r="C199" t="n">
+      <c r="D199" t="n">
         <v>33.80645161290322</v>
       </c>
     </row>
@@ -2628,9 +3227,12 @@
         <v>1650</v>
       </c>
       <c r="B200" t="n">
+        <v>3</v>
+      </c>
+      <c r="C200" t="n">
         <v>45</v>
       </c>
-      <c r="C200" t="n">
+      <c r="D200" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
@@ -2639,9 +3241,12 @@
         <v>1100</v>
       </c>
       <c r="B201" t="n">
+        <v>3</v>
+      </c>
+      <c r="C201" t="n">
         <v>29</v>
       </c>
-      <c r="C201" t="n">
+      <c r="D201" t="n">
         <v>37.93103448275862</v>
       </c>
     </row>
@@ -2650,9 +3255,12 @@
         <v>1133</v>
       </c>
       <c r="B202" t="n">
+        <v>3</v>
+      </c>
+      <c r="C202" t="n">
         <v>33</v>
       </c>
-      <c r="C202" t="n">
+      <c r="D202" t="n">
         <v>34.33333333333334</v>
       </c>
     </row>
@@ -2661,9 +3269,12 @@
         <v>1500</v>
       </c>
       <c r="B203" t="n">
+        <v>3</v>
+      </c>
+      <c r="C203" t="n">
         <v>45</v>
       </c>
-      <c r="C203" t="n">
+      <c r="D203" t="n">
         <v>33.33333333333334</v>
       </c>
     </row>
@@ -2672,9 +3283,12 @@
         <v>1530</v>
       </c>
       <c r="B204" t="n">
+        <v>3</v>
+      </c>
+      <c r="C204" t="n">
         <v>35</v>
       </c>
-      <c r="C204" t="n">
+      <c r="D204" t="n">
         <v>43.71428571428572</v>
       </c>
     </row>
@@ -2683,9 +3297,12 @@
         <v>1520</v>
       </c>
       <c r="B205" t="n">
+        <v>3</v>
+      </c>
+      <c r="C205" t="n">
         <v>55</v>
       </c>
-      <c r="C205" t="n">
+      <c r="D205" t="n">
         <v>27.63636363636364</v>
       </c>
     </row>
@@ -2694,9 +3311,12 @@
         <v>1600</v>
       </c>
       <c r="B206" t="n">
+        <v>3</v>
+      </c>
+      <c r="C206" t="n">
         <v>32</v>
       </c>
-      <c r="C206" t="n">
+      <c r="D206" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2705,9 +3325,12 @@
         <v>1620</v>
       </c>
       <c r="B207" t="n">
+        <v>3</v>
+      </c>
+      <c r="C207" t="n">
         <v>54</v>
       </c>
-      <c r="C207" t="n">
+      <c r="D207" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2716,9 +3339,12 @@
         <v>1700</v>
       </c>
       <c r="B208" t="n">
+        <v>3</v>
+      </c>
+      <c r="C208" t="n">
         <v>60</v>
       </c>
-      <c r="C208" t="n">
+      <c r="D208" t="n">
         <v>28.33333333333333</v>
       </c>
     </row>
@@ -2727,9 +3353,12 @@
         <v>1820</v>
       </c>
       <c r="B209" t="n">
+        <v>3</v>
+      </c>
+      <c r="C209" t="n">
         <v>46</v>
       </c>
-      <c r="C209" t="n">
+      <c r="D209" t="n">
         <v>39.56521739130435</v>
       </c>
     </row>
@@ -2738,9 +3367,12 @@
         <v>1850</v>
       </c>
       <c r="B210" t="n">
+        <v>3</v>
+      </c>
+      <c r="C210" t="n">
         <v>66</v>
       </c>
-      <c r="C210" t="n">
+      <c r="D210" t="n">
         <v>28.03030303030303</v>
       </c>
     </row>
@@ -2749,9 +3381,12 @@
         <v>1939</v>
       </c>
       <c r="B211" t="n">
+        <v>3</v>
+      </c>
+      <c r="C211" t="n">
         <v>71</v>
       </c>
-      <c r="C211" t="n">
+      <c r="D211" t="n">
         <v>27.30985915492958</v>
       </c>
     </row>
@@ -2760,9 +3395,12 @@
         <v>1958</v>
       </c>
       <c r="B212" t="n">
+        <v>3</v>
+      </c>
+      <c r="C212" t="n">
         <v>74</v>
       </c>
-      <c r="C212" t="n">
+      <c r="D212" t="n">
         <v>26.45945945945946</v>
       </c>
     </row>
@@ -2771,9 +3409,12 @@
         <v>1750</v>
       </c>
       <c r="B213" t="n">
+        <v>3</v>
+      </c>
+      <c r="C213" t="n">
         <v>87</v>
       </c>
-      <c r="C213" t="n">
+      <c r="D213" t="n">
         <v>20.11494252873563</v>
       </c>
     </row>
@@ -2782,9 +3423,12 @@
         <v>2090</v>
       </c>
       <c r="B214" t="n">
+        <v>3</v>
+      </c>
+      <c r="C214" t="n">
         <v>62</v>
       </c>
-      <c r="C214" t="n">
+      <c r="D214" t="n">
         <v>33.70967741935484</v>
       </c>
     </row>
@@ -2793,9 +3437,12 @@
         <v>2102</v>
       </c>
       <c r="B215" t="n">
+        <v>3</v>
+      </c>
+      <c r="C215" t="n">
         <v>68</v>
       </c>
-      <c r="C215" t="n">
+      <c r="D215" t="n">
         <v>30.91176470588235</v>
       </c>
     </row>
@@ -2804,9 +3451,12 @@
         <v>2162</v>
       </c>
       <c r="B216" t="n">
+        <v>3</v>
+      </c>
+      <c r="C216" t="n">
         <v>75</v>
       </c>
-      <c r="C216" t="n">
+      <c r="D216" t="n">
         <v>28.82666666666667</v>
       </c>
     </row>
@@ -2815,9 +3465,12 @@
         <v>2150</v>
       </c>
       <c r="B217" t="n">
+        <v>3</v>
+      </c>
+      <c r="C217" t="n">
         <v>80</v>
       </c>
-      <c r="C217" t="n">
+      <c r="D217" t="n">
         <v>26.875</v>
       </c>
     </row>
@@ -2826,9 +3479,12 @@
         <v>2250</v>
       </c>
       <c r="B218" t="n">
+        <v>3</v>
+      </c>
+      <c r="C218" t="n">
         <v>74</v>
       </c>
-      <c r="C218" t="n">
+      <c r="D218" t="n">
         <v>30.40540540540541</v>
       </c>
     </row>
@@ -2837,9 +3493,12 @@
         <v>2359</v>
       </c>
       <c r="B219" t="n">
+        <v>3</v>
+      </c>
+      <c r="C219" t="n">
         <v>80</v>
       </c>
-      <c r="C219" t="n">
+      <c r="D219" t="n">
         <v>29.4875</v>
       </c>
     </row>
@@ -2848,9 +3507,12 @@
         <v>2400</v>
       </c>
       <c r="B220" t="n">
+        <v>3</v>
+      </c>
+      <c r="C220" t="n">
         <v>112</v>
       </c>
-      <c r="C220" t="n">
+      <c r="D220" t="n">
         <v>21.42857142857143</v>
       </c>
     </row>
@@ -2859,9 +3521,12 @@
         <v>2459</v>
       </c>
       <c r="B221" t="n">
+        <v>3</v>
+      </c>
+      <c r="C221" t="n">
         <v>96</v>
       </c>
-      <c r="C221" t="n">
+      <c r="D221" t="n">
         <v>25.61458333333333</v>
       </c>
     </row>
@@ -2870,9 +3535,12 @@
         <v>2400</v>
       </c>
       <c r="B222" t="n">
+        <v>3</v>
+      </c>
+      <c r="C222" t="n">
         <v>112</v>
       </c>
-      <c r="C222" t="n">
+      <c r="D222" t="n">
         <v>21.42857142857143</v>
       </c>
     </row>
@@ -2881,9 +3549,12 @@
         <v>2459</v>
       </c>
       <c r="B223" t="n">
+        <v>3</v>
+      </c>
+      <c r="C223" t="n">
         <v>96</v>
       </c>
-      <c r="C223" t="n">
+      <c r="D223" t="n">
         <v>25.61458333333333</v>
       </c>
     </row>
@@ -2892,9 +3563,12 @@
         <v>2535</v>
       </c>
       <c r="B224" t="n">
+        <v>3</v>
+      </c>
+      <c r="C224" t="n">
         <v>86</v>
       </c>
-      <c r="C224" t="n">
+      <c r="D224" t="n">
         <v>29.47674418604651</v>
       </c>
     </row>
@@ -2903,9 +3577,12 @@
         <v>2650</v>
       </c>
       <c r="B225" t="n">
+        <v>3</v>
+      </c>
+      <c r="C225" t="n">
         <v>90</v>
       </c>
-      <c r="C225" t="n">
+      <c r="D225" t="n">
         <v>29.44444444444444</v>
       </c>
     </row>
@@ -2914,9 +3591,12 @@
         <v>2650</v>
       </c>
       <c r="B226" t="n">
+        <v>3</v>
+      </c>
+      <c r="C226" t="n">
         <v>98</v>
       </c>
-      <c r="C226" t="n">
+      <c r="D226" t="n">
         <v>27.04081632653061</v>
       </c>
     </row>
@@ -2925,9 +3605,12 @@
         <v>2900</v>
       </c>
       <c r="B227" t="n">
+        <v>3</v>
+      </c>
+      <c r="C227" t="n">
         <v>105</v>
       </c>
-      <c r="C227" t="n">
+      <c r="D227" t="n">
         <v>27.61904761904762</v>
       </c>
     </row>
@@ -2936,9 +3619,12 @@
         <v>2950</v>
       </c>
       <c r="B228" t="n">
+        <v>3</v>
+      </c>
+      <c r="C228" t="n">
         <v>70</v>
       </c>
-      <c r="C228" t="n">
+      <c r="D228" t="n">
         <v>42.14285714285715</v>
       </c>
     </row>
@@ -2947,9 +3633,12 @@
         <v>3000</v>
       </c>
       <c r="B229" t="n">
+        <v>3</v>
+      </c>
+      <c r="C229" t="n">
         <v>88</v>
       </c>
-      <c r="C229" t="n">
+      <c r="D229" t="n">
         <v>34.09090909090909</v>
       </c>
     </row>
@@ -2958,9 +3647,12 @@
         <v>3234</v>
       </c>
       <c r="B230" t="n">
+        <v>3</v>
+      </c>
+      <c r="C230" t="n">
         <v>105</v>
       </c>
-      <c r="C230" t="n">
+      <c r="D230" t="n">
         <v>30.8</v>
       </c>
     </row>
@@ -2969,9 +3661,12 @@
         <v>3243</v>
       </c>
       <c r="B231" t="n">
+        <v>3</v>
+      </c>
+      <c r="C231" t="n">
         <v>120</v>
       </c>
-      <c r="C231" t="n">
+      <c r="D231" t="n">
         <v>27.025</v>
       </c>
     </row>
@@ -2980,9 +3675,12 @@
         <v>4200</v>
       </c>
       <c r="B232" t="n">
+        <v>3</v>
+      </c>
+      <c r="C232" t="n">
         <v>117</v>
       </c>
-      <c r="C232" t="n">
+      <c r="D232" t="n">
         <v>35.8974358974359</v>
       </c>
     </row>
@@ -2991,9 +3689,12 @@
         <v>4938</v>
       </c>
       <c r="B233" t="n">
+        <v>3</v>
+      </c>
+      <c r="C233" t="n">
         <v>173</v>
       </c>
-      <c r="C233" t="n">
+      <c r="D233" t="n">
         <v>28.54335260115607</v>
       </c>
     </row>
@@ -3002,9 +3703,12 @@
         <v>1100</v>
       </c>
       <c r="B234" t="n">
+        <v>3</v>
+      </c>
+      <c r="C234" t="n">
         <v>31</v>
       </c>
-      <c r="C234" t="n">
+      <c r="D234" t="n">
         <v>35.48387096774194</v>
       </c>
     </row>
@@ -3013,9 +3717,12 @@
         <v>700</v>
       </c>
       <c r="B235" t="n">
+        <v>3</v>
+      </c>
+      <c r="C235" t="n">
         <v>23</v>
       </c>
-      <c r="C235" t="n">
+      <c r="D235" t="n">
         <v>30.43478260869565</v>
       </c>
     </row>
@@ -3024,9 +3731,12 @@
         <v>880</v>
       </c>
       <c r="B236" t="n">
+        <v>3</v>
+      </c>
+      <c r="C236" t="n">
         <v>21</v>
       </c>
-      <c r="C236" t="n">
+      <c r="D236" t="n">
         <v>41.90476190476191</v>
       </c>
     </row>
@@ -3035,9 +3745,12 @@
         <v>930</v>
       </c>
       <c r="B237" t="n">
+        <v>3</v>
+      </c>
+      <c r="C237" t="n">
         <v>15</v>
       </c>
-      <c r="C237" t="n">
+      <c r="D237" t="n">
         <v>62</v>
       </c>
     </row>
@@ -3046,9 +3759,12 @@
         <v>940</v>
       </c>
       <c r="B238" t="n">
+        <v>3</v>
+      </c>
+      <c r="C238" t="n">
         <v>27</v>
       </c>
-      <c r="C238" t="n">
+      <c r="D238" t="n">
         <v>34.81481481481482</v>
       </c>
     </row>
@@ -3057,9 +3773,12 @@
         <v>950</v>
       </c>
       <c r="B239" t="n">
+        <v>3</v>
+      </c>
+      <c r="C239" t="n">
         <v>21</v>
       </c>
-      <c r="C239" t="n">
+      <c r="D239" t="n">
         <v>45.23809523809524</v>
       </c>
     </row>
@@ -3068,9 +3787,12 @@
         <v>950</v>
       </c>
       <c r="B240" t="n">
+        <v>3</v>
+      </c>
+      <c r="C240" t="n">
         <v>21</v>
       </c>
-      <c r="C240" t="n">
+      <c r="D240" t="n">
         <v>45.23809523809524</v>
       </c>
     </row>
@@ -3079,9 +3801,12 @@
         <v>1000</v>
       </c>
       <c r="B241" t="n">
+        <v>3</v>
+      </c>
+      <c r="C241" t="n">
         <v>21</v>
       </c>
-      <c r="C241" t="n">
+      <c r="D241" t="n">
         <v>47.61904761904762</v>
       </c>
     </row>
@@ -3090,9 +3815,12 @@
         <v>1380</v>
       </c>
       <c r="B242" t="n">
+        <v>3</v>
+      </c>
+      <c r="C242" t="n">
         <v>36</v>
       </c>
-      <c r="C242" t="n">
+      <c r="D242" t="n">
         <v>38.33333333333334</v>
       </c>
     </row>
@@ -3101,9 +3829,12 @@
         <v>1700</v>
       </c>
       <c r="B243" t="n">
+        <v>3</v>
+      </c>
+      <c r="C243" t="n">
         <v>57</v>
       </c>
-      <c r="C243" t="n">
+      <c r="D243" t="n">
         <v>29.82456140350877</v>
       </c>
     </row>
@@ -3112,9 +3843,12 @@
         <v>1740</v>
       </c>
       <c r="B244" t="n">
+        <v>3</v>
+      </c>
+      <c r="C244" t="n">
         <v>49</v>
       </c>
-      <c r="C244" t="n">
+      <c r="D244" t="n">
         <v>35.51020408163265</v>
       </c>
     </row>
@@ -3123,9 +3857,12 @@
         <v>2367</v>
       </c>
       <c r="B245" t="n">
+        <v>3</v>
+      </c>
+      <c r="C245" t="n">
         <v>76</v>
       </c>
-      <c r="C245" t="n">
+      <c r="D245" t="n">
         <v>31.14473684210526</v>
       </c>
     </row>
@@ -3134,9 +3871,12 @@
         <v>2800</v>
       </c>
       <c r="B246" t="n">
+        <v>3</v>
+      </c>
+      <c r="C246" t="n">
         <v>83</v>
       </c>
-      <c r="C246" t="n">
+      <c r="D246" t="n">
         <v>33.73493975903614</v>
       </c>
     </row>
@@ -3145,9 +3885,12 @@
         <v>3000</v>
       </c>
       <c r="B247" t="n">
+        <v>3</v>
+      </c>
+      <c r="C247" t="n">
         <v>104</v>
       </c>
-      <c r="C247" t="n">
+      <c r="D247" t="n">
         <v>28.84615384615385</v>
       </c>
     </row>
@@ -3156,9 +3899,12 @@
         <v>1365</v>
       </c>
       <c r="B248" t="n">
+        <v>3</v>
+      </c>
+      <c r="C248" t="n">
         <v>44</v>
       </c>
-      <c r="C248" t="n">
+      <c r="D248" t="n">
         <v>31.02272727272727</v>
       </c>
     </row>
@@ -3167,9 +3913,12 @@
         <v>855</v>
       </c>
       <c r="B249" t="n">
+        <v>3</v>
+      </c>
+      <c r="C249" t="n">
         <v>20</v>
       </c>
-      <c r="C249" t="n">
+      <c r="D249" t="n">
         <v>42.75</v>
       </c>
     </row>
@@ -3178,9 +3927,12 @@
         <v>1250</v>
       </c>
       <c r="B250" t="n">
+        <v>3</v>
+      </c>
+      <c r="C250" t="n">
         <v>30</v>
       </c>
-      <c r="C250" t="n">
+      <c r="D250" t="n">
         <v>41.66666666666666</v>
       </c>
     </row>
@@ -3189,9 +3941,12 @@
         <v>2132</v>
       </c>
       <c r="B251" t="n">
+        <v>3</v>
+      </c>
+      <c r="C251" t="n">
         <v>69</v>
       </c>
-      <c r="C251" t="n">
+      <c r="D251" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
@@ -3200,9 +3955,12 @@
         <v>2840</v>
       </c>
       <c r="B252" t="n">
+        <v>3</v>
+      </c>
+      <c r="C252" t="n">
         <v>77</v>
       </c>
-      <c r="C252" t="n">
+      <c r="D252" t="n">
         <v>36.88311688311688</v>
       </c>
     </row>
@@ -3211,9 +3969,12 @@
         <v>2614</v>
       </c>
       <c r="B253" t="n">
+        <v>3</v>
+      </c>
+      <c r="C253" t="n">
         <v>96</v>
       </c>
-      <c r="C253" t="n">
+      <c r="D253" t="n">
         <v>27.22916666666667</v>
       </c>
     </row>
@@ -3222,9 +3983,12 @@
         <v>693</v>
       </c>
       <c r="B254" t="n">
+        <v>3</v>
+      </c>
+      <c r="C254" t="n">
         <v>19</v>
       </c>
-      <c r="C254" t="n">
+      <c r="D254" t="n">
         <v>36.47368421052632</v>
       </c>
     </row>
@@ -3233,9 +3997,12 @@
         <v>1000</v>
       </c>
       <c r="B255" t="n">
+        <v>3</v>
+      </c>
+      <c r="C255" t="n">
         <v>20</v>
       </c>
-      <c r="C255" t="n">
+      <c r="D255" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3244,9 +4011,12 @@
         <v>2200</v>
       </c>
       <c r="B256" t="n">
+        <v>3</v>
+      </c>
+      <c r="C256" t="n">
         <v>27</v>
       </c>
-      <c r="C256" t="n">
+      <c r="D256" t="n">
         <v>81.48148148148148</v>
       </c>
     </row>
@@ -3255,9 +4025,12 @@
         <v>1900</v>
       </c>
       <c r="B257" t="n">
+        <v>3</v>
+      </c>
+      <c r="C257" t="n">
         <v>60</v>
       </c>
-      <c r="C257" t="n">
+      <c r="D257" t="n">
         <v>31.66666666666667</v>
       </c>
     </row>
@@ -3266,9 +4039,12 @@
         <v>2347</v>
       </c>
       <c r="B258" t="n">
+        <v>3</v>
+      </c>
+      <c r="C258" t="n">
         <v>72</v>
       </c>
-      <c r="C258" t="n">
+      <c r="D258" t="n">
         <v>32.59722222222222</v>
       </c>
     </row>
@@ -3277,9 +4053,12 @@
         <v>3460</v>
       </c>
       <c r="B259" t="n">
+        <v>3</v>
+      </c>
+      <c r="C259" t="n">
         <v>103</v>
       </c>
-      <c r="C259" t="n">
+      <c r="D259" t="n">
         <v>33.59223300970874</v>
       </c>
     </row>
@@ -3288,9 +4067,12 @@
         <v>1100</v>
       </c>
       <c r="B260" t="n">
+        <v>3</v>
+      </c>
+      <c r="C260" t="n">
         <v>25</v>
       </c>
-      <c r="C260" t="n">
+      <c r="D260" t="n">
         <v>44</v>
       </c>
     </row>
@@ -3299,9 +4081,12 @@
         <v>1200</v>
       </c>
       <c r="B261" t="n">
+        <v>3</v>
+      </c>
+      <c r="C261" t="n">
         <v>30</v>
       </c>
-      <c r="C261" t="n">
+      <c r="D261" t="n">
         <v>40</v>
       </c>
     </row>
@@ -3310,9 +4095,12 @@
         <v>1313</v>
       </c>
       <c r="B262" t="n">
+        <v>3</v>
+      </c>
+      <c r="C262" t="n">
         <v>40</v>
       </c>
-      <c r="C262" t="n">
+      <c r="D262" t="n">
         <v>32.825</v>
       </c>
     </row>
@@ -3321,9 +4109,12 @@
         <v>1490</v>
       </c>
       <c r="B263" t="n">
+        <v>3</v>
+      </c>
+      <c r="C263" t="n">
         <v>54</v>
       </c>
-      <c r="C263" t="n">
+      <c r="D263" t="n">
         <v>27.59259259259259</v>
       </c>
     </row>
@@ -3332,9 +4123,12 @@
         <v>1850</v>
       </c>
       <c r="B264" t="n">
+        <v>3</v>
+      </c>
+      <c r="C264" t="n">
         <v>59</v>
       </c>
-      <c r="C264" t="n">
+      <c r="D264" t="n">
         <v>31.35593220338983</v>
       </c>
     </row>
@@ -3343,9 +4137,12 @@
         <v>1880</v>
       </c>
       <c r="B265" t="n">
+        <v>3</v>
+      </c>
+      <c r="C265" t="n">
         <v>62</v>
       </c>
-      <c r="C265" t="n">
+      <c r="D265" t="n">
         <v>30.32258064516129</v>
       </c>
     </row>
@@ -3354,9 +4151,12 @@
         <v>1900</v>
       </c>
       <c r="B266" t="n">
+        <v>3</v>
+      </c>
+      <c r="C266" t="n">
         <v>64</v>
       </c>
-      <c r="C266" t="n">
+      <c r="D266" t="n">
         <v>29.6875</v>
       </c>
     </row>
@@ -3365,9 +4165,12 @@
         <v>1900</v>
       </c>
       <c r="B267" t="n">
+        <v>3</v>
+      </c>
+      <c r="C267" t="n">
         <v>48</v>
       </c>
-      <c r="C267" t="n">
+      <c r="D267" t="n">
         <v>39.58333333333334</v>
       </c>
     </row>
@@ -3376,9 +4179,12 @@
         <v>2008</v>
       </c>
       <c r="B268" t="n">
+        <v>3</v>
+      </c>
+      <c r="C268" t="n">
         <v>87</v>
       </c>
-      <c r="C268" t="n">
+      <c r="D268" t="n">
         <v>23.08045977011494</v>
       </c>
     </row>
@@ -3387,9 +4193,12 @@
         <v>2960</v>
       </c>
       <c r="B269" t="n">
+        <v>3</v>
+      </c>
+      <c r="C269" t="n">
         <v>106</v>
       </c>
-      <c r="C269" t="n">
+      <c r="D269" t="n">
         <v>27.92452830188679</v>
       </c>
     </row>
@@ -3398,9 +4207,12 @@
         <v>3200</v>
       </c>
       <c r="B270" t="n">
+        <v>3</v>
+      </c>
+      <c r="C270" t="n">
         <v>114</v>
       </c>
-      <c r="C270" t="n">
+      <c r="D270" t="n">
         <v>28.07017543859649</v>
       </c>
     </row>
@@ -3409,9 +4221,12 @@
         <v>3220</v>
       </c>
       <c r="B271" t="n">
+        <v>3</v>
+      </c>
+      <c r="C271" t="n">
         <v>110</v>
       </c>
-      <c r="C271" t="n">
+      <c r="D271" t="n">
         <v>29.27272727272727</v>
       </c>
     </row>
@@ -3420,9 +4235,12 @@
         <v>3380</v>
       </c>
       <c r="B272" t="n">
+        <v>3</v>
+      </c>
+      <c r="C272" t="n">
         <v>129</v>
       </c>
-      <c r="C272" t="n">
+      <c r="D272" t="n">
         <v>26.2015503875969</v>
       </c>
     </row>
@@ -3431,9 +4249,12 @@
         <v>3950</v>
       </c>
       <c r="B273" t="n">
+        <v>3</v>
+      </c>
+      <c r="C273" t="n">
         <v>125</v>
       </c>
-      <c r="C273" t="n">
+      <c r="D273" t="n">
         <v>31.6</v>
       </c>
     </row>
@@ -3442,9 +4263,12 @@
         <v>645</v>
       </c>
       <c r="B274" t="n">
+        <v>3</v>
+      </c>
+      <c r="C274" t="n">
         <v>15</v>
       </c>
-      <c r="C274" t="n">
+      <c r="D274" t="n">
         <v>43</v>
       </c>
     </row>
@@ -3453,9 +4277,12 @@
         <v>682</v>
       </c>
       <c r="B275" t="n">
+        <v>3</v>
+      </c>
+      <c r="C275" t="n">
         <v>17</v>
       </c>
-      <c r="C275" t="n">
+      <c r="D275" t="n">
         <v>40.11764705882353</v>
       </c>
     </row>
@@ -3464,9 +4291,12 @@
         <v>745</v>
       </c>
       <c r="B276" t="n">
+        <v>3</v>
+      </c>
+      <c r="C276" t="n">
         <v>20</v>
       </c>
-      <c r="C276" t="n">
+      <c r="D276" t="n">
         <v>37.25</v>
       </c>
     </row>
@@ -3475,9 +4305,12 @@
         <v>1780</v>
       </c>
       <c r="B277" t="n">
+        <v>3</v>
+      </c>
+      <c r="C277" t="n">
         <v>45</v>
       </c>
-      <c r="C277" t="n">
+      <c r="D277" t="n">
         <v>39.55555555555556</v>
       </c>
     </row>
@@ -3486,9 +4319,12 @@
         <v>1595</v>
       </c>
       <c r="B278" t="n">
+        <v>3</v>
+      </c>
+      <c r="C278" t="n">
         <v>54</v>
       </c>
-      <c r="C278" t="n">
+      <c r="D278" t="n">
         <v>29.53703703703704</v>
       </c>
     </row>
@@ -3497,9 +4333,12 @@
         <v>4200</v>
       </c>
       <c r="B279" t="n">
+        <v>3</v>
+      </c>
+      <c r="C279" t="n">
         <v>105</v>
       </c>
-      <c r="C279" t="n">
+      <c r="D279" t="n">
         <v>40</v>
       </c>
     </row>
@@ -3508,9 +4347,12 @@
         <v>9500</v>
       </c>
       <c r="B280" t="n">
+        <v>3</v>
+      </c>
+      <c r="C280" t="n">
         <v>150</v>
       </c>
-      <c r="C280" t="n">
+      <c r="D280" t="n">
         <v>63.33333333333334</v>
       </c>
     </row>
@@ -3519,9 +4361,12 @@
         <v>973</v>
       </c>
       <c r="B281" t="n">
+        <v>3</v>
+      </c>
+      <c r="C281" t="n">
         <v>29</v>
       </c>
-      <c r="C281" t="n">
+      <c r="D281" t="n">
         <v>33.55172413793103</v>
       </c>
     </row>
@@ -3530,9 +4375,12 @@
         <v>1100</v>
       </c>
       <c r="B282" t="n">
+        <v>3</v>
+      </c>
+      <c r="C282" t="n">
         <v>36</v>
       </c>
-      <c r="C282" t="n">
+      <c r="D282" t="n">
         <v>30.55555555555556</v>
       </c>
     </row>
@@ -3541,9 +4389,12 @@
         <v>1851</v>
       </c>
       <c r="B283" t="n">
+        <v>3</v>
+      </c>
+      <c r="C283" t="n">
         <v>50</v>
       </c>
-      <c r="C283" t="n">
+      <c r="D283" t="n">
         <v>37.02</v>
       </c>
     </row>
@@ -3552,9 +4403,12 @@
         <v>1105</v>
       </c>
       <c r="B284" t="n">
+        <v>3</v>
+      </c>
+      <c r="C284" t="n">
         <v>33</v>
       </c>
-      <c r="C284" t="n">
+      <c r="D284" t="n">
         <v>33.48484848484848</v>
       </c>
     </row>
@@ -3563,9 +4417,12 @@
         <v>1200</v>
       </c>
       <c r="B285" t="n">
+        <v>3</v>
+      </c>
+      <c r="C285" t="n">
         <v>40</v>
       </c>
-      <c r="C285" t="n">
+      <c r="D285" t="n">
         <v>30</v>
       </c>
     </row>
@@ -3574,9 +4431,12 @@
         <v>1704</v>
       </c>
       <c r="B286" t="n">
+        <v>3</v>
+      </c>
+      <c r="C286" t="n">
         <v>56</v>
       </c>
-      <c r="C286" t="n">
+      <c r="D286" t="n">
         <v>30.42857142857143</v>
       </c>
     </row>
@@ -3585,9 +4445,12 @@
         <v>800</v>
       </c>
       <c r="B287" t="n">
+        <v>3</v>
+      </c>
+      <c r="C287" t="n">
         <v>15</v>
       </c>
-      <c r="C287" t="n">
+      <c r="D287" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
@@ -3596,9 +4459,12 @@
         <v>985</v>
       </c>
       <c r="B288" t="n">
+        <v>3</v>
+      </c>
+      <c r="C288" t="n">
         <v>34</v>
       </c>
-      <c r="C288" t="n">
+      <c r="D288" t="n">
         <v>28.97058823529412</v>
       </c>
     </row>
@@ -3607,9 +4473,12 @@
         <v>1000</v>
       </c>
       <c r="B289" t="n">
+        <v>3</v>
+      </c>
+      <c r="C289" t="n">
         <v>29</v>
       </c>
-      <c r="C289" t="n">
+      <c r="D289" t="n">
         <v>34.48275862068966</v>
       </c>
     </row>
@@ -3618,9 +4487,12 @@
         <v>1006</v>
       </c>
       <c r="B290" t="n">
+        <v>3</v>
+      </c>
+      <c r="C290" t="n">
         <v>26</v>
       </c>
-      <c r="C290" t="n">
+      <c r="D290" t="n">
         <v>38.69230769230769</v>
       </c>
     </row>
@@ -3629,9 +4501,12 @@
         <v>1100</v>
       </c>
       <c r="B291" t="n">
+        <v>3</v>
+      </c>
+      <c r="C291" t="n">
         <v>37</v>
       </c>
-      <c r="C291" t="n">
+      <c r="D291" t="n">
         <v>29.72972972972973</v>
       </c>
     </row>
@@ -3640,9 +4515,12 @@
         <v>1220</v>
       </c>
       <c r="B292" t="n">
+        <v>3</v>
+      </c>
+      <c r="C292" t="n">
         <v>32</v>
       </c>
-      <c r="C292" t="n">
+      <c r="D292" t="n">
         <v>38.125</v>
       </c>
     </row>
@@ -3651,9 +4529,12 @@
         <v>1230</v>
       </c>
       <c r="B293" t="n">
+        <v>3</v>
+      </c>
+      <c r="C293" t="n">
         <v>35</v>
       </c>
-      <c r="C293" t="n">
+      <c r="D293" t="n">
         <v>35.14285714285715</v>
       </c>
     </row>
@@ -3662,9 +4543,12 @@
         <v>1270</v>
       </c>
       <c r="B294" t="n">
+        <v>3</v>
+      </c>
+      <c r="C294" t="n">
         <v>30</v>
       </c>
-      <c r="C294" t="n">
+      <c r="D294" t="n">
         <v>42.33333333333334</v>
       </c>
     </row>
@@ -3673,9 +4557,12 @@
         <v>1280</v>
       </c>
       <c r="B295" t="n">
+        <v>3</v>
+      </c>
+      <c r="C295" t="n">
         <v>31</v>
       </c>
-      <c r="C295" t="n">
+      <c r="D295" t="n">
         <v>41.29032258064516</v>
       </c>
     </row>
@@ -3684,9 +4571,12 @@
         <v>1290</v>
       </c>
       <c r="B296" t="n">
+        <v>3</v>
+      </c>
+      <c r="C296" t="n">
         <v>38</v>
       </c>
-      <c r="C296" t="n">
+      <c r="D296" t="n">
         <v>33.94736842105263</v>
       </c>
     </row>
@@ -3695,9 +4585,12 @@
         <v>1300</v>
       </c>
       <c r="B297" t="n">
+        <v>3</v>
+      </c>
+      <c r="C297" t="n">
         <v>39</v>
       </c>
-      <c r="C297" t="n">
+      <c r="D297" t="n">
         <v>33.33333333333334</v>
       </c>
     </row>
@@ -3706,9 +4599,12 @@
         <v>1340</v>
       </c>
       <c r="B298" t="n">
+        <v>3</v>
+      </c>
+      <c r="C298" t="n">
         <v>34</v>
       </c>
-      <c r="C298" t="n">
+      <c r="D298" t="n">
         <v>39.41176470588236</v>
       </c>
     </row>
@@ -3717,9 +4613,12 @@
         <v>1350</v>
       </c>
       <c r="B299" t="n">
+        <v>3</v>
+      </c>
+      <c r="C299" t="n">
         <v>39</v>
       </c>
-      <c r="C299" t="n">
+      <c r="D299" t="n">
         <v>34.61538461538461</v>
       </c>
     </row>
@@ -3728,9 +4627,12 @@
         <v>1380</v>
       </c>
       <c r="B300" t="n">
+        <v>3</v>
+      </c>
+      <c r="C300" t="n">
         <v>40</v>
       </c>
-      <c r="C300" t="n">
+      <c r="D300" t="n">
         <v>34.5</v>
       </c>
     </row>
@@ -3739,9 +4641,12 @@
         <v>1390</v>
       </c>
       <c r="B301" t="n">
+        <v>3</v>
+      </c>
+      <c r="C301" t="n">
         <v>47</v>
       </c>
-      <c r="C301" t="n">
+      <c r="D301" t="n">
         <v>29.57446808510638</v>
       </c>
     </row>
@@ -3750,9 +4655,12 @@
         <v>1390</v>
       </c>
       <c r="B302" t="n">
+        <v>3</v>
+      </c>
+      <c r="C302" t="n">
         <v>40</v>
       </c>
-      <c r="C302" t="n">
+      <c r="D302" t="n">
         <v>34.75</v>
       </c>
     </row>
@@ -3761,9 +4669,12 @@
         <v>1400</v>
       </c>
       <c r="B303" t="n">
+        <v>3</v>
+      </c>
+      <c r="C303" t="n">
         <v>52</v>
       </c>
-      <c r="C303" t="n">
+      <c r="D303" t="n">
         <v>26.92307692307692</v>
       </c>
     </row>
@@ -3772,9 +4683,12 @@
         <v>1400</v>
       </c>
       <c r="B304" t="n">
+        <v>3</v>
+      </c>
+      <c r="C304" t="n">
         <v>40</v>
       </c>
-      <c r="C304" t="n">
+      <c r="D304" t="n">
         <v>35</v>
       </c>
     </row>
@@ -3783,9 +4697,12 @@
         <v>1400</v>
       </c>
       <c r="B305" t="n">
+        <v>3</v>
+      </c>
+      <c r="C305" t="n">
         <v>33</v>
       </c>
-      <c r="C305" t="n">
+      <c r="D305" t="n">
         <v>42.42424242424242</v>
       </c>
     </row>
@@ -3794,9 +4711,12 @@
         <v>1500</v>
       </c>
       <c r="B306" t="n">
+        <v>3</v>
+      </c>
+      <c r="C306" t="n">
         <v>40</v>
       </c>
-      <c r="C306" t="n">
+      <c r="D306" t="n">
         <v>37.5</v>
       </c>
     </row>
@@ -3805,9 +4725,12 @@
         <v>1550</v>
       </c>
       <c r="B307" t="n">
+        <v>3</v>
+      </c>
+      <c r="C307" t="n">
         <v>50</v>
       </c>
-      <c r="C307" t="n">
+      <c r="D307" t="n">
         <v>31</v>
       </c>
     </row>
@@ -3816,9 +4739,12 @@
         <v>1570</v>
       </c>
       <c r="B308" t="n">
+        <v>3</v>
+      </c>
+      <c r="C308" t="n">
         <v>51</v>
       </c>
-      <c r="C308" t="n">
+      <c r="D308" t="n">
         <v>30.7843137254902</v>
       </c>
     </row>
@@ -3827,9 +4753,12 @@
         <v>1590</v>
       </c>
       <c r="B309" t="n">
+        <v>3</v>
+      </c>
+      <c r="C309" t="n">
         <v>45</v>
       </c>
-      <c r="C309" t="n">
+      <c r="D309" t="n">
         <v>35.33333333333334</v>
       </c>
     </row>
@@ -3838,9 +4767,12 @@
         <v>1600</v>
       </c>
       <c r="B310" t="n">
+        <v>3</v>
+      </c>
+      <c r="C310" t="n">
         <v>35</v>
       </c>
-      <c r="C310" t="n">
+      <c r="D310" t="n">
         <v>45.71428571428572</v>
       </c>
     </row>
@@ -3849,9 +4781,12 @@
         <v>1600</v>
       </c>
       <c r="B311" t="n">
+        <v>3</v>
+      </c>
+      <c r="C311" t="n">
         <v>37</v>
       </c>
-      <c r="C311" t="n">
+      <c r="D311" t="n">
         <v>43.24324324324324</v>
       </c>
     </row>
@@ -3860,9 +4795,12 @@
         <v>1627</v>
       </c>
       <c r="B312" t="n">
+        <v>3</v>
+      </c>
+      <c r="C312" t="n">
         <v>46</v>
       </c>
-      <c r="C312" t="n">
+      <c r="D312" t="n">
         <v>35.3695652173913</v>
       </c>
     </row>
@@ -3871,9 +4809,12 @@
         <v>1690</v>
       </c>
       <c r="B313" t="n">
+        <v>3</v>
+      </c>
+      <c r="C313" t="n">
         <v>56</v>
       </c>
-      <c r="C313" t="n">
+      <c r="D313" t="n">
         <v>30.17857142857143</v>
       </c>
     </row>
@@ -3882,9 +4823,12 @@
         <v>1696</v>
       </c>
       <c r="B314" t="n">
+        <v>3</v>
+      </c>
+      <c r="C314" t="n">
         <v>57</v>
       </c>
-      <c r="C314" t="n">
+      <c r="D314" t="n">
         <v>29.75438596491228</v>
       </c>
     </row>
@@ -3893,9 +4837,12 @@
         <v>1700</v>
       </c>
       <c r="B315" t="n">
+        <v>3</v>
+      </c>
+      <c r="C315" t="n">
         <v>45</v>
       </c>
-      <c r="C315" t="n">
+      <c r="D315" t="n">
         <v>37.77777777777778</v>
       </c>
     </row>
@@ -3904,9 +4851,12 @@
         <v>1700</v>
       </c>
       <c r="B316" t="n">
+        <v>3</v>
+      </c>
+      <c r="C316" t="n">
         <v>47</v>
       </c>
-      <c r="C316" t="n">
+      <c r="D316" t="n">
         <v>36.17021276595744</v>
       </c>
     </row>
@@ -3915,9 +4865,12 @@
         <v>1705</v>
       </c>
       <c r="B317" t="n">
+        <v>3</v>
+      </c>
+      <c r="C317" t="n">
         <v>75</v>
       </c>
-      <c r="C317" t="n">
+      <c r="D317" t="n">
         <v>22.73333333333333</v>
       </c>
     </row>
@@ -3926,9 +4879,12 @@
         <v>1750</v>
       </c>
       <c r="B318" t="n">
+        <v>3</v>
+      </c>
+      <c r="C318" t="n">
         <v>51</v>
       </c>
-      <c r="C318" t="n">
+      <c r="D318" t="n">
         <v>34.31372549019608</v>
       </c>
     </row>
@@ -3937,9 +4893,12 @@
         <v>1750</v>
       </c>
       <c r="B319" t="n">
+        <v>3</v>
+      </c>
+      <c r="C319" t="n">
         <v>49</v>
       </c>
-      <c r="C319" t="n">
+      <c r="D319" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
@@ -3948,9 +4907,12 @@
         <v>1800</v>
       </c>
       <c r="B320" t="n">
+        <v>3</v>
+      </c>
+      <c r="C320" t="n">
         <v>40</v>
       </c>
-      <c r="C320" t="n">
+      <c r="D320" t="n">
         <v>45</v>
       </c>
     </row>
@@ -3959,9 +4921,12 @@
         <v>1830</v>
       </c>
       <c r="B321" t="n">
+        <v>3</v>
+      </c>
+      <c r="C321" t="n">
         <v>64</v>
       </c>
-      <c r="C321" t="n">
+      <c r="D321" t="n">
         <v>28.59375</v>
       </c>
     </row>
@@ -3970,9 +4935,12 @@
         <v>1726</v>
       </c>
       <c r="B322" t="n">
+        <v>3</v>
+      </c>
+      <c r="C322" t="n">
         <v>62</v>
       </c>
-      <c r="C322" t="n">
+      <c r="D322" t="n">
         <v>27.83870967741936</v>
       </c>
     </row>
@@ -3981,9 +4949,12 @@
         <v>1850</v>
       </c>
       <c r="B323" t="n">
+        <v>3</v>
+      </c>
+      <c r="C323" t="n">
         <v>35</v>
       </c>
-      <c r="C323" t="n">
+      <c r="D323" t="n">
         <v>52.85714285714285</v>
       </c>
     </row>
@@ -3992,9 +4963,12 @@
         <v>1875</v>
       </c>
       <c r="B324" t="n">
+        <v>3</v>
+      </c>
+      <c r="C324" t="n">
         <v>42</v>
       </c>
-      <c r="C324" t="n">
+      <c r="D324" t="n">
         <v>44.64285714285715</v>
       </c>
     </row>
@@ -4003,9 +4977,12 @@
         <v>1900</v>
       </c>
       <c r="B325" t="n">
+        <v>3</v>
+      </c>
+      <c r="C325" t="n">
         <v>45</v>
       </c>
-      <c r="C325" t="n">
+      <c r="D325" t="n">
         <v>42.22222222222222</v>
       </c>
     </row>
@@ -4014,9 +4991,12 @@
         <v>1930</v>
       </c>
       <c r="B326" t="n">
+        <v>3</v>
+      </c>
+      <c r="C326" t="n">
         <v>64</v>
       </c>
-      <c r="C326" t="n">
+      <c r="D326" t="n">
         <v>30.15625</v>
       </c>
     </row>
@@ -4025,9 +5005,12 @@
         <v>1990</v>
       </c>
       <c r="B327" t="n">
+        <v>3</v>
+      </c>
+      <c r="C327" t="n">
         <v>61</v>
       </c>
-      <c r="C327" t="n">
+      <c r="D327" t="n">
         <v>32.62295081967213</v>
       </c>
     </row>
@@ -4036,9 +5019,12 @@
         <v>2000</v>
       </c>
       <c r="B328" t="n">
+        <v>3</v>
+      </c>
+      <c r="C328" t="n">
         <v>50</v>
       </c>
-      <c r="C328" t="n">
+      <c r="D328" t="n">
         <v>40</v>
       </c>
     </row>
@@ -4047,9 +5033,12 @@
         <v>2044</v>
       </c>
       <c r="B329" t="n">
+        <v>3</v>
+      </c>
+      <c r="C329" t="n">
         <v>64</v>
       </c>
-      <c r="C329" t="n">
+      <c r="D329" t="n">
         <v>31.9375</v>
       </c>
     </row>
@@ -4058,9 +5047,12 @@
         <v>2060</v>
       </c>
       <c r="B330" t="n">
+        <v>3</v>
+      </c>
+      <c r="C330" t="n">
         <v>69</v>
       </c>
-      <c r="C330" t="n">
+      <c r="D330" t="n">
         <v>29.85507246376812</v>
       </c>
     </row>
@@ -4069,9 +5061,12 @@
         <v>2100</v>
       </c>
       <c r="B331" t="n">
+        <v>3</v>
+      </c>
+      <c r="C331" t="n">
         <v>50</v>
       </c>
-      <c r="C331" t="n">
+      <c r="D331" t="n">
         <v>42</v>
       </c>
     </row>
@@ -4080,9 +5075,12 @@
         <v>1922</v>
       </c>
       <c r="B332" t="n">
+        <v>3</v>
+      </c>
+      <c r="C332" t="n">
         <v>73</v>
       </c>
-      <c r="C332" t="n">
+      <c r="D332" t="n">
         <v>26.32876712328767</v>
       </c>
     </row>
@@ -4091,9 +5089,12 @@
         <v>2190</v>
       </c>
       <c r="B333" t="n">
+        <v>3</v>
+      </c>
+      <c r="C333" t="n">
         <v>70</v>
       </c>
-      <c r="C333" t="n">
+      <c r="D333" t="n">
         <v>31.28571428571428</v>
       </c>
     </row>
@@ -4102,9 +5103,12 @@
         <v>2250</v>
       </c>
       <c r="B334" t="n">
+        <v>3</v>
+      </c>
+      <c r="C334" t="n">
         <v>66</v>
       </c>
-      <c r="C334" t="n">
+      <c r="D334" t="n">
         <v>34.09090909090909</v>
       </c>
     </row>
@@ -4113,9 +5117,12 @@
         <v>2250</v>
       </c>
       <c r="B335" t="n">
+        <v>3</v>
+      </c>
+      <c r="C335" t="n">
         <v>55</v>
       </c>
-      <c r="C335" t="n">
+      <c r="D335" t="n">
         <v>40.90909090909091</v>
       </c>
     </row>
@@ -4124,9 +5131,12 @@
         <v>2300</v>
       </c>
       <c r="B336" t="n">
+        <v>3</v>
+      </c>
+      <c r="C336" t="n">
         <v>65</v>
       </c>
-      <c r="C336" t="n">
+      <c r="D336" t="n">
         <v>35.38461538461539</v>
       </c>
     </row>
@@ -4135,9 +5145,12 @@
         <v>2300</v>
       </c>
       <c r="B337" t="n">
+        <v>3</v>
+      </c>
+      <c r="C337" t="n">
         <v>80</v>
       </c>
-      <c r="C337" t="n">
+      <c r="D337" t="n">
         <v>28.75</v>
       </c>
     </row>
@@ -4146,9 +5159,12 @@
         <v>2309</v>
       </c>
       <c r="B338" t="n">
+        <v>3</v>
+      </c>
+      <c r="C338" t="n">
         <v>88</v>
       </c>
-      <c r="C338" t="n">
+      <c r="D338" t="n">
         <v>26.23863636363636</v>
       </c>
     </row>
@@ -4157,9 +5173,12 @@
         <v>2450</v>
       </c>
       <c r="B339" t="n">
+        <v>3</v>
+      </c>
+      <c r="C339" t="n">
         <v>54</v>
       </c>
-      <c r="C339" t="n">
+      <c r="D339" t="n">
         <v>45.37037037037037</v>
       </c>
     </row>
@@ -4168,9 +5187,12 @@
         <v>2471</v>
       </c>
       <c r="B340" t="n">
+        <v>3</v>
+      </c>
+      <c r="C340" t="n">
         <v>89</v>
       </c>
-      <c r="C340" t="n">
+      <c r="D340" t="n">
         <v>27.76404494382022</v>
       </c>
     </row>
@@ -4179,9 +5201,12 @@
         <v>2500</v>
       </c>
       <c r="B341" t="n">
+        <v>3</v>
+      </c>
+      <c r="C341" t="n">
         <v>52</v>
       </c>
-      <c r="C341" t="n">
+      <c r="D341" t="n">
         <v>48.07692307692308</v>
       </c>
     </row>
@@ -4190,9 +5215,12 @@
         <v>2500</v>
       </c>
       <c r="B342" t="n">
+        <v>3</v>
+      </c>
+      <c r="C342" t="n">
         <v>32</v>
       </c>
-      <c r="C342" t="n">
+      <c r="D342" t="n">
         <v>78.125</v>
       </c>
     </row>
@@ -4201,9 +5229,12 @@
         <v>2500</v>
       </c>
       <c r="B343" t="n">
+        <v>3</v>
+      </c>
+      <c r="C343" t="n">
         <v>63</v>
       </c>
-      <c r="C343" t="n">
+      <c r="D343" t="n">
         <v>39.68253968253968</v>
       </c>
     </row>
@@ -4212,9 +5243,12 @@
         <v>2500</v>
       </c>
       <c r="B344" t="n">
+        <v>3</v>
+      </c>
+      <c r="C344" t="n">
         <v>76</v>
       </c>
-      <c r="C344" t="n">
+      <c r="D344" t="n">
         <v>32.89473684210526</v>
       </c>
     </row>
@@ -4223,9 +5257,12 @@
         <v>2587</v>
       </c>
       <c r="B345" t="n">
+        <v>3</v>
+      </c>
+      <c r="C345" t="n">
         <v>73</v>
       </c>
-      <c r="C345" t="n">
+      <c r="D345" t="n">
         <v>35.43835616438356</v>
       </c>
     </row>
@@ -4234,9 +5271,12 @@
         <v>2700</v>
       </c>
       <c r="B346" t="n">
+        <v>3</v>
+      </c>
+      <c r="C346" t="n">
         <v>101</v>
       </c>
-      <c r="C346" t="n">
+      <c r="D346" t="n">
         <v>26.73267326732673</v>
       </c>
     </row>
@@ -4245,9 +5285,12 @@
         <v>2700</v>
       </c>
       <c r="B347" t="n">
+        <v>3</v>
+      </c>
+      <c r="C347" t="n">
         <v>84</v>
       </c>
-      <c r="C347" t="n">
+      <c r="D347" t="n">
         <v>32.14285714285715</v>
       </c>
     </row>
@@ -4256,9 +5299,12 @@
         <v>2750</v>
       </c>
       <c r="B348" t="n">
+        <v>3</v>
+      </c>
+      <c r="C348" t="n">
         <v>81</v>
       </c>
-      <c r="C348" t="n">
+      <c r="D348" t="n">
         <v>33.95061728395062</v>
       </c>
     </row>
@@ -4267,9 +5313,12 @@
         <v>2800</v>
       </c>
       <c r="B349" t="n">
+        <v>3</v>
+      </c>
+      <c r="C349" t="n">
         <v>68</v>
       </c>
-      <c r="C349" t="n">
+      <c r="D349" t="n">
         <v>41.1764705882353</v>
       </c>
     </row>
@@ -4278,9 +5327,12 @@
         <v>2800</v>
       </c>
       <c r="B350" t="n">
+        <v>3</v>
+      </c>
+      <c r="C350" t="n">
         <v>60</v>
       </c>
-      <c r="C350" t="n">
+      <c r="D350" t="n">
         <v>46.66666666666666</v>
       </c>
     </row>
@@ -4289,9 +5341,12 @@
         <v>2886</v>
       </c>
       <c r="B351" t="n">
+        <v>3</v>
+      </c>
+      <c r="C351" t="n">
         <v>85</v>
       </c>
-      <c r="C351" t="n">
+      <c r="D351" t="n">
         <v>33.95294117647059</v>
       </c>
     </row>
@@ -4300,9 +5355,12 @@
         <v>2900</v>
       </c>
       <c r="B352" t="n">
+        <v>3</v>
+      </c>
+      <c r="C352" t="n">
         <v>110</v>
       </c>
-      <c r="C352" t="n">
+      <c r="D352" t="n">
         <v>26.36363636363636</v>
       </c>
     </row>
@@ -4311,9 +5369,12 @@
         <v>3000</v>
       </c>
       <c r="B353" t="n">
+        <v>3</v>
+      </c>
+      <c r="C353" t="n">
         <v>95</v>
       </c>
-      <c r="C353" t="n">
+      <c r="D353" t="n">
         <v>31.57894736842105</v>
       </c>
     </row>
@@ -4322,9 +5383,12 @@
         <v>3000</v>
       </c>
       <c r="B354" t="n">
+        <v>3</v>
+      </c>
+      <c r="C354" t="n">
         <v>101</v>
       </c>
-      <c r="C354" t="n">
+      <c r="D354" t="n">
         <v>29.7029702970297</v>
       </c>
     </row>
@@ -4333,9 +5397,12 @@
         <v>3000</v>
       </c>
       <c r="B355" t="n">
+        <v>3</v>
+      </c>
+      <c r="C355" t="n">
         <v>90</v>
       </c>
-      <c r="C355" t="n">
+      <c r="D355" t="n">
         <v>33.33333333333334</v>
       </c>
     </row>
@@ -4344,9 +5411,12 @@
         <v>2840</v>
       </c>
       <c r="B356" t="n">
+        <v>3</v>
+      </c>
+      <c r="C356" t="n">
         <v>100</v>
       </c>
-      <c r="C356" t="n">
+      <c r="D356" t="n">
         <v>28.4</v>
       </c>
     </row>
@@ -4355,9 +5425,12 @@
         <v>3100</v>
       </c>
       <c r="B357" t="n">
+        <v>3</v>
+      </c>
+      <c r="C357" t="n">
         <v>100</v>
       </c>
-      <c r="C357" t="n">
+      <c r="D357" t="n">
         <v>31</v>
       </c>
     </row>
@@ -4366,9 +5439,12 @@
         <v>3179</v>
       </c>
       <c r="B358" t="n">
+        <v>3</v>
+      </c>
+      <c r="C358" t="n">
         <v>72</v>
       </c>
-      <c r="C358" t="n">
+      <c r="D358" t="n">
         <v>44.15277777777778</v>
       </c>
     </row>
@@ -4377,9 +5453,12 @@
         <v>3200</v>
       </c>
       <c r="B359" t="n">
+        <v>3</v>
+      </c>
+      <c r="C359" t="n">
         <v>114</v>
       </c>
-      <c r="C359" t="n">
+      <c r="D359" t="n">
         <v>28.07017543859649</v>
       </c>
     </row>
@@ -4388,9 +5467,12 @@
         <v>3200</v>
       </c>
       <c r="B360" t="n">
+        <v>3</v>
+      </c>
+      <c r="C360" t="n">
         <v>110</v>
       </c>
-      <c r="C360" t="n">
+      <c r="D360" t="n">
         <v>29.09090909090909</v>
       </c>
     </row>
@@ -4399,9 +5481,12 @@
         <v>3000</v>
       </c>
       <c r="B361" t="n">
+        <v>3</v>
+      </c>
+      <c r="C361" t="n">
         <v>110</v>
       </c>
-      <c r="C361" t="n">
+      <c r="D361" t="n">
         <v>27.27272727272727</v>
       </c>
     </row>
@@ -4410,9 +5495,12 @@
         <v>3200</v>
       </c>
       <c r="B362" t="n">
+        <v>3</v>
+      </c>
+      <c r="C362" t="n">
         <v>105</v>
       </c>
-      <c r="C362" t="n">
+      <c r="D362" t="n">
         <v>30.47619047619047</v>
       </c>
     </row>
@@ -4421,9 +5509,12 @@
         <v>3300</v>
       </c>
       <c r="B363" t="n">
+        <v>3</v>
+      </c>
+      <c r="C363" t="n">
         <v>101</v>
       </c>
-      <c r="C363" t="n">
+      <c r="D363" t="n">
         <v>32.67326732673267</v>
       </c>
     </row>
@@ -4432,9 +5523,12 @@
         <v>3300</v>
       </c>
       <c r="B364" t="n">
+        <v>3</v>
+      </c>
+      <c r="C364" t="n">
         <v>95</v>
       </c>
-      <c r="C364" t="n">
+      <c r="D364" t="n">
         <v>34.73684210526316</v>
       </c>
     </row>
@@ -4443,9 +5537,12 @@
         <v>3300</v>
       </c>
       <c r="B365" t="n">
+        <v>3</v>
+      </c>
+      <c r="C365" t="n">
         <v>108</v>
       </c>
-      <c r="C365" t="n">
+      <c r="D365" t="n">
         <v>30.55555555555556</v>
       </c>
     </row>
@@ -4454,9 +5551,12 @@
         <v>3460</v>
       </c>
       <c r="B366" t="n">
+        <v>3</v>
+      </c>
+      <c r="C366" t="n">
         <v>103</v>
       </c>
-      <c r="C366" t="n">
+      <c r="D366" t="n">
         <v>33.59223300970874</v>
       </c>
     </row>
@@ -4465,9 +5565,12 @@
         <v>3500</v>
       </c>
       <c r="B367" t="n">
+        <v>3</v>
+      </c>
+      <c r="C367" t="n">
         <v>78</v>
       </c>
-      <c r="C367" t="n">
+      <c r="D367" t="n">
         <v>44.87179487179487</v>
       </c>
     </row>
@@ -4476,9 +5579,12 @@
         <v>3650</v>
       </c>
       <c r="B368" t="n">
+        <v>3</v>
+      </c>
+      <c r="C368" t="n">
         <v>120</v>
       </c>
-      <c r="C368" t="n">
+      <c r="D368" t="n">
         <v>30.41666666666667</v>
       </c>
     </row>
@@ -4487,9 +5593,12 @@
         <v>3660</v>
       </c>
       <c r="B369" t="n">
+        <v>3</v>
+      </c>
+      <c r="C369" t="n">
         <v>100</v>
       </c>
-      <c r="C369" t="n">
+      <c r="D369" t="n">
         <v>36.6</v>
       </c>
     </row>
@@ -4498,9 +5607,12 @@
         <v>3680</v>
       </c>
       <c r="B370" t="n">
+        <v>3</v>
+      </c>
+      <c r="C370" t="n">
         <v>112</v>
       </c>
-      <c r="C370" t="n">
+      <c r="D370" t="n">
         <v>32.85714285714285</v>
       </c>
     </row>
@@ -4509,9 +5621,12 @@
         <v>3700</v>
       </c>
       <c r="B371" t="n">
+        <v>3</v>
+      </c>
+      <c r="C371" t="n">
         <v>145</v>
       </c>
-      <c r="C371" t="n">
+      <c r="D371" t="n">
         <v>25.51724137931035</v>
       </c>
     </row>
@@ -4520,9 +5635,12 @@
         <v>4500</v>
       </c>
       <c r="B372" t="n">
+        <v>3</v>
+      </c>
+      <c r="C372" t="n">
         <v>117</v>
       </c>
-      <c r="C372" t="n">
+      <c r="D372" t="n">
         <v>38.46153846153846</v>
       </c>
     </row>
@@ -4531,9 +5649,12 @@
         <v>4600</v>
       </c>
       <c r="B373" t="n">
+        <v>3</v>
+      </c>
+      <c r="C373" t="n">
         <v>131</v>
       </c>
-      <c r="C373" t="n">
+      <c r="D373" t="n">
         <v>35.11450381679389</v>
       </c>
     </row>
@@ -4542,9 +5663,12 @@
         <v>4930</v>
       </c>
       <c r="B374" t="n">
+        <v>3</v>
+      </c>
+      <c r="C374" t="n">
         <v>117</v>
       </c>
-      <c r="C374" t="n">
+      <c r="D374" t="n">
         <v>42.13675213675214</v>
       </c>
     </row>
@@ -4553,9 +5677,12 @@
         <v>4937</v>
       </c>
       <c r="B375" t="n">
+        <v>3</v>
+      </c>
+      <c r="C375" t="n">
         <v>173</v>
       </c>
-      <c r="C375" t="n">
+      <c r="D375" t="n">
         <v>28.53757225433526</v>
       </c>
     </row>
@@ -4564,9 +5691,12 @@
         <v>5100</v>
       </c>
       <c r="B376" t="n">
+        <v>3</v>
+      </c>
+      <c r="C376" t="n">
         <v>100</v>
       </c>
-      <c r="C376" t="n">
+      <c r="D376" t="n">
         <v>51</v>
       </c>
     </row>
@@ -4575,9 +5705,12 @@
         <v>5233</v>
       </c>
       <c r="B377" t="n">
+        <v>3</v>
+      </c>
+      <c r="C377" t="n">
         <v>162</v>
       </c>
-      <c r="C377" t="n">
+      <c r="D377" t="n">
         <v>32.30246913580247</v>
       </c>
     </row>
@@ -4586,9 +5719,12 @@
         <v>5249</v>
       </c>
       <c r="B378" t="n">
+        <v>3</v>
+      </c>
+      <c r="C378" t="n">
         <v>162</v>
       </c>
-      <c r="C378" t="n">
+      <c r="D378" t="n">
         <v>32.40123456790123</v>
       </c>
     </row>
@@ -4597,9 +5733,12 @@
         <v>5000</v>
       </c>
       <c r="B379" t="n">
+        <v>3</v>
+      </c>
+      <c r="C379" t="n">
         <v>152</v>
       </c>
-      <c r="C379" t="n">
+      <c r="D379" t="n">
         <v>32.89473684210526</v>
       </c>
     </row>
@@ -4608,9 +5747,12 @@
         <v>5307</v>
       </c>
       <c r="B380" t="n">
+        <v>3</v>
+      </c>
+      <c r="C380" t="n">
         <v>175</v>
       </c>
-      <c r="C380" t="n">
+      <c r="D380" t="n">
         <v>30.32571428571429</v>
       </c>
     </row>
@@ -4619,9 +5761,12 @@
         <v>5950</v>
       </c>
       <c r="B381" t="n">
+        <v>3</v>
+      </c>
+      <c r="C381" t="n">
         <v>235</v>
       </c>
-      <c r="C381" t="n">
+      <c r="D381" t="n">
         <v>25.31914893617021</v>
       </c>
     </row>
@@ -4630,9 +5775,12 @@
         <v>7450</v>
       </c>
       <c r="B382" t="n">
+        <v>3</v>
+      </c>
+      <c r="C382" t="n">
         <v>180</v>
       </c>
-      <c r="C382" t="n">
+      <c r="D382" t="n">
         <v>41.38888888888889</v>
       </c>
     </row>
@@ -4641,9 +5789,12 @@
         <v>25000</v>
       </c>
       <c r="B383" t="n">
+        <v>3</v>
+      </c>
+      <c r="C383" t="n">
         <v>415</v>
       </c>
-      <c r="C383" t="n">
+      <c r="D383" t="n">
         <v>60.24096385542169</v>
       </c>
     </row>
@@ -4652,9 +5803,12 @@
         <v>730</v>
       </c>
       <c r="B384" t="n">
+        <v>3</v>
+      </c>
+      <c r="C384" t="n">
         <v>11</v>
       </c>
-      <c r="C384" t="n">
+      <c r="D384" t="n">
         <v>66.36363636363636</v>
       </c>
     </row>
@@ -4663,9 +5817,12 @@
         <v>738</v>
       </c>
       <c r="B385" t="n">
+        <v>3</v>
+      </c>
+      <c r="C385" t="n">
         <v>14</v>
       </c>
-      <c r="C385" t="n">
+      <c r="D385" t="n">
         <v>52.71428571428572</v>
       </c>
     </row>
@@ -4674,9 +5831,12 @@
         <v>821</v>
       </c>
       <c r="B386" t="n">
+        <v>3</v>
+      </c>
+      <c r="C386" t="n">
         <v>18</v>
       </c>
-      <c r="C386" t="n">
+      <c r="D386" t="n">
         <v>45.61111111111111</v>
       </c>
     </row>
@@ -4685,9 +5845,12 @@
         <v>850</v>
       </c>
       <c r="B387" t="n">
+        <v>3</v>
+      </c>
+      <c r="C387" t="n">
         <v>16</v>
       </c>
-      <c r="C387" t="n">
+      <c r="D387" t="n">
         <v>53.125</v>
       </c>
     </row>
@@ -4696,9 +5859,12 @@
         <v>854</v>
       </c>
       <c r="B388" t="n">
+        <v>3</v>
+      </c>
+      <c r="C388" t="n">
         <v>25</v>
       </c>
-      <c r="C388" t="n">
+      <c r="D388" t="n">
         <v>34.16</v>
       </c>
     </row>
@@ -4707,9 +5873,12 @@
         <v>910</v>
       </c>
       <c r="B389" t="n">
+        <v>3</v>
+      </c>
+      <c r="C389" t="n">
         <v>24</v>
       </c>
-      <c r="C389" t="n">
+      <c r="D389" t="n">
         <v>37.91666666666666</v>
       </c>
     </row>
@@ -4718,9 +5887,12 @@
         <v>940</v>
       </c>
       <c r="B390" t="n">
+        <v>3</v>
+      </c>
+      <c r="C390" t="n">
         <v>19</v>
       </c>
-      <c r="C390" t="n">
+      <c r="D390" t="n">
         <v>49.47368421052632</v>
       </c>
     </row>
@@ -4729,9 +5901,12 @@
         <v>950</v>
       </c>
       <c r="B391" t="n">
+        <v>3</v>
+      </c>
+      <c r="C391" t="n">
         <v>20</v>
       </c>
-      <c r="C391" t="n">
+      <c r="D391" t="n">
         <v>47.5</v>
       </c>
     </row>
@@ -4740,9 +5915,12 @@
         <v>950</v>
       </c>
       <c r="B392" t="n">
+        <v>3</v>
+      </c>
+      <c r="C392" t="n">
         <v>21</v>
       </c>
-      <c r="C392" t="n">
+      <c r="D392" t="n">
         <v>45.23809523809524</v>
       </c>
     </row>
@@ -4751,9 +5929,12 @@
         <v>976</v>
       </c>
       <c r="B393" t="n">
+        <v>3</v>
+      </c>
+      <c r="C393" t="n">
         <v>23</v>
       </c>
-      <c r="C393" t="n">
+      <c r="D393" t="n">
         <v>42.43478260869565</v>
       </c>
     </row>
@@ -4762,9 +5943,12 @@
         <v>990</v>
       </c>
       <c r="B394" t="n">
+        <v>3</v>
+      </c>
+      <c r="C394" t="n">
         <v>27</v>
       </c>
-      <c r="C394" t="n">
+      <c r="D394" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
@@ -4773,9 +5957,12 @@
         <v>1190</v>
       </c>
       <c r="B395" t="n">
+        <v>3</v>
+      </c>
+      <c r="C395" t="n">
         <v>29</v>
       </c>
-      <c r="C395" t="n">
+      <c r="D395" t="n">
         <v>41.03448275862069</v>
       </c>
     </row>
@@ -4784,9 +5971,12 @@
         <v>1095</v>
       </c>
       <c r="B396" t="n">
+        <v>3</v>
+      </c>
+      <c r="C396" t="n">
         <v>30</v>
       </c>
-      <c r="C396" t="n">
+      <c r="D396" t="n">
         <v>36.5</v>
       </c>
     </row>
@@ -4795,9 +5985,12 @@
         <v>1210</v>
       </c>
       <c r="B397" t="n">
+        <v>3</v>
+      </c>
+      <c r="C397" t="n">
         <v>40</v>
       </c>
-      <c r="C397" t="n">
+      <c r="D397" t="n">
         <v>30.25</v>
       </c>
     </row>
@@ -4806,9 +5999,12 @@
         <v>1250</v>
       </c>
       <c r="B398" t="n">
+        <v>3</v>
+      </c>
+      <c r="C398" t="n">
         <v>28</v>
       </c>
-      <c r="C398" t="n">
+      <c r="D398" t="n">
         <v>44.64285714285715</v>
       </c>
     </row>
@@ -4817,9 +6013,12 @@
         <v>1255</v>
       </c>
       <c r="B399" t="n">
+        <v>3</v>
+      </c>
+      <c r="C399" t="n">
         <v>24</v>
       </c>
-      <c r="C399" t="n">
+      <c r="D399" t="n">
         <v>52.29166666666666</v>
       </c>
     </row>
@@ -4828,9 +6027,12 @@
         <v>1255</v>
       </c>
       <c r="B400" t="n">
+        <v>3</v>
+      </c>
+      <c r="C400" t="n">
         <v>24</v>
       </c>
-      <c r="C400" t="n">
+      <c r="D400" t="n">
         <v>52.29166666666666</v>
       </c>
     </row>
@@ -4839,9 +6041,12 @@
         <v>1300</v>
       </c>
       <c r="B401" t="n">
+        <v>3</v>
+      </c>
+      <c r="C401" t="n">
         <v>32</v>
       </c>
-      <c r="C401" t="n">
+      <c r="D401" t="n">
         <v>40.625</v>
       </c>
     </row>
@@ -4850,9 +6055,12 @@
         <v>1380</v>
       </c>
       <c r="B402" t="n">
+        <v>3</v>
+      </c>
+      <c r="C402" t="n">
         <v>32</v>
       </c>
-      <c r="C402" t="n">
+      <c r="D402" t="n">
         <v>43.125</v>
       </c>
     </row>
@@ -4861,9 +6069,12 @@
         <v>1500</v>
       </c>
       <c r="B403" t="n">
+        <v>3</v>
+      </c>
+      <c r="C403" t="n">
         <v>42</v>
       </c>
-      <c r="C403" t="n">
+      <c r="D403" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
@@ -4872,9 +6083,12 @@
         <v>1500</v>
       </c>
       <c r="B404" t="n">
+        <v>3</v>
+      </c>
+      <c r="C404" t="n">
         <v>34</v>
       </c>
-      <c r="C404" t="n">
+      <c r="D404" t="n">
         <v>44.11764705882353</v>
       </c>
     </row>
@@ -4883,9 +6097,12 @@
         <v>1510</v>
       </c>
       <c r="B405" t="n">
+        <v>3</v>
+      </c>
+      <c r="C405" t="n">
         <v>29</v>
       </c>
-      <c r="C405" t="n">
+      <c r="D405" t="n">
         <v>52.06896551724138</v>
       </c>
     </row>
@@ -4894,9 +6111,12 @@
         <v>1550</v>
       </c>
       <c r="B406" t="n">
+        <v>3</v>
+      </c>
+      <c r="C406" t="n">
         <v>30</v>
       </c>
-      <c r="C406" t="n">
+      <c r="D406" t="n">
         <v>51.66666666666666</v>
       </c>
     </row>
@@ -4905,9 +6125,12 @@
         <v>1560</v>
       </c>
       <c r="B407" t="n">
+        <v>3</v>
+      </c>
+      <c r="C407" t="n">
         <v>50</v>
       </c>
-      <c r="C407" t="n">
+      <c r="D407" t="n">
         <v>31.2</v>
       </c>
     </row>
@@ -4916,9 +6139,12 @@
         <v>1580</v>
       </c>
       <c r="B408" t="n">
+        <v>3</v>
+      </c>
+      <c r="C408" t="n">
         <v>35</v>
       </c>
-      <c r="C408" t="n">
+      <c r="D408" t="n">
         <v>45.14285714285715</v>
       </c>
     </row>
@@ -4927,9 +6153,12 @@
         <v>1640</v>
       </c>
       <c r="B409" t="n">
+        <v>3</v>
+      </c>
+      <c r="C409" t="n">
         <v>47</v>
       </c>
-      <c r="C409" t="n">
+      <c r="D409" t="n">
         <v>34.8936170212766</v>
       </c>
     </row>
@@ -4938,9 +6167,12 @@
         <v>1650</v>
       </c>
       <c r="B410" t="n">
+        <v>3</v>
+      </c>
+      <c r="C410" t="n">
         <v>40</v>
       </c>
-      <c r="C410" t="n">
+      <c r="D410" t="n">
         <v>41.25</v>
       </c>
     </row>
@@ -4949,9 +6181,12 @@
         <v>1665</v>
       </c>
       <c r="B411" t="n">
+        <v>3</v>
+      </c>
+      <c r="C411" t="n">
         <v>34</v>
       </c>
-      <c r="C411" t="n">
+      <c r="D411" t="n">
         <v>48.97058823529412</v>
       </c>
     </row>
@@ -4960,9 +6195,12 @@
         <v>1865</v>
       </c>
       <c r="B412" t="n">
+        <v>3</v>
+      </c>
+      <c r="C412" t="n">
         <v>55</v>
       </c>
-      <c r="C412" t="n">
+      <c r="D412" t="n">
         <v>33.90909090909091</v>
       </c>
     </row>
@@ -4971,9 +6209,12 @@
         <v>1920</v>
       </c>
       <c r="B413" t="n">
+        <v>3</v>
+      </c>
+      <c r="C413" t="n">
         <v>64</v>
       </c>
-      <c r="C413" t="n">
+      <c r="D413" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4982,9 +6223,12 @@
         <v>2000</v>
       </c>
       <c r="B414" t="n">
+        <v>3</v>
+      </c>
+      <c r="C414" t="n">
         <v>42</v>
       </c>
-      <c r="C414" t="n">
+      <c r="D414" t="n">
         <v>47.61904761904762</v>
       </c>
     </row>
@@ -4993,9 +6237,12 @@
         <v>2000</v>
       </c>
       <c r="B415" t="n">
+        <v>3</v>
+      </c>
+      <c r="C415" t="n">
         <v>41</v>
       </c>
-      <c r="C415" t="n">
+      <c r="D415" t="n">
         <v>48.78048780487805</v>
       </c>
     </row>
@@ -5004,9 +6251,12 @@
         <v>2130</v>
       </c>
       <c r="B416" t="n">
+        <v>3</v>
+      </c>
+      <c r="C416" t="n">
         <v>73</v>
       </c>
-      <c r="C416" t="n">
+      <c r="D416" t="n">
         <v>29.17808219178082</v>
       </c>
     </row>
@@ -5015,9 +6265,12 @@
         <v>2200</v>
       </c>
       <c r="B417" t="n">
+        <v>3</v>
+      </c>
+      <c r="C417" t="n">
         <v>57</v>
       </c>
-      <c r="C417" t="n">
+      <c r="D417" t="n">
         <v>38.59649122807018</v>
       </c>
     </row>
@@ -5026,9 +6279,12 @@
         <v>2300</v>
       </c>
       <c r="B418" t="n">
+        <v>3</v>
+      </c>
+      <c r="C418" t="n">
         <v>80</v>
       </c>
-      <c r="C418" t="n">
+      <c r="D418" t="n">
         <v>28.75</v>
       </c>
     </row>
@@ -5037,9 +6293,12 @@
         <v>2500</v>
       </c>
       <c r="B419" t="n">
+        <v>3</v>
+      </c>
+      <c r="C419" t="n">
         <v>60</v>
       </c>
-      <c r="C419" t="n">
+      <c r="D419" t="n">
         <v>41.66666666666666</v>
       </c>
     </row>
@@ -5048,9 +6307,12 @@
         <v>3750</v>
       </c>
       <c r="B420" t="n">
+        <v>3</v>
+      </c>
+      <c r="C420" t="n">
         <v>70</v>
       </c>
-      <c r="C420" t="n">
+      <c r="D420" t="n">
         <v>53.57142857142857</v>
       </c>
     </row>
@@ -5059,9 +6321,12 @@
         <v>3800</v>
       </c>
       <c r="B421" t="n">
+        <v>3</v>
+      </c>
+      <c r="C421" t="n">
         <v>138</v>
       </c>
-      <c r="C421" t="n">
+      <c r="D421" t="n">
         <v>27.53623188405797</v>
       </c>
     </row>
@@ -5070,9 +6335,12 @@
         <v>4100</v>
       </c>
       <c r="B422" t="n">
+        <v>3</v>
+      </c>
+      <c r="C422" t="n">
         <v>127</v>
       </c>
-      <c r="C422" t="n">
+      <c r="D422" t="n">
         <v>32.28346456692913</v>
       </c>
     </row>
@@ -5081,9 +6349,12 @@
         <v>4300</v>
       </c>
       <c r="B423" t="n">
+        <v>3</v>
+      </c>
+      <c r="C423" t="n">
         <v>148</v>
       </c>
-      <c r="C423" t="n">
+      <c r="D423" t="n">
         <v>29.05405405405405</v>
       </c>
     </row>
@@ -5092,9 +6363,12 @@
         <v>4500</v>
       </c>
       <c r="B424" t="n">
+        <v>3</v>
+      </c>
+      <c r="C424" t="n">
         <v>115</v>
       </c>
-      <c r="C424" t="n">
+      <c r="D424" t="n">
         <v>39.1304347826087</v>
       </c>
     </row>
@@ -5103,9 +6377,12 @@
         <v>15000</v>
       </c>
       <c r="B425" t="n">
+        <v>3</v>
+      </c>
+      <c r="C425" t="n">
         <v>347</v>
       </c>
-      <c r="C425" t="n">
+      <c r="D425" t="n">
         <v>43.22766570605187</v>
       </c>
     </row>
@@ -5114,9 +6391,12 @@
         <v>637</v>
       </c>
       <c r="B426" t="n">
+        <v>3</v>
+      </c>
+      <c r="C426" t="n">
         <v>14</v>
       </c>
-      <c r="C426" t="n">
+      <c r="D426" t="n">
         <v>45.5</v>
       </c>
     </row>
@@ -5125,9 +6405,12 @@
         <v>680</v>
       </c>
       <c r="B427" t="n">
+        <v>3</v>
+      </c>
+      <c r="C427" t="n">
         <v>14</v>
       </c>
-      <c r="C427" t="n">
+      <c r="D427" t="n">
         <v>48.57142857142857</v>
       </c>
     </row>
@@ -5136,9 +6419,12 @@
         <v>700</v>
       </c>
       <c r="B428" t="n">
+        <v>3</v>
+      </c>
+      <c r="C428" t="n">
         <v>18</v>
       </c>
-      <c r="C428" t="n">
+      <c r="D428" t="n">
         <v>38.88888888888889</v>
       </c>
     </row>
@@ -5147,9 +6433,12 @@
         <v>960</v>
       </c>
       <c r="B429" t="n">
+        <v>3</v>
+      </c>
+      <c r="C429" t="n">
         <v>20</v>
       </c>
-      <c r="C429" t="n">
+      <c r="D429" t="n">
         <v>48</v>
       </c>
     </row>
@@ -5158,9 +6447,12 @@
         <v>775</v>
       </c>
       <c r="B430" t="n">
+        <v>3</v>
+      </c>
+      <c r="C430" t="n">
         <v>20</v>
       </c>
-      <c r="C430" t="n">
+      <c r="D430" t="n">
         <v>38.75</v>
       </c>
     </row>
@@ -5169,9 +6461,12 @@
         <v>1250</v>
       </c>
       <c r="B431" t="n">
+        <v>3</v>
+      </c>
+      <c r="C431" t="n">
         <v>40</v>
       </c>
-      <c r="C431" t="n">
+      <c r="D431" t="n">
         <v>31.25</v>
       </c>
     </row>
@@ -5180,9 +6475,12 @@
         <v>1380</v>
       </c>
       <c r="B432" t="n">
+        <v>3</v>
+      </c>
+      <c r="C432" t="n">
         <v>30</v>
       </c>
-      <c r="C432" t="n">
+      <c r="D432" t="n">
         <v>46</v>
       </c>
     </row>
@@ -5191,9 +6489,12 @@
         <v>1630</v>
       </c>
       <c r="B433" t="n">
+        <v>3</v>
+      </c>
+      <c r="C433" t="n">
         <v>54</v>
       </c>
-      <c r="C433" t="n">
+      <c r="D433" t="n">
         <v>30.18518518518519</v>
       </c>
     </row>
@@ -5202,9 +6503,12 @@
         <v>1650</v>
       </c>
       <c r="B434" t="n">
+        <v>3</v>
+      </c>
+      <c r="C434" t="n">
         <v>50</v>
       </c>
-      <c r="C434" t="n">
+      <c r="D434" t="n">
         <v>33</v>
       </c>
     </row>
@@ -5213,9 +6517,12 @@
         <v>1765</v>
       </c>
       <c r="B435" t="n">
+        <v>3</v>
+      </c>
+      <c r="C435" t="n">
         <v>62</v>
       </c>
-      <c r="C435" t="n">
+      <c r="D435" t="n">
         <v>28.46774193548387</v>
       </c>
     </row>
@@ -5224,9 +6531,12 @@
         <v>1900</v>
       </c>
       <c r="B436" t="n">
+        <v>3</v>
+      </c>
+      <c r="C436" t="n">
         <v>64</v>
       </c>
-      <c r="C436" t="n">
+      <c r="D436" t="n">
         <v>29.6875</v>
       </c>
     </row>
@@ -5235,9 +6545,12 @@
         <v>1787</v>
       </c>
       <c r="B437" t="n">
+        <v>3</v>
+      </c>
+      <c r="C437" t="n">
         <v>77</v>
       </c>
-      <c r="C437" t="n">
+      <c r="D437" t="n">
         <v>23.20779220779221</v>
       </c>
     </row>
@@ -5246,9 +6559,12 @@
         <v>1920</v>
       </c>
       <c r="B438" t="n">
+        <v>3</v>
+      </c>
+      <c r="C438" t="n">
         <v>64</v>
       </c>
-      <c r="C438" t="n">
+      <c r="D438" t="n">
         <v>30</v>
       </c>
     </row>
@@ -5257,9 +6573,12 @@
         <v>2132</v>
       </c>
       <c r="B439" t="n">
+        <v>3</v>
+      </c>
+      <c r="C439" t="n">
         <v>69</v>
       </c>
-      <c r="C439" t="n">
+      <c r="D439" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
@@ -5268,9 +6587,12 @@
         <v>2132</v>
       </c>
       <c r="B440" t="n">
+        <v>3</v>
+      </c>
+      <c r="C440" t="n">
         <v>69</v>
       </c>
-      <c r="C440" t="n">
+      <c r="D440" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
@@ -5279,9 +6601,12 @@
         <v>2200</v>
       </c>
       <c r="B441" t="n">
+        <v>3</v>
+      </c>
+      <c r="C441" t="n">
         <v>60</v>
       </c>
-      <c r="C441" t="n">
+      <c r="D441" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
@@ -5290,9 +6615,12 @@
         <v>2272</v>
       </c>
       <c r="B442" t="n">
+        <v>3</v>
+      </c>
+      <c r="C442" t="n">
         <v>69</v>
       </c>
-      <c r="C442" t="n">
+      <c r="D442" t="n">
         <v>32.92753623188405</v>
       </c>
     </row>
@@ -5301,9 +6629,12 @@
         <v>2400</v>
       </c>
       <c r="B443" t="n">
+        <v>3</v>
+      </c>
+      <c r="C443" t="n">
         <v>70</v>
       </c>
-      <c r="C443" t="n">
+      <c r="D443" t="n">
         <v>34.28571428571428</v>
       </c>
     </row>
@@ -5312,9 +6643,12 @@
         <v>2350</v>
       </c>
       <c r="B444" t="n">
+        <v>3</v>
+      </c>
+      <c r="C444" t="n">
         <v>70</v>
       </c>
-      <c r="C444" t="n">
+      <c r="D444" t="n">
         <v>33.57142857142857</v>
       </c>
     </row>
@@ -5323,9 +6657,12 @@
         <v>2657</v>
       </c>
       <c r="B445" t="n">
+        <v>3</v>
+      </c>
+      <c r="C445" t="n">
         <v>40</v>
       </c>
-      <c r="C445" t="n">
+      <c r="D445" t="n">
         <v>66.425</v>
       </c>
     </row>
@@ -5334,9 +6671,12 @@
         <v>2999</v>
       </c>
       <c r="B446" t="n">
+        <v>3</v>
+      </c>
+      <c r="C446" t="n">
         <v>76</v>
       </c>
-      <c r="C446" t="n">
+      <c r="D446" t="n">
         <v>39.46052631578947</v>
       </c>
     </row>
@@ -5345,9 +6685,12 @@
         <v>3000</v>
       </c>
       <c r="B447" t="n">
+        <v>3</v>
+      </c>
+      <c r="C447" t="n">
         <v>80</v>
       </c>
-      <c r="C447" t="n">
+      <c r="D447" t="n">
         <v>37.5</v>
       </c>
     </row>
@@ -5356,9 +6699,12 @@
         <v>3460</v>
       </c>
       <c r="B448" t="n">
+        <v>3</v>
+      </c>
+      <c r="C448" t="n">
         <v>103</v>
       </c>
-      <c r="C448" t="n">
+      <c r="D448" t="n">
         <v>33.59223300970874</v>
       </c>
     </row>
@@ -5367,9 +6713,12 @@
         <v>3600</v>
       </c>
       <c r="B449" t="n">
+        <v>3</v>
+      </c>
+      <c r="C449" t="n">
         <v>124</v>
       </c>
-      <c r="C449" t="n">
+      <c r="D449" t="n">
         <v>29.03225806451613</v>
       </c>
     </row>
@@ -5378,9 +6727,12 @@
         <v>16000</v>
       </c>
       <c r="B450" t="n">
+        <v>3</v>
+      </c>
+      <c r="C450" t="n">
         <v>347</v>
       </c>
-      <c r="C450" t="n">
+      <c r="D450" t="n">
         <v>46.10951008645533</v>
       </c>
     </row>
@@ -5389,9 +6741,12 @@
         <v>20000</v>
       </c>
       <c r="B451" t="n">
+        <v>3</v>
+      </c>
+      <c r="C451" t="n">
         <v>180</v>
       </c>
-      <c r="C451" t="n">
+      <c r="D451" t="n">
         <v>111.1111111111111</v>
       </c>
     </row>
@@ -5400,9 +6755,12 @@
         <v>2290</v>
       </c>
       <c r="B452" t="n">
+        <v>3</v>
+      </c>
+      <c r="C452" t="n">
         <v>70</v>
       </c>
-      <c r="C452" t="n">
+      <c r="D452" t="n">
         <v>32.71428571428572</v>
       </c>
     </row>
@@ -5411,9 +6769,12 @@
         <v>2927</v>
       </c>
       <c r="B453" t="n">
+        <v>3</v>
+      </c>
+      <c r="C453" t="n">
         <v>116</v>
       </c>
-      <c r="C453" t="n">
+      <c r="D453" t="n">
         <v>25.23275862068965</v>
       </c>
     </row>
@@ -5422,9 +6783,12 @@
         <v>700</v>
       </c>
       <c r="B454" t="n">
+        <v>3</v>
+      </c>
+      <c r="C454" t="n">
         <v>14</v>
       </c>
-      <c r="C454" t="n">
+      <c r="D454" t="n">
         <v>50</v>
       </c>
     </row>
@@ -5433,9 +6797,12 @@
         <v>755</v>
       </c>
       <c r="B455" t="n">
+        <v>3</v>
+      </c>
+      <c r="C455" t="n">
         <v>19</v>
       </c>
-      <c r="C455" t="n">
+      <c r="D455" t="n">
         <v>39.73684210526316</v>
       </c>
     </row>
@@ -5444,9 +6811,12 @@
         <v>990</v>
       </c>
       <c r="B456" t="n">
+        <v>3</v>
+      </c>
+      <c r="C456" t="n">
         <v>24</v>
       </c>
-      <c r="C456" t="n">
+      <c r="D456" t="n">
         <v>41.25</v>
       </c>
     </row>
@@ -5455,9 +6825,12 @@
         <v>1058</v>
       </c>
       <c r="B457" t="n">
+        <v>3</v>
+      </c>
+      <c r="C457" t="n">
         <v>21</v>
       </c>
-      <c r="C457" t="n">
+      <c r="D457" t="n">
         <v>50.38095238095238</v>
       </c>
     </row>
@@ -5466,9 +6839,12 @@
         <v>1095</v>
       </c>
       <c r="B458" t="n">
+        <v>3</v>
+      </c>
+      <c r="C458" t="n">
         <v>20</v>
       </c>
-      <c r="C458" t="n">
+      <c r="D458" t="n">
         <v>54.75</v>
       </c>
     </row>
@@ -5477,9 +6853,12 @@
         <v>1100</v>
       </c>
       <c r="B459" t="n">
+        <v>3</v>
+      </c>
+      <c r="C459" t="n">
         <v>37</v>
       </c>
-      <c r="C459" t="n">
+      <c r="D459" t="n">
         <v>29.72972972972973</v>
       </c>
     </row>
@@ -5488,9 +6867,12 @@
         <v>1280</v>
       </c>
       <c r="B460" t="n">
+        <v>3</v>
+      </c>
+      <c r="C460" t="n">
         <v>29</v>
       </c>
-      <c r="C460" t="n">
+      <c r="D460" t="n">
         <v>44.13793103448276</v>
       </c>
     </row>
@@ -5499,9 +6881,12 @@
         <v>1350</v>
       </c>
       <c r="B461" t="n">
+        <v>3</v>
+      </c>
+      <c r="C461" t="n">
         <v>35</v>
       </c>
-      <c r="C461" t="n">
+      <c r="D461" t="n">
         <v>38.57142857142857</v>
       </c>
     </row>
@@ -5510,9 +6895,12 @@
         <v>1400</v>
       </c>
       <c r="B462" t="n">
+        <v>3</v>
+      </c>
+      <c r="C462" t="n">
         <v>45</v>
       </c>
-      <c r="C462" t="n">
+      <c r="D462" t="n">
         <v>31.11111111111111</v>
       </c>
     </row>
@@ -5521,9 +6909,12 @@
         <v>1550</v>
       </c>
       <c r="B463" t="n">
+        <v>3</v>
+      </c>
+      <c r="C463" t="n">
         <v>33</v>
       </c>
-      <c r="C463" t="n">
+      <c r="D463" t="n">
         <v>46.96969696969697</v>
       </c>
     </row>
@@ -5532,9 +6923,12 @@
         <v>1900</v>
       </c>
       <c r="B464" t="n">
+        <v>3</v>
+      </c>
+      <c r="C464" t="n">
         <v>64</v>
       </c>
-      <c r="C464" t="n">
+      <c r="D464" t="n">
         <v>29.6875</v>
       </c>
     </row>
@@ -5543,9 +6937,12 @@
         <v>2200</v>
       </c>
       <c r="B465" t="n">
+        <v>3</v>
+      </c>
+      <c r="C465" t="n">
         <v>55</v>
       </c>
-      <c r="C465" t="n">
+      <c r="D465" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5554,9 +6951,12 @@
         <v>3140</v>
       </c>
       <c r="B466" t="n">
+        <v>3</v>
+      </c>
+      <c r="C466" t="n">
         <v>100</v>
       </c>
-      <c r="C466" t="n">
+      <c r="D466" t="n">
         <v>31.4</v>
       </c>
     </row>
@@ -5565,9 +6965,12 @@
         <v>600</v>
       </c>
       <c r="B467" t="n">
+        <v>3</v>
+      </c>
+      <c r="C467" t="n">
         <v>20</v>
       </c>
-      <c r="C467" t="n">
+      <c r="D467" t="n">
         <v>30</v>
       </c>
     </row>
@@ -5576,9 +6979,12 @@
         <v>600</v>
       </c>
       <c r="B468" t="n">
+        <v>3</v>
+      </c>
+      <c r="C468" t="n">
         <v>16</v>
       </c>
-      <c r="C468" t="n">
+      <c r="D468" t="n">
         <v>37.5</v>
       </c>
     </row>
@@ -5587,9 +6993,12 @@
         <v>890</v>
       </c>
       <c r="B469" t="n">
+        <v>3</v>
+      </c>
+      <c r="C469" t="n">
         <v>20</v>
       </c>
-      <c r="C469" t="n">
+      <c r="D469" t="n">
         <v>44.5</v>
       </c>
     </row>
@@ -5598,9 +7007,12 @@
         <v>1050</v>
       </c>
       <c r="B470" t="n">
+        <v>3</v>
+      </c>
+      <c r="C470" t="n">
         <v>30</v>
       </c>
-      <c r="C470" t="n">
+      <c r="D470" t="n">
         <v>35</v>
       </c>
     </row>
@@ -5609,9 +7021,12 @@
         <v>1100</v>
       </c>
       <c r="B471" t="n">
+        <v>3</v>
+      </c>
+      <c r="C471" t="n">
         <v>31</v>
       </c>
-      <c r="C471" t="n">
+      <c r="D471" t="n">
         <v>35.48387096774194</v>
       </c>
     </row>
@@ -5620,9 +7035,12 @@
         <v>1650</v>
       </c>
       <c r="B472" t="n">
+        <v>3</v>
+      </c>
+      <c r="C472" t="n">
         <v>49</v>
       </c>
-      <c r="C472" t="n">
+      <c r="D472" t="n">
         <v>33.67346938775511</v>
       </c>
     </row>
@@ -5631,9 +7049,12 @@
         <v>2090</v>
       </c>
       <c r="B473" t="n">
+        <v>3</v>
+      </c>
+      <c r="C473" t="n">
         <v>73</v>
       </c>
-      <c r="C473" t="n">
+      <c r="D473" t="n">
         <v>28.63013698630137</v>
       </c>
     </row>
@@ -5642,9 +7063,12 @@
         <v>6300</v>
       </c>
       <c r="B474" t="n">
+        <v>3</v>
+      </c>
+      <c r="C474" t="n">
         <v>112</v>
       </c>
-      <c r="C474" t="n">
+      <c r="D474" t="n">
         <v>56.25</v>
       </c>
     </row>
@@ -5653,9 +7077,12 @@
         <v>930</v>
       </c>
       <c r="B475" t="n">
+        <v>3</v>
+      </c>
+      <c r="C475" t="n">
         <v>16</v>
       </c>
-      <c r="C475" t="n">
+      <c r="D475" t="n">
         <v>58.125</v>
       </c>
     </row>
@@ -5664,9 +7091,12 @@
         <v>1980</v>
       </c>
       <c r="B476" t="n">
+        <v>3</v>
+      </c>
+      <c r="C476" t="n">
         <v>84</v>
       </c>
-      <c r="C476" t="n">
+      <c r="D476" t="n">
         <v>23.57142857142857</v>
       </c>
     </row>
@@ -5675,9 +7105,12 @@
         <v>885</v>
       </c>
       <c r="B477" t="n">
+        <v>3</v>
+      </c>
+      <c r="C477" t="n">
         <v>23</v>
       </c>
-      <c r="C477" t="n">
+      <c r="D477" t="n">
         <v>38.47826086956522</v>
       </c>
     </row>
@@ -5686,9 +7119,12 @@
         <v>1060</v>
       </c>
       <c r="B478" t="n">
+        <v>3</v>
+      </c>
+      <c r="C478" t="n">
         <v>47</v>
       </c>
-      <c r="C478" t="n">
+      <c r="D478" t="n">
         <v>22.5531914893617</v>
       </c>
     </row>
@@ -5697,9 +7133,12 @@
         <v>1200</v>
       </c>
       <c r="B479" t="n">
+        <v>3</v>
+      </c>
+      <c r="C479" t="n">
         <v>48</v>
       </c>
-      <c r="C479" t="n">
+      <c r="D479" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5708,9 +7147,12 @@
         <v>1500</v>
       </c>
       <c r="B480" t="n">
+        <v>3</v>
+      </c>
+      <c r="C480" t="n">
         <v>38</v>
       </c>
-      <c r="C480" t="n">
+      <c r="D480" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
@@ -5719,9 +7161,12 @@
         <v>890</v>
       </c>
       <c r="B481" t="n">
+        <v>3</v>
+      </c>
+      <c r="C481" t="n">
         <v>20</v>
       </c>
-      <c r="C481" t="n">
+      <c r="D481" t="n">
         <v>44.5</v>
       </c>
     </row>
@@ -5730,9 +7175,12 @@
         <v>1300</v>
       </c>
       <c r="B482" t="n">
+        <v>3</v>
+      </c>
+      <c r="C482" t="n">
         <v>42</v>
       </c>
-      <c r="C482" t="n">
+      <c r="D482" t="n">
         <v>30.95238095238095</v>
       </c>
     </row>
@@ -5741,9 +7189,12 @@
         <v>900</v>
       </c>
       <c r="B483" t="n">
+        <v>3</v>
+      </c>
+      <c r="C483" t="n">
         <v>29</v>
       </c>
-      <c r="C483" t="n">
+      <c r="D483" t="n">
         <v>31.03448275862069</v>
       </c>
     </row>
@@ -5752,9 +7203,12 @@
         <v>1150</v>
       </c>
       <c r="B484" t="n">
+        <v>3</v>
+      </c>
+      <c r="C484" t="n">
         <v>24</v>
       </c>
-      <c r="C484" t="n">
+      <c r="D484" t="n">
         <v>47.91666666666666</v>
       </c>
     </row>
@@ -5763,9 +7217,12 @@
         <v>840</v>
       </c>
       <c r="B485" t="n">
+        <v>3</v>
+      </c>
+      <c r="C485" t="n">
         <v>22</v>
       </c>
-      <c r="C485" t="n">
+      <c r="D485" t="n">
         <v>38.18181818181818</v>
       </c>
     </row>
@@ -5774,9 +7231,12 @@
         <v>928</v>
       </c>
       <c r="B486" t="n">
+        <v>3</v>
+      </c>
+      <c r="C486" t="n">
         <v>29</v>
       </c>
-      <c r="C486" t="n">
+      <c r="D486" t="n">
         <v>32</v>
       </c>
     </row>
@@ -5785,9 +7245,12 @@
         <v>981</v>
       </c>
       <c r="B487" t="n">
+        <v>3</v>
+      </c>
+      <c r="C487" t="n">
         <v>30</v>
       </c>
-      <c r="C487" t="n">
+      <c r="D487" t="n">
         <v>32.7</v>
       </c>
     </row>
@@ -5796,9 +7259,12 @@
         <v>1180</v>
       </c>
       <c r="B488" t="n">
+        <v>3</v>
+      </c>
+      <c r="C488" t="n">
         <v>31</v>
       </c>
-      <c r="C488" t="n">
+      <c r="D488" t="n">
         <v>38.06451612903226</v>
       </c>
     </row>
@@ -5807,9 +7273,12 @@
         <v>1198</v>
       </c>
       <c r="B489" t="n">
+        <v>3</v>
+      </c>
+      <c r="C489" t="n">
         <v>33</v>
       </c>
-      <c r="C489" t="n">
+      <c r="D489" t="n">
         <v>36.3030303030303</v>
       </c>
     </row>
@@ -5818,9 +7287,12 @@
         <v>1450</v>
       </c>
       <c r="B490" t="n">
+        <v>3</v>
+      </c>
+      <c r="C490" t="n">
         <v>47</v>
       </c>
-      <c r="C490" t="n">
+      <c r="D490" t="n">
         <v>30.85106382978723</v>
       </c>
     </row>
@@ -5829,9 +7301,12 @@
         <v>3000</v>
       </c>
       <c r="B491" t="n">
+        <v>3</v>
+      </c>
+      <c r="C491" t="n">
         <v>50</v>
       </c>
-      <c r="C491" t="n">
+      <c r="D491" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5840,9 +7315,12 @@
         <v>875</v>
       </c>
       <c r="B492" t="n">
+        <v>3</v>
+      </c>
+      <c r="C492" t="n">
         <v>18</v>
       </c>
-      <c r="C492" t="n">
+      <c r="D492" t="n">
         <v>48.61111111111111</v>
       </c>
     </row>
@@ -5851,9 +7329,12 @@
         <v>998</v>
       </c>
       <c r="B493" t="n">
+        <v>3</v>
+      </c>
+      <c r="C493" t="n">
         <v>34</v>
       </c>
-      <c r="C493" t="n">
+      <c r="D493" t="n">
         <v>29.35294117647059</v>
       </c>
     </row>
@@ -5862,9 +7343,12 @@
         <v>1000</v>
       </c>
       <c r="B494" t="n">
+        <v>3</v>
+      </c>
+      <c r="C494" t="n">
         <v>25</v>
       </c>
-      <c r="C494" t="n">
+      <c r="D494" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5873,9 +7357,12 @@
         <v>1250</v>
       </c>
       <c r="B495" t="n">
+        <v>3</v>
+      </c>
+      <c r="C495" t="n">
         <v>31</v>
       </c>
-      <c r="C495" t="n">
+      <c r="D495" t="n">
         <v>40.32258064516129</v>
       </c>
     </row>
@@ -5884,9 +7371,12 @@
         <v>1480</v>
       </c>
       <c r="B496" t="n">
+        <v>3</v>
+      </c>
+      <c r="C496" t="n">
         <v>40</v>
       </c>
-      <c r="C496" t="n">
+      <c r="D496" t="n">
         <v>37</v>
       </c>
     </row>
@@ -5895,9 +7385,12 @@
         <v>1900</v>
       </c>
       <c r="B497" t="n">
+        <v>3</v>
+      </c>
+      <c r="C497" t="n">
         <v>46</v>
       </c>
-      <c r="C497" t="n">
+      <c r="D497" t="n">
         <v>41.30434782608695</v>
       </c>
     </row>
@@ -5906,9 +7399,12 @@
         <v>2500</v>
       </c>
       <c r="B498" t="n">
+        <v>3</v>
+      </c>
+      <c r="C498" t="n">
         <v>70</v>
       </c>
-      <c r="C498" t="n">
+      <c r="D498" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
@@ -5917,9 +7413,12 @@
         <v>950</v>
       </c>
       <c r="B499" t="n">
+        <v>3</v>
+      </c>
+      <c r="C499" t="n">
         <v>28</v>
       </c>
-      <c r="C499" t="n">
+      <c r="D499" t="n">
         <v>33.92857142857143</v>
       </c>
     </row>
@@ -5928,9 +7427,12 @@
         <v>1180</v>
       </c>
       <c r="B500" t="n">
+        <v>3</v>
+      </c>
+      <c r="C500" t="n">
         <v>27</v>
       </c>
-      <c r="C500" t="n">
+      <c r="D500" t="n">
         <v>43.7037037037037</v>
       </c>
     </row>
@@ -5939,9 +7441,12 @@
         <v>1550</v>
       </c>
       <c r="B501" t="n">
+        <v>3</v>
+      </c>
+      <c r="C501" t="n">
         <v>40</v>
       </c>
-      <c r="C501" t="n">
+      <c r="D501" t="n">
         <v>38.75</v>
       </c>
     </row>
@@ -5950,9 +7455,12 @@
         <v>1333</v>
       </c>
       <c r="B502" t="n">
+        <v>3</v>
+      </c>
+      <c r="C502" t="n">
         <v>41</v>
       </c>
-      <c r="C502" t="n">
+      <c r="D502" t="n">
         <v>32.51219512195122</v>
       </c>
     </row>
@@ -5961,9 +7469,12 @@
         <v>1580</v>
       </c>
       <c r="B503" t="n">
+        <v>3</v>
+      </c>
+      <c r="C503" t="n">
         <v>40</v>
       </c>
-      <c r="C503" t="n">
+      <c r="D503" t="n">
         <v>39.5</v>
       </c>
     </row>
@@ -5972,9 +7483,12 @@
         <v>850</v>
       </c>
       <c r="B504" t="n">
+        <v>3</v>
+      </c>
+      <c r="C504" t="n">
         <v>27</v>
       </c>
-      <c r="C504" t="n">
+      <c r="D504" t="n">
         <v>31.48148148148148</v>
       </c>
     </row>
@@ -5983,9 +7497,12 @@
         <v>488</v>
       </c>
       <c r="B505" t="n">
+        <v>3</v>
+      </c>
+      <c r="C505" t="n">
         <v>13</v>
       </c>
-      <c r="C505" t="n">
+      <c r="D505" t="n">
         <v>37.53846153846154</v>
       </c>
     </row>
@@ -5994,9 +7511,12 @@
         <v>619</v>
       </c>
       <c r="B506" t="n">
+        <v>3</v>
+      </c>
+      <c r="C506" t="n">
         <v>18</v>
       </c>
-      <c r="C506" t="n">
+      <c r="D506" t="n">
         <v>34.38888888888889</v>
       </c>
     </row>
@@ -6005,9 +7525,12 @@
         <v>820</v>
       </c>
       <c r="B507" t="n">
+        <v>3</v>
+      </c>
+      <c r="C507" t="n">
         <v>23</v>
       </c>
-      <c r="C507" t="n">
+      <c r="D507" t="n">
         <v>35.65217391304348</v>
       </c>
     </row>
@@ -6016,9 +7539,12 @@
         <v>1350</v>
       </c>
       <c r="B508" t="n">
+        <v>3</v>
+      </c>
+      <c r="C508" t="n">
         <v>32</v>
       </c>
-      <c r="C508" t="n">
+      <c r="D508" t="n">
         <v>42.1875</v>
       </c>
     </row>
@@ -6027,9 +7553,12 @@
         <v>1475</v>
       </c>
       <c r="B509" t="n">
+        <v>3</v>
+      </c>
+      <c r="C509" t="n">
         <v>57</v>
       </c>
-      <c r="C509" t="n">
+      <c r="D509" t="n">
         <v>25.87719298245614</v>
       </c>
     </row>
@@ -6038,9 +7567,12 @@
         <v>1397</v>
       </c>
       <c r="B510" t="n">
+        <v>3</v>
+      </c>
+      <c r="C510" t="n">
         <v>38</v>
       </c>
-      <c r="C510" t="n">
+      <c r="D510" t="n">
         <v>36.76315789473684</v>
       </c>
     </row>
@@ -6049,9 +7581,12 @@
         <v>1460</v>
       </c>
       <c r="B511" t="n">
+        <v>3</v>
+      </c>
+      <c r="C511" t="n">
         <v>52</v>
       </c>
-      <c r="C511" t="n">
+      <c r="D511" t="n">
         <v>28.07692307692308</v>
       </c>
     </row>
@@ -6060,9 +7595,12 @@
         <v>3200</v>
       </c>
       <c r="B512" t="n">
+        <v>3</v>
+      </c>
+      <c r="C512" t="n">
         <v>114</v>
       </c>
-      <c r="C512" t="n">
+      <c r="D512" t="n">
         <v>28.07017543859649</v>
       </c>
     </row>
@@ -6071,9 +7609,12 @@
         <v>5000</v>
       </c>
       <c r="B513" t="n">
+        <v>3</v>
+      </c>
+      <c r="C513" t="n">
         <v>136</v>
       </c>
-      <c r="C513" t="n">
+      <c r="D513" t="n">
         <v>36.76470588235294</v>
       </c>
     </row>
@@ -6082,9 +7623,12 @@
         <v>790</v>
       </c>
       <c r="B514" t="n">
+        <v>3</v>
+      </c>
+      <c r="C514" t="n">
         <v>22</v>
       </c>
-      <c r="C514" t="n">
+      <c r="D514" t="n">
         <v>35.90909090909091</v>
       </c>
     </row>
@@ -6093,9 +7637,12 @@
         <v>800</v>
       </c>
       <c r="B515" t="n">
+        <v>3</v>
+      </c>
+      <c r="C515" t="n">
         <v>14</v>
       </c>
-      <c r="C515" t="n">
+      <c r="D515" t="n">
         <v>57.14285714285715</v>
       </c>
     </row>
@@ -6104,9 +7651,12 @@
         <v>810</v>
       </c>
       <c r="B516" t="n">
+        <v>3</v>
+      </c>
+      <c r="C516" t="n">
         <v>18</v>
       </c>
-      <c r="C516" t="n">
+      <c r="D516" t="n">
         <v>45</v>
       </c>
     </row>
@@ -6115,9 +7665,12 @@
         <v>940</v>
       </c>
       <c r="B517" t="n">
+        <v>3</v>
+      </c>
+      <c r="C517" t="n">
         <v>26</v>
       </c>
-      <c r="C517" t="n">
+      <c r="D517" t="n">
         <v>36.15384615384615</v>
       </c>
     </row>
@@ -6126,9 +7679,12 @@
         <v>898</v>
       </c>
       <c r="B518" t="n">
+        <v>3</v>
+      </c>
+      <c r="C518" t="n">
         <v>27</v>
       </c>
-      <c r="C518" t="n">
+      <c r="D518" t="n">
         <v>33.25925925925926</v>
       </c>
     </row>
@@ -6137,9 +7693,12 @@
         <v>1137</v>
       </c>
       <c r="B519" t="n">
+        <v>3</v>
+      </c>
+      <c r="C519" t="n">
         <v>33</v>
       </c>
-      <c r="C519" t="n">
+      <c r="D519" t="n">
         <v>34.45454545454545</v>
       </c>
     </row>
@@ -6148,9 +7707,12 @@
         <v>810</v>
       </c>
       <c r="B520" t="n">
+        <v>3</v>
+      </c>
+      <c r="C520" t="n">
         <v>18</v>
       </c>
-      <c r="C520" t="n">
+      <c r="D520" t="n">
         <v>45</v>
       </c>
     </row>
@@ -6159,9 +7721,12 @@
         <v>940</v>
       </c>
       <c r="B521" t="n">
+        <v>3</v>
+      </c>
+      <c r="C521" t="n">
         <v>26</v>
       </c>
-      <c r="C521" t="n">
+      <c r="D521" t="n">
         <v>36.15384615384615</v>
       </c>
     </row>
@@ -6170,9 +7735,12 @@
         <v>898</v>
       </c>
       <c r="B522" t="n">
+        <v>3</v>
+      </c>
+      <c r="C522" t="n">
         <v>27</v>
       </c>
-      <c r="C522" t="n">
+      <c r="D522" t="n">
         <v>33.25925925925926</v>
       </c>
     </row>
@@ -6181,9 +7749,12 @@
         <v>1137</v>
       </c>
       <c r="B523" t="n">
+        <v>3</v>
+      </c>
+      <c r="C523" t="n">
         <v>33</v>
       </c>
-      <c r="C523" t="n">
+      <c r="D523" t="n">
         <v>34.45454545454545</v>
       </c>
     </row>
@@ -6192,9 +7763,12 @@
         <v>1600</v>
       </c>
       <c r="B524" t="n">
+        <v>3</v>
+      </c>
+      <c r="C524" t="n">
         <v>60</v>
       </c>
-      <c r="C524" t="n">
+      <c r="D524" t="n">
         <v>26.66666666666667</v>
       </c>
     </row>
@@ -6203,9 +7777,12 @@
         <v>2097</v>
       </c>
       <c r="B525" t="n">
+        <v>3</v>
+      </c>
+      <c r="C525" t="n">
         <v>58</v>
       </c>
-      <c r="C525" t="n">
+      <c r="D525" t="n">
         <v>36.1551724137931</v>
       </c>
     </row>
@@ -6214,9 +7791,12 @@
         <v>733</v>
       </c>
       <c r="B526" t="n">
+        <v>3</v>
+      </c>
+      <c r="C526" t="n">
         <v>20</v>
       </c>
-      <c r="C526" t="n">
+      <c r="D526" t="n">
         <v>36.65</v>
       </c>
     </row>
@@ -6225,9 +7805,12 @@
         <v>12000</v>
       </c>
       <c r="B527" t="n">
+        <v>3</v>
+      </c>
+      <c r="C527" t="n">
         <v>230</v>
       </c>
-      <c r="C527" t="n">
+      <c r="D527" t="n">
         <v>52.17391304347826</v>
       </c>
     </row>
@@ -6236,9 +7819,12 @@
         <v>1166</v>
       </c>
       <c r="B528" t="n">
+        <v>3</v>
+      </c>
+      <c r="C528" t="n">
         <v>27</v>
       </c>
-      <c r="C528" t="n">
+      <c r="D528" t="n">
         <v>43.18518518518518</v>
       </c>
     </row>
@@ -6247,9 +7833,12 @@
         <v>1500</v>
       </c>
       <c r="B529" t="n">
+        <v>3</v>
+      </c>
+      <c r="C529" t="n">
         <v>38</v>
       </c>
-      <c r="C529" t="n">
+      <c r="D529" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
@@ -6258,9 +7847,12 @@
         <v>1900</v>
       </c>
       <c r="B530" t="n">
+        <v>3</v>
+      </c>
+      <c r="C530" t="n">
         <v>45</v>
       </c>
-      <c r="C530" t="n">
+      <c r="D530" t="n">
         <v>42.22222222222222</v>
       </c>
     </row>
@@ -6269,9 +7861,12 @@
         <v>1900</v>
       </c>
       <c r="B531" t="n">
+        <v>3</v>
+      </c>
+      <c r="C531" t="n">
         <v>64</v>
       </c>
-      <c r="C531" t="n">
+      <c r="D531" t="n">
         <v>29.6875</v>
       </c>
     </row>
@@ -6280,9 +7875,12 @@
         <v>1950</v>
       </c>
       <c r="B532" t="n">
+        <v>3</v>
+      </c>
+      <c r="C532" t="n">
         <v>45</v>
       </c>
-      <c r="C532" t="n">
+      <c r="D532" t="n">
         <v>43.33333333333334</v>
       </c>
     </row>
@@ -6291,9 +7889,12 @@
         <v>2000</v>
       </c>
       <c r="B533" t="n">
+        <v>3</v>
+      </c>
+      <c r="C533" t="n">
         <v>65</v>
       </c>
-      <c r="C533" t="n">
+      <c r="D533" t="n">
         <v>30.76923076923077</v>
       </c>
     </row>
@@ -6302,9 +7903,12 @@
         <v>2950</v>
       </c>
       <c r="B534" t="n">
+        <v>3</v>
+      </c>
+      <c r="C534" t="n">
         <v>95</v>
       </c>
-      <c r="C534" t="n">
+      <c r="D534" t="n">
         <v>31.05263157894737</v>
       </c>
     </row>
@@ -6313,9 +7917,12 @@
         <v>1200</v>
       </c>
       <c r="B535" t="n">
+        <v>3</v>
+      </c>
+      <c r="C535" t="n">
         <v>20</v>
       </c>
-      <c r="C535" t="n">
+      <c r="D535" t="n">
         <v>60</v>
       </c>
     </row>
@@ -6324,9 +7931,12 @@
         <v>1300</v>
       </c>
       <c r="B536" t="n">
+        <v>3</v>
+      </c>
+      <c r="C536" t="n">
         <v>20</v>
       </c>
-      <c r="C536" t="n">
+      <c r="D536" t="n">
         <v>65</v>
       </c>
     </row>
@@ -6335,9 +7945,12 @@
         <v>1400</v>
       </c>
       <c r="B537" t="n">
+        <v>3</v>
+      </c>
+      <c r="C537" t="n">
         <v>20</v>
       </c>
-      <c r="C537" t="n">
+      <c r="D537" t="n">
         <v>70</v>
       </c>
     </row>
@@ -6346,9 +7959,12 @@
         <v>1690</v>
       </c>
       <c r="B538" t="n">
+        <v>3</v>
+      </c>
+      <c r="C538" t="n">
         <v>58</v>
       </c>
-      <c r="C538" t="n">
+      <c r="D538" t="n">
         <v>29.13793103448276</v>
       </c>
     </row>
@@ -6357,9 +7973,12 @@
         <v>1940</v>
       </c>
       <c r="B539" t="n">
+        <v>3</v>
+      </c>
+      <c r="C539" t="n">
         <v>40</v>
       </c>
-      <c r="C539" t="n">
+      <c r="D539" t="n">
         <v>48.5</v>
       </c>
     </row>
@@ -6368,9 +7987,12 @@
         <v>2100</v>
       </c>
       <c r="B540" t="n">
+        <v>3</v>
+      </c>
+      <c r="C540" t="n">
         <v>70</v>
       </c>
-      <c r="C540" t="n">
+      <c r="D540" t="n">
         <v>30</v>
       </c>
     </row>
@@ -6379,9 +8001,12 @@
         <v>2490</v>
       </c>
       <c r="B541" t="n">
+        <v>3</v>
+      </c>
+      <c r="C541" t="n">
         <v>70</v>
       </c>
-      <c r="C541" t="n">
+      <c r="D541" t="n">
         <v>35.57142857142857</v>
       </c>
     </row>
@@ -6390,9 +8015,12 @@
         <v>1490</v>
       </c>
       <c r="B542" t="n">
+        <v>3</v>
+      </c>
+      <c r="C542" t="n">
         <v>48</v>
       </c>
-      <c r="C542" t="n">
+      <c r="D542" t="n">
         <v>31.04166666666667</v>
       </c>
     </row>
@@ -6401,9 +8029,12 @@
         <v>2020</v>
       </c>
       <c r="B543" t="n">
+        <v>3</v>
+      </c>
+      <c r="C543" t="n">
         <v>58</v>
       </c>
-      <c r="C543" t="n">
+      <c r="D543" t="n">
         <v>34.82758620689656</v>
       </c>
     </row>
@@ -6412,9 +8043,12 @@
         <v>2050</v>
       </c>
       <c r="B544" t="n">
+        <v>3</v>
+      </c>
+      <c r="C544" t="n">
         <v>70</v>
       </c>
-      <c r="C544" t="n">
+      <c r="D544" t="n">
         <v>29.28571428571428</v>
       </c>
     </row>
@@ -6423,9 +8057,12 @@
         <v>1220</v>
       </c>
       <c r="B545" t="n">
+        <v>3</v>
+      </c>
+      <c r="C545" t="n">
         <v>42</v>
       </c>
-      <c r="C545" t="n">
+      <c r="D545" t="n">
         <v>29.04761904761905</v>
       </c>
     </row>
@@ -6434,9 +8071,12 @@
         <v>1610</v>
       </c>
       <c r="B546" t="n">
+        <v>3</v>
+      </c>
+      <c r="C546" t="n">
         <v>44</v>
       </c>
-      <c r="C546" t="n">
+      <c r="D546" t="n">
         <v>36.59090909090909</v>
       </c>
     </row>

--- a/data/house/house.xlsx
+++ b/data/house/house.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,26 +413,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D546"/>
+  <dimension ref="A1:C546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>loyer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>toto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>surface</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>loyer_m2</t>
         </is>
@@ -455,12 +438,9 @@
         <v>1330</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
-      </c>
-      <c r="D2" t="n">
         <v>35.94594594594594</v>
       </c>
     </row>
@@ -469,12 +449,9 @@
         <v>1400</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D3" t="n">
         <v>43.75</v>
       </c>
     </row>
@@ -483,12 +460,9 @@
         <v>904</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
-      </c>
-      <c r="D4" t="n">
         <v>34.76923076923077</v>
       </c>
     </row>
@@ -497,12 +471,9 @@
         <v>955</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D5" t="n">
         <v>31.83333333333333</v>
       </c>
     </row>
@@ -511,12 +482,9 @@
         <v>2545</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C6" t="n">
-        <v>70</v>
-      </c>
-      <c r="D6" t="n">
         <v>36.35714285714285</v>
       </c>
     </row>
@@ -525,12 +493,9 @@
         <v>970</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
-      </c>
-      <c r="D7" t="n">
         <v>40.41666666666666</v>
       </c>
     </row>
@@ -539,12 +504,9 @@
         <v>1560</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C8" t="n">
-        <v>41</v>
-      </c>
-      <c r="D8" t="n">
         <v>38.04878048780488</v>
       </c>
     </row>
@@ -553,12 +515,9 @@
         <v>1960</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
-      </c>
-      <c r="D9" t="n">
         <v>29.25373134328358</v>
       </c>
     </row>
@@ -567,12 +526,9 @@
         <v>2000</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>63</v>
-      </c>
-      <c r="D10" t="n">
         <v>31.74603174603175</v>
       </c>
     </row>
@@ -581,12 +537,9 @@
         <v>2600</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>70</v>
-      </c>
-      <c r="D11" t="n">
         <v>37.14285714285715</v>
       </c>
     </row>
@@ -595,12 +548,9 @@
         <v>3280</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
-      </c>
-      <c r="D12" t="n">
         <v>40.49382716049383</v>
       </c>
     </row>
@@ -609,12 +559,9 @@
         <v>16000</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>347</v>
       </c>
       <c r="C13" t="n">
-        <v>347</v>
-      </c>
-      <c r="D13" t="n">
         <v>46.10951008645533</v>
       </c>
     </row>
@@ -623,12 +570,9 @@
         <v>980</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
-      </c>
-      <c r="D14" t="n">
         <v>37.69230769230769</v>
       </c>
     </row>
@@ -637,12 +581,9 @@
         <v>1250</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
-      </c>
-      <c r="D15" t="n">
         <v>34.72222222222222</v>
       </c>
     </row>
@@ -651,12 +592,9 @@
         <v>752</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
-      </c>
-      <c r="D16" t="n">
         <v>39.57894736842105</v>
       </c>
     </row>
@@ -665,12 +603,9 @@
         <v>815</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D17" t="n">
         <v>40.75</v>
       </c>
     </row>
@@ -679,12 +614,9 @@
         <v>1147</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
-      </c>
-      <c r="D18" t="n">
         <v>45.88</v>
       </c>
     </row>
@@ -693,12 +625,9 @@
         <v>1500</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>35</v>
-      </c>
-      <c r="D19" t="n">
         <v>42.85714285714285</v>
       </c>
     </row>
@@ -707,12 +636,9 @@
         <v>3587</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="C20" t="n">
-        <v>120</v>
-      </c>
-      <c r="D20" t="n">
         <v>29.89166666666667</v>
       </c>
     </row>
@@ -721,12 +647,9 @@
         <v>1355</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C21" t="n">
-        <v>40</v>
-      </c>
-      <c r="D21" t="n">
         <v>33.875</v>
       </c>
     </row>
@@ -735,12 +658,9 @@
         <v>1245</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
-      </c>
-      <c r="D22" t="n">
         <v>41.5</v>
       </c>
     </row>
@@ -749,12 +669,9 @@
         <v>1100</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
-      </c>
-      <c r="D23" t="n">
         <v>44</v>
       </c>
     </row>
@@ -763,12 +680,9 @@
         <v>1120</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C24" t="n">
-        <v>21</v>
-      </c>
-      <c r="D24" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
@@ -777,12 +691,9 @@
         <v>1225</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C25" t="n">
-        <v>44</v>
-      </c>
-      <c r="D25" t="n">
         <v>27.84090909090909</v>
       </c>
     </row>
@@ -791,12 +702,9 @@
         <v>1250</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C26" t="n">
-        <v>35</v>
-      </c>
-      <c r="D26" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
@@ -805,12 +713,9 @@
         <v>1280</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C27" t="n">
-        <v>54</v>
-      </c>
-      <c r="D27" t="n">
         <v>23.7037037037037</v>
       </c>
     </row>
@@ -819,12 +724,9 @@
         <v>1114</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C28" t="n">
-        <v>39</v>
-      </c>
-      <c r="D28" t="n">
         <v>28.56410256410257</v>
       </c>
     </row>
@@ -833,12 +735,9 @@
         <v>1290</v>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C29" t="n">
-        <v>34</v>
-      </c>
-      <c r="D29" t="n">
         <v>37.94117647058823</v>
       </c>
     </row>
@@ -847,12 +746,9 @@
         <v>1300</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>28</v>
-      </c>
-      <c r="D30" t="n">
         <v>46.42857142857143</v>
       </c>
     </row>
@@ -861,12 +757,9 @@
         <v>1300</v>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>32</v>
-      </c>
-      <c r="D31" t="n">
         <v>40.625</v>
       </c>
     </row>
@@ -875,12 +768,9 @@
         <v>1304</v>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C32" t="n">
-        <v>40</v>
-      </c>
-      <c r="D32" t="n">
         <v>32.6</v>
       </c>
     </row>
@@ -889,12 +779,9 @@
         <v>1340</v>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C33" t="n">
-        <v>42</v>
-      </c>
-      <c r="D33" t="n">
         <v>31.90476190476191</v>
       </c>
     </row>
@@ -903,12 +790,9 @@
         <v>1344</v>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C34" t="n">
-        <v>31</v>
-      </c>
-      <c r="D34" t="n">
         <v>43.35483870967742</v>
       </c>
     </row>
@@ -917,12 +801,9 @@
         <v>1290</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C35" t="n">
-        <v>33</v>
-      </c>
-      <c r="D35" t="n">
         <v>39.09090909090909</v>
       </c>
     </row>
@@ -931,12 +812,9 @@
         <v>1364</v>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>39</v>
-      </c>
-      <c r="D36" t="n">
         <v>34.97435897435897</v>
       </c>
     </row>
@@ -945,12 +823,9 @@
         <v>1400</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C37" t="n">
-        <v>47</v>
-      </c>
-      <c r="D37" t="n">
         <v>29.78723404255319</v>
       </c>
     </row>
@@ -959,12 +834,9 @@
         <v>1400</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C38" t="n">
-        <v>33</v>
-      </c>
-      <c r="D38" t="n">
         <v>42.42424242424242</v>
       </c>
     </row>
@@ -973,12 +845,9 @@
         <v>1420</v>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C39" t="n">
-        <v>37</v>
-      </c>
-      <c r="D39" t="n">
         <v>38.37837837837838</v>
       </c>
     </row>
@@ -987,12 +856,9 @@
         <v>1420</v>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C40" t="n">
-        <v>42</v>
-      </c>
-      <c r="D40" t="n">
         <v>33.80952380952381</v>
       </c>
     </row>
@@ -1001,12 +867,9 @@
         <v>1445</v>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C41" t="n">
-        <v>46</v>
-      </c>
-      <c r="D41" t="n">
         <v>31.41304347826087</v>
       </c>
     </row>
@@ -1015,12 +878,9 @@
         <v>1500</v>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C42" t="n">
-        <v>37</v>
-      </c>
-      <c r="D42" t="n">
         <v>40.54054054054054</v>
       </c>
     </row>
@@ -1029,12 +889,9 @@
         <v>1544</v>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>46</v>
-      </c>
-      <c r="D43" t="n">
         <v>33.56521739130435</v>
       </c>
     </row>
@@ -1043,12 +900,9 @@
         <v>1550</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C44" t="n">
-        <v>42</v>
-      </c>
-      <c r="D44" t="n">
         <v>36.90476190476191</v>
       </c>
     </row>
@@ -1057,12 +911,9 @@
         <v>1500</v>
       </c>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C45" t="n">
-        <v>49</v>
-      </c>
-      <c r="D45" t="n">
         <v>30.61224489795918</v>
       </c>
     </row>
@@ -1071,12 +922,9 @@
         <v>1612</v>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C46" t="n">
-        <v>48</v>
-      </c>
-      <c r="D46" t="n">
         <v>33.58333333333334</v>
       </c>
     </row>
@@ -1085,12 +933,9 @@
         <v>1650</v>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>50</v>
-      </c>
-      <c r="D47" t="n">
         <v>33</v>
       </c>
     </row>
@@ -1099,12 +944,9 @@
         <v>1533</v>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C48" t="n">
-        <v>54</v>
-      </c>
-      <c r="D48" t="n">
         <v>28.38888888888889</v>
       </c>
     </row>
@@ -1113,12 +955,9 @@
         <v>1663</v>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C49" t="n">
-        <v>54</v>
-      </c>
-      <c r="D49" t="n">
         <v>30.7962962962963</v>
       </c>
     </row>
@@ -1127,12 +966,9 @@
         <v>1584</v>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C50" t="n">
-        <v>45</v>
-      </c>
-      <c r="D50" t="n">
         <v>35.2</v>
       </c>
     </row>
@@ -1141,12 +977,9 @@
         <v>1680</v>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C51" t="n">
-        <v>53</v>
-      </c>
-      <c r="D51" t="n">
         <v>31.69811320754717</v>
       </c>
     </row>
@@ -1155,12 +988,9 @@
         <v>1700</v>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C52" t="n">
-        <v>40</v>
-      </c>
-      <c r="D52" t="n">
         <v>42.5</v>
       </c>
     </row>
@@ -1169,12 +999,9 @@
         <v>1700</v>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C53" t="n">
-        <v>35</v>
-      </c>
-      <c r="D53" t="n">
         <v>48.57142857142857</v>
       </c>
     </row>
@@ -1183,12 +1010,9 @@
         <v>1700</v>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C54" t="n">
-        <v>40</v>
-      </c>
-      <c r="D54" t="n">
         <v>42.5</v>
       </c>
     </row>
@@ -1197,12 +1021,9 @@
         <v>1700</v>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C55" t="n">
-        <v>35</v>
-      </c>
-      <c r="D55" t="n">
         <v>48.57142857142857</v>
       </c>
     </row>
@@ -1211,12 +1032,9 @@
         <v>1700</v>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C56" t="n">
-        <v>60</v>
-      </c>
-      <c r="D56" t="n">
         <v>28.33333333333333</v>
       </c>
     </row>
@@ -1225,12 +1043,9 @@
         <v>1600</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C57" t="n">
-        <v>30</v>
-      </c>
-      <c r="D57" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
@@ -1239,12 +1054,9 @@
         <v>1700</v>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C58" t="n">
-        <v>34</v>
-      </c>
-      <c r="D58" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1253,12 +1065,9 @@
         <v>1710</v>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C59" t="n">
-        <v>64</v>
-      </c>
-      <c r="D59" t="n">
         <v>26.71875</v>
       </c>
     </row>
@@ -1267,12 +1076,9 @@
         <v>1600</v>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C60" t="n">
-        <v>47</v>
-      </c>
-      <c r="D60" t="n">
         <v>34.04255319148936</v>
       </c>
     </row>
@@ -1281,12 +1087,9 @@
         <v>1750</v>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="C61" t="n">
-        <v>43</v>
-      </c>
-      <c r="D61" t="n">
         <v>40.69767441860465</v>
       </c>
     </row>
@@ -1295,12 +1098,9 @@
         <v>1765</v>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C62" t="n">
-        <v>62</v>
-      </c>
-      <c r="D62" t="n">
         <v>28.46774193548387</v>
       </c>
     </row>
@@ -1309,12 +1109,9 @@
         <v>1790</v>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C63" t="n">
-        <v>50</v>
-      </c>
-      <c r="D63" t="n">
         <v>35.8</v>
       </c>
     </row>
@@ -1323,12 +1120,9 @@
         <v>1689</v>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C64" t="n">
-        <v>53</v>
-      </c>
-      <c r="D64" t="n">
         <v>31.86792452830189</v>
       </c>
     </row>
@@ -1337,12 +1131,9 @@
         <v>1795</v>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C65" t="n">
-        <v>50</v>
-      </c>
-      <c r="D65" t="n">
         <v>35.9</v>
       </c>
     </row>
@@ -1351,12 +1142,9 @@
         <v>1800</v>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C66" t="n">
-        <v>50</v>
-      </c>
-      <c r="D66" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1365,12 +1153,9 @@
         <v>1700</v>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C67" t="n">
-        <v>60</v>
-      </c>
-      <c r="D67" t="n">
         <v>28.33333333333333</v>
       </c>
     </row>
@@ -1379,12 +1164,9 @@
         <v>1800</v>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C68" t="n">
-        <v>42</v>
-      </c>
-      <c r="D68" t="n">
         <v>42.85714285714285</v>
       </c>
     </row>
@@ -1393,12 +1175,9 @@
         <v>1850</v>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C69" t="n">
-        <v>52</v>
-      </c>
-      <c r="D69" t="n">
         <v>35.57692307692308</v>
       </c>
     </row>
@@ -1407,12 +1186,9 @@
         <v>1850</v>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C70" t="n">
-        <v>45</v>
-      </c>
-      <c r="D70" t="n">
         <v>41.11111111111111</v>
       </c>
     </row>
@@ -1421,12 +1197,9 @@
         <v>1750</v>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C71" t="n">
-        <v>41</v>
-      </c>
-      <c r="D71" t="n">
         <v>42.68292682926829</v>
       </c>
     </row>
@@ -1435,12 +1208,9 @@
         <v>1850</v>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C72" t="n">
-        <v>63</v>
-      </c>
-      <c r="D72" t="n">
         <v>29.36507936507936</v>
       </c>
     </row>
@@ -1449,12 +1219,9 @@
         <v>1850</v>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C73" t="n">
-        <v>53</v>
-      </c>
-      <c r="D73" t="n">
         <v>34.90566037735849</v>
       </c>
     </row>
@@ -1463,12 +1230,9 @@
         <v>1850</v>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C74" t="n">
-        <v>45</v>
-      </c>
-      <c r="D74" t="n">
         <v>41.11111111111111</v>
       </c>
     </row>
@@ -1477,12 +1241,9 @@
         <v>1875</v>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C75" t="n">
-        <v>53</v>
-      </c>
-      <c r="D75" t="n">
         <v>35.37735849056604</v>
       </c>
     </row>
@@ -1491,12 +1252,9 @@
         <v>1900</v>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C76" t="n">
-        <v>55</v>
-      </c>
-      <c r="D76" t="n">
         <v>34.54545454545455</v>
       </c>
     </row>
@@ -1505,12 +1263,9 @@
         <v>1950</v>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C77" t="n">
-        <v>46</v>
-      </c>
-      <c r="D77" t="n">
         <v>42.39130434782609</v>
       </c>
     </row>
@@ -1519,12 +1274,9 @@
         <v>1750</v>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="C78" t="n">
-        <v>73</v>
-      </c>
-      <c r="D78" t="n">
         <v>23.97260273972603</v>
       </c>
     </row>
@@ -1533,12 +1285,9 @@
         <v>2000</v>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C79" t="n">
-        <v>53</v>
-      </c>
-      <c r="D79" t="n">
         <v>37.73584905660378</v>
       </c>
     </row>
@@ -1547,12 +1296,9 @@
         <v>2044</v>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C80" t="n">
-        <v>64</v>
-      </c>
-      <c r="D80" t="n">
         <v>31.9375</v>
       </c>
     </row>
@@ -1561,12 +1307,9 @@
         <v>2100</v>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C81" t="n">
-        <v>38</v>
-      </c>
-      <c r="D81" t="n">
         <v>55.26315789473684</v>
       </c>
     </row>
@@ -1575,12 +1318,9 @@
         <v>2100</v>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="C82" t="n">
-        <v>65</v>
-      </c>
-      <c r="D82" t="n">
         <v>32.30769230769231</v>
       </c>
     </row>
@@ -1589,12 +1329,9 @@
         <v>2100</v>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C83" t="n">
-        <v>59</v>
-      </c>
-      <c r="D83" t="n">
         <v>35.59322033898305</v>
       </c>
     </row>
@@ -1603,12 +1340,9 @@
         <v>2100</v>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C84" t="n">
-        <v>47</v>
-      </c>
-      <c r="D84" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -1617,12 +1351,9 @@
         <v>2107</v>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="C85" t="n">
-        <v>75</v>
-      </c>
-      <c r="D85" t="n">
         <v>28.09333333333333</v>
       </c>
     </row>
@@ -1631,12 +1362,9 @@
         <v>2116</v>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="C86" t="n">
-        <v>83</v>
-      </c>
-      <c r="D86" t="n">
         <v>25.49397590361446</v>
       </c>
     </row>
@@ -1645,12 +1373,9 @@
         <v>2132</v>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C87" t="n">
-        <v>69</v>
-      </c>
-      <c r="D87" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
@@ -1659,12 +1384,9 @@
         <v>2000</v>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C88" t="n">
-        <v>68</v>
-      </c>
-      <c r="D88" t="n">
         <v>29.41176470588235</v>
       </c>
     </row>
@@ -1673,12 +1395,9 @@
         <v>2180</v>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C89" t="n">
-        <v>69</v>
-      </c>
-      <c r="D89" t="n">
         <v>31.59420289855073</v>
       </c>
     </row>
@@ -1687,12 +1406,9 @@
         <v>2100</v>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="C90" t="n">
-        <v>72</v>
-      </c>
-      <c r="D90" t="n">
         <v>29.16666666666667</v>
       </c>
     </row>
@@ -1701,12 +1417,9 @@
         <v>2200</v>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C91" t="n">
-        <v>40</v>
-      </c>
-      <c r="D91" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1715,12 +1428,9 @@
         <v>2200</v>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C92" t="n">
-        <v>50</v>
-      </c>
-      <c r="D92" t="n">
         <v>44</v>
       </c>
     </row>
@@ -1729,12 +1439,9 @@
         <v>2200</v>
       </c>
       <c r="B93" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C93" t="n">
-        <v>60</v>
-      </c>
-      <c r="D93" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
@@ -1743,12 +1450,9 @@
         <v>2216</v>
       </c>
       <c r="B94" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C94" t="n">
-        <v>68</v>
-      </c>
-      <c r="D94" t="n">
         <v>32.58823529411764</v>
       </c>
     </row>
@@ -1757,12 +1461,9 @@
         <v>2240</v>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C95" t="n">
-        <v>69</v>
-      </c>
-      <c r="D95" t="n">
         <v>32.46376811594203</v>
       </c>
     </row>
@@ -1771,12 +1472,9 @@
         <v>2249</v>
       </c>
       <c r="B96" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C96" t="n">
-        <v>35</v>
-      </c>
-      <c r="D96" t="n">
         <v>64.25714285714285</v>
       </c>
     </row>
@@ -1785,12 +1483,9 @@
         <v>2282</v>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="C97" t="n">
-        <v>78</v>
-      </c>
-      <c r="D97" t="n">
         <v>29.25641025641026</v>
       </c>
     </row>
@@ -1799,12 +1494,9 @@
         <v>2300</v>
       </c>
       <c r="B98" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="C98" t="n">
-        <v>65</v>
-      </c>
-      <c r="D98" t="n">
         <v>35.38461538461539</v>
       </c>
     </row>
@@ -1813,12 +1505,9 @@
         <v>2300</v>
       </c>
       <c r="B99" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C99" t="n">
-        <v>54</v>
-      </c>
-      <c r="D99" t="n">
         <v>42.5925925925926</v>
       </c>
     </row>
@@ -1827,12 +1516,9 @@
         <v>2320</v>
       </c>
       <c r="B100" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C100" t="n">
-        <v>60</v>
-      </c>
-      <c r="D100" t="n">
         <v>38.66666666666666</v>
       </c>
     </row>
@@ -1841,12 +1527,9 @@
         <v>2324</v>
       </c>
       <c r="B101" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C101" t="n">
-        <v>64</v>
-      </c>
-      <c r="D101" t="n">
         <v>36.3125</v>
       </c>
     </row>
@@ -1855,12 +1538,9 @@
         <v>2324</v>
       </c>
       <c r="B102" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C102" t="n">
-        <v>64</v>
-      </c>
-      <c r="D102" t="n">
         <v>36.3125</v>
       </c>
     </row>
@@ -1869,12 +1549,9 @@
         <v>2367</v>
       </c>
       <c r="B103" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="C103" t="n">
-        <v>76</v>
-      </c>
-      <c r="D103" t="n">
         <v>31.14473684210526</v>
       </c>
     </row>
@@ -1883,12 +1560,9 @@
         <v>2400</v>
       </c>
       <c r="B104" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C104" t="n">
-        <v>70</v>
-      </c>
-      <c r="D104" t="n">
         <v>34.28571428571428</v>
       </c>
     </row>
@@ -1897,12 +1571,9 @@
         <v>2400</v>
       </c>
       <c r="B105" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C105" t="n">
-        <v>70</v>
-      </c>
-      <c r="D105" t="n">
         <v>34.28571428571428</v>
       </c>
     </row>
@@ -1911,12 +1582,9 @@
         <v>2445</v>
       </c>
       <c r="B106" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C106" t="n">
-        <v>71</v>
-      </c>
-      <c r="D106" t="n">
         <v>34.43661971830986</v>
       </c>
     </row>
@@ -1925,12 +1593,9 @@
         <v>2450</v>
       </c>
       <c r="B107" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="C107" t="n">
-        <v>84</v>
-      </c>
-      <c r="D107" t="n">
         <v>29.16666666666667</v>
       </c>
     </row>
@@ -1939,12 +1604,9 @@
         <v>2450</v>
       </c>
       <c r="B108" t="n">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="C108" t="n">
-        <v>90</v>
-      </c>
-      <c r="D108" t="n">
         <v>27.22222222222222</v>
       </c>
     </row>
@@ -1953,12 +1615,9 @@
         <v>2280</v>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="C109" t="n">
-        <v>96</v>
-      </c>
-      <c r="D109" t="n">
         <v>23.75</v>
       </c>
     </row>
@@ -1967,12 +1626,9 @@
         <v>2250</v>
       </c>
       <c r="B110" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="C110" t="n">
-        <v>89</v>
-      </c>
-      <c r="D110" t="n">
         <v>25.28089887640449</v>
       </c>
     </row>
@@ -1981,12 +1637,9 @@
         <v>2415</v>
       </c>
       <c r="B111" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="C111" t="n">
-        <v>75</v>
-      </c>
-      <c r="D111" t="n">
         <v>32.2</v>
       </c>
     </row>
@@ -1995,12 +1648,9 @@
         <v>2470</v>
       </c>
       <c r="B112" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C112" t="n">
-        <v>55</v>
-      </c>
-      <c r="D112" t="n">
         <v>44.90909090909091</v>
       </c>
     </row>
@@ -2009,12 +1659,9 @@
         <v>2600</v>
       </c>
       <c r="B113" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C113" t="n">
-        <v>56</v>
-      </c>
-      <c r="D113" t="n">
         <v>46.42857142857143</v>
       </c>
     </row>
@@ -2023,12 +1670,9 @@
         <v>2650</v>
       </c>
       <c r="B114" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C114" t="n">
-        <v>56</v>
-      </c>
-      <c r="D114" t="n">
         <v>47.32142857142857</v>
       </c>
     </row>
@@ -2037,12 +1681,9 @@
         <v>2650</v>
       </c>
       <c r="B115" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C115" t="n">
-        <v>56</v>
-      </c>
-      <c r="D115" t="n">
         <v>47.32142857142857</v>
       </c>
     </row>
@@ -2051,12 +1692,9 @@
         <v>2675</v>
       </c>
       <c r="B116" t="n">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="C116" t="n">
-        <v>91</v>
-      </c>
-      <c r="D116" t="n">
         <v>29.39560439560439</v>
       </c>
     </row>
@@ -2065,12 +1703,9 @@
         <v>2550</v>
       </c>
       <c r="B117" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C117" t="n">
-        <v>100</v>
-      </c>
-      <c r="D117" t="n">
         <v>25.5</v>
       </c>
     </row>
@@ -2079,12 +1714,9 @@
         <v>2700</v>
       </c>
       <c r="B118" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="C118" t="n">
-        <v>73</v>
-      </c>
-      <c r="D118" t="n">
         <v>36.98630136986301</v>
       </c>
     </row>
@@ -2093,12 +1725,9 @@
         <v>2780</v>
       </c>
       <c r="B119" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C119" t="n">
-        <v>94</v>
-      </c>
-      <c r="D119" t="n">
         <v>29.57446808510638</v>
       </c>
     </row>
@@ -2107,12 +1736,9 @@
         <v>2800</v>
       </c>
       <c r="B120" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C120" t="n">
-        <v>50</v>
-      </c>
-      <c r="D120" t="n">
         <v>56</v>
       </c>
     </row>
@@ -2121,12 +1747,9 @@
         <v>2800</v>
       </c>
       <c r="B121" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C121" t="n">
-        <v>60</v>
-      </c>
-      <c r="D121" t="n">
         <v>46.66666666666666</v>
       </c>
     </row>
@@ -2135,12 +1758,9 @@
         <v>2850</v>
       </c>
       <c r="B122" t="n">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="C122" t="n">
-        <v>90</v>
-      </c>
-      <c r="D122" t="n">
         <v>31.66666666666667</v>
       </c>
     </row>
@@ -2149,12 +1769,9 @@
         <v>2941</v>
       </c>
       <c r="B123" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="C123" t="n">
-        <v>96</v>
-      </c>
-      <c r="D123" t="n">
         <v>30.63541666666667</v>
       </c>
     </row>
@@ -2163,12 +1780,9 @@
         <v>2941</v>
       </c>
       <c r="B124" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="C124" t="n">
-        <v>96</v>
-      </c>
-      <c r="D124" t="n">
         <v>30.63541666666667</v>
       </c>
     </row>
@@ -2177,12 +1791,9 @@
         <v>3000</v>
       </c>
       <c r="B125" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C125" t="n">
-        <v>50</v>
-      </c>
-      <c r="D125" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2191,12 +1802,9 @@
         <v>2800</v>
       </c>
       <c r="B126" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="C126" t="n">
-        <v>83</v>
-      </c>
-      <c r="D126" t="n">
         <v>33.73493975903614</v>
       </c>
     </row>
@@ -2205,12 +1813,9 @@
         <v>3000</v>
       </c>
       <c r="B127" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="C127" t="n">
-        <v>99</v>
-      </c>
-      <c r="D127" t="n">
         <v>30.3030303030303</v>
       </c>
     </row>
@@ -2219,12 +1824,9 @@
         <v>3000</v>
       </c>
       <c r="B128" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="C128" t="n">
-        <v>88</v>
-      </c>
-      <c r="D128" t="n">
         <v>34.09090909090909</v>
       </c>
     </row>
@@ -2233,12 +1835,9 @@
         <v>3010</v>
       </c>
       <c r="B129" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="C129" t="n">
-        <v>104</v>
-      </c>
-      <c r="D129" t="n">
         <v>28.94230769230769</v>
       </c>
     </row>
@@ -2247,12 +1846,9 @@
         <v>2950</v>
       </c>
       <c r="B130" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="C130" t="n">
-        <v>85</v>
-      </c>
-      <c r="D130" t="n">
         <v>34.70588235294117</v>
       </c>
     </row>
@@ -2261,12 +1857,9 @@
         <v>3200</v>
       </c>
       <c r="B131" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C131" t="n">
-        <v>70</v>
-      </c>
-      <c r="D131" t="n">
         <v>45.71428571428572</v>
       </c>
     </row>
@@ -2275,12 +1868,9 @@
         <v>3200</v>
       </c>
       <c r="B132" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C132" t="n">
-        <v>60</v>
-      </c>
-      <c r="D132" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
@@ -2289,12 +1879,9 @@
         <v>3200</v>
       </c>
       <c r="B133" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="C133" t="n">
-        <v>84</v>
-      </c>
-      <c r="D133" t="n">
         <v>38.09523809523809</v>
       </c>
     </row>
@@ -2303,12 +1890,9 @@
         <v>3234</v>
       </c>
       <c r="B134" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C134" t="n">
-        <v>103</v>
-      </c>
-      <c r="D134" t="n">
         <v>31.39805825242718</v>
       </c>
     </row>
@@ -2317,12 +1901,9 @@
         <v>3300</v>
       </c>
       <c r="B135" t="n">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="C135" t="n">
-        <v>108</v>
-      </c>
-      <c r="D135" t="n">
         <v>30.55555555555556</v>
       </c>
     </row>
@@ -2331,12 +1912,9 @@
         <v>3420</v>
       </c>
       <c r="B136" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C136" t="n">
-        <v>70</v>
-      </c>
-      <c r="D136" t="n">
         <v>48.85714285714285</v>
       </c>
     </row>
@@ -2345,12 +1923,9 @@
         <v>3350</v>
       </c>
       <c r="B137" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="C137" t="n">
-        <v>88</v>
-      </c>
-      <c r="D137" t="n">
         <v>38.06818181818182</v>
       </c>
     </row>
@@ -2359,12 +1934,9 @@
         <v>3130</v>
       </c>
       <c r="B138" t="n">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="C138" t="n">
-        <v>101</v>
-      </c>
-      <c r="D138" t="n">
         <v>30.99009900990099</v>
       </c>
     </row>
@@ -2373,12 +1945,9 @@
         <v>3500</v>
       </c>
       <c r="B139" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C139" t="n">
-        <v>103</v>
-      </c>
-      <c r="D139" t="n">
         <v>33.98058252427185</v>
       </c>
     </row>
@@ -2387,12 +1956,9 @@
         <v>3700</v>
       </c>
       <c r="B140" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C140" t="n">
-        <v>70</v>
-      </c>
-      <c r="D140" t="n">
         <v>52.85714285714285</v>
       </c>
     </row>
@@ -2401,12 +1967,9 @@
         <v>3705</v>
       </c>
       <c r="B141" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C141" t="n">
-        <v>53</v>
-      </c>
-      <c r="D141" t="n">
         <v>69.90566037735849</v>
       </c>
     </row>
@@ -2415,12 +1978,9 @@
         <v>3705</v>
       </c>
       <c r="B142" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C142" t="n">
-        <v>53</v>
-      </c>
-      <c r="D142" t="n">
         <v>69.90566037735849</v>
       </c>
     </row>
@@ -2429,12 +1989,9 @@
         <v>3800</v>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="C143" t="n">
-        <v>72</v>
-      </c>
-      <c r="D143" t="n">
         <v>52.77777777777778</v>
       </c>
     </row>
@@ -2443,12 +2000,9 @@
         <v>3900</v>
       </c>
       <c r="B144" t="n">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="C144" t="n">
-        <v>91</v>
-      </c>
-      <c r="D144" t="n">
         <v>42.85714285714285</v>
       </c>
     </row>
@@ -2457,12 +2011,9 @@
         <v>3700</v>
       </c>
       <c r="B145" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="C145" t="n">
-        <v>97</v>
-      </c>
-      <c r="D145" t="n">
         <v>38.14432989690722</v>
       </c>
     </row>
@@ -2471,12 +2022,9 @@
         <v>4000</v>
       </c>
       <c r="B146" t="n">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="C146" t="n">
-        <v>135</v>
-      </c>
-      <c r="D146" t="n">
         <v>29.62962962962963</v>
       </c>
     </row>
@@ -2485,12 +2033,9 @@
         <v>4000</v>
       </c>
       <c r="B147" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C147" t="n">
-        <v>80</v>
-      </c>
-      <c r="D147" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2499,12 +2044,9 @@
         <v>3850</v>
       </c>
       <c r="B148" t="n">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="C148" t="n">
-        <v>116</v>
-      </c>
-      <c r="D148" t="n">
         <v>33.18965517241379</v>
       </c>
     </row>
@@ -2513,12 +2055,9 @@
         <v>4407</v>
       </c>
       <c r="B149" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="C149" t="n">
-        <v>152</v>
-      </c>
-      <c r="D149" t="n">
         <v>28.99342105263158</v>
       </c>
     </row>
@@ -2527,12 +2066,9 @@
         <v>5000</v>
       </c>
       <c r="B150" t="n">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="C150" t="n">
-        <v>159</v>
-      </c>
-      <c r="D150" t="n">
         <v>31.44654088050314</v>
       </c>
     </row>
@@ -2541,12 +2077,9 @@
         <v>5233</v>
       </c>
       <c r="B151" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="C151" t="n">
-        <v>162</v>
-      </c>
-      <c r="D151" t="n">
         <v>32.30246913580247</v>
       </c>
     </row>
@@ -2555,12 +2088,9 @@
         <v>5249</v>
       </c>
       <c r="B152" t="n">
-        <v>3</v>
+        <v>137</v>
       </c>
       <c r="C152" t="n">
-        <v>137</v>
-      </c>
-      <c r="D152" t="n">
         <v>38.31386861313869</v>
       </c>
     </row>
@@ -2569,12 +2099,9 @@
         <v>5500</v>
       </c>
       <c r="B153" t="n">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="C153" t="n">
-        <v>160</v>
-      </c>
-      <c r="D153" t="n">
         <v>34.375</v>
       </c>
     </row>
@@ -2583,12 +2110,9 @@
         <v>5600</v>
       </c>
       <c r="B154" t="n">
-        <v>3</v>
+        <v>157</v>
       </c>
       <c r="C154" t="n">
-        <v>157</v>
-      </c>
-      <c r="D154" t="n">
         <v>35.6687898089172</v>
       </c>
     </row>
@@ -2597,12 +2121,9 @@
         <v>5970</v>
       </c>
       <c r="B155" t="n">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="C155" t="n">
-        <v>160</v>
-      </c>
-      <c r="D155" t="n">
         <v>37.3125</v>
       </c>
     </row>
@@ -2611,12 +2132,9 @@
         <v>6000</v>
       </c>
       <c r="B156" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="C156" t="n">
-        <v>152</v>
-      </c>
-      <c r="D156" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
@@ -2625,12 +2143,9 @@
         <v>6000</v>
       </c>
       <c r="B157" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="C157" t="n">
-        <v>152</v>
-      </c>
-      <c r="D157" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
@@ -2639,12 +2154,9 @@
         <v>7450</v>
       </c>
       <c r="B158" t="n">
-        <v>3</v>
+        <v>180</v>
       </c>
       <c r="C158" t="n">
-        <v>180</v>
-      </c>
-      <c r="D158" t="n">
         <v>41.38888888888889</v>
       </c>
     </row>
@@ -2653,12 +2165,9 @@
         <v>7280</v>
       </c>
       <c r="B159" t="n">
-        <v>3</v>
+        <v>182</v>
       </c>
       <c r="C159" t="n">
-        <v>182</v>
-      </c>
-      <c r="D159" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2667,12 +2176,9 @@
         <v>10000</v>
       </c>
       <c r="B160" t="n">
-        <v>3</v>
+        <v>220</v>
       </c>
       <c r="C160" t="n">
-        <v>220</v>
-      </c>
-      <c r="D160" t="n">
         <v>45.45454545454545</v>
       </c>
     </row>
@@ -2681,12 +2187,9 @@
         <v>14300</v>
       </c>
       <c r="B161" t="n">
-        <v>3</v>
+        <v>347</v>
       </c>
       <c r="C161" t="n">
-        <v>347</v>
-      </c>
-      <c r="D161" t="n">
         <v>41.21037463976946</v>
       </c>
     </row>
@@ -2695,12 +2198,9 @@
         <v>15000</v>
       </c>
       <c r="B162" t="n">
-        <v>3</v>
+        <v>347</v>
       </c>
       <c r="C162" t="n">
-        <v>347</v>
-      </c>
-      <c r="D162" t="n">
         <v>43.22766570605187</v>
       </c>
     </row>
@@ -2709,12 +2209,9 @@
         <v>775</v>
       </c>
       <c r="B163" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C163" t="n">
-        <v>20</v>
-      </c>
-      <c r="D163" t="n">
         <v>38.75</v>
       </c>
     </row>
@@ -2723,12 +2220,9 @@
         <v>816</v>
       </c>
       <c r="B164" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C164" t="n">
-        <v>19</v>
-      </c>
-      <c r="D164" t="n">
         <v>42.94736842105263</v>
       </c>
     </row>
@@ -2737,12 +2231,9 @@
         <v>800</v>
       </c>
       <c r="B165" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C165" t="n">
-        <v>19</v>
-      </c>
-      <c r="D165" t="n">
         <v>42.10526315789474</v>
       </c>
     </row>
@@ -2751,12 +2242,9 @@
         <v>900</v>
       </c>
       <c r="B166" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C166" t="n">
-        <v>18</v>
-      </c>
-      <c r="D166" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2765,12 +2253,9 @@
         <v>900</v>
       </c>
       <c r="B167" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C167" t="n">
-        <v>28</v>
-      </c>
-      <c r="D167" t="n">
         <v>32.14285714285715</v>
       </c>
     </row>
@@ -2779,12 +2264,9 @@
         <v>888</v>
       </c>
       <c r="B168" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C168" t="n">
-        <v>24</v>
-      </c>
-      <c r="D168" t="n">
         <v>37</v>
       </c>
     </row>
@@ -2793,12 +2275,9 @@
         <v>960</v>
       </c>
       <c r="B169" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C169" t="n">
-        <v>21</v>
-      </c>
-      <c r="D169" t="n">
         <v>45.71428571428572</v>
       </c>
     </row>
@@ -2807,12 +2286,9 @@
         <v>966</v>
       </c>
       <c r="B170" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C170" t="n">
-        <v>30</v>
-      </c>
-      <c r="D170" t="n">
         <v>32.2</v>
       </c>
     </row>
@@ -2821,12 +2297,9 @@
         <v>1000</v>
       </c>
       <c r="B171" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C171" t="n">
-        <v>19</v>
-      </c>
-      <c r="D171" t="n">
         <v>52.63157894736842</v>
       </c>
     </row>
@@ -2835,12 +2308,9 @@
         <v>1040</v>
       </c>
       <c r="B172" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C172" t="n">
-        <v>26</v>
-      </c>
-      <c r="D172" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2849,12 +2319,9 @@
         <v>1048</v>
       </c>
       <c r="B173" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C173" t="n">
-        <v>31</v>
-      </c>
-      <c r="D173" t="n">
         <v>33.80645161290322</v>
       </c>
     </row>
@@ -2863,12 +2330,9 @@
         <v>1072</v>
       </c>
       <c r="B174" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C174" t="n">
-        <v>32</v>
-      </c>
-      <c r="D174" t="n">
         <v>33.5</v>
       </c>
     </row>
@@ -2877,12 +2341,9 @@
         <v>1090</v>
       </c>
       <c r="B175" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C175" t="n">
-        <v>20</v>
-      </c>
-      <c r="D175" t="n">
         <v>54.5</v>
       </c>
     </row>
@@ -2891,12 +2352,9 @@
         <v>1100</v>
       </c>
       <c r="B176" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C176" t="n">
-        <v>26</v>
-      </c>
-      <c r="D176" t="n">
         <v>42.30769230769231</v>
       </c>
     </row>
@@ -2905,12 +2363,9 @@
         <v>1150</v>
       </c>
       <c r="B177" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C177" t="n">
-        <v>21</v>
-      </c>
-      <c r="D177" t="n">
         <v>54.76190476190476</v>
       </c>
     </row>
@@ -2919,12 +2374,9 @@
         <v>1180</v>
       </c>
       <c r="B178" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C178" t="n">
-        <v>23</v>
-      </c>
-      <c r="D178" t="n">
         <v>51.30434782608695</v>
       </c>
     </row>
@@ -2933,12 +2385,9 @@
         <v>1200</v>
       </c>
       <c r="B179" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C179" t="n">
-        <v>30</v>
-      </c>
-      <c r="D179" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2947,12 +2396,9 @@
         <v>1200</v>
       </c>
       <c r="B180" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C180" t="n">
-        <v>32</v>
-      </c>
-      <c r="D180" t="n">
         <v>37.5</v>
       </c>
     </row>
@@ -2961,12 +2407,9 @@
         <v>1200</v>
       </c>
       <c r="B181" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C181" t="n">
-        <v>20</v>
-      </c>
-      <c r="D181" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2975,12 +2418,9 @@
         <v>1200</v>
       </c>
       <c r="B182" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C182" t="n">
-        <v>20</v>
-      </c>
-      <c r="D182" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2989,12 +2429,9 @@
         <v>1218</v>
       </c>
       <c r="B183" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C183" t="n">
-        <v>28</v>
-      </c>
-      <c r="D183" t="n">
         <v>43.5</v>
       </c>
     </row>
@@ -3003,12 +2440,9 @@
         <v>1250</v>
       </c>
       <c r="B184" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C184" t="n">
-        <v>21</v>
-      </c>
-      <c r="D184" t="n">
         <v>59.52380952380953</v>
       </c>
     </row>
@@ -3017,12 +2451,9 @@
         <v>1250</v>
       </c>
       <c r="B185" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C185" t="n">
-        <v>34</v>
-      </c>
-      <c r="D185" t="n">
         <v>36.76470588235294</v>
       </c>
     </row>
@@ -3031,12 +2462,9 @@
         <v>1300</v>
       </c>
       <c r="B186" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C186" t="n">
-        <v>22</v>
-      </c>
-      <c r="D186" t="n">
         <v>59.09090909090909</v>
       </c>
     </row>
@@ -3045,12 +2473,9 @@
         <v>1329</v>
       </c>
       <c r="B187" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C187" t="n">
-        <v>35</v>
-      </c>
-      <c r="D187" t="n">
         <v>37.97142857142857</v>
       </c>
     </row>
@@ -3059,12 +2484,9 @@
         <v>1340</v>
       </c>
       <c r="B188" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C188" t="n">
-        <v>30</v>
-      </c>
-      <c r="D188" t="n">
         <v>44.66666666666666</v>
       </c>
     </row>
@@ -3073,12 +2495,9 @@
         <v>1500</v>
       </c>
       <c r="B189" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C189" t="n">
-        <v>32</v>
-      </c>
-      <c r="D189" t="n">
         <v>46.875</v>
       </c>
     </row>
@@ -3087,12 +2506,9 @@
         <v>1500</v>
       </c>
       <c r="B190" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C190" t="n">
-        <v>32</v>
-      </c>
-      <c r="D190" t="n">
         <v>46.875</v>
       </c>
     </row>
@@ -3101,12 +2517,9 @@
         <v>1550</v>
       </c>
       <c r="B191" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C191" t="n">
-        <v>59</v>
-      </c>
-      <c r="D191" t="n">
         <v>26.27118644067797</v>
       </c>
     </row>
@@ -3115,12 +2528,9 @@
         <v>1900</v>
       </c>
       <c r="B192" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C192" t="n">
-        <v>50</v>
-      </c>
-      <c r="D192" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3129,12 +2539,9 @@
         <v>1910</v>
       </c>
       <c r="B193" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C193" t="n">
-        <v>71</v>
-      </c>
-      <c r="D193" t="n">
         <v>26.90140845070422</v>
       </c>
     </row>
@@ -3143,12 +2550,9 @@
         <v>2700</v>
       </c>
       <c r="B194" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C194" t="n">
-        <v>50</v>
-      </c>
-      <c r="D194" t="n">
         <v>54</v>
       </c>
     </row>
@@ -3157,12 +2561,9 @@
         <v>2950</v>
       </c>
       <c r="B195" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="C195" t="n">
-        <v>82</v>
-      </c>
-      <c r="D195" t="n">
         <v>35.97560975609756</v>
       </c>
     </row>
@@ -3171,12 +2572,9 @@
         <v>2700</v>
       </c>
       <c r="B196" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C196" t="n">
-        <v>50</v>
-      </c>
-      <c r="D196" t="n">
         <v>54</v>
       </c>
     </row>
@@ -3185,12 +2583,9 @@
         <v>6500</v>
       </c>
       <c r="B197" t="n">
-        <v>3</v>
+        <v>161</v>
       </c>
       <c r="C197" t="n">
-        <v>161</v>
-      </c>
-      <c r="D197" t="n">
         <v>40.37267080745342</v>
       </c>
     </row>
@@ -3199,12 +2594,9 @@
         <v>7500</v>
       </c>
       <c r="B198" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="C198" t="n">
-        <v>150</v>
-      </c>
-      <c r="D198" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3213,12 +2605,9 @@
         <v>1048</v>
       </c>
       <c r="B199" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C199" t="n">
-        <v>31</v>
-      </c>
-      <c r="D199" t="n">
         <v>33.80645161290322</v>
       </c>
     </row>
@@ -3227,12 +2616,9 @@
         <v>1650</v>
       </c>
       <c r="B200" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C200" t="n">
-        <v>45</v>
-      </c>
-      <c r="D200" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
@@ -3241,12 +2627,9 @@
         <v>1100</v>
       </c>
       <c r="B201" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C201" t="n">
-        <v>29</v>
-      </c>
-      <c r="D201" t="n">
         <v>37.93103448275862</v>
       </c>
     </row>
@@ -3255,12 +2638,9 @@
         <v>1133</v>
       </c>
       <c r="B202" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C202" t="n">
-        <v>33</v>
-      </c>
-      <c r="D202" t="n">
         <v>34.33333333333334</v>
       </c>
     </row>
@@ -3269,12 +2649,9 @@
         <v>1500</v>
       </c>
       <c r="B203" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C203" t="n">
-        <v>45</v>
-      </c>
-      <c r="D203" t="n">
         <v>33.33333333333334</v>
       </c>
     </row>
@@ -3283,12 +2660,9 @@
         <v>1530</v>
       </c>
       <c r="B204" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C204" t="n">
-        <v>35</v>
-      </c>
-      <c r="D204" t="n">
         <v>43.71428571428572</v>
       </c>
     </row>
@@ -3297,12 +2671,9 @@
         <v>1520</v>
       </c>
       <c r="B205" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C205" t="n">
-        <v>55</v>
-      </c>
-      <c r="D205" t="n">
         <v>27.63636363636364</v>
       </c>
     </row>
@@ -3311,12 +2682,9 @@
         <v>1600</v>
       </c>
       <c r="B206" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C206" t="n">
-        <v>32</v>
-      </c>
-      <c r="D206" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3325,12 +2693,9 @@
         <v>1620</v>
       </c>
       <c r="B207" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C207" t="n">
-        <v>54</v>
-      </c>
-      <c r="D207" t="n">
         <v>30</v>
       </c>
     </row>
@@ -3339,12 +2704,9 @@
         <v>1700</v>
       </c>
       <c r="B208" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C208" t="n">
-        <v>60</v>
-      </c>
-      <c r="D208" t="n">
         <v>28.33333333333333</v>
       </c>
     </row>
@@ -3353,12 +2715,9 @@
         <v>1820</v>
       </c>
       <c r="B209" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C209" t="n">
-        <v>46</v>
-      </c>
-      <c r="D209" t="n">
         <v>39.56521739130435</v>
       </c>
     </row>
@@ -3367,12 +2726,9 @@
         <v>1850</v>
       </c>
       <c r="B210" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C210" t="n">
-        <v>66</v>
-      </c>
-      <c r="D210" t="n">
         <v>28.03030303030303</v>
       </c>
     </row>
@@ -3381,12 +2737,9 @@
         <v>1939</v>
       </c>
       <c r="B211" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C211" t="n">
-        <v>71</v>
-      </c>
-      <c r="D211" t="n">
         <v>27.30985915492958</v>
       </c>
     </row>
@@ -3395,12 +2748,9 @@
         <v>1958</v>
       </c>
       <c r="B212" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="C212" t="n">
-        <v>74</v>
-      </c>
-      <c r="D212" t="n">
         <v>26.45945945945946</v>
       </c>
     </row>
@@ -3409,12 +2759,9 @@
         <v>1750</v>
       </c>
       <c r="B213" t="n">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="C213" t="n">
-        <v>87</v>
-      </c>
-      <c r="D213" t="n">
         <v>20.11494252873563</v>
       </c>
     </row>
@@ -3423,12 +2770,9 @@
         <v>2090</v>
       </c>
       <c r="B214" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C214" t="n">
-        <v>62</v>
-      </c>
-      <c r="D214" t="n">
         <v>33.70967741935484</v>
       </c>
     </row>
@@ -3437,12 +2781,9 @@
         <v>2102</v>
       </c>
       <c r="B215" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C215" t="n">
-        <v>68</v>
-      </c>
-      <c r="D215" t="n">
         <v>30.91176470588235</v>
       </c>
     </row>
@@ -3451,12 +2792,9 @@
         <v>2162</v>
       </c>
       <c r="B216" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="C216" t="n">
-        <v>75</v>
-      </c>
-      <c r="D216" t="n">
         <v>28.82666666666667</v>
       </c>
     </row>
@@ -3465,12 +2803,9 @@
         <v>2150</v>
       </c>
       <c r="B217" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C217" t="n">
-        <v>80</v>
-      </c>
-      <c r="D217" t="n">
         <v>26.875</v>
       </c>
     </row>
@@ -3479,12 +2814,9 @@
         <v>2250</v>
       </c>
       <c r="B218" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="C218" t="n">
-        <v>74</v>
-      </c>
-      <c r="D218" t="n">
         <v>30.40540540540541</v>
       </c>
     </row>
@@ -3493,12 +2825,9 @@
         <v>2359</v>
       </c>
       <c r="B219" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C219" t="n">
-        <v>80</v>
-      </c>
-      <c r="D219" t="n">
         <v>29.4875</v>
       </c>
     </row>
@@ -3507,12 +2836,9 @@
         <v>2400</v>
       </c>
       <c r="B220" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="C220" t="n">
-        <v>112</v>
-      </c>
-      <c r="D220" t="n">
         <v>21.42857142857143</v>
       </c>
     </row>
@@ -3521,12 +2847,9 @@
         <v>2459</v>
       </c>
       <c r="B221" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="C221" t="n">
-        <v>96</v>
-      </c>
-      <c r="D221" t="n">
         <v>25.61458333333333</v>
       </c>
     </row>
@@ -3535,12 +2858,9 @@
         <v>2400</v>
       </c>
       <c r="B222" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="C222" t="n">
-        <v>112</v>
-      </c>
-      <c r="D222" t="n">
         <v>21.42857142857143</v>
       </c>
     </row>
@@ -3549,12 +2869,9 @@
         <v>2459</v>
       </c>
       <c r="B223" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="C223" t="n">
-        <v>96</v>
-      </c>
-      <c r="D223" t="n">
         <v>25.61458333333333</v>
       </c>
     </row>
@@ -3563,12 +2880,9 @@
         <v>2535</v>
       </c>
       <c r="B224" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="C224" t="n">
-        <v>86</v>
-      </c>
-      <c r="D224" t="n">
         <v>29.47674418604651</v>
       </c>
     </row>
@@ -3577,12 +2891,9 @@
         <v>2650</v>
       </c>
       <c r="B225" t="n">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="C225" t="n">
-        <v>90</v>
-      </c>
-      <c r="D225" t="n">
         <v>29.44444444444444</v>
       </c>
     </row>
@@ -3591,12 +2902,9 @@
         <v>2650</v>
       </c>
       <c r="B226" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="C226" t="n">
-        <v>98</v>
-      </c>
-      <c r="D226" t="n">
         <v>27.04081632653061</v>
       </c>
     </row>
@@ -3605,12 +2913,9 @@
         <v>2900</v>
       </c>
       <c r="B227" t="n">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="C227" t="n">
-        <v>105</v>
-      </c>
-      <c r="D227" t="n">
         <v>27.61904761904762</v>
       </c>
     </row>
@@ -3619,12 +2924,9 @@
         <v>2950</v>
       </c>
       <c r="B228" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C228" t="n">
-        <v>70</v>
-      </c>
-      <c r="D228" t="n">
         <v>42.14285714285715</v>
       </c>
     </row>
@@ -3633,12 +2935,9 @@
         <v>3000</v>
       </c>
       <c r="B229" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="C229" t="n">
-        <v>88</v>
-      </c>
-      <c r="D229" t="n">
         <v>34.09090909090909</v>
       </c>
     </row>
@@ -3647,12 +2946,9 @@
         <v>3234</v>
       </c>
       <c r="B230" t="n">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="C230" t="n">
-        <v>105</v>
-      </c>
-      <c r="D230" t="n">
         <v>30.8</v>
       </c>
     </row>
@@ -3661,12 +2957,9 @@
         <v>3243</v>
       </c>
       <c r="B231" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="C231" t="n">
-        <v>120</v>
-      </c>
-      <c r="D231" t="n">
         <v>27.025</v>
       </c>
     </row>
@@ -3675,12 +2968,9 @@
         <v>4200</v>
       </c>
       <c r="B232" t="n">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="C232" t="n">
-        <v>117</v>
-      </c>
-      <c r="D232" t="n">
         <v>35.8974358974359</v>
       </c>
     </row>
@@ -3689,12 +2979,9 @@
         <v>4938</v>
       </c>
       <c r="B233" t="n">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="C233" t="n">
-        <v>173</v>
-      </c>
-      <c r="D233" t="n">
         <v>28.54335260115607</v>
       </c>
     </row>
@@ -3703,12 +2990,9 @@
         <v>1100</v>
       </c>
       <c r="B234" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C234" t="n">
-        <v>31</v>
-      </c>
-      <c r="D234" t="n">
         <v>35.48387096774194</v>
       </c>
     </row>
@@ -3717,12 +3001,9 @@
         <v>700</v>
       </c>
       <c r="B235" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C235" t="n">
-        <v>23</v>
-      </c>
-      <c r="D235" t="n">
         <v>30.43478260869565</v>
       </c>
     </row>
@@ -3731,12 +3012,9 @@
         <v>880</v>
       </c>
       <c r="B236" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C236" t="n">
-        <v>21</v>
-      </c>
-      <c r="D236" t="n">
         <v>41.90476190476191</v>
       </c>
     </row>
@@ -3745,12 +3023,9 @@
         <v>930</v>
       </c>
       <c r="B237" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C237" t="n">
-        <v>15</v>
-      </c>
-      <c r="D237" t="n">
         <v>62</v>
       </c>
     </row>
@@ -3759,12 +3034,9 @@
         <v>940</v>
       </c>
       <c r="B238" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C238" t="n">
-        <v>27</v>
-      </c>
-      <c r="D238" t="n">
         <v>34.81481481481482</v>
       </c>
     </row>
@@ -3773,12 +3045,9 @@
         <v>950</v>
       </c>
       <c r="B239" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C239" t="n">
-        <v>21</v>
-      </c>
-      <c r="D239" t="n">
         <v>45.23809523809524</v>
       </c>
     </row>
@@ -3787,12 +3056,9 @@
         <v>950</v>
       </c>
       <c r="B240" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C240" t="n">
-        <v>21</v>
-      </c>
-      <c r="D240" t="n">
         <v>45.23809523809524</v>
       </c>
     </row>
@@ -3801,12 +3067,9 @@
         <v>1000</v>
       </c>
       <c r="B241" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C241" t="n">
-        <v>21</v>
-      </c>
-      <c r="D241" t="n">
         <v>47.61904761904762</v>
       </c>
     </row>
@@ -3815,12 +3078,9 @@
         <v>1380</v>
       </c>
       <c r="B242" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C242" t="n">
-        <v>36</v>
-      </c>
-      <c r="D242" t="n">
         <v>38.33333333333334</v>
       </c>
     </row>
@@ -3829,12 +3089,9 @@
         <v>1700</v>
       </c>
       <c r="B243" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="C243" t="n">
-        <v>57</v>
-      </c>
-      <c r="D243" t="n">
         <v>29.82456140350877</v>
       </c>
     </row>
@@ -3843,12 +3100,9 @@
         <v>1740</v>
       </c>
       <c r="B244" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C244" t="n">
-        <v>49</v>
-      </c>
-      <c r="D244" t="n">
         <v>35.51020408163265</v>
       </c>
     </row>
@@ -3857,12 +3111,9 @@
         <v>2367</v>
       </c>
       <c r="B245" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="C245" t="n">
-        <v>76</v>
-      </c>
-      <c r="D245" t="n">
         <v>31.14473684210526</v>
       </c>
     </row>
@@ -3871,12 +3122,9 @@
         <v>2800</v>
       </c>
       <c r="B246" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="C246" t="n">
-        <v>83</v>
-      </c>
-      <c r="D246" t="n">
         <v>33.73493975903614</v>
       </c>
     </row>
@@ -3885,12 +3133,9 @@
         <v>3000</v>
       </c>
       <c r="B247" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="C247" t="n">
-        <v>104</v>
-      </c>
-      <c r="D247" t="n">
         <v>28.84615384615385</v>
       </c>
     </row>
@@ -3899,12 +3144,9 @@
         <v>1365</v>
       </c>
       <c r="B248" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C248" t="n">
-        <v>44</v>
-      </c>
-      <c r="D248" t="n">
         <v>31.02272727272727</v>
       </c>
     </row>
@@ -3913,12 +3155,9 @@
         <v>855</v>
       </c>
       <c r="B249" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C249" t="n">
-        <v>20</v>
-      </c>
-      <c r="D249" t="n">
         <v>42.75</v>
       </c>
     </row>
@@ -3927,12 +3166,9 @@
         <v>1250</v>
       </c>
       <c r="B250" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C250" t="n">
-        <v>30</v>
-      </c>
-      <c r="D250" t="n">
         <v>41.66666666666666</v>
       </c>
     </row>
@@ -3941,12 +3177,9 @@
         <v>2132</v>
       </c>
       <c r="B251" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C251" t="n">
-        <v>69</v>
-      </c>
-      <c r="D251" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
@@ -3955,12 +3188,9 @@
         <v>2840</v>
       </c>
       <c r="B252" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="C252" t="n">
-        <v>77</v>
-      </c>
-      <c r="D252" t="n">
         <v>36.88311688311688</v>
       </c>
     </row>
@@ -3969,12 +3199,9 @@
         <v>2614</v>
       </c>
       <c r="B253" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="C253" t="n">
-        <v>96</v>
-      </c>
-      <c r="D253" t="n">
         <v>27.22916666666667</v>
       </c>
     </row>
@@ -3983,12 +3210,9 @@
         <v>693</v>
       </c>
       <c r="B254" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C254" t="n">
-        <v>19</v>
-      </c>
-      <c r="D254" t="n">
         <v>36.47368421052632</v>
       </c>
     </row>
@@ -3997,12 +3221,9 @@
         <v>1000</v>
       </c>
       <c r="B255" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C255" t="n">
-        <v>20</v>
-      </c>
-      <c r="D255" t="n">
         <v>50</v>
       </c>
     </row>
@@ -4011,12 +3232,9 @@
         <v>2200</v>
       </c>
       <c r="B256" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C256" t="n">
-        <v>27</v>
-      </c>
-      <c r="D256" t="n">
         <v>81.48148148148148</v>
       </c>
     </row>
@@ -4025,12 +3243,9 @@
         <v>1900</v>
       </c>
       <c r="B257" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C257" t="n">
-        <v>60</v>
-      </c>
-      <c r="D257" t="n">
         <v>31.66666666666667</v>
       </c>
     </row>
@@ -4039,12 +3254,9 @@
         <v>2347</v>
       </c>
       <c r="B258" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="C258" t="n">
-        <v>72</v>
-      </c>
-      <c r="D258" t="n">
         <v>32.59722222222222</v>
       </c>
     </row>
@@ -4053,12 +3265,9 @@
         <v>3460</v>
       </c>
       <c r="B259" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C259" t="n">
-        <v>103</v>
-      </c>
-      <c r="D259" t="n">
         <v>33.59223300970874</v>
       </c>
     </row>
@@ -4067,12 +3276,9 @@
         <v>1100</v>
       </c>
       <c r="B260" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C260" t="n">
-        <v>25</v>
-      </c>
-      <c r="D260" t="n">
         <v>44</v>
       </c>
     </row>
@@ -4081,12 +3287,9 @@
         <v>1200</v>
       </c>
       <c r="B261" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C261" t="n">
-        <v>30</v>
-      </c>
-      <c r="D261" t="n">
         <v>40</v>
       </c>
     </row>
@@ -4095,12 +3298,9 @@
         <v>1313</v>
       </c>
       <c r="B262" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C262" t="n">
-        <v>40</v>
-      </c>
-      <c r="D262" t="n">
         <v>32.825</v>
       </c>
     </row>
@@ -4109,12 +3309,9 @@
         <v>1490</v>
       </c>
       <c r="B263" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C263" t="n">
-        <v>54</v>
-      </c>
-      <c r="D263" t="n">
         <v>27.59259259259259</v>
       </c>
     </row>
@@ -4123,12 +3320,9 @@
         <v>1850</v>
       </c>
       <c r="B264" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C264" t="n">
-        <v>59</v>
-      </c>
-      <c r="D264" t="n">
         <v>31.35593220338983</v>
       </c>
     </row>
@@ -4137,12 +3331,9 @@
         <v>1880</v>
       </c>
       <c r="B265" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C265" t="n">
-        <v>62</v>
-      </c>
-      <c r="D265" t="n">
         <v>30.32258064516129</v>
       </c>
     </row>
@@ -4151,12 +3342,9 @@
         <v>1900</v>
       </c>
       <c r="B266" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C266" t="n">
-        <v>64</v>
-      </c>
-      <c r="D266" t="n">
         <v>29.6875</v>
       </c>
     </row>
@@ -4165,12 +3353,9 @@
         <v>1900</v>
       </c>
       <c r="B267" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C267" t="n">
-        <v>48</v>
-      </c>
-      <c r="D267" t="n">
         <v>39.58333333333334</v>
       </c>
     </row>
@@ -4179,12 +3364,9 @@
         <v>2008</v>
       </c>
       <c r="B268" t="n">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="C268" t="n">
-        <v>87</v>
-      </c>
-      <c r="D268" t="n">
         <v>23.08045977011494</v>
       </c>
     </row>
@@ -4193,12 +3375,9 @@
         <v>2960</v>
       </c>
       <c r="B269" t="n">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="C269" t="n">
-        <v>106</v>
-      </c>
-      <c r="D269" t="n">
         <v>27.92452830188679</v>
       </c>
     </row>
@@ -4207,12 +3386,9 @@
         <v>3200</v>
       </c>
       <c r="B270" t="n">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="C270" t="n">
-        <v>114</v>
-      </c>
-      <c r="D270" t="n">
         <v>28.07017543859649</v>
       </c>
     </row>
@@ -4221,12 +3397,9 @@
         <v>3220</v>
       </c>
       <c r="B271" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="C271" t="n">
-        <v>110</v>
-      </c>
-      <c r="D271" t="n">
         <v>29.27272727272727</v>
       </c>
     </row>
@@ -4235,12 +3408,9 @@
         <v>3380</v>
       </c>
       <c r="B272" t="n">
-        <v>3</v>
+        <v>129</v>
       </c>
       <c r="C272" t="n">
-        <v>129</v>
-      </c>
-      <c r="D272" t="n">
         <v>26.2015503875969</v>
       </c>
     </row>
@@ -4249,12 +3419,9 @@
         <v>3950</v>
       </c>
       <c r="B273" t="n">
-        <v>3</v>
+        <v>125</v>
       </c>
       <c r="C273" t="n">
-        <v>125</v>
-      </c>
-      <c r="D273" t="n">
         <v>31.6</v>
       </c>
     </row>
@@ -4263,12 +3430,9 @@
         <v>645</v>
       </c>
       <c r="B274" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C274" t="n">
-        <v>15</v>
-      </c>
-      <c r="D274" t="n">
         <v>43</v>
       </c>
     </row>
@@ -4277,12 +3441,9 @@
         <v>682</v>
       </c>
       <c r="B275" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C275" t="n">
-        <v>17</v>
-      </c>
-      <c r="D275" t="n">
         <v>40.11764705882353</v>
       </c>
     </row>
@@ -4291,12 +3452,9 @@
         <v>745</v>
       </c>
       <c r="B276" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C276" t="n">
-        <v>20</v>
-      </c>
-      <c r="D276" t="n">
         <v>37.25</v>
       </c>
     </row>
@@ -4305,12 +3463,9 @@
         <v>1780</v>
       </c>
       <c r="B277" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C277" t="n">
-        <v>45</v>
-      </c>
-      <c r="D277" t="n">
         <v>39.55555555555556</v>
       </c>
     </row>
@@ -4319,12 +3474,9 @@
         <v>1595</v>
       </c>
       <c r="B278" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C278" t="n">
-        <v>54</v>
-      </c>
-      <c r="D278" t="n">
         <v>29.53703703703704</v>
       </c>
     </row>
@@ -4333,12 +3485,9 @@
         <v>4200</v>
       </c>
       <c r="B279" t="n">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="C279" t="n">
-        <v>105</v>
-      </c>
-      <c r="D279" t="n">
         <v>40</v>
       </c>
     </row>
@@ -4347,12 +3496,9 @@
         <v>9500</v>
       </c>
       <c r="B280" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="C280" t="n">
-        <v>150</v>
-      </c>
-      <c r="D280" t="n">
         <v>63.33333333333334</v>
       </c>
     </row>
@@ -4361,12 +3507,9 @@
         <v>973</v>
       </c>
       <c r="B281" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C281" t="n">
-        <v>29</v>
-      </c>
-      <c r="D281" t="n">
         <v>33.55172413793103</v>
       </c>
     </row>
@@ -4375,12 +3518,9 @@
         <v>1100</v>
       </c>
       <c r="B282" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C282" t="n">
-        <v>36</v>
-      </c>
-      <c r="D282" t="n">
         <v>30.55555555555556</v>
       </c>
     </row>
@@ -4389,12 +3529,9 @@
         <v>1851</v>
       </c>
       <c r="B283" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C283" t="n">
-        <v>50</v>
-      </c>
-      <c r="D283" t="n">
         <v>37.02</v>
       </c>
     </row>
@@ -4403,12 +3540,9 @@
         <v>1105</v>
       </c>
       <c r="B284" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C284" t="n">
-        <v>33</v>
-      </c>
-      <c r="D284" t="n">
         <v>33.48484848484848</v>
       </c>
     </row>
@@ -4417,12 +3551,9 @@
         <v>1200</v>
       </c>
       <c r="B285" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C285" t="n">
-        <v>40</v>
-      </c>
-      <c r="D285" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4431,12 +3562,9 @@
         <v>1704</v>
       </c>
       <c r="B286" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C286" t="n">
-        <v>56</v>
-      </c>
-      <c r="D286" t="n">
         <v>30.42857142857143</v>
       </c>
     </row>
@@ -4445,12 +3573,9 @@
         <v>800</v>
       </c>
       <c r="B287" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C287" t="n">
-        <v>15</v>
-      </c>
-      <c r="D287" t="n">
         <v>53.33333333333334</v>
       </c>
     </row>
@@ -4459,12 +3584,9 @@
         <v>985</v>
       </c>
       <c r="B288" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C288" t="n">
-        <v>34</v>
-      </c>
-      <c r="D288" t="n">
         <v>28.97058823529412</v>
       </c>
     </row>
@@ -4473,12 +3595,9 @@
         <v>1000</v>
       </c>
       <c r="B289" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C289" t="n">
-        <v>29</v>
-      </c>
-      <c r="D289" t="n">
         <v>34.48275862068966</v>
       </c>
     </row>
@@ -4487,12 +3606,9 @@
         <v>1006</v>
       </c>
       <c r="B290" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C290" t="n">
-        <v>26</v>
-      </c>
-      <c r="D290" t="n">
         <v>38.69230769230769</v>
       </c>
     </row>
@@ -4501,12 +3617,9 @@
         <v>1100</v>
       </c>
       <c r="B291" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C291" t="n">
-        <v>37</v>
-      </c>
-      <c r="D291" t="n">
         <v>29.72972972972973</v>
       </c>
     </row>
@@ -4515,12 +3628,9 @@
         <v>1220</v>
       </c>
       <c r="B292" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C292" t="n">
-        <v>32</v>
-      </c>
-      <c r="D292" t="n">
         <v>38.125</v>
       </c>
     </row>
@@ -4529,12 +3639,9 @@
         <v>1230</v>
       </c>
       <c r="B293" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C293" t="n">
-        <v>35</v>
-      </c>
-      <c r="D293" t="n">
         <v>35.14285714285715</v>
       </c>
     </row>
@@ -4543,12 +3650,9 @@
         <v>1270</v>
       </c>
       <c r="B294" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C294" t="n">
-        <v>30</v>
-      </c>
-      <c r="D294" t="n">
         <v>42.33333333333334</v>
       </c>
     </row>
@@ -4557,12 +3661,9 @@
         <v>1280</v>
       </c>
       <c r="B295" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C295" t="n">
-        <v>31</v>
-      </c>
-      <c r="D295" t="n">
         <v>41.29032258064516</v>
       </c>
     </row>
@@ -4571,12 +3672,9 @@
         <v>1290</v>
       </c>
       <c r="B296" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C296" t="n">
-        <v>38</v>
-      </c>
-      <c r="D296" t="n">
         <v>33.94736842105263</v>
       </c>
     </row>
@@ -4585,12 +3683,9 @@
         <v>1300</v>
       </c>
       <c r="B297" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C297" t="n">
-        <v>39</v>
-      </c>
-      <c r="D297" t="n">
         <v>33.33333333333334</v>
       </c>
     </row>
@@ -4599,12 +3694,9 @@
         <v>1340</v>
       </c>
       <c r="B298" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C298" t="n">
-        <v>34</v>
-      </c>
-      <c r="D298" t="n">
         <v>39.41176470588236</v>
       </c>
     </row>
@@ -4613,12 +3705,9 @@
         <v>1350</v>
       </c>
       <c r="B299" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C299" t="n">
-        <v>39</v>
-      </c>
-      <c r="D299" t="n">
         <v>34.61538461538461</v>
       </c>
     </row>
@@ -4627,12 +3716,9 @@
         <v>1380</v>
       </c>
       <c r="B300" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C300" t="n">
-        <v>40</v>
-      </c>
-      <c r="D300" t="n">
         <v>34.5</v>
       </c>
     </row>
@@ -4641,12 +3727,9 @@
         <v>1390</v>
       </c>
       <c r="B301" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C301" t="n">
-        <v>47</v>
-      </c>
-      <c r="D301" t="n">
         <v>29.57446808510638</v>
       </c>
     </row>
@@ -4655,12 +3738,9 @@
         <v>1390</v>
       </c>
       <c r="B302" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C302" t="n">
-        <v>40</v>
-      </c>
-      <c r="D302" t="n">
         <v>34.75</v>
       </c>
     </row>
@@ -4669,12 +3749,9 @@
         <v>1400</v>
       </c>
       <c r="B303" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C303" t="n">
-        <v>52</v>
-      </c>
-      <c r="D303" t="n">
         <v>26.92307692307692</v>
       </c>
     </row>
@@ -4683,12 +3760,9 @@
         <v>1400</v>
       </c>
       <c r="B304" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C304" t="n">
-        <v>40</v>
-      </c>
-      <c r="D304" t="n">
         <v>35</v>
       </c>
     </row>
@@ -4697,12 +3771,9 @@
         <v>1400</v>
       </c>
       <c r="B305" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C305" t="n">
-        <v>33</v>
-      </c>
-      <c r="D305" t="n">
         <v>42.42424242424242</v>
       </c>
     </row>
@@ -4711,12 +3782,9 @@
         <v>1500</v>
       </c>
       <c r="B306" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C306" t="n">
-        <v>40</v>
-      </c>
-      <c r="D306" t="n">
         <v>37.5</v>
       </c>
     </row>
@@ -4725,12 +3793,9 @@
         <v>1550</v>
       </c>
       <c r="B307" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C307" t="n">
-        <v>50</v>
-      </c>
-      <c r="D307" t="n">
         <v>31</v>
       </c>
     </row>
@@ -4739,12 +3804,9 @@
         <v>1570</v>
       </c>
       <c r="B308" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="C308" t="n">
-        <v>51</v>
-      </c>
-      <c r="D308" t="n">
         <v>30.7843137254902</v>
       </c>
     </row>
@@ -4753,12 +3815,9 @@
         <v>1590</v>
       </c>
       <c r="B309" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C309" t="n">
-        <v>45</v>
-      </c>
-      <c r="D309" t="n">
         <v>35.33333333333334</v>
       </c>
     </row>
@@ -4767,12 +3826,9 @@
         <v>1600</v>
       </c>
       <c r="B310" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C310" t="n">
-        <v>35</v>
-      </c>
-      <c r="D310" t="n">
         <v>45.71428571428572</v>
       </c>
     </row>
@@ -4781,12 +3837,9 @@
         <v>1600</v>
       </c>
       <c r="B311" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C311" t="n">
-        <v>37</v>
-      </c>
-      <c r="D311" t="n">
         <v>43.24324324324324</v>
       </c>
     </row>
@@ -4795,12 +3848,9 @@
         <v>1627</v>
       </c>
       <c r="B312" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C312" t="n">
-        <v>46</v>
-      </c>
-      <c r="D312" t="n">
         <v>35.3695652173913</v>
       </c>
     </row>
@@ -4809,12 +3859,9 @@
         <v>1690</v>
       </c>
       <c r="B313" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C313" t="n">
-        <v>56</v>
-      </c>
-      <c r="D313" t="n">
         <v>30.17857142857143</v>
       </c>
     </row>
@@ -4823,12 +3870,9 @@
         <v>1696</v>
       </c>
       <c r="B314" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="C314" t="n">
-        <v>57</v>
-      </c>
-      <c r="D314" t="n">
         <v>29.75438596491228</v>
       </c>
     </row>
@@ -4837,12 +3881,9 @@
         <v>1700</v>
       </c>
       <c r="B315" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C315" t="n">
-        <v>45</v>
-      </c>
-      <c r="D315" t="n">
         <v>37.77777777777778</v>
       </c>
     </row>
@@ -4851,12 +3892,9 @@
         <v>1700</v>
       </c>
       <c r="B316" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C316" t="n">
-        <v>47</v>
-      </c>
-      <c r="D316" t="n">
         <v>36.17021276595744</v>
       </c>
     </row>
@@ -4865,12 +3903,9 @@
         <v>1705</v>
       </c>
       <c r="B317" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="C317" t="n">
-        <v>75</v>
-      </c>
-      <c r="D317" t="n">
         <v>22.73333333333333</v>
       </c>
     </row>
@@ -4879,12 +3914,9 @@
         <v>1750</v>
       </c>
       <c r="B318" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="C318" t="n">
-        <v>51</v>
-      </c>
-      <c r="D318" t="n">
         <v>34.31372549019608</v>
       </c>
     </row>
@@ -4893,12 +3925,9 @@
         <v>1750</v>
       </c>
       <c r="B319" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C319" t="n">
-        <v>49</v>
-      </c>
-      <c r="D319" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
@@ -4907,12 +3936,9 @@
         <v>1800</v>
       </c>
       <c r="B320" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C320" t="n">
-        <v>40</v>
-      </c>
-      <c r="D320" t="n">
         <v>45</v>
       </c>
     </row>
@@ -4921,12 +3947,9 @@
         <v>1830</v>
       </c>
       <c r="B321" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C321" t="n">
-        <v>64</v>
-      </c>
-      <c r="D321" t="n">
         <v>28.59375</v>
       </c>
     </row>
@@ -4935,12 +3958,9 @@
         <v>1726</v>
       </c>
       <c r="B322" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C322" t="n">
-        <v>62</v>
-      </c>
-      <c r="D322" t="n">
         <v>27.83870967741936</v>
       </c>
     </row>
@@ -4949,12 +3969,9 @@
         <v>1850</v>
       </c>
       <c r="B323" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C323" t="n">
-        <v>35</v>
-      </c>
-      <c r="D323" t="n">
         <v>52.85714285714285</v>
       </c>
     </row>
@@ -4963,12 +3980,9 @@
         <v>1875</v>
       </c>
       <c r="B324" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C324" t="n">
-        <v>42</v>
-      </c>
-      <c r="D324" t="n">
         <v>44.64285714285715</v>
       </c>
     </row>
@@ -4977,12 +3991,9 @@
         <v>1900</v>
       </c>
       <c r="B325" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C325" t="n">
-        <v>45</v>
-      </c>
-      <c r="D325" t="n">
         <v>42.22222222222222</v>
       </c>
     </row>
@@ -4991,12 +4002,9 @@
         <v>1930</v>
       </c>
       <c r="B326" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C326" t="n">
-        <v>64</v>
-      </c>
-      <c r="D326" t="n">
         <v>30.15625</v>
       </c>
     </row>
@@ -5005,12 +4013,9 @@
         <v>1990</v>
       </c>
       <c r="B327" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="C327" t="n">
-        <v>61</v>
-      </c>
-      <c r="D327" t="n">
         <v>32.62295081967213</v>
       </c>
     </row>
@@ -5019,12 +4024,9 @@
         <v>2000</v>
       </c>
       <c r="B328" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C328" t="n">
-        <v>50</v>
-      </c>
-      <c r="D328" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5033,12 +4035,9 @@
         <v>2044</v>
       </c>
       <c r="B329" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C329" t="n">
-        <v>64</v>
-      </c>
-      <c r="D329" t="n">
         <v>31.9375</v>
       </c>
     </row>
@@ -5047,12 +4046,9 @@
         <v>2060</v>
       </c>
       <c r="B330" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C330" t="n">
-        <v>69</v>
-      </c>
-      <c r="D330" t="n">
         <v>29.85507246376812</v>
       </c>
     </row>
@@ -5061,12 +4057,9 @@
         <v>2100</v>
       </c>
       <c r="B331" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C331" t="n">
-        <v>50</v>
-      </c>
-      <c r="D331" t="n">
         <v>42</v>
       </c>
     </row>
@@ -5075,12 +4068,9 @@
         <v>1922</v>
       </c>
       <c r="B332" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="C332" t="n">
-        <v>73</v>
-      </c>
-      <c r="D332" t="n">
         <v>26.32876712328767</v>
       </c>
     </row>
@@ -5089,12 +4079,9 @@
         <v>2190</v>
       </c>
       <c r="B333" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C333" t="n">
-        <v>70</v>
-      </c>
-      <c r="D333" t="n">
         <v>31.28571428571428</v>
       </c>
     </row>
@@ -5103,12 +4090,9 @@
         <v>2250</v>
       </c>
       <c r="B334" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C334" t="n">
-        <v>66</v>
-      </c>
-      <c r="D334" t="n">
         <v>34.09090909090909</v>
       </c>
     </row>
@@ -5117,12 +4101,9 @@
         <v>2250</v>
       </c>
       <c r="B335" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C335" t="n">
-        <v>55</v>
-      </c>
-      <c r="D335" t="n">
         <v>40.90909090909091</v>
       </c>
     </row>
@@ -5131,12 +4112,9 @@
         <v>2300</v>
       </c>
       <c r="B336" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="C336" t="n">
-        <v>65</v>
-      </c>
-      <c r="D336" t="n">
         <v>35.38461538461539</v>
       </c>
     </row>
@@ -5145,12 +4123,9 @@
         <v>2300</v>
       </c>
       <c r="B337" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C337" t="n">
-        <v>80</v>
-      </c>
-      <c r="D337" t="n">
         <v>28.75</v>
       </c>
     </row>
@@ -5159,12 +4134,9 @@
         <v>2309</v>
       </c>
       <c r="B338" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="C338" t="n">
-        <v>88</v>
-      </c>
-      <c r="D338" t="n">
         <v>26.23863636363636</v>
       </c>
     </row>
@@ -5173,12 +4145,9 @@
         <v>2450</v>
       </c>
       <c r="B339" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C339" t="n">
-        <v>54</v>
-      </c>
-      <c r="D339" t="n">
         <v>45.37037037037037</v>
       </c>
     </row>
@@ -5187,12 +4156,9 @@
         <v>2471</v>
       </c>
       <c r="B340" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="C340" t="n">
-        <v>89</v>
-      </c>
-      <c r="D340" t="n">
         <v>27.76404494382022</v>
       </c>
     </row>
@@ -5201,12 +4167,9 @@
         <v>2500</v>
       </c>
       <c r="B341" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C341" t="n">
-        <v>52</v>
-      </c>
-      <c r="D341" t="n">
         <v>48.07692307692308</v>
       </c>
     </row>
@@ -5215,12 +4178,9 @@
         <v>2500</v>
       </c>
       <c r="B342" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C342" t="n">
-        <v>32</v>
-      </c>
-      <c r="D342" t="n">
         <v>78.125</v>
       </c>
     </row>
@@ -5229,12 +4189,9 @@
         <v>2500</v>
       </c>
       <c r="B343" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C343" t="n">
-        <v>63</v>
-      </c>
-      <c r="D343" t="n">
         <v>39.68253968253968</v>
       </c>
     </row>
@@ -5243,12 +4200,9 @@
         <v>2500</v>
       </c>
       <c r="B344" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="C344" t="n">
-        <v>76</v>
-      </c>
-      <c r="D344" t="n">
         <v>32.89473684210526</v>
       </c>
     </row>
@@ -5257,12 +4211,9 @@
         <v>2587</v>
       </c>
       <c r="B345" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="C345" t="n">
-        <v>73</v>
-      </c>
-      <c r="D345" t="n">
         <v>35.43835616438356</v>
       </c>
     </row>
@@ -5271,12 +4222,9 @@
         <v>2700</v>
       </c>
       <c r="B346" t="n">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="C346" t="n">
-        <v>101</v>
-      </c>
-      <c r="D346" t="n">
         <v>26.73267326732673</v>
       </c>
     </row>
@@ -5285,12 +4233,9 @@
         <v>2700</v>
       </c>
       <c r="B347" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="C347" t="n">
-        <v>84</v>
-      </c>
-      <c r="D347" t="n">
         <v>32.14285714285715</v>
       </c>
     </row>
@@ -5299,12 +4244,9 @@
         <v>2750</v>
       </c>
       <c r="B348" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="C348" t="n">
-        <v>81</v>
-      </c>
-      <c r="D348" t="n">
         <v>33.95061728395062</v>
       </c>
     </row>
@@ -5313,12 +4255,9 @@
         <v>2800</v>
       </c>
       <c r="B349" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C349" t="n">
-        <v>68</v>
-      </c>
-      <c r="D349" t="n">
         <v>41.1764705882353</v>
       </c>
     </row>
@@ -5327,12 +4266,9 @@
         <v>2800</v>
       </c>
       <c r="B350" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C350" t="n">
-        <v>60</v>
-      </c>
-      <c r="D350" t="n">
         <v>46.66666666666666</v>
       </c>
     </row>
@@ -5341,12 +4277,9 @@
         <v>2886</v>
       </c>
       <c r="B351" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="C351" t="n">
-        <v>85</v>
-      </c>
-      <c r="D351" t="n">
         <v>33.95294117647059</v>
       </c>
     </row>
@@ -5355,12 +4288,9 @@
         <v>2900</v>
       </c>
       <c r="B352" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="C352" t="n">
-        <v>110</v>
-      </c>
-      <c r="D352" t="n">
         <v>26.36363636363636</v>
       </c>
     </row>
@@ -5369,12 +4299,9 @@
         <v>3000</v>
       </c>
       <c r="B353" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="C353" t="n">
-        <v>95</v>
-      </c>
-      <c r="D353" t="n">
         <v>31.57894736842105</v>
       </c>
     </row>
@@ -5383,12 +4310,9 @@
         <v>3000</v>
       </c>
       <c r="B354" t="n">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="C354" t="n">
-        <v>101</v>
-      </c>
-      <c r="D354" t="n">
         <v>29.7029702970297</v>
       </c>
     </row>
@@ -5397,12 +4321,9 @@
         <v>3000</v>
       </c>
       <c r="B355" t="n">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="C355" t="n">
-        <v>90</v>
-      </c>
-      <c r="D355" t="n">
         <v>33.33333333333334</v>
       </c>
     </row>
@@ -5411,12 +4332,9 @@
         <v>2840</v>
       </c>
       <c r="B356" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C356" t="n">
-        <v>100</v>
-      </c>
-      <c r="D356" t="n">
         <v>28.4</v>
       </c>
     </row>
@@ -5425,12 +4343,9 @@
         <v>3100</v>
       </c>
       <c r="B357" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C357" t="n">
-        <v>100</v>
-      </c>
-      <c r="D357" t="n">
         <v>31</v>
       </c>
     </row>
@@ -5439,12 +4354,9 @@
         <v>3179</v>
       </c>
       <c r="B358" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="C358" t="n">
-        <v>72</v>
-      </c>
-      <c r="D358" t="n">
         <v>44.15277777777778</v>
       </c>
     </row>
@@ -5453,12 +4365,9 @@
         <v>3200</v>
       </c>
       <c r="B359" t="n">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="C359" t="n">
-        <v>114</v>
-      </c>
-      <c r="D359" t="n">
         <v>28.07017543859649</v>
       </c>
     </row>
@@ -5467,12 +4376,9 @@
         <v>3200</v>
       </c>
       <c r="B360" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="C360" t="n">
-        <v>110</v>
-      </c>
-      <c r="D360" t="n">
         <v>29.09090909090909</v>
       </c>
     </row>
@@ -5481,12 +4387,9 @@
         <v>3000</v>
       </c>
       <c r="B361" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="C361" t="n">
-        <v>110</v>
-      </c>
-      <c r="D361" t="n">
         <v>27.27272727272727</v>
       </c>
     </row>
@@ -5495,12 +4398,9 @@
         <v>3200</v>
       </c>
       <c r="B362" t="n">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="C362" t="n">
-        <v>105</v>
-      </c>
-      <c r="D362" t="n">
         <v>30.47619047619047</v>
       </c>
     </row>
@@ -5509,12 +4409,9 @@
         <v>3300</v>
       </c>
       <c r="B363" t="n">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="C363" t="n">
-        <v>101</v>
-      </c>
-      <c r="D363" t="n">
         <v>32.67326732673267</v>
       </c>
     </row>
@@ -5523,12 +4420,9 @@
         <v>3300</v>
       </c>
       <c r="B364" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="C364" t="n">
-        <v>95</v>
-      </c>
-      <c r="D364" t="n">
         <v>34.73684210526316</v>
       </c>
     </row>
@@ -5537,12 +4431,9 @@
         <v>3300</v>
       </c>
       <c r="B365" t="n">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="C365" t="n">
-        <v>108</v>
-      </c>
-      <c r="D365" t="n">
         <v>30.55555555555556</v>
       </c>
     </row>
@@ -5551,12 +4442,9 @@
         <v>3460</v>
       </c>
       <c r="B366" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C366" t="n">
-        <v>103</v>
-      </c>
-      <c r="D366" t="n">
         <v>33.59223300970874</v>
       </c>
     </row>
@@ -5565,12 +4453,9 @@
         <v>3500</v>
       </c>
       <c r="B367" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="C367" t="n">
-        <v>78</v>
-      </c>
-      <c r="D367" t="n">
         <v>44.87179487179487</v>
       </c>
     </row>
@@ -5579,12 +4464,9 @@
         <v>3650</v>
       </c>
       <c r="B368" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="C368" t="n">
-        <v>120</v>
-      </c>
-      <c r="D368" t="n">
         <v>30.41666666666667</v>
       </c>
     </row>
@@ -5593,12 +4475,9 @@
         <v>3660</v>
       </c>
       <c r="B369" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C369" t="n">
-        <v>100</v>
-      </c>
-      <c r="D369" t="n">
         <v>36.6</v>
       </c>
     </row>
@@ -5607,12 +4486,9 @@
         <v>3680</v>
       </c>
       <c r="B370" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="C370" t="n">
-        <v>112</v>
-      </c>
-      <c r="D370" t="n">
         <v>32.85714285714285</v>
       </c>
     </row>
@@ -5621,12 +4497,9 @@
         <v>3700</v>
       </c>
       <c r="B371" t="n">
-        <v>3</v>
+        <v>145</v>
       </c>
       <c r="C371" t="n">
-        <v>145</v>
-      </c>
-      <c r="D371" t="n">
         <v>25.51724137931035</v>
       </c>
     </row>
@@ -5635,12 +4508,9 @@
         <v>4500</v>
       </c>
       <c r="B372" t="n">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="C372" t="n">
-        <v>117</v>
-      </c>
-      <c r="D372" t="n">
         <v>38.46153846153846</v>
       </c>
     </row>
@@ -5649,12 +4519,9 @@
         <v>4600</v>
       </c>
       <c r="B373" t="n">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="C373" t="n">
-        <v>131</v>
-      </c>
-      <c r="D373" t="n">
         <v>35.11450381679389</v>
       </c>
     </row>
@@ -5663,12 +4530,9 @@
         <v>4930</v>
       </c>
       <c r="B374" t="n">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="C374" t="n">
-        <v>117</v>
-      </c>
-      <c r="D374" t="n">
         <v>42.13675213675214</v>
       </c>
     </row>
@@ -5677,12 +4541,9 @@
         <v>4937</v>
       </c>
       <c r="B375" t="n">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="C375" t="n">
-        <v>173</v>
-      </c>
-      <c r="D375" t="n">
         <v>28.53757225433526</v>
       </c>
     </row>
@@ -5691,12 +4552,9 @@
         <v>5100</v>
       </c>
       <c r="B376" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C376" t="n">
-        <v>100</v>
-      </c>
-      <c r="D376" t="n">
         <v>51</v>
       </c>
     </row>
@@ -5705,12 +4563,9 @@
         <v>5233</v>
       </c>
       <c r="B377" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="C377" t="n">
-        <v>162</v>
-      </c>
-      <c r="D377" t="n">
         <v>32.30246913580247</v>
       </c>
     </row>
@@ -5719,12 +4574,9 @@
         <v>5249</v>
       </c>
       <c r="B378" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="C378" t="n">
-        <v>162</v>
-      </c>
-      <c r="D378" t="n">
         <v>32.40123456790123</v>
       </c>
     </row>
@@ -5733,12 +4585,9 @@
         <v>5000</v>
       </c>
       <c r="B379" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="C379" t="n">
-        <v>152</v>
-      </c>
-      <c r="D379" t="n">
         <v>32.89473684210526</v>
       </c>
     </row>
@@ -5747,12 +4596,9 @@
         <v>5307</v>
       </c>
       <c r="B380" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="C380" t="n">
-        <v>175</v>
-      </c>
-      <c r="D380" t="n">
         <v>30.32571428571429</v>
       </c>
     </row>
@@ -5761,12 +4607,9 @@
         <v>5950</v>
       </c>
       <c r="B381" t="n">
-        <v>3</v>
+        <v>235</v>
       </c>
       <c r="C381" t="n">
-        <v>235</v>
-      </c>
-      <c r="D381" t="n">
         <v>25.31914893617021</v>
       </c>
     </row>
@@ -5775,12 +4618,9 @@
         <v>7450</v>
       </c>
       <c r="B382" t="n">
-        <v>3</v>
+        <v>180</v>
       </c>
       <c r="C382" t="n">
-        <v>180</v>
-      </c>
-      <c r="D382" t="n">
         <v>41.38888888888889</v>
       </c>
     </row>
@@ -5789,12 +4629,9 @@
         <v>25000</v>
       </c>
       <c r="B383" t="n">
-        <v>3</v>
+        <v>415</v>
       </c>
       <c r="C383" t="n">
-        <v>415</v>
-      </c>
-      <c r="D383" t="n">
         <v>60.24096385542169</v>
       </c>
     </row>
@@ -5803,12 +4640,9 @@
         <v>730</v>
       </c>
       <c r="B384" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C384" t="n">
-        <v>11</v>
-      </c>
-      <c r="D384" t="n">
         <v>66.36363636363636</v>
       </c>
     </row>
@@ -5817,12 +4651,9 @@
         <v>738</v>
       </c>
       <c r="B385" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C385" t="n">
-        <v>14</v>
-      </c>
-      <c r="D385" t="n">
         <v>52.71428571428572</v>
       </c>
     </row>
@@ -5831,12 +4662,9 @@
         <v>821</v>
       </c>
       <c r="B386" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C386" t="n">
-        <v>18</v>
-      </c>
-      <c r="D386" t="n">
         <v>45.61111111111111</v>
       </c>
     </row>
@@ -5845,12 +4673,9 @@
         <v>850</v>
       </c>
       <c r="B387" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>16</v>
-      </c>
-      <c r="D387" t="n">
         <v>53.125</v>
       </c>
     </row>
@@ -5859,12 +4684,9 @@
         <v>854</v>
       </c>
       <c r="B388" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C388" t="n">
-        <v>25</v>
-      </c>
-      <c r="D388" t="n">
         <v>34.16</v>
       </c>
     </row>
@@ -5873,12 +4695,9 @@
         <v>910</v>
       </c>
       <c r="B389" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C389" t="n">
-        <v>24</v>
-      </c>
-      <c r="D389" t="n">
         <v>37.91666666666666</v>
       </c>
     </row>
@@ -5887,12 +4706,9 @@
         <v>940</v>
       </c>
       <c r="B390" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C390" t="n">
-        <v>19</v>
-      </c>
-      <c r="D390" t="n">
         <v>49.47368421052632</v>
       </c>
     </row>
@@ -5901,12 +4717,9 @@
         <v>950</v>
       </c>
       <c r="B391" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C391" t="n">
-        <v>20</v>
-      </c>
-      <c r="D391" t="n">
         <v>47.5</v>
       </c>
     </row>
@@ -5915,12 +4728,9 @@
         <v>950</v>
       </c>
       <c r="B392" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C392" t="n">
-        <v>21</v>
-      </c>
-      <c r="D392" t="n">
         <v>45.23809523809524</v>
       </c>
     </row>
@@ -5929,12 +4739,9 @@
         <v>976</v>
       </c>
       <c r="B393" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C393" t="n">
-        <v>23</v>
-      </c>
-      <c r="D393" t="n">
         <v>42.43478260869565</v>
       </c>
     </row>
@@ -5943,12 +4750,9 @@
         <v>990</v>
       </c>
       <c r="B394" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C394" t="n">
-        <v>27</v>
-      </c>
-      <c r="D394" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
@@ -5957,12 +4761,9 @@
         <v>1190</v>
       </c>
       <c r="B395" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C395" t="n">
-        <v>29</v>
-      </c>
-      <c r="D395" t="n">
         <v>41.03448275862069</v>
       </c>
     </row>
@@ -5971,12 +4772,9 @@
         <v>1095</v>
       </c>
       <c r="B396" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C396" t="n">
-        <v>30</v>
-      </c>
-      <c r="D396" t="n">
         <v>36.5</v>
       </c>
     </row>
@@ -5985,12 +4783,9 @@
         <v>1210</v>
       </c>
       <c r="B397" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C397" t="n">
-        <v>40</v>
-      </c>
-      <c r="D397" t="n">
         <v>30.25</v>
       </c>
     </row>
@@ -5999,12 +4794,9 @@
         <v>1250</v>
       </c>
       <c r="B398" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C398" t="n">
-        <v>28</v>
-      </c>
-      <c r="D398" t="n">
         <v>44.64285714285715</v>
       </c>
     </row>
@@ -6013,12 +4805,9 @@
         <v>1255</v>
       </c>
       <c r="B399" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C399" t="n">
-        <v>24</v>
-      </c>
-      <c r="D399" t="n">
         <v>52.29166666666666</v>
       </c>
     </row>
@@ -6027,12 +4816,9 @@
         <v>1255</v>
       </c>
       <c r="B400" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C400" t="n">
-        <v>24</v>
-      </c>
-      <c r="D400" t="n">
         <v>52.29166666666666</v>
       </c>
     </row>
@@ -6041,12 +4827,9 @@
         <v>1300</v>
       </c>
       <c r="B401" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C401" t="n">
-        <v>32</v>
-      </c>
-      <c r="D401" t="n">
         <v>40.625</v>
       </c>
     </row>
@@ -6055,12 +4838,9 @@
         <v>1380</v>
       </c>
       <c r="B402" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C402" t="n">
-        <v>32</v>
-      </c>
-      <c r="D402" t="n">
         <v>43.125</v>
       </c>
     </row>
@@ -6069,12 +4849,9 @@
         <v>1500</v>
       </c>
       <c r="B403" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C403" t="n">
-        <v>42</v>
-      </c>
-      <c r="D403" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
@@ -6083,12 +4860,9 @@
         <v>1500</v>
       </c>
       <c r="B404" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C404" t="n">
-        <v>34</v>
-      </c>
-      <c r="D404" t="n">
         <v>44.11764705882353</v>
       </c>
     </row>
@@ -6097,12 +4871,9 @@
         <v>1510</v>
       </c>
       <c r="B405" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C405" t="n">
-        <v>29</v>
-      </c>
-      <c r="D405" t="n">
         <v>52.06896551724138</v>
       </c>
     </row>
@@ -6111,12 +4882,9 @@
         <v>1550</v>
       </c>
       <c r="B406" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C406" t="n">
-        <v>30</v>
-      </c>
-      <c r="D406" t="n">
         <v>51.66666666666666</v>
       </c>
     </row>
@@ -6125,12 +4893,9 @@
         <v>1560</v>
       </c>
       <c r="B407" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C407" t="n">
-        <v>50</v>
-      </c>
-      <c r="D407" t="n">
         <v>31.2</v>
       </c>
     </row>
@@ -6139,12 +4904,9 @@
         <v>1580</v>
       </c>
       <c r="B408" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C408" t="n">
-        <v>35</v>
-      </c>
-      <c r="D408" t="n">
         <v>45.14285714285715</v>
       </c>
     </row>
@@ -6153,12 +4915,9 @@
         <v>1640</v>
       </c>
       <c r="B409" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C409" t="n">
-        <v>47</v>
-      </c>
-      <c r="D409" t="n">
         <v>34.8936170212766</v>
       </c>
     </row>
@@ -6167,12 +4926,9 @@
         <v>1650</v>
       </c>
       <c r="B410" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C410" t="n">
-        <v>40</v>
-      </c>
-      <c r="D410" t="n">
         <v>41.25</v>
       </c>
     </row>
@@ -6181,12 +4937,9 @@
         <v>1665</v>
       </c>
       <c r="B411" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C411" t="n">
-        <v>34</v>
-      </c>
-      <c r="D411" t="n">
         <v>48.97058823529412</v>
       </c>
     </row>
@@ -6195,12 +4948,9 @@
         <v>1865</v>
       </c>
       <c r="B412" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C412" t="n">
-        <v>55</v>
-      </c>
-      <c r="D412" t="n">
         <v>33.90909090909091</v>
       </c>
     </row>
@@ -6209,12 +4959,9 @@
         <v>1920</v>
       </c>
       <c r="B413" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C413" t="n">
-        <v>64</v>
-      </c>
-      <c r="D413" t="n">
         <v>30</v>
       </c>
     </row>
@@ -6223,12 +4970,9 @@
         <v>2000</v>
       </c>
       <c r="B414" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C414" t="n">
-        <v>42</v>
-      </c>
-      <c r="D414" t="n">
         <v>47.61904761904762</v>
       </c>
     </row>
@@ -6237,12 +4981,9 @@
         <v>2000</v>
       </c>
       <c r="B415" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C415" t="n">
-        <v>41</v>
-      </c>
-      <c r="D415" t="n">
         <v>48.78048780487805</v>
       </c>
     </row>
@@ -6251,12 +4992,9 @@
         <v>2130</v>
       </c>
       <c r="B416" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="C416" t="n">
-        <v>73</v>
-      </c>
-      <c r="D416" t="n">
         <v>29.17808219178082</v>
       </c>
     </row>
@@ -6265,12 +5003,9 @@
         <v>2200</v>
       </c>
       <c r="B417" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="C417" t="n">
-        <v>57</v>
-      </c>
-      <c r="D417" t="n">
         <v>38.59649122807018</v>
       </c>
     </row>
@@ -6279,12 +5014,9 @@
         <v>2300</v>
       </c>
       <c r="B418" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C418" t="n">
-        <v>80</v>
-      </c>
-      <c r="D418" t="n">
         <v>28.75</v>
       </c>
     </row>
@@ -6293,12 +5025,9 @@
         <v>2500</v>
       </c>
       <c r="B419" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C419" t="n">
-        <v>60</v>
-      </c>
-      <c r="D419" t="n">
         <v>41.66666666666666</v>
       </c>
     </row>
@@ -6307,12 +5036,9 @@
         <v>3750</v>
       </c>
       <c r="B420" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C420" t="n">
-        <v>70</v>
-      </c>
-      <c r="D420" t="n">
         <v>53.57142857142857</v>
       </c>
     </row>
@@ -6321,12 +5047,9 @@
         <v>3800</v>
       </c>
       <c r="B421" t="n">
-        <v>3</v>
+        <v>138</v>
       </c>
       <c r="C421" t="n">
-        <v>138</v>
-      </c>
-      <c r="D421" t="n">
         <v>27.53623188405797</v>
       </c>
     </row>
@@ -6335,12 +5058,9 @@
         <v>4100</v>
       </c>
       <c r="B422" t="n">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="C422" t="n">
-        <v>127</v>
-      </c>
-      <c r="D422" t="n">
         <v>32.28346456692913</v>
       </c>
     </row>
@@ -6349,12 +5069,9 @@
         <v>4300</v>
       </c>
       <c r="B423" t="n">
-        <v>3</v>
+        <v>148</v>
       </c>
       <c r="C423" t="n">
-        <v>148</v>
-      </c>
-      <c r="D423" t="n">
         <v>29.05405405405405</v>
       </c>
     </row>
@@ -6363,12 +5080,9 @@
         <v>4500</v>
       </c>
       <c r="B424" t="n">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C424" t="n">
-        <v>115</v>
-      </c>
-      <c r="D424" t="n">
         <v>39.1304347826087</v>
       </c>
     </row>
@@ -6377,12 +5091,9 @@
         <v>15000</v>
       </c>
       <c r="B425" t="n">
-        <v>3</v>
+        <v>347</v>
       </c>
       <c r="C425" t="n">
-        <v>347</v>
-      </c>
-      <c r="D425" t="n">
         <v>43.22766570605187</v>
       </c>
     </row>
@@ -6391,12 +5102,9 @@
         <v>637</v>
       </c>
       <c r="B426" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C426" t="n">
-        <v>14</v>
-      </c>
-      <c r="D426" t="n">
         <v>45.5</v>
       </c>
     </row>
@@ -6405,12 +5113,9 @@
         <v>680</v>
       </c>
       <c r="B427" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C427" t="n">
-        <v>14</v>
-      </c>
-      <c r="D427" t="n">
         <v>48.57142857142857</v>
       </c>
     </row>
@@ -6419,12 +5124,9 @@
         <v>700</v>
       </c>
       <c r="B428" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C428" t="n">
-        <v>18</v>
-      </c>
-      <c r="D428" t="n">
         <v>38.88888888888889</v>
       </c>
     </row>
@@ -6433,12 +5135,9 @@
         <v>960</v>
       </c>
       <c r="B429" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C429" t="n">
-        <v>20</v>
-      </c>
-      <c r="D429" t="n">
         <v>48</v>
       </c>
     </row>
@@ -6447,12 +5146,9 @@
         <v>775</v>
       </c>
       <c r="B430" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C430" t="n">
-        <v>20</v>
-      </c>
-      <c r="D430" t="n">
         <v>38.75</v>
       </c>
     </row>
@@ -6461,12 +5157,9 @@
         <v>1250</v>
       </c>
       <c r="B431" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C431" t="n">
-        <v>40</v>
-      </c>
-      <c r="D431" t="n">
         <v>31.25</v>
       </c>
     </row>
@@ -6475,12 +5168,9 @@
         <v>1380</v>
       </c>
       <c r="B432" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C432" t="n">
-        <v>30</v>
-      </c>
-      <c r="D432" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6489,12 +5179,9 @@
         <v>1630</v>
       </c>
       <c r="B433" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C433" t="n">
-        <v>54</v>
-      </c>
-      <c r="D433" t="n">
         <v>30.18518518518519</v>
       </c>
     </row>
@@ -6503,12 +5190,9 @@
         <v>1650</v>
       </c>
       <c r="B434" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C434" t="n">
-        <v>50</v>
-      </c>
-      <c r="D434" t="n">
         <v>33</v>
       </c>
     </row>
@@ -6517,12 +5201,9 @@
         <v>1765</v>
       </c>
       <c r="B435" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C435" t="n">
-        <v>62</v>
-      </c>
-      <c r="D435" t="n">
         <v>28.46774193548387</v>
       </c>
     </row>
@@ -6531,12 +5212,9 @@
         <v>1900</v>
       </c>
       <c r="B436" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C436" t="n">
-        <v>64</v>
-      </c>
-      <c r="D436" t="n">
         <v>29.6875</v>
       </c>
     </row>
@@ -6545,12 +5223,9 @@
         <v>1787</v>
       </c>
       <c r="B437" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="C437" t="n">
-        <v>77</v>
-      </c>
-      <c r="D437" t="n">
         <v>23.20779220779221</v>
       </c>
     </row>
@@ -6559,12 +5234,9 @@
         <v>1920</v>
       </c>
       <c r="B438" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C438" t="n">
-        <v>64</v>
-      </c>
-      <c r="D438" t="n">
         <v>30</v>
       </c>
     </row>
@@ -6573,12 +5245,9 @@
         <v>2132</v>
       </c>
       <c r="B439" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C439" t="n">
-        <v>69</v>
-      </c>
-      <c r="D439" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
@@ -6587,12 +5256,9 @@
         <v>2132</v>
       </c>
       <c r="B440" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C440" t="n">
-        <v>69</v>
-      </c>
-      <c r="D440" t="n">
         <v>30.89855072463768</v>
       </c>
     </row>
@@ -6601,12 +5267,9 @@
         <v>2200</v>
       </c>
       <c r="B441" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C441" t="n">
-        <v>60</v>
-      </c>
-      <c r="D441" t="n">
         <v>36.66666666666666</v>
       </c>
     </row>
@@ -6615,12 +5278,9 @@
         <v>2272</v>
       </c>
       <c r="B442" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C442" t="n">
-        <v>69</v>
-      </c>
-      <c r="D442" t="n">
         <v>32.92753623188405</v>
       </c>
     </row>
@@ -6629,12 +5289,9 @@
         <v>2400</v>
       </c>
       <c r="B443" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C443" t="n">
-        <v>70</v>
-      </c>
-      <c r="D443" t="n">
         <v>34.28571428571428</v>
       </c>
     </row>
@@ -6643,12 +5300,9 @@
         <v>2350</v>
       </c>
       <c r="B444" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C444" t="n">
-        <v>70</v>
-      </c>
-      <c r="D444" t="n">
         <v>33.57142857142857</v>
       </c>
     </row>
@@ -6657,12 +5311,9 @@
         <v>2657</v>
       </c>
       <c r="B445" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C445" t="n">
-        <v>40</v>
-      </c>
-      <c r="D445" t="n">
         <v>66.425</v>
       </c>
     </row>
@@ -6671,12 +5322,9 @@
         <v>2999</v>
       </c>
       <c r="B446" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="C446" t="n">
-        <v>76</v>
-      </c>
-      <c r="D446" t="n">
         <v>39.46052631578947</v>
       </c>
     </row>
@@ -6685,12 +5333,9 @@
         <v>3000</v>
       </c>
       <c r="B447" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C447" t="n">
-        <v>80</v>
-      </c>
-      <c r="D447" t="n">
         <v>37.5</v>
       </c>
     </row>
@@ -6699,12 +5344,9 @@
         <v>3460</v>
       </c>
       <c r="B448" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C448" t="n">
-        <v>103</v>
-      </c>
-      <c r="D448" t="n">
         <v>33.59223300970874</v>
       </c>
     </row>
@@ -6713,12 +5355,9 @@
         <v>3600</v>
       </c>
       <c r="B449" t="n">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="C449" t="n">
-        <v>124</v>
-      </c>
-      <c r="D449" t="n">
         <v>29.03225806451613</v>
       </c>
     </row>
@@ -6727,12 +5366,9 @@
         <v>16000</v>
       </c>
       <c r="B450" t="n">
-        <v>3</v>
+        <v>347</v>
       </c>
       <c r="C450" t="n">
-        <v>347</v>
-      </c>
-      <c r="D450" t="n">
         <v>46.10951008645533</v>
       </c>
     </row>
@@ -6741,12 +5377,9 @@
         <v>20000</v>
       </c>
       <c r="B451" t="n">
-        <v>3</v>
+        <v>180</v>
       </c>
       <c r="C451" t="n">
-        <v>180</v>
-      </c>
-      <c r="D451" t="n">
         <v>111.1111111111111</v>
       </c>
     </row>
@@ -6755,12 +5388,9 @@
         <v>2290</v>
       </c>
       <c r="B452" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C452" t="n">
-        <v>70</v>
-      </c>
-      <c r="D452" t="n">
         <v>32.71428571428572</v>
       </c>
     </row>
@@ -6769,12 +5399,9 @@
         <v>2927</v>
       </c>
       <c r="B453" t="n">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="C453" t="n">
-        <v>116</v>
-      </c>
-      <c r="D453" t="n">
         <v>25.23275862068965</v>
       </c>
     </row>
@@ -6783,12 +5410,9 @@
         <v>700</v>
       </c>
       <c r="B454" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C454" t="n">
-        <v>14</v>
-      </c>
-      <c r="D454" t="n">
         <v>50</v>
       </c>
     </row>
@@ -6797,12 +5421,9 @@
         <v>755</v>
       </c>
       <c r="B455" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C455" t="n">
-        <v>19</v>
-      </c>
-      <c r="D455" t="n">
         <v>39.73684210526316</v>
       </c>
     </row>
@@ -6811,12 +5432,9 @@
         <v>990</v>
       </c>
       <c r="B456" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C456" t="n">
-        <v>24</v>
-      </c>
-      <c r="D456" t="n">
         <v>41.25</v>
       </c>
     </row>
@@ -6825,12 +5443,9 @@
         <v>1058</v>
       </c>
       <c r="B457" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C457" t="n">
-        <v>21</v>
-      </c>
-      <c r="D457" t="n">
         <v>50.38095238095238</v>
       </c>
     </row>
@@ -6839,12 +5454,9 @@
         <v>1095</v>
       </c>
       <c r="B458" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C458" t="n">
-        <v>20</v>
-      </c>
-      <c r="D458" t="n">
         <v>54.75</v>
       </c>
     </row>
@@ -6853,12 +5465,9 @@
         <v>1100</v>
       </c>
       <c r="B459" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C459" t="n">
-        <v>37</v>
-      </c>
-      <c r="D459" t="n">
         <v>29.72972972972973</v>
       </c>
     </row>
@@ -6867,12 +5476,9 @@
         <v>1280</v>
       </c>
       <c r="B460" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C460" t="n">
-        <v>29</v>
-      </c>
-      <c r="D460" t="n">
         <v>44.13793103448276</v>
       </c>
     </row>
@@ -6881,12 +5487,9 @@
         <v>1350</v>
       </c>
       <c r="B461" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C461" t="n">
-        <v>35</v>
-      </c>
-      <c r="D461" t="n">
         <v>38.57142857142857</v>
       </c>
     </row>
@@ -6895,12 +5498,9 @@
         <v>1400</v>
       </c>
       <c r="B462" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C462" t="n">
-        <v>45</v>
-      </c>
-      <c r="D462" t="n">
         <v>31.11111111111111</v>
       </c>
     </row>
@@ -6909,12 +5509,9 @@
         <v>1550</v>
       </c>
       <c r="B463" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C463" t="n">
-        <v>33</v>
-      </c>
-      <c r="D463" t="n">
         <v>46.96969696969697</v>
       </c>
     </row>
@@ -6923,12 +5520,9 @@
         <v>1900</v>
       </c>
       <c r="B464" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C464" t="n">
-        <v>64</v>
-      </c>
-      <c r="D464" t="n">
         <v>29.6875</v>
       </c>
     </row>
@@ -6937,12 +5531,9 @@
         <v>2200</v>
       </c>
       <c r="B465" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C465" t="n">
-        <v>55</v>
-      </c>
-      <c r="D465" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6951,12 +5542,9 @@
         <v>3140</v>
       </c>
       <c r="B466" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C466" t="n">
-        <v>100</v>
-      </c>
-      <c r="D466" t="n">
         <v>31.4</v>
       </c>
     </row>
@@ -6965,12 +5553,9 @@
         <v>600</v>
       </c>
       <c r="B467" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C467" t="n">
-        <v>20</v>
-      </c>
-      <c r="D467" t="n">
         <v>30</v>
       </c>
     </row>
@@ -6979,12 +5564,9 @@
         <v>600</v>
       </c>
       <c r="B468" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>16</v>
-      </c>
-      <c r="D468" t="n">
         <v>37.5</v>
       </c>
     </row>
@@ -6993,12 +5575,9 @@
         <v>890</v>
       </c>
       <c r="B469" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C469" t="n">
-        <v>20</v>
-      </c>
-      <c r="D469" t="n">
         <v>44.5</v>
       </c>
     </row>
@@ -7007,12 +5586,9 @@
         <v>1050</v>
       </c>
       <c r="B470" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C470" t="n">
-        <v>30</v>
-      </c>
-      <c r="D470" t="n">
         <v>35</v>
       </c>
     </row>
@@ -7021,12 +5597,9 @@
         <v>1100</v>
       </c>
       <c r="B471" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C471" t="n">
-        <v>31</v>
-      </c>
-      <c r="D471" t="n">
         <v>35.48387096774194</v>
       </c>
     </row>
@@ -7035,12 +5608,9 @@
         <v>1650</v>
       </c>
       <c r="B472" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C472" t="n">
-        <v>49</v>
-      </c>
-      <c r="D472" t="n">
         <v>33.67346938775511</v>
       </c>
     </row>
@@ -7049,12 +5619,9 @@
         <v>2090</v>
       </c>
       <c r="B473" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="C473" t="n">
-        <v>73</v>
-      </c>
-      <c r="D473" t="n">
         <v>28.63013698630137</v>
       </c>
     </row>
@@ -7063,12 +5630,9 @@
         <v>6300</v>
       </c>
       <c r="B474" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="C474" t="n">
-        <v>112</v>
-      </c>
-      <c r="D474" t="n">
         <v>56.25</v>
       </c>
     </row>
@@ -7077,12 +5641,9 @@
         <v>930</v>
       </c>
       <c r="B475" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C475" t="n">
-        <v>16</v>
-      </c>
-      <c r="D475" t="n">
         <v>58.125</v>
       </c>
     </row>
@@ -7091,12 +5652,9 @@
         <v>1980</v>
       </c>
       <c r="B476" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="C476" t="n">
-        <v>84</v>
-      </c>
-      <c r="D476" t="n">
         <v>23.57142857142857</v>
       </c>
     </row>
@@ -7105,12 +5663,9 @@
         <v>885</v>
       </c>
       <c r="B477" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C477" t="n">
-        <v>23</v>
-      </c>
-      <c r="D477" t="n">
         <v>38.47826086956522</v>
       </c>
     </row>
@@ -7119,12 +5674,9 @@
         <v>1060</v>
       </c>
       <c r="B478" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C478" t="n">
-        <v>47</v>
-      </c>
-      <c r="D478" t="n">
         <v>22.5531914893617</v>
       </c>
     </row>
@@ -7133,12 +5685,9 @@
         <v>1200</v>
       </c>
       <c r="B479" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C479" t="n">
-        <v>48</v>
-      </c>
-      <c r="D479" t="n">
         <v>25</v>
       </c>
     </row>
@@ -7147,12 +5696,9 @@
         <v>1500</v>
       </c>
       <c r="B480" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C480" t="n">
-        <v>38</v>
-      </c>
-      <c r="D480" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
@@ -7161,12 +5707,9 @@
         <v>890</v>
       </c>
       <c r="B481" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C481" t="n">
-        <v>20</v>
-      </c>
-      <c r="D481" t="n">
         <v>44.5</v>
       </c>
     </row>
@@ -7175,12 +5718,9 @@
         <v>1300</v>
       </c>
       <c r="B482" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C482" t="n">
-        <v>42</v>
-      </c>
-      <c r="D482" t="n">
         <v>30.95238095238095</v>
       </c>
     </row>
@@ -7189,12 +5729,9 @@
         <v>900</v>
       </c>
       <c r="B483" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C483" t="n">
-        <v>29</v>
-      </c>
-      <c r="D483" t="n">
         <v>31.03448275862069</v>
       </c>
     </row>
@@ -7203,12 +5740,9 @@
         <v>1150</v>
       </c>
       <c r="B484" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C484" t="n">
-        <v>24</v>
-      </c>
-      <c r="D484" t="n">
         <v>47.91666666666666</v>
       </c>
     </row>
@@ -7217,12 +5751,9 @@
         <v>840</v>
       </c>
       <c r="B485" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C485" t="n">
-        <v>22</v>
-      </c>
-      <c r="D485" t="n">
         <v>38.18181818181818</v>
       </c>
     </row>
@@ -7231,12 +5762,9 @@
         <v>928</v>
       </c>
       <c r="B486" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C486" t="n">
-        <v>29</v>
-      </c>
-      <c r="D486" t="n">
         <v>32</v>
       </c>
     </row>
@@ -7245,12 +5773,9 @@
         <v>981</v>
       </c>
       <c r="B487" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C487" t="n">
-        <v>30</v>
-      </c>
-      <c r="D487" t="n">
         <v>32.7</v>
       </c>
     </row>
@@ -7259,12 +5784,9 @@
         <v>1180</v>
       </c>
       <c r="B488" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C488" t="n">
-        <v>31</v>
-      </c>
-      <c r="D488" t="n">
         <v>38.06451612903226</v>
       </c>
     </row>
@@ -7273,12 +5795,9 @@
         <v>1198</v>
       </c>
       <c r="B489" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C489" t="n">
-        <v>33</v>
-      </c>
-      <c r="D489" t="n">
         <v>36.3030303030303</v>
       </c>
     </row>
@@ -7287,12 +5806,9 @@
         <v>1450</v>
       </c>
       <c r="B490" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C490" t="n">
-        <v>47</v>
-      </c>
-      <c r="D490" t="n">
         <v>30.85106382978723</v>
       </c>
     </row>
@@ -7301,12 +5817,9 @@
         <v>3000</v>
       </c>
       <c r="B491" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C491" t="n">
-        <v>50</v>
-      </c>
-      <c r="D491" t="n">
         <v>60</v>
       </c>
     </row>
@@ -7315,12 +5828,9 @@
         <v>875</v>
       </c>
       <c r="B492" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C492" t="n">
-        <v>18</v>
-      </c>
-      <c r="D492" t="n">
         <v>48.61111111111111</v>
       </c>
     </row>
@@ -7329,12 +5839,9 @@
         <v>998</v>
       </c>
       <c r="B493" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C493" t="n">
-        <v>34</v>
-      </c>
-      <c r="D493" t="n">
         <v>29.35294117647059</v>
       </c>
     </row>
@@ -7343,12 +5850,9 @@
         <v>1000</v>
       </c>
       <c r="B494" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C494" t="n">
-        <v>25</v>
-      </c>
-      <c r="D494" t="n">
         <v>40</v>
       </c>
     </row>
@@ -7357,12 +5861,9 @@
         <v>1250</v>
       </c>
       <c r="B495" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C495" t="n">
-        <v>31</v>
-      </c>
-      <c r="D495" t="n">
         <v>40.32258064516129</v>
       </c>
     </row>
@@ -7371,12 +5872,9 @@
         <v>1480</v>
       </c>
       <c r="B496" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C496" t="n">
-        <v>40</v>
-      </c>
-      <c r="D496" t="n">
         <v>37</v>
       </c>
     </row>
@@ -7385,12 +5883,9 @@
         <v>1900</v>
       </c>
       <c r="B497" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C497" t="n">
-        <v>46</v>
-      </c>
-      <c r="D497" t="n">
         <v>41.30434782608695</v>
       </c>
     </row>
@@ -7399,12 +5894,9 @@
         <v>2500</v>
       </c>
       <c r="B498" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C498" t="n">
-        <v>70</v>
-      </c>
-      <c r="D498" t="n">
         <v>35.71428571428572</v>
       </c>
     </row>
@@ -7413,12 +5905,9 @@
         <v>950</v>
       </c>
       <c r="B499" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C499" t="n">
-        <v>28</v>
-      </c>
-      <c r="D499" t="n">
         <v>33.92857142857143</v>
       </c>
     </row>
@@ -7427,12 +5916,9 @@
         <v>1180</v>
       </c>
       <c r="B500" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C500" t="n">
-        <v>27</v>
-      </c>
-      <c r="D500" t="n">
         <v>43.7037037037037</v>
       </c>
     </row>
@@ -7441,12 +5927,9 @@
         <v>1550</v>
       </c>
       <c r="B501" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C501" t="n">
-        <v>40</v>
-      </c>
-      <c r="D501" t="n">
         <v>38.75</v>
       </c>
     </row>
@@ -7455,12 +5938,9 @@
         <v>1333</v>
       </c>
       <c r="B502" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C502" t="n">
-        <v>41</v>
-      </c>
-      <c r="D502" t="n">
         <v>32.51219512195122</v>
       </c>
     </row>
@@ -7469,12 +5949,9 @@
         <v>1580</v>
       </c>
       <c r="B503" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C503" t="n">
-        <v>40</v>
-      </c>
-      <c r="D503" t="n">
         <v>39.5</v>
       </c>
     </row>
@@ -7483,12 +5960,9 @@
         <v>850</v>
       </c>
       <c r="B504" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C504" t="n">
-        <v>27</v>
-      </c>
-      <c r="D504" t="n">
         <v>31.48148148148148</v>
       </c>
     </row>
@@ -7497,12 +5971,9 @@
         <v>488</v>
       </c>
       <c r="B505" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C505" t="n">
-        <v>13</v>
-      </c>
-      <c r="D505" t="n">
         <v>37.53846153846154</v>
       </c>
     </row>
@@ -7511,12 +5982,9 @@
         <v>619</v>
       </c>
       <c r="B506" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C506" t="n">
-        <v>18</v>
-      </c>
-      <c r="D506" t="n">
         <v>34.38888888888889</v>
       </c>
     </row>
@@ -7525,12 +5993,9 @@
         <v>820</v>
       </c>
       <c r="B507" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C507" t="n">
-        <v>23</v>
-      </c>
-      <c r="D507" t="n">
         <v>35.65217391304348</v>
       </c>
     </row>
@@ -7539,12 +6004,9 @@
         <v>1350</v>
       </c>
       <c r="B508" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C508" t="n">
-        <v>32</v>
-      </c>
-      <c r="D508" t="n">
         <v>42.1875</v>
       </c>
     </row>
@@ -7553,12 +6015,9 @@
         <v>1475</v>
       </c>
       <c r="B509" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="C509" t="n">
-        <v>57</v>
-      </c>
-      <c r="D509" t="n">
         <v>25.87719298245614</v>
       </c>
     </row>
@@ -7567,12 +6026,9 @@
         <v>1397</v>
       </c>
       <c r="B510" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C510" t="n">
-        <v>38</v>
-      </c>
-      <c r="D510" t="n">
         <v>36.76315789473684</v>
       </c>
     </row>
@@ -7581,12 +6037,9 @@
         <v>1460</v>
       </c>
       <c r="B511" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C511" t="n">
-        <v>52</v>
-      </c>
-      <c r="D511" t="n">
         <v>28.07692307692308</v>
       </c>
     </row>
@@ -7595,12 +6048,9 @@
         <v>3200</v>
       </c>
       <c r="B512" t="n">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="C512" t="n">
-        <v>114</v>
-      </c>
-      <c r="D512" t="n">
         <v>28.07017543859649</v>
       </c>
     </row>
@@ -7609,12 +6059,9 @@
         <v>5000</v>
       </c>
       <c r="B513" t="n">
-        <v>3</v>
+        <v>136</v>
       </c>
       <c r="C513" t="n">
-        <v>136</v>
-      </c>
-      <c r="D513" t="n">
         <v>36.76470588235294</v>
       </c>
     </row>
@@ -7623,12 +6070,9 @@
         <v>790</v>
       </c>
       <c r="B514" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C514" t="n">
-        <v>22</v>
-      </c>
-      <c r="D514" t="n">
         <v>35.90909090909091</v>
       </c>
     </row>
@@ -7637,12 +6081,9 @@
         <v>800</v>
       </c>
       <c r="B515" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C515" t="n">
-        <v>14</v>
-      </c>
-      <c r="D515" t="n">
         <v>57.14285714285715</v>
       </c>
     </row>
@@ -7651,12 +6092,9 @@
         <v>810</v>
       </c>
       <c r="B516" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C516" t="n">
-        <v>18</v>
-      </c>
-      <c r="D516" t="n">
         <v>45</v>
       </c>
     </row>
@@ -7665,12 +6103,9 @@
         <v>940</v>
       </c>
       <c r="B517" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C517" t="n">
-        <v>26</v>
-      </c>
-      <c r="D517" t="n">
         <v>36.15384615384615</v>
       </c>
     </row>
@@ -7679,12 +6114,9 @@
         <v>898</v>
       </c>
       <c r="B518" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C518" t="n">
-        <v>27</v>
-      </c>
-      <c r="D518" t="n">
         <v>33.25925925925926</v>
       </c>
     </row>
@@ -7693,12 +6125,9 @@
         <v>1137</v>
       </c>
       <c r="B519" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C519" t="n">
-        <v>33</v>
-      </c>
-      <c r="D519" t="n">
         <v>34.45454545454545</v>
       </c>
     </row>
@@ -7707,12 +6136,9 @@
         <v>810</v>
       </c>
       <c r="B520" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C520" t="n">
-        <v>18</v>
-      </c>
-      <c r="D520" t="n">
         <v>45</v>
       </c>
     </row>
@@ -7721,12 +6147,9 @@
         <v>940</v>
       </c>
       <c r="B521" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C521" t="n">
-        <v>26</v>
-      </c>
-      <c r="D521" t="n">
         <v>36.15384615384615</v>
       </c>
     </row>
@@ -7735,12 +6158,9 @@
         <v>898</v>
       </c>
       <c r="B522" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C522" t="n">
-        <v>27</v>
-      </c>
-      <c r="D522" t="n">
         <v>33.25925925925926</v>
       </c>
     </row>
@@ -7749,12 +6169,9 @@
         <v>1137</v>
       </c>
       <c r="B523" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C523" t="n">
-        <v>33</v>
-      </c>
-      <c r="D523" t="n">
         <v>34.45454545454545</v>
       </c>
     </row>
@@ -7763,12 +6180,9 @@
         <v>1600</v>
       </c>
       <c r="B524" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C524" t="n">
-        <v>60</v>
-      </c>
-      <c r="D524" t="n">
         <v>26.66666666666667</v>
       </c>
     </row>
@@ -7777,12 +6191,9 @@
         <v>2097</v>
       </c>
       <c r="B525" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C525" t="n">
-        <v>58</v>
-      </c>
-      <c r="D525" t="n">
         <v>36.1551724137931</v>
       </c>
     </row>
@@ -7791,12 +6202,9 @@
         <v>733</v>
       </c>
       <c r="B526" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C526" t="n">
-        <v>20</v>
-      </c>
-      <c r="D526" t="n">
         <v>36.65</v>
       </c>
     </row>
@@ -7805,12 +6213,9 @@
         <v>12000</v>
       </c>
       <c r="B527" t="n">
-        <v>3</v>
+        <v>230</v>
       </c>
       <c r="C527" t="n">
-        <v>230</v>
-      </c>
-      <c r="D527" t="n">
         <v>52.17391304347826</v>
       </c>
     </row>
@@ -7819,12 +6224,9 @@
         <v>1166</v>
       </c>
       <c r="B528" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C528" t="n">
-        <v>27</v>
-      </c>
-      <c r="D528" t="n">
         <v>43.18518518518518</v>
       </c>
     </row>
@@ -7833,12 +6235,9 @@
         <v>1500</v>
       </c>
       <c r="B529" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C529" t="n">
-        <v>38</v>
-      </c>
-      <c r="D529" t="n">
         <v>39.47368421052632</v>
       </c>
     </row>
@@ -7847,12 +6246,9 @@
         <v>1900</v>
       </c>
       <c r="B530" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C530" t="n">
-        <v>45</v>
-      </c>
-      <c r="D530" t="n">
         <v>42.22222222222222</v>
       </c>
     </row>
@@ -7861,12 +6257,9 @@
         <v>1900</v>
       </c>
       <c r="B531" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C531" t="n">
-        <v>64</v>
-      </c>
-      <c r="D531" t="n">
         <v>29.6875</v>
       </c>
     </row>
@@ -7875,12 +6268,9 @@
         <v>1950</v>
       </c>
       <c r="B532" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C532" t="n">
-        <v>45</v>
-      </c>
-      <c r="D532" t="n">
         <v>43.33333333333334</v>
       </c>
     </row>
@@ -7889,12 +6279,9 @@
         <v>2000</v>
       </c>
       <c r="B533" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="C533" t="n">
-        <v>65</v>
-      </c>
-      <c r="D533" t="n">
         <v>30.76923076923077</v>
       </c>
     </row>
@@ -7903,12 +6290,9 @@
         <v>2950</v>
       </c>
       <c r="B534" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="C534" t="n">
-        <v>95</v>
-      </c>
-      <c r="D534" t="n">
         <v>31.05263157894737</v>
       </c>
     </row>
@@ -7917,12 +6301,9 @@
         <v>1200</v>
       </c>
       <c r="B535" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C535" t="n">
-        <v>20</v>
-      </c>
-      <c r="D535" t="n">
         <v>60</v>
       </c>
     </row>
@@ -7931,12 +6312,9 @@
         <v>1300</v>
       </c>
       <c r="B536" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C536" t="n">
-        <v>20</v>
-      </c>
-      <c r="D536" t="n">
         <v>65</v>
       </c>
     </row>
@@ -7945,12 +6323,9 @@
         <v>1400</v>
       </c>
       <c r="B537" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C537" t="n">
-        <v>20</v>
-      </c>
-      <c r="D537" t="n">
         <v>70</v>
       </c>
     </row>
@@ -7959,12 +6334,9 @@
         <v>1690</v>
       </c>
       <c r="B538" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C538" t="n">
-        <v>58</v>
-      </c>
-      <c r="D538" t="n">
         <v>29.13793103448276</v>
       </c>
     </row>
@@ -7973,12 +6345,9 @@
         <v>1940</v>
       </c>
       <c r="B539" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C539" t="n">
-        <v>40</v>
-      </c>
-      <c r="D539" t="n">
         <v>48.5</v>
       </c>
     </row>
@@ -7987,12 +6356,9 @@
         <v>2100</v>
       </c>
       <c r="B540" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C540" t="n">
-        <v>70</v>
-      </c>
-      <c r="D540" t="n">
         <v>30</v>
       </c>
     </row>
@@ -8001,12 +6367,9 @@
         <v>2490</v>
       </c>
       <c r="B541" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C541" t="n">
-        <v>70</v>
-      </c>
-      <c r="D541" t="n">
         <v>35.57142857142857</v>
       </c>
     </row>
@@ -8015,12 +6378,9 @@
         <v>1490</v>
       </c>
       <c r="B542" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C542" t="n">
-        <v>48</v>
-      </c>
-      <c r="D542" t="n">
         <v>31.04166666666667</v>
       </c>
     </row>
@@ -8029,12 +6389,9 @@
         <v>2020</v>
       </c>
       <c r="B543" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C543" t="n">
-        <v>58</v>
-      </c>
-      <c r="D543" t="n">
         <v>34.82758620689656</v>
       </c>
     </row>
@@ -8043,12 +6400,9 @@
         <v>2050</v>
       </c>
       <c r="B544" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C544" t="n">
-        <v>70</v>
-      </c>
-      <c r="D544" t="n">
         <v>29.28571428571428</v>
       </c>
     </row>
@@ -8057,12 +6411,9 @@
         <v>1220</v>
       </c>
       <c r="B545" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C545" t="n">
-        <v>42</v>
-      </c>
-      <c r="D545" t="n">
         <v>29.04761904761905</v>
       </c>
     </row>
@@ -8071,12 +6422,9 @@
         <v>1610</v>
       </c>
       <c r="B546" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C546" t="n">
-        <v>44</v>
-      </c>
-      <c r="D546" t="n">
         <v>36.59090909090909</v>
       </c>
     </row>
